--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -10,18 +10,21 @@
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$R47</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
   <si>
+    <t>Área: PRINCIPAL</t>
+  </si>
+  <si>
     <t>PRODUCIR</t>
   </si>
   <si>
@@ -143,6 +146,12 @@
   </si>
   <si>
     <t>GLUP! KOLITA  CAJA X 12BOT X 1.0LTS</t>
+  </si>
+  <si>
+    <t>PRODT-0090</t>
+  </si>
+  <si>
+    <t>GLUP! MANZANA VERDE CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
     <t>PRODT-0104</t>
@@ -308,7 +317,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -365,10 +374,26 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="18"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -428,6 +453,13 @@
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -609,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -643,15 +675,16 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -661,113 +694,158 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="49">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1575,1442 +1653,1716 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:T77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" customWidth="1"/>
+    <col min="16" max="16" width="2.140625" customWidth="1"/>
+    <col min="17" max="17" width="0.28515625" customWidth="1"/>
+    <col min="18" max="18" width="3.42578125" customWidth="1"/>
+    <col min="19" max="19" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="J1" s="4">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+      <c r="J1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3"/>
+      <c r="O1" s="4">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="O2" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" ht="35.1" customHeight="1" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="27.95" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23">
+        <v>80</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="24">
+        <f>4330+17760+17600</f>
+        <v>39690</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="26">
+        <f>+J5/H5</f>
+        <v>496.125</v>
+      </c>
+      <c r="N5" s="27">
+        <v>804</v>
+      </c>
+      <c r="O5" s="28">
+        <f>IFERROR(ROUND((+M5/N5),1),0)</f>
+        <v>0.6</v>
+      </c>
+      <c r="S5" s="29"/>
+    </row>
+    <row r="6" ht="27.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="34">
+        <v>80</v>
+      </c>
+      <c r="I6" s="33"/>
+      <c r="J6" s="35">
+        <f>9807-2</f>
+        <v>9805</v>
+      </c>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="37">
+        <f>+J6/H6</f>
+        <v>122.5625</v>
+      </c>
+      <c r="N6" s="38">
+        <v>111</v>
+      </c>
+      <c r="O6" s="39">
+        <f>IFERROR(ROUND((+M6/N6),1),0)</f>
+        <v>1.1</v>
+      </c>
+      <c r="R6" s="29"/>
+    </row>
+    <row r="7" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34">
+        <v>80</v>
+      </c>
+      <c r="I7" s="33"/>
+      <c r="J7" s="37">
+        <f>33673+9319</f>
+        <v>42992</v>
+      </c>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="37">
+        <f>+J7/H7</f>
+        <v>537.4</v>
+      </c>
+      <c r="N7" s="38">
+        <v>240</v>
+      </c>
+      <c r="O7" s="39">
+        <f>IFERROR(ROUND((+M7/N7),1),0)</f>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="8" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="34">
+        <v>80</v>
+      </c>
+      <c r="I8" s="33"/>
+      <c r="J8" s="37">
+        <f>22+2000</f>
+        <v>2022</v>
+      </c>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="37">
+        <f>+J8/H8</f>
+        <v>25.275</v>
+      </c>
+      <c r="N8" s="38">
+        <v>83</v>
+      </c>
+      <c r="O8" s="39">
+        <f>IFERROR(ROUND((+M8/N8),1),0)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" ht="24.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34">
+        <v>80</v>
+      </c>
+      <c r="I9" s="33"/>
+      <c r="J9" s="37">
+        <v>0</v>
+      </c>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="37">
+        <f>+J9/H9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="38">
+        <v>86</v>
+      </c>
+      <c r="O9" s="39">
+        <f>IFERROR(ROUND((+M9/N9),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="34">
+        <v>80</v>
+      </c>
+      <c r="I10" s="33"/>
+      <c r="J10" s="37">
+        <f>38317+13200</f>
+        <v>51517</v>
+      </c>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="37">
+        <f>+J10/H10</f>
+        <v>643.9625</v>
+      </c>
+      <c r="N10" s="38">
+        <v>261</v>
+      </c>
+      <c r="O10" s="39">
+        <f>IFERROR(ROUND((+M10/N10),1),0)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34">
+        <v>80</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="37">
+        <v>6962</v>
+      </c>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="37">
+        <f>+J11/H11</f>
+        <v>87.025</v>
+      </c>
+      <c r="N11" s="38">
+        <v>6</v>
+      </c>
+      <c r="O11" s="39">
+        <f>IFERROR(ROUND((+M11/N11),1),0)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="12" ht="27.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34">
+        <v>80</v>
+      </c>
+      <c r="I12" s="33"/>
+      <c r="J12" s="35">
+        <f>23196-1</f>
+        <v>23195</v>
+      </c>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="37">
+        <f>+J12/H12</f>
+        <v>289.9375</v>
+      </c>
+      <c r="N12" s="38">
+        <v>60</v>
+      </c>
+      <c r="O12" s="39">
+        <f>IFERROR(ROUND((+M12/N12),1),0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="R12" s="42"/>
+    </row>
+    <row r="13" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="34">
+        <v>80</v>
+      </c>
+      <c r="I13" s="33"/>
+      <c r="J13" s="37">
+        <v>1685</v>
+      </c>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="37">
+        <f>+J13/H13</f>
+        <v>21.0625</v>
+      </c>
+      <c r="N13" s="38">
+        <v>6</v>
+      </c>
+      <c r="O13" s="39">
+        <f>IFERROR(ROUND((+M13/N13),1),0)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="14" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46">
+        <v>78</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="24">
+        <v>22854</v>
+      </c>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="24">
+        <f>+J14/H14</f>
+        <v>293</v>
+      </c>
+      <c r="N14" s="48">
+        <v>118</v>
+      </c>
+      <c r="O14" s="49">
+        <f>IFERROR(ROUND((+M14/N14),1),0)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="34">
+        <v>78</v>
+      </c>
+      <c r="I15" s="33"/>
+      <c r="J15" s="37">
+        <v>927</v>
+      </c>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="37">
+        <f>+J15/H15</f>
+        <v>11.884615384615385</v>
+      </c>
+      <c r="N15" s="38">
+        <v>14</v>
+      </c>
+      <c r="O15" s="39">
+        <f>IFERROR(ROUND((+M15/N15),1),0)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34">
+        <v>78</v>
+      </c>
+      <c r="I16" s="33"/>
+      <c r="J16" s="37">
+        <v>15986</v>
+      </c>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="37">
+        <f>+J16/H16</f>
+        <v>204.94871794871796</v>
+      </c>
+      <c r="N16" s="38">
+        <v>49</v>
+      </c>
+      <c r="O16" s="39">
+        <f>IFERROR(ROUND((+M16/N16),1),0)</f>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="17" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="34">
+        <v>78</v>
+      </c>
+      <c r="I17" s="33"/>
+      <c r="J17" s="37">
+        <f>37+12714</f>
+        <v>12751</v>
+      </c>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="37">
+        <f>+J17/H17</f>
+        <v>163.47435897435898</v>
+      </c>
+      <c r="N17" s="38">
+        <v>45</v>
+      </c>
+      <c r="O17" s="39">
+        <f>IFERROR(ROUND((+M17/N17),1),0)</f>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="18" ht="27.95" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34">
+        <v>78</v>
+      </c>
+      <c r="I18" s="33"/>
+      <c r="J18" s="37">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="37">
+        <f>+J18/H18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="38">
+        <v>0</v>
+      </c>
+      <c r="O18" s="39">
+        <f>IFERROR(ROUND((+M18/N18),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34">
+        <v>78</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="37">
+        <v>1143</v>
+      </c>
+      <c r="K19" s="36"/>
+      <c r="L19" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="37">
+        <f>+J19/H19</f>
+        <v>14.653846153846153</v>
+      </c>
+      <c r="N19" s="38">
+        <v>7</v>
+      </c>
+      <c r="O19" s="39">
+        <f>IFERROR(ROUND((+M19/N19),1),0)</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="20" ht="27.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34">
+        <v>78</v>
+      </c>
+      <c r="I20" s="33"/>
+      <c r="J20" s="37">
+        <v>1</v>
+      </c>
+      <c r="K20" s="36"/>
+      <c r="L20" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="37">
+        <f>+J20/H20</f>
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="N20" s="38">
+        <v>8</v>
+      </c>
+      <c r="O20" s="39">
+        <f>IFERROR(ROUND((+M20/N20),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="27.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34">
+        <v>78</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="37">
+        <v>3936</v>
+      </c>
+      <c r="K21" s="36"/>
+      <c r="L21" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="37">
+        <f>+J21/H21</f>
+        <v>50.46153846153846</v>
+      </c>
+      <c r="N21" s="38">
+        <v>9</v>
+      </c>
+      <c r="O21" s="39">
+        <f>IFERROR(ROUND((+M21/N21),1),0)</f>
+        <v>5.6</v>
+      </c>
+      <c r="R21" s="42"/>
+    </row>
+    <row r="22" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46">
+        <v>160</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="24">
+        <f>10406+7520</f>
+        <v>17926</v>
+      </c>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="24">
+        <f>+J22/H22</f>
+        <v>112.0375</v>
+      </c>
+      <c r="N22" s="48">
+        <v>46</v>
+      </c>
+      <c r="O22" s="49">
+        <f>IFERROR(ROUND((+M22/N22),1),0)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="23" ht="27.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="34">
+        <v>160</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="37">
+        <v>5731</v>
+      </c>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="37">
+        <f>+J23/H23</f>
+        <v>35.81875</v>
+      </c>
+      <c r="N23" s="38">
+        <v>6</v>
+      </c>
+      <c r="O23" s="39">
+        <f>IFERROR(ROUND((+M23/N23),1),0)</f>
+        <v>6</v>
+      </c>
+      <c r="R23" s="50"/>
+    </row>
+    <row r="24" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="34">
+        <v>160</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="37">
+        <v>14044</v>
+      </c>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="37">
+        <f>+J24/H24</f>
+        <v>87.775</v>
+      </c>
+      <c r="N24" s="38">
+        <v>20</v>
+      </c>
+      <c r="O24" s="39">
+        <f>IFERROR(ROUND((+M24/N24),1),0)</f>
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="25" ht="27.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="34">
+        <v>160</v>
+      </c>
+      <c r="I25" s="33"/>
+      <c r="J25" s="37">
+        <v>6809</v>
+      </c>
+      <c r="K25" s="33"/>
+      <c r="L25" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="37">
+        <f>+J25/H25</f>
+        <v>42.55625</v>
+      </c>
+      <c r="N25" s="38">
+        <v>20</v>
+      </c>
+      <c r="O25" s="39">
+        <f>IFERROR(ROUND((+M25/N25),1),0)</f>
+        <v>2.1</v>
+      </c>
+      <c r="R25" s="50"/>
+    </row>
+    <row r="26" ht="27.95" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34">
+        <v>160</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="37">
+        <v>7182</v>
+      </c>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="37">
+        <f>+J26/H26</f>
+        <v>44.8875</v>
+      </c>
+      <c r="N26" s="38">
+        <v>4</v>
+      </c>
+      <c r="O26" s="39">
+        <f>IFERROR(ROUND((+M26/N26),1),0)</f>
+        <v>11.2</v>
+      </c>
+      <c r="T26" s="29"/>
+    </row>
+    <row r="27" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="57">
+        <v>50</v>
+      </c>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58">
+        <f>40613+6650</f>
+        <v>47263</v>
+      </c>
+      <c r="K27" s="56"/>
+      <c r="L27" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="24">
+        <f>+J27/H27</f>
+        <v>945.26</v>
+      </c>
+      <c r="N27" s="48">
+        <v>108</v>
+      </c>
+      <c r="O27" s="49">
+        <f>IFERROR(ROUND((+M27/N27),1),0)</f>
+        <v>8.8</v>
+      </c>
+    </row>
+    <row r="28" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64">
+        <v>50</v>
+      </c>
+      <c r="I28" s="63"/>
+      <c r="J28" s="37">
+        <v>32624</v>
+      </c>
+      <c r="K28" s="63"/>
+      <c r="L28" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" s="37">
+        <f>+J28/H28</f>
+        <v>652.48</v>
+      </c>
+      <c r="N28" s="38">
+        <v>130</v>
+      </c>
+      <c r="O28" s="39">
+        <f>IFERROR(ROUND((+M28/N28),1),0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64">
+        <v>50</v>
+      </c>
+      <c r="I29" s="63"/>
+      <c r="J29" s="37">
+        <v>1733</v>
+      </c>
+      <c r="K29" s="63"/>
+      <c r="L29" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" s="37">
+        <f>+J29/H29</f>
+        <v>34.66</v>
+      </c>
+      <c r="N29" s="38">
+        <v>46</v>
+      </c>
+      <c r="O29" s="39">
+        <f>IFERROR(ROUND((+M29/N29),1),0)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="64">
+        <v>50</v>
+      </c>
+      <c r="I30" s="63"/>
+      <c r="J30" s="37">
+        <v>2368</v>
+      </c>
+      <c r="K30" s="63"/>
+      <c r="L30" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="37">
+        <f>+J30/H30</f>
+        <v>47.36</v>
+      </c>
+      <c r="N30" s="38">
+        <v>80</v>
+      </c>
+      <c r="O30" s="39">
+        <f>IFERROR(ROUND((+M30/N30),1),0)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="57">
+        <v>160</v>
+      </c>
+      <c r="I31" s="56"/>
+      <c r="J31" s="24">
+        <v>1177</v>
+      </c>
+      <c r="K31" s="56"/>
+      <c r="L31" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="24">
+        <f>+J31/H31</f>
+        <v>7.35625</v>
+      </c>
+      <c r="N31" s="48">
+        <v>15</v>
+      </c>
+      <c r="O31" s="49">
+        <f>IFERROR(ROUND((+M31/N31),1),0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="64">
+        <v>160</v>
+      </c>
+      <c r="I32" s="63"/>
+      <c r="J32" s="37">
+        <v>3202</v>
+      </c>
+      <c r="K32" s="63"/>
+      <c r="L32" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" s="37">
+        <f>+J32/H32</f>
+        <v>20.0125</v>
+      </c>
+      <c r="N32" s="38">
+        <v>24</v>
+      </c>
+      <c r="O32" s="39">
+        <f>IFERROR(ROUND((+M32/N32),1),0)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="33" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="64">
+        <v>160</v>
+      </c>
+      <c r="I33" s="63"/>
+      <c r="J33" s="37">
+        <v>18536</v>
+      </c>
+      <c r="K33" s="63"/>
+      <c r="L33" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="37">
+        <f>+J33/H33</f>
+        <v>115.85</v>
+      </c>
+      <c r="N33" s="38">
+        <v>21</v>
+      </c>
+      <c r="O33" s="39">
+        <f>IFERROR(ROUND((+M33/N33),1),0)</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="34" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64">
+        <v>160</v>
+      </c>
+      <c r="I34" s="63"/>
+      <c r="J34" s="37">
+        <v>8602</v>
+      </c>
+      <c r="K34" s="63"/>
+      <c r="L34" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" s="37">
+        <f>+J34/H34</f>
+        <v>53.7625</v>
+      </c>
+      <c r="N34" s="38">
+        <v>15</v>
+      </c>
+      <c r="O34" s="39">
+        <f>IFERROR(ROUND((+M34/N34),1),0)</f>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="35" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="57">
+        <v>70</v>
+      </c>
+      <c r="I35" s="56"/>
+      <c r="J35" s="24">
+        <v>0</v>
+      </c>
+      <c r="K35" s="56"/>
+      <c r="L35" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M35" s="24">
+        <f>+J35/H35</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="48">
+        <v>0</v>
+      </c>
+      <c r="O35" s="49">
+        <f>IFERROR(ROUND((+M35/N35),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="64">
+        <v>50</v>
+      </c>
+      <c r="I36" s="63"/>
+      <c r="J36" s="37">
+        <v>0</v>
+      </c>
+      <c r="K36" s="63"/>
+      <c r="L36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="37">
+        <f>+J36/H36</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="38">
+        <v>1</v>
+      </c>
+      <c r="O36" s="39">
+        <f>IFERROR(ROUND((+M36/N36),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="62"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="64">
+        <v>160</v>
+      </c>
+      <c r="I37" s="63"/>
+      <c r="J37" s="37">
+        <v>440</v>
+      </c>
+      <c r="K37" s="63"/>
+      <c r="L37" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" s="37">
+        <f>+J37/H37</f>
+        <v>2.75</v>
+      </c>
+      <c r="N37" s="38">
+        <v>1</v>
+      </c>
+      <c r="O37" s="39">
+        <f>IFERROR(ROUND((+M37/N37),1),0)</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="38" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64">
+        <v>160</v>
+      </c>
+      <c r="I38" s="63"/>
+      <c r="J38" s="37">
+        <v>0</v>
+      </c>
+      <c r="K38" s="63"/>
+      <c r="L38" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" s="37">
+        <f>+J38/H38</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="39">
+        <f>IFERROR(ROUND((+M38/N38),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="68">
+        <v>84</v>
+      </c>
+      <c r="I39" s="69"/>
+      <c r="J39" s="70">
+        <f>52-1</f>
+        <v>51</v>
+      </c>
+      <c r="K39" s="69"/>
+      <c r="L39" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="M39" s="37">
+        <f>+J39/H39</f>
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="N39" s="38">
+        <v>0</v>
+      </c>
+      <c r="O39" s="39">
+        <f>IFERROR(ROUND((+M39/N39),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="68">
+        <v>50</v>
+      </c>
+      <c r="I40" s="69"/>
+      <c r="J40" s="72">
+        <f>12+1</f>
+        <v>13</v>
+      </c>
+      <c r="K40" s="69"/>
+      <c r="L40" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="M40" s="37">
+        <f>+J40/H40</f>
+        <v>0.26</v>
+      </c>
+      <c r="N40" s="38">
+        <v>14</v>
+      </c>
+      <c r="O40" s="39">
+        <f>IFERROR(ROUND((+M40/N40),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="68">
+        <v>136</v>
+      </c>
+      <c r="I41" s="69"/>
+      <c r="J41" s="73">
+        <v>5733</v>
+      </c>
+      <c r="K41" s="69"/>
+      <c r="L41" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="37">
+        <f>+J41/H41</f>
+        <v>42.154411764705884</v>
+      </c>
+      <c r="N41" s="38">
+        <v>27</v>
+      </c>
+      <c r="O41" s="39">
+        <f>IFERROR(ROUND((+M41/N41),1),0)</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="42" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="77">
+        <v>160</v>
+      </c>
+      <c r="I42" s="78"/>
+      <c r="J42" s="37">
+        <v>1</v>
+      </c>
+      <c r="K42" s="78"/>
+      <c r="L42" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="M42" s="80">
+        <f>+J42/H42</f>
+        <v>0.00625</v>
+      </c>
+      <c r="N42" s="38">
         <v>2</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="J2" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="11"/>
-    </row>
-    <row r="4" ht="35.1" customHeight="1" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="27.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="21">
-        <v>80</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23">
-        <f>1342+14000+18000</f>
-        <v>33342</v>
-      </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="25">
-        <f>+E5/C5</f>
-        <v>416.775</v>
-      </c>
-      <c r="I5" s="26">
-        <v>804</v>
-      </c>
-      <c r="J5" s="27">
-        <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="28"/>
-    </row>
-    <row r="6" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="O42" s="39">
+        <f>IFERROR(ROUND((+M42/N42),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="77">
+        <v>160</v>
+      </c>
+      <c r="I43" s="78"/>
+      <c r="J43" s="80">
+        <v>2320</v>
+      </c>
+      <c r="K43" s="78"/>
+      <c r="L43" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="31">
-        <v>80</v>
-      </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33">
-        <f>17597-2</f>
-        <v>17595</v>
-      </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="35">
-        <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>219.9375</v>
-      </c>
-      <c r="I6" s="36">
-        <v>111</v>
-      </c>
-      <c r="J6" s="37">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="31">
-        <v>80</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="35">
-        <f>20652+18800</f>
-        <v>39452</v>
-      </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="35">
-        <f t="shared" si="1"/>
-        <v>493.15</v>
-      </c>
-      <c r="I7" s="36">
-        <v>240</v>
-      </c>
-      <c r="J7" s="37">
-        <f t="shared" si="0"/>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="31">
-        <v>80</v>
-      </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="35">
-        <v>7354</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="35">
-        <f t="shared" si="1"/>
-        <v>91.925</v>
-      </c>
-      <c r="I8" s="36">
-        <v>83</v>
-      </c>
-      <c r="J8" s="37">
-        <f t="shared" si="0"/>
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="31">
-        <v>80</v>
-      </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="35">
+      <c r="M43" s="80">
+        <f>+J43/H43</f>
+        <v>14.5</v>
+      </c>
+      <c r="N43" s="38">
         <v>0</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="35">
-        <f t="shared" si="1"/>
+      <c r="O43" s="39">
+        <f>IFERROR(ROUND((+M43/N43),1),0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="36">
-        <v>86</v>
-      </c>
-      <c r="J9" s="37">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="44" ht="27.95" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="82" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="85"/>
+      <c r="H44" s="84">
+        <v>160</v>
+      </c>
+      <c r="I44" s="85"/>
+      <c r="J44" s="86">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="31">
-        <v>80</v>
-      </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="35">
-        <f>23647+18720</f>
-        <v>42367</v>
-      </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="35">
-        <f t="shared" si="1"/>
-        <v>529.5875</v>
-      </c>
-      <c r="I10" s="36">
-        <v>261</v>
-      </c>
-      <c r="J10" s="37">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="31">
-        <v>80</v>
-      </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="35">
-        <v>7248</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="35">
-        <f t="shared" si="1"/>
-        <v>90.6</v>
-      </c>
-      <c r="I11" s="36">
-        <v>6</v>
-      </c>
-      <c r="J11" s="37">
-        <f t="shared" si="0"/>
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="31">
-        <v>80</v>
-      </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="35">
-        <f>20614+6047</f>
-        <v>26661</v>
-      </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="35">
-        <f t="shared" si="1"/>
-        <v>333.2625</v>
-      </c>
-      <c r="I12" s="36">
-        <v>60</v>
-      </c>
-      <c r="J12" s="37">
-        <f t="shared" si="0"/>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="31">
-        <v>80</v>
-      </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="35">
-        <v>1993</v>
-      </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="35">
-        <f t="shared" si="1"/>
-        <v>24.9125</v>
-      </c>
-      <c r="I13" s="36">
-        <v>6</v>
-      </c>
-      <c r="J13" s="37">
-        <f t="shared" si="0"/>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="42">
-        <v>78</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="23">
-        <f>8438+13018</f>
-        <v>21456</v>
-      </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="23">
-        <f t="shared" si="1"/>
-        <v>275.0769230769231</v>
-      </c>
-      <c r="I14" s="45">
-        <v>118</v>
-      </c>
-      <c r="J14" s="46">
-        <f t="shared" si="0"/>
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="31">
-        <v>78</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="35">
-        <v>2233</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="35">
-        <f t="shared" si="1"/>
-        <v>28.628205128205128</v>
-      </c>
-      <c r="I15" s="36">
-        <v>14</v>
-      </c>
-      <c r="J15" s="37">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="31">
-        <v>78</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="35">
-        <v>20178</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="35">
-        <f t="shared" si="1"/>
-        <v>258.6923076923077</v>
-      </c>
-      <c r="I16" s="36">
-        <v>49</v>
-      </c>
-      <c r="J16" s="37">
-        <f t="shared" si="0"/>
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="31">
-        <v>78</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="35">
-        <v>460</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="35">
-        <f t="shared" si="1"/>
-        <v>5.897435897435898</v>
-      </c>
-      <c r="I17" s="36">
-        <v>45</v>
-      </c>
-      <c r="J17" s="37">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="31">
-        <v>78</v>
-      </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="35">
-        <v>2012</v>
-      </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="35">
-        <f t="shared" si="1"/>
-        <v>25.794871794871796</v>
-      </c>
-      <c r="I18" s="36">
-        <v>7</v>
-      </c>
-      <c r="J18" s="37">
-        <f t="shared" si="0"/>
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="31">
-        <v>78</v>
-      </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="35">
-        <v>1</v>
-      </c>
-      <c r="F19" s="34"/>
-      <c r="G19" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="35">
-        <f t="shared" si="1"/>
-        <v>0.01282051282051282</v>
-      </c>
-      <c r="I19" s="36">
-        <v>8</v>
-      </c>
-      <c r="J19" s="37">
-        <f t="shared" si="0"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="88">
+        <f>+J44/H44</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="31">
-        <v>78</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="35">
-        <v>4784</v>
-      </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="35">
-        <f t="shared" si="1"/>
-        <v>61.333333333333336</v>
-      </c>
-      <c r="I20" s="36">
-        <v>9</v>
-      </c>
-      <c r="J20" s="37">
-        <f t="shared" si="0"/>
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="42">
-        <v>160</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="23">
-        <f>154+8960</f>
-        <v>9114</v>
-      </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="23">
-        <f t="shared" si="1"/>
-        <v>56.9625</v>
-      </c>
-      <c r="I21" s="45">
-        <v>46</v>
-      </c>
-      <c r="J21" s="46">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="31">
-        <v>160</v>
-      </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="35">
-        <v>7103</v>
-      </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="35">
-        <f t="shared" si="1"/>
-        <v>44.39375</v>
-      </c>
-      <c r="I22" s="36">
-        <v>6</v>
-      </c>
-      <c r="J22" s="37">
-        <f t="shared" si="0"/>
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="31">
-        <v>160</v>
-      </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="35">
-        <f>16626+1080</f>
-        <v>17706</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="35">
-        <f t="shared" si="1"/>
-        <v>110.6625</v>
-      </c>
-      <c r="I23" s="36">
-        <v>20</v>
-      </c>
-      <c r="J23" s="37">
-        <f t="shared" si="0"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="31">
-        <v>160</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="35">
-        <v>9077</v>
-      </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="35">
-        <f t="shared" si="1"/>
-        <v>56.73125</v>
-      </c>
-      <c r="I24" s="36">
-        <v>20</v>
-      </c>
-      <c r="J24" s="37">
-        <f t="shared" si="0"/>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="31">
-        <v>160</v>
-      </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="35">
-        <v>7794</v>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="35">
-        <f t="shared" si="1"/>
-        <v>48.7125</v>
-      </c>
-      <c r="I25" s="36">
-        <v>4</v>
-      </c>
-      <c r="J25" s="37">
-        <f t="shared" si="0"/>
-        <v>12.2</v>
-      </c>
-      <c r="L25" s="28"/>
-    </row>
-    <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="50">
-        <v>50</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="52">
-        <f>26153-1+11900</f>
-        <v>38052</v>
-      </c>
-      <c r="F26" s="51"/>
-      <c r="G26" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="23">
-        <f t="shared" si="1"/>
-        <v>761.04</v>
-      </c>
-      <c r="I26" s="45">
-        <v>108</v>
-      </c>
-      <c r="J26" s="46">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="55">
-        <v>50</v>
-      </c>
-      <c r="D27" s="56"/>
-      <c r="E27" s="35">
-        <v>37849</v>
-      </c>
-      <c r="F27" s="56"/>
-      <c r="G27" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="35">
-        <f t="shared" si="1"/>
-        <v>756.98</v>
-      </c>
-      <c r="I27" s="36">
-        <v>130</v>
-      </c>
-      <c r="J27" s="37">
-        <f t="shared" si="0"/>
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="55">
-        <v>50</v>
-      </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="35">
-        <v>33</v>
-      </c>
-      <c r="F28" s="56"/>
-      <c r="G28" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="35">
-        <f t="shared" si="1"/>
-        <v>0.66</v>
-      </c>
-      <c r="I28" s="36">
-        <v>46</v>
-      </c>
-      <c r="J28" s="37">
-        <f t="shared" si="0"/>
+      <c r="N44" s="89">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="55">
-        <v>50</v>
-      </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="35">
-        <v>38</v>
-      </c>
-      <c r="F29" s="56"/>
-      <c r="G29" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="35">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
-      </c>
-      <c r="I29" s="36">
-        <v>80</v>
-      </c>
-      <c r="J29" s="37">
-        <f t="shared" si="0"/>
+      <c r="O44" s="90">
+        <f>IFERROR(ROUND((+M44/N44),1),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="50">
-        <v>160</v>
-      </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="23">
-        <v>5452</v>
-      </c>
-      <c r="F30" s="51"/>
-      <c r="G30" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="23">
-        <f t="shared" si="1"/>
-        <v>34.075</v>
-      </c>
-      <c r="I30" s="45">
-        <v>15</v>
-      </c>
-      <c r="J30" s="46">
-        <f t="shared" si="0"/>
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="55">
-        <v>160</v>
-      </c>
-      <c r="D31" s="56"/>
-      <c r="E31" s="35">
-        <v>122</v>
-      </c>
-      <c r="F31" s="56"/>
-      <c r="G31" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="35">
-        <f t="shared" si="1"/>
-        <v>0.7625</v>
-      </c>
-      <c r="I31" s="36">
-        <v>24</v>
-      </c>
-      <c r="J31" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="55">
-        <v>160</v>
-      </c>
-      <c r="D32" s="56"/>
-      <c r="E32" s="35">
-        <v>6256</v>
-      </c>
-      <c r="F32" s="56"/>
-      <c r="G32" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="35">
-        <f t="shared" si="1"/>
-        <v>39.1</v>
-      </c>
-      <c r="I32" s="36">
-        <v>21</v>
-      </c>
-      <c r="J32" s="37">
-        <f t="shared" si="0"/>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="55">
-        <v>160</v>
-      </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="35">
-        <v>8792</v>
-      </c>
-      <c r="F33" s="56"/>
-      <c r="G33" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="35">
-        <f t="shared" si="1"/>
-        <v>54.95</v>
-      </c>
-      <c r="I33" s="36">
-        <v>15</v>
-      </c>
-      <c r="J33" s="37">
-        <f t="shared" si="0"/>
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="50">
-        <v>70</v>
-      </c>
-      <c r="D34" s="51"/>
-      <c r="E34" s="23">
-        <v>0</v>
-      </c>
-      <c r="F34" s="51"/>
-      <c r="G34" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="45">
-        <v>0</v>
-      </c>
-      <c r="J34" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="55">
-        <v>50</v>
-      </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="35">
-        <v>0</v>
-      </c>
-      <c r="F35" s="56"/>
-      <c r="G35" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="36">
-        <v>1</v>
-      </c>
-      <c r="J35" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="55">
-        <v>160</v>
-      </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="35">
-        <v>561</v>
-      </c>
-      <c r="F36" s="56"/>
-      <c r="G36" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="35">
-        <f t="shared" si="1"/>
-        <v>3.50625</v>
-      </c>
-      <c r="I36" s="36">
-        <v>1</v>
-      </c>
-      <c r="J36" s="37">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="55">
-        <v>160</v>
-      </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="35">
-        <v>0</v>
-      </c>
-      <c r="F37" s="56"/>
-      <c r="G37" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="36">
-        <v>0</v>
-      </c>
-      <c r="J37" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="58" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="59">
-        <v>84</v>
-      </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="61">
-        <v>65</v>
-      </c>
-      <c r="F38" s="60"/>
-      <c r="G38" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="35">
-        <f t="shared" si="1"/>
-        <v>0.7738095238095238</v>
-      </c>
-      <c r="I38" s="36">
-        <v>0</v>
-      </c>
-      <c r="J38" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="59">
-        <v>50</v>
-      </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="63">
-        <v>32</v>
-      </c>
-      <c r="F39" s="60"/>
-      <c r="G39" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="35">
-        <f t="shared" si="1"/>
-        <v>0.64</v>
-      </c>
-      <c r="I39" s="36">
-        <v>14</v>
-      </c>
-      <c r="J39" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="59">
-        <v>136</v>
-      </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="64">
-        <v>6545</v>
-      </c>
-      <c r="F40" s="60"/>
-      <c r="G40" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="35">
-        <f t="shared" si="1"/>
-        <v>48.125</v>
-      </c>
-      <c r="I40" s="36">
-        <v>27</v>
-      </c>
-      <c r="J40" s="37">
-        <f t="shared" si="0"/>
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="67">
-        <v>160</v>
-      </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="35">
-        <v>1</v>
-      </c>
-      <c r="F41" s="68"/>
-      <c r="G41" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="70">
-        <f t="shared" si="1"/>
-        <v>0.00625</v>
-      </c>
-      <c r="I41" s="36">
-        <v>2</v>
-      </c>
-      <c r="J41" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="67">
-        <v>160</v>
-      </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="70">
-        <v>2416</v>
-      </c>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="70">
-        <f>+E42/C42</f>
-        <v>15.1</v>
-      </c>
-      <c r="I42" s="36">
-        <v>0</v>
-      </c>
-      <c r="J42" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="71" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="72" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="73">
-        <v>160</v>
-      </c>
-      <c r="D43" s="74"/>
-      <c r="E43" s="75">
-        <v>0</v>
-      </c>
-      <c r="F43" s="74"/>
-      <c r="G43" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="77">
-        <f>+E43/C43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="78">
-        <v>0</v>
-      </c>
-      <c r="J43" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="23.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
-      <c r="D44" s="80"/>
-      <c r="E44" s="81">
-        <f>SUM(E5:E43)</f>
-        <v>384144</v>
-      </c>
-      <c r="F44" s="80"/>
-      <c r="G44" s="80"/>
-      <c r="H44" s="82">
-        <f>SUM(H5:H43)</f>
-        <v>4889.527206959707</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="83"/>
-      <c r="B45" s="83"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="84"/>
-    </row>
-    <row r="46" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="83"/>
-      <c r="B46" s="83"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="84"/>
-    </row>
-    <row r="47" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="84"/>
-    </row>
-    <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="84"/>
-    </row>
-    <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="84"/>
-    </row>
-    <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="84"/>
-    </row>
-    <row r="51" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="84"/>
-    </row>
-    <row r="52" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="84"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="84"/>
-    </row>
-    <row r="54" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="84"/>
-    </row>
-    <row r="55" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="84"/>
-    </row>
-    <row r="56" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E56" s="85"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="84"/>
-    </row>
-    <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="84"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E58" s="85"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="84"/>
-    </row>
-    <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="84"/>
-    </row>
-    <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E60" s="85"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="84"/>
-    </row>
-    <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="84"/>
-    </row>
-    <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="85"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="84"/>
-    </row>
-    <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="85"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="84"/>
-    </row>
-    <row r="64" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E64" s="85"/>
-      <c r="H64" s="84"/>
-    </row>
-    <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="85"/>
-      <c r="H65" s="84"/>
-    </row>
-    <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E66" s="85"/>
-      <c r="H66" s="84"/>
-    </row>
-    <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E67" s="85"/>
-      <c r="H67" s="84"/>
-    </row>
-    <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E68" s="85"/>
-      <c r="H68" s="84"/>
-    </row>
-    <row r="69" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E69" s="85"/>
-      <c r="H69" s="84"/>
-    </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="28"/>
-    </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G74" s="86"/>
+    <row r="45" ht="3.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="91"/>
+      <c r="B45" s="91"/>
+      <c r="C45" s="91"/>
+      <c r="D45" s="91"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="92"/>
+    </row>
+    <row r="46" ht="26.25" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="93"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="93"/>
+      <c r="J46" s="94">
+        <f>SUM(J5:J45)</f>
+        <v>411221</v>
+      </c>
+      <c r="K46" s="93"/>
+      <c r="L46" s="93"/>
+      <c r="M46" s="95">
+        <f>SUM(M5:M45)</f>
+        <v>5221.879952057747</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="91"/>
+      <c r="B47" s="91"/>
+      <c r="C47" s="91"/>
+      <c r="D47" s="91"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="92"/>
+    </row>
+    <row r="48" ht="21" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="91"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="91"/>
+      <c r="D48" s="91"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="92"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="92"/>
+    </row>
+    <row r="50" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="92"/>
+    </row>
+    <row r="51" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="92"/>
+    </row>
+    <row r="52" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="92"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="92"/>
+    </row>
+    <row r="54" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="92"/>
+    </row>
+    <row r="55" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="92"/>
+    </row>
+    <row r="56" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="92"/>
+    </row>
+    <row r="57" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="92"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J58" s="96"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="92"/>
+    </row>
+    <row r="59" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="92"/>
+    </row>
+    <row r="60" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J60" s="96"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="92"/>
+    </row>
+    <row r="61" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="92"/>
+    </row>
+    <row r="62" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J62" s="96"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="92"/>
+    </row>
+    <row r="63" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="92"/>
+    </row>
+    <row r="64" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J64" s="96"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="92"/>
+    </row>
+    <row r="65" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J65" s="96"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="29"/>
+      <c r="M65" s="92"/>
+    </row>
+    <row r="66" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J66" s="96"/>
+      <c r="M66" s="92"/>
+    </row>
+    <row r="67" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J67" s="96"/>
+      <c r="M67" s="92"/>
+    </row>
+    <row r="68" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J68" s="96"/>
+      <c r="M68" s="92"/>
+    </row>
+    <row r="69" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J69" s="96"/>
+      <c r="M69" s="92"/>
+    </row>
+    <row r="70" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J70" s="96"/>
+      <c r="M70" s="92"/>
+    </row>
+    <row r="71" ht="21" customHeight="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J71" s="96"/>
+      <c r="M71" s="92"/>
+    </row>
+    <row r="73" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J73" s="29"/>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="97"/>
+    </row>
+    <row r="76" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="G76" s="97"/>
+      <c r="L76" s="98"/>
+    </row>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G77" s="29"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1">
+  <conditionalFormatting sqref="I1">
     <cfRule type="cellIs" dxfId="0" priority="70" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="cellIs" dxfId="1" priority="69" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
+  <conditionalFormatting sqref="M5">
     <cfRule type="cellIs" dxfId="2" priority="80" operator="lessThan">
       <formula>1000</formula>
     </cfRule>
@@ -3018,7 +3370,7 @@
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
+  <conditionalFormatting sqref="M6">
     <cfRule type="cellIs" dxfId="4" priority="78" operator="lessThan">
       <formula>300</formula>
     </cfRule>
@@ -3026,7 +3378,7 @@
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
+  <conditionalFormatting sqref="M7">
     <cfRule type="cellIs" dxfId="6" priority="76" operator="lessThan">
       <formula>500</formula>
     </cfRule>
@@ -3034,7 +3386,7 @@
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H9">
+  <conditionalFormatting sqref="M8:M9">
     <cfRule type="cellIs" dxfId="8" priority="71" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3042,7 +3394,7 @@
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
+  <conditionalFormatting sqref="M10">
     <cfRule type="cellIs" dxfId="10" priority="67" operator="lessThan">
       <formula>500</formula>
     </cfRule>
@@ -3050,7 +3402,7 @@
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+  <conditionalFormatting sqref="M11">
     <cfRule type="cellIs" dxfId="12" priority="65" operator="lessThan">
       <formula>10</formula>
     </cfRule>
@@ -3058,7 +3410,7 @@
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="M12">
     <cfRule type="cellIs" dxfId="14" priority="63" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3066,7 +3418,7 @@
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="M13">
     <cfRule type="cellIs" dxfId="16" priority="61" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -3074,7 +3426,7 @@
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="M14">
     <cfRule type="cellIs" dxfId="18" priority="59" operator="lessThan">
       <formula>400</formula>
     </cfRule>
@@ -3082,7 +3434,7 @@
       <formula>1300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H17">
+  <conditionalFormatting sqref="M15:M17">
     <cfRule type="cellIs" dxfId="20" priority="55" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3090,106 +3442,114 @@
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="22" priority="49" operator="lessThan">
+  <conditionalFormatting sqref="M18">
+    <cfRule type="cellIs" dxfId="22" priority="53" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="54" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19:M20">
+    <cfRule type="cellIs" dxfId="24" priority="49" operator="lessThan">
       <formula>200</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="50" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="cellIs" dxfId="24" priority="51" operator="lessThan">
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="26" priority="51" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="52" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
-    <cfRule type="cellIs" dxfId="26" priority="47" operator="lessThan">
+  <conditionalFormatting sqref="M22">
+    <cfRule type="cellIs" dxfId="28" priority="47" operator="lessThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="48" operator="greaterThan">
       <formula>250</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H23">
-    <cfRule type="cellIs" dxfId="28" priority="43" operator="lessThan">
+  <conditionalFormatting sqref="M23:M24">
+    <cfRule type="cellIs" dxfId="30" priority="43" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="44" operator="greaterThan">
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="cellIs" dxfId="30" priority="41" operator="lessThan">
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="32" priority="41" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="42" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="42" operator="greaterThan">
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="cellIs" dxfId="32" priority="37" operator="lessThan">
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="34" priority="37" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="38" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="38" operator="greaterThan">
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26:H27">
-    <cfRule type="cellIs" dxfId="34" priority="33" operator="lessThan">
+  <conditionalFormatting sqref="M27:M28">
+    <cfRule type="cellIs" dxfId="36" priority="33" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="34" operator="greaterThan">
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28:H29">
-    <cfRule type="cellIs" dxfId="36" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="M29:M30">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="lessThan">
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="37" priority="32" operator="greaterThan">
+  <conditionalFormatting sqref="M29">
+    <cfRule type="cellIs" dxfId="39" priority="32" operator="greaterThan">
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="cellIs" dxfId="38" priority="28" operator="greaterThan">
+  <conditionalFormatting sqref="M30">
+    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H33">
-    <cfRule type="cellIs" dxfId="39" priority="12" operator="lessThan">
+  <conditionalFormatting sqref="M31:M34">
+    <cfRule type="cellIs" dxfId="41" priority="12" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="13" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H35 H38:H43">
-    <cfRule type="cellIs" dxfId="41" priority="25" operator="lessThan">
+  <conditionalFormatting sqref="M35:M36 M39:M44">
+    <cfRule type="cellIs" dxfId="43" priority="25" operator="lessThan">
       <formula>200</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="26" operator="greaterThan">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H37">
-    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="M37:M38">
+    <cfRule type="cellIs" dxfId="45" priority="5" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="6" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J43">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="O5:O44">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -10,14 +10,14 @@
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J46</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
@@ -145,12 +145,6 @@
     <t>GLUP! KOLITA  CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
-    <t>PRODT-0090</t>
-  </si>
-  <si>
-    <t>GLUP! MANZANA VERDE CAJA X 12BOT X 1.0LTS</t>
-  </si>
-  <si>
     <t>PRODT-0104</t>
   </si>
   <si>
@@ -287,24 +281,6 @@
   </si>
   <si>
     <t>AGUA BONAO CAJA X 20BOT X 0.355LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0117</t>
-  </si>
-  <si>
-    <t>POWER X SABOR ORIGINAL CAJA X 12BOT X 1LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0118</t>
-  </si>
-  <si>
-    <t>POWER X SABOR CAFE CAJA X 12BOT X 1LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0119</t>
-  </si>
-  <si>
-    <t>POWER X SABOR NARANJA CAJA X 12BOT X 1LTS</t>
   </si>
   <si>
     <t>PRODT-0120</t>
@@ -633,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -745,21 +721,8 @@
     </xf>
     <xf numFmtId="3" fontId="12" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -772,8 +735,8 @@
     <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -791,20 +754,20 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="47">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1182,46 +1145,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1652,11 +1575,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1690,7 +1613,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.5833333333321207</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1743,23 +1666,23 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>22280+23962+27122</f>
-        <v>73364</v>
+        <f>8459+25760+30160</f>
+        <v>64379</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="25">
-        <f t="shared" ref="H5:H47" si="0">+E5/C5</f>
-        <v>917.05</v>
+        <f t="shared" ref="H5:H43" si="0">+E5/C5</f>
+        <v>804.7375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
-        <f t="shared" ref="J5:J47" si="1">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.1</v>
+        <f t="shared" ref="J5:J43" si="1">IFERROR(ROUND((+H5/I5),1),0)</f>
+        <v>1</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1775,8 +1698,8 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>6080-2</f>
-        <v>6078</v>
+        <f>115-2</f>
+        <v>113</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -1784,14 +1707,14 @@
       </c>
       <c r="H6" s="35">
         <f t="shared" si="0"/>
-        <v>75.975</v>
+        <v>1.4125</v>
       </c>
       <c r="I6" s="36">
         <v>111</v>
       </c>
       <c r="J6" s="37">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1806,7 +1729,7 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="35">
-        <v>35578</v>
+        <v>14588</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -1814,14 +1737,14 @@
       </c>
       <c r="H7" s="35">
         <f t="shared" si="0"/>
-        <v>444.725</v>
+        <v>182.35</v>
       </c>
       <c r="I7" s="36">
         <v>240</v>
       </c>
       <c r="J7" s="37">
         <f t="shared" si="1"/>
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1836,8 +1759,8 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="35">
-        <f>4274+21316</f>
-        <v>25590</v>
+        <f>21739+15440</f>
+        <v>37179</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -1845,14 +1768,14 @@
       </c>
       <c r="H8" s="35">
         <f t="shared" si="0"/>
-        <v>319.875</v>
+        <v>464.7375</v>
       </c>
       <c r="I8" s="36">
         <v>83</v>
       </c>
       <c r="J8" s="37">
         <f t="shared" si="1"/>
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1897,8 +1820,8 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="35">
-        <f>47247+17643</f>
-        <v>64890</v>
+        <f>42174+16560</f>
+        <v>58734</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -1906,14 +1829,14 @@
       </c>
       <c r="H10" s="35">
         <f t="shared" si="0"/>
-        <v>811.125</v>
+        <v>734.175</v>
       </c>
       <c r="I10" s="36">
         <v>261</v>
       </c>
       <c r="J10" s="37">
         <f t="shared" si="1"/>
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1928,7 +1851,7 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="35">
-        <v>6867</v>
+        <v>6025</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -1936,14 +1859,14 @@
       </c>
       <c r="H11" s="35">
         <f t="shared" si="0"/>
-        <v>85.8375</v>
+        <v>75.3125</v>
       </c>
       <c r="I11" s="36">
         <v>6</v>
       </c>
       <c r="J11" s="37">
         <f t="shared" si="1"/>
-        <v>14.3</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1958,8 +1881,8 @@
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="33">
-        <f>20694-1</f>
-        <v>20693</v>
+        <f>13135-1</f>
+        <v>13134</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -1967,14 +1890,14 @@
       </c>
       <c r="H12" s="35">
         <f t="shared" si="0"/>
-        <v>258.6625</v>
+        <v>164.175</v>
       </c>
       <c r="I12" s="36">
         <v>60</v>
       </c>
       <c r="J12" s="37">
         <f t="shared" si="1"/>
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1989,7 +1912,7 @@
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="35">
-        <v>1270</v>
+        <v>238</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -1997,14 +1920,14 @@
       </c>
       <c r="H13" s="35">
         <f t="shared" si="0"/>
-        <v>15.875</v>
+        <v>2.975</v>
       </c>
       <c r="I13" s="36">
         <v>6</v>
       </c>
       <c r="J13" s="37">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,7 +1942,7 @@
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="23">
-        <v>18734</v>
+        <v>9087</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44" t="s">
@@ -2027,14 +1950,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="0"/>
-        <v>240.17948717948718</v>
+        <v>116.5</v>
       </c>
       <c r="I14" s="45">
         <v>118</v>
       </c>
       <c r="J14" s="46">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2049,8 +1972,8 @@
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="35">
-        <f>197+6771</f>
-        <v>6968</v>
+        <f>8914+2730</f>
+        <v>11644</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -2058,14 +1981,14 @@
       </c>
       <c r="H15" s="35">
         <f t="shared" si="0"/>
-        <v>89.33333333333333</v>
+        <v>149.28205128205127</v>
       </c>
       <c r="I15" s="36">
         <v>14</v>
       </c>
       <c r="J15" s="37">
         <f t="shared" si="1"/>
-        <v>6.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2080,7 +2003,7 @@
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="35">
-        <v>14521</v>
+        <v>10052</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -2088,14 +2011,14 @@
       </c>
       <c r="H16" s="35">
         <f t="shared" si="0"/>
-        <v>186.16666666666666</v>
+        <v>128.87179487179486</v>
       </c>
       <c r="I16" s="36">
         <v>49</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="1"/>
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2110,8 +2033,7 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="35">
-        <f>16660+13149</f>
-        <v>29809</v>
+        <v>25895</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -2119,17 +2041,17 @@
       </c>
       <c r="H17" s="35">
         <f t="shared" si="0"/>
-        <v>382.1666666666667</v>
+        <v>331.9871794871795</v>
       </c>
       <c r="I17" s="36">
         <v>45</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="1"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="18" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>42</v>
       </c>
@@ -2141,22 +2063,23 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="35">
-        <v>0</v>
-      </c>
-      <c r="F18" s="32"/>
+        <f>6+9594</f>
+        <v>9600</v>
+      </c>
+      <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H18" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>123.07692307692308</v>
       </c>
       <c r="I18" s="36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J18" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2171,7 +2094,7 @@
       </c>
       <c r="D19" s="32"/>
       <c r="E19" s="35">
-        <v>725</v>
+        <v>1</v>
       </c>
       <c r="F19" s="34"/>
       <c r="G19" s="32" t="s">
@@ -2179,14 +2102,14 @@
       </c>
       <c r="H19" s="35">
         <f t="shared" si="0"/>
-        <v>9.294871794871796</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="I19" s="36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="37">
         <f t="shared" si="1"/>
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2201,7 +2124,7 @@
       </c>
       <c r="D20" s="32"/>
       <c r="E20" s="35">
-        <v>1</v>
+        <v>2439</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -2209,74 +2132,74 @@
       </c>
       <c r="H20" s="35">
         <f t="shared" si="0"/>
-        <v>0.01282051282051282</v>
+        <v>31.26923076923077</v>
       </c>
       <c r="I20" s="36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="31">
-        <v>78</v>
-      </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="35">
-        <v>3284</v>
-      </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="32" t="s">
+      <c r="C21" s="42">
+        <v>160</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="23">
+        <v>4995</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="35">
-        <f t="shared" si="0"/>
-        <v>42.1025641025641</v>
-      </c>
-      <c r="I21" s="36">
-        <v>9</v>
-      </c>
-      <c r="J21" s="37">
-        <f t="shared" si="1"/>
-        <v>4.7</v>
+      <c r="H21" s="23">
+        <f t="shared" si="0"/>
+        <v>31.21875</v>
+      </c>
+      <c r="I21" s="45">
+        <v>46</v>
+      </c>
+      <c r="J21" s="46">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="42">
+      <c r="C22" s="31">
         <v>160</v>
       </c>
-      <c r="D22" s="43"/>
-      <c r="E22" s="23">
-        <v>14055</v>
-      </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43" t="s">
+      <c r="D22" s="32"/>
+      <c r="E22" s="35">
+        <v>3486</v>
+      </c>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="23">
-        <f t="shared" si="0"/>
-        <v>87.84375</v>
-      </c>
-      <c r="I22" s="45">
-        <v>46</v>
-      </c>
-      <c r="J22" s="46">
-        <f t="shared" si="1"/>
-        <v>1.9</v>
+      <c r="H22" s="35">
+        <f t="shared" si="0"/>
+        <v>21.7875</v>
+      </c>
+      <c r="I22" s="36">
+        <v>6</v>
+      </c>
+      <c r="J22" s="37">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2291,8 +2214,7 @@
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="35">
-        <f>4986</f>
-        <v>4986</v>
+        <v>8377</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -2300,14 +2222,14 @@
       </c>
       <c r="H23" s="35">
         <f t="shared" si="0"/>
-        <v>31.1625</v>
+        <v>52.35625</v>
       </c>
       <c r="I23" s="36">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J23" s="37">
         <f t="shared" si="1"/>
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2322,26 +2244,26 @@
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="35">
-        <f>12737</f>
-        <v>12737</v>
+        <f>3992+15520</f>
+        <v>19512</v>
       </c>
       <c r="F24" s="32"/>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="47" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="35">
         <f t="shared" si="0"/>
-        <v>79.60625</v>
+        <v>121.95</v>
       </c>
       <c r="I24" s="36">
         <v>20</v>
       </c>
       <c r="J24" s="37">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>56</v>
       </c>
@@ -2353,84 +2275,84 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="35">
-        <v>5352</v>
+        <v>5775</v>
       </c>
       <c r="F25" s="32"/>
-      <c r="G25" s="47" t="s">
+      <c r="G25" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="35">
         <f t="shared" si="0"/>
-        <v>33.45</v>
+        <v>36.09375</v>
       </c>
       <c r="I25" s="36">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J25" s="37">
         <f t="shared" si="1"/>
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="26" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="31">
-        <v>160</v>
-      </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="35">
-        <v>6430</v>
-      </c>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="35">
-        <f t="shared" si="0"/>
-        <v>40.1875</v>
-      </c>
-      <c r="I26" s="36">
-        <v>4</v>
-      </c>
-      <c r="J26" s="37">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L26" s="28"/>
+      <c r="C26" s="50">
+        <v>50</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52">
+        <v>43759</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="23">
+        <f t="shared" si="0"/>
+        <v>875.18</v>
+      </c>
+      <c r="I26" s="45">
+        <v>108</v>
+      </c>
+      <c r="J26" s="46">
+        <f t="shared" si="1"/>
+        <v>8.1</v>
+      </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="50">
+      <c r="C27" s="55">
         <v>50</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="52">
-        <f>45823+3081</f>
-        <v>48904</v>
-      </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="44" t="s">
+      <c r="D27" s="56"/>
+      <c r="E27" s="35">
+        <f>26044+10800</f>
+        <v>36844</v>
+      </c>
+      <c r="F27" s="56"/>
+      <c r="G27" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="23">
-        <f t="shared" si="0"/>
-        <v>978.08</v>
-      </c>
-      <c r="I27" s="45">
-        <v>108</v>
-      </c>
-      <c r="J27" s="46">
-        <f t="shared" si="1"/>
-        <v>9.1</v>
+      <c r="H27" s="35">
+        <f t="shared" si="0"/>
+        <v>736.88</v>
+      </c>
+      <c r="I27" s="36">
+        <v>130</v>
+      </c>
+      <c r="J27" s="37">
+        <f t="shared" si="1"/>
+        <v>5.7</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2445,7 +2367,7 @@
       </c>
       <c r="D28" s="56"/>
       <c r="E28" s="35">
-        <v>30129</v>
+        <v>2623</v>
       </c>
       <c r="F28" s="56"/>
       <c r="G28" s="34" t="s">
@@ -2453,14 +2375,14 @@
       </c>
       <c r="H28" s="35">
         <f t="shared" si="0"/>
-        <v>602.58</v>
+        <v>52.46</v>
       </c>
       <c r="I28" s="36">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="J28" s="37">
         <f t="shared" si="1"/>
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2475,7 +2397,7 @@
       </c>
       <c r="D29" s="56"/>
       <c r="E29" s="35">
-        <v>2518</v>
+        <v>2703</v>
       </c>
       <c r="F29" s="56"/>
       <c r="G29" s="34" t="s">
@@ -2483,74 +2405,74 @@
       </c>
       <c r="H29" s="35">
         <f t="shared" si="0"/>
-        <v>50.36</v>
+        <v>54.06</v>
       </c>
       <c r="I29" s="36">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J29" s="37">
         <f t="shared" si="1"/>
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="55">
-        <v>50</v>
-      </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="35">
-        <v>4083</v>
-      </c>
-      <c r="F30" s="56"/>
-      <c r="G30" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="35">
-        <f t="shared" si="0"/>
-        <v>81.66</v>
-      </c>
-      <c r="I30" s="36">
-        <v>80</v>
-      </c>
-      <c r="J30" s="37">
-        <f t="shared" si="1"/>
-        <v>1</v>
+      <c r="C30" s="50">
+        <v>160</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="23">
+        <v>2</v>
+      </c>
+      <c r="F30" s="51"/>
+      <c r="G30" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="23">
+        <f t="shared" si="0"/>
+        <v>0.0125</v>
+      </c>
+      <c r="I30" s="45">
+        <v>15</v>
+      </c>
+      <c r="J30" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="50">
+      <c r="C31" s="55">
         <v>160</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="23">
-        <v>277</v>
-      </c>
-      <c r="F31" s="51"/>
-      <c r="G31" s="44" t="s">
+      <c r="D31" s="56"/>
+      <c r="E31" s="35">
+        <v>14082</v>
+      </c>
+      <c r="F31" s="56"/>
+      <c r="G31" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="23">
-        <f t="shared" si="0"/>
-        <v>1.73125</v>
-      </c>
-      <c r="I31" s="45">
-        <v>15</v>
-      </c>
-      <c r="J31" s="46">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
+      <c r="H31" s="35">
+        <f t="shared" si="0"/>
+        <v>88.0125</v>
+      </c>
+      <c r="I31" s="36">
+        <v>24</v>
+      </c>
+      <c r="J31" s="37">
+        <f t="shared" si="1"/>
+        <v>3.7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2565,7 +2487,7 @@
       </c>
       <c r="D32" s="56"/>
       <c r="E32" s="35">
-        <v>11677</v>
+        <v>18506</v>
       </c>
       <c r="F32" s="56"/>
       <c r="G32" s="34" t="s">
@@ -2573,14 +2495,14 @@
       </c>
       <c r="H32" s="35">
         <f t="shared" si="0"/>
-        <v>72.98125</v>
+        <v>115.6625</v>
       </c>
       <c r="I32" s="36">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J32" s="37">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2595,7 +2517,7 @@
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="35">
-        <v>21331</v>
+        <v>5177</v>
       </c>
       <c r="F33" s="56"/>
       <c r="G33" s="34" t="s">
@@ -2603,72 +2525,72 @@
       </c>
       <c r="H33" s="35">
         <f t="shared" si="0"/>
-        <v>133.31875</v>
+        <v>32.35625</v>
       </c>
       <c r="I33" s="36">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J33" s="37">
         <f t="shared" si="1"/>
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="55">
-        <v>160</v>
-      </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="35">
-        <v>7957</v>
-      </c>
-      <c r="F34" s="56"/>
-      <c r="G34" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="35">
-        <f t="shared" si="0"/>
-        <v>49.73125</v>
-      </c>
-      <c r="I34" s="36">
-        <v>15</v>
-      </c>
-      <c r="J34" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
+      <c r="C34" s="50">
+        <v>70</v>
+      </c>
+      <c r="D34" s="51"/>
+      <c r="E34" s="23">
+        <v>0</v>
+      </c>
+      <c r="F34" s="51"/>
+      <c r="G34" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="45">
+        <v>0</v>
+      </c>
+      <c r="J34" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="50">
-        <v>70</v>
-      </c>
-      <c r="D35" s="51"/>
-      <c r="E35" s="23">
+      <c r="C35" s="55">
+        <v>50</v>
+      </c>
+      <c r="D35" s="56"/>
+      <c r="E35" s="35">
         <v>0</v>
       </c>
-      <c r="F35" s="51"/>
-      <c r="G35" s="44" t="s">
+      <c r="F35" s="56"/>
+      <c r="G35" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="45">
-        <v>0</v>
-      </c>
-      <c r="J35" s="46">
+      <c r="I35" s="36">
+        <v>1</v>
+      </c>
+      <c r="J35" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2681,26 +2603,27 @@
         <v>79</v>
       </c>
       <c r="C36" s="55">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D36" s="56"/>
-      <c r="E36" s="35">
-        <v>0</v>
+      <c r="E36" s="33">
+        <f>363-1</f>
+        <v>362</v>
       </c>
       <c r="F36" s="56"/>
       <c r="G36" s="34" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H36" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.2625</v>
       </c>
       <c r="I36" s="36">
         <v>1</v>
       </c>
       <c r="J36" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2715,7 +2638,7 @@
       </c>
       <c r="D37" s="56"/>
       <c r="E37" s="35">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="F37" s="56"/>
       <c r="G37" s="34" t="s">
@@ -2723,37 +2646,38 @@
       </c>
       <c r="H37" s="35">
         <f t="shared" si="0"/>
-        <v>2.59375</v>
+        <v>0</v>
       </c>
       <c r="I37" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="37">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="55">
-        <v>160</v>
-      </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="35">
-        <v>0</v>
-      </c>
-      <c r="F38" s="56"/>
-      <c r="G38" s="34" t="s">
-        <v>31</v>
+      <c r="C38" s="59">
+        <v>84</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="61">
+        <f>3191-2</f>
+        <v>3189</v>
+      </c>
+      <c r="F38" s="60"/>
+      <c r="G38" s="62" t="s">
+        <v>16</v>
       </c>
       <c r="H38" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37.964285714285715</v>
       </c>
       <c r="I38" s="36">
         <v>0</v>
@@ -2771,12 +2695,11 @@
         <v>85</v>
       </c>
       <c r="C39" s="59">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D39" s="60"/>
-      <c r="E39" s="61">
-        <f>2401-1</f>
-        <v>2400</v>
+      <c r="E39" s="63">
+        <v>1715</v>
       </c>
       <c r="F39" s="60"/>
       <c r="G39" s="62" t="s">
@@ -2784,14 +2707,14 @@
       </c>
       <c r="H39" s="35">
         <f t="shared" si="0"/>
-        <v>28.571428571428573</v>
+        <v>34.3</v>
       </c>
       <c r="I39" s="36">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J39" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2802,12 +2725,12 @@
         <v>87</v>
       </c>
       <c r="C40" s="59">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="D40" s="60"/>
-      <c r="E40" s="63">
-        <f>1412+1</f>
-        <v>1413</v>
+      <c r="E40" s="64">
+        <f>11040+1</f>
+        <v>11041</v>
       </c>
       <c r="F40" s="60"/>
       <c r="G40" s="62" t="s">
@@ -2815,47 +2738,47 @@
       </c>
       <c r="H40" s="35">
         <f t="shared" si="0"/>
-        <v>28.26</v>
+        <v>81.18382352941177</v>
       </c>
       <c r="I40" s="36">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J40" s="37">
         <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="67">
+        <v>160</v>
+      </c>
+      <c r="D41" s="68"/>
+      <c r="E41" s="35">
+        <v>6683</v>
+      </c>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="70">
+        <f t="shared" si="0"/>
+        <v>41.76875</v>
+      </c>
+      <c r="I41" s="36">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="59">
-        <v>136</v>
-      </c>
-      <c r="D41" s="60"/>
-      <c r="E41" s="64">
-        <v>9531</v>
-      </c>
-      <c r="F41" s="60"/>
-      <c r="G41" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="35">
-        <f t="shared" si="0"/>
-        <v>70.08088235294117</v>
-      </c>
-      <c r="I41" s="36">
-        <v>27</v>
-      </c>
       <c r="J41" s="37">
         <f t="shared" si="1"/>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="42" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="65" t="s">
         <v>90</v>
       </c>
@@ -2863,341 +2786,229 @@
         <v>91</v>
       </c>
       <c r="C42" s="67">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D42" s="68"/>
-      <c r="E42" s="52">
-        <v>0</v>
+      <c r="E42" s="70">
+        <v>2257</v>
       </c>
       <c r="F42" s="68"/>
       <c r="G42" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="52">
-        <f t="shared" si="0"/>
+      <c r="H42" s="70">
+        <f t="shared" si="0"/>
+        <v>14.10625</v>
+      </c>
+      <c r="I42" s="36">
         <v>0</v>
       </c>
-      <c r="I42" s="45">
+      <c r="J42" s="37">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="46">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="73">
+        <v>160</v>
+      </c>
+      <c r="D43" s="74"/>
+      <c r="E43" s="75">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="72">
-        <v>78</v>
-      </c>
-      <c r="D43" s="73"/>
-      <c r="E43" s="74">
+      <c r="F43" s="74"/>
+      <c r="G43" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="77">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="73"/>
-      <c r="G43" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="74">
-        <f t="shared" si="0"/>
+      <c r="I43" s="78">
         <v>0</v>
       </c>
-      <c r="I43" s="36">
+      <c r="J43" s="79">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J43" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="72">
-        <v>78</v>
-      </c>
-      <c r="D44" s="73"/>
-      <c r="E44" s="74">
-        <v>0</v>
-      </c>
-      <c r="F44" s="73"/>
-      <c r="G44" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="74">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="36">
-        <v>0</v>
-      </c>
-      <c r="J44" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="72">
-        <v>160</v>
-      </c>
-      <c r="D45" s="73"/>
-      <c r="E45" s="35">
-        <v>4480</v>
-      </c>
-      <c r="F45" s="73"/>
-      <c r="G45" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="74">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="I45" s="36">
-        <v>2</v>
-      </c>
-      <c r="J45" s="37">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="72">
-        <v>160</v>
-      </c>
-      <c r="D46" s="73"/>
-      <c r="E46" s="74">
-        <v>2290</v>
-      </c>
-      <c r="F46" s="73"/>
-      <c r="G46" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46" s="74">
-        <f t="shared" si="0"/>
-        <v>14.3125</v>
-      </c>
-      <c r="I46" s="36">
-        <v>0</v>
-      </c>
-      <c r="J46" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="76" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="78">
-        <v>160</v>
-      </c>
-      <c r="D47" s="79"/>
-      <c r="E47" s="80">
-        <v>0</v>
-      </c>
-      <c r="F47" s="79"/>
-      <c r="G47" s="81" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47" s="82">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="83">
-        <v>0</v>
-      </c>
-      <c r="J47" s="84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="86">
-        <f>SUM(E5:E47)</f>
-        <v>499337</v>
-      </c>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="87">
-        <f>SUM(H5:H47)</f>
-        <v>6292.892471180779</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="88"/>
-      <c r="B49" s="88"/>
+    </row>
+    <row r="44" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="81"/>
+    </row>
+    <row r="45" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="82"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83">
+        <f>SUM(E5:E44)</f>
+        <v>454196</v>
+      </c>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="84">
+        <f>SUM(H5:H44)</f>
+        <v>5740.490609243697</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="80"/>
+      <c r="B46" s="80"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="81"/>
+    </row>
+    <row r="47" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="81"/>
+    </row>
+    <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="81"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
-      <c r="H49" s="89"/>
-    </row>
-    <row r="50" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="88"/>
-      <c r="B50" s="88"/>
+      <c r="H49" s="81"/>
+    </row>
+    <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E50" s="28"/>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
-      <c r="H50" s="89"/>
+      <c r="H50" s="81"/>
     </row>
     <row r="51" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E51" s="28"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
-      <c r="H51" s="89"/>
+      <c r="H51" s="81"/>
     </row>
     <row r="52" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
-      <c r="H52" s="89"/>
+      <c r="H52" s="81"/>
     </row>
     <row r="53" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
-      <c r="H53" s="89"/>
+      <c r="H53" s="81"/>
     </row>
     <row r="54" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
-      <c r="H54" s="89"/>
+      <c r="H54" s="81"/>
     </row>
     <row r="55" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
-      <c r="H55" s="89"/>
+      <c r="H55" s="81"/>
     </row>
     <row r="56" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
-      <c r="H56" s="89"/>
+      <c r="H56" s="81"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="28"/>
+      <c r="E57" s="85"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
-      <c r="H57" s="89"/>
+      <c r="H57" s="81"/>
     </row>
     <row r="58" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
-      <c r="H58" s="89"/>
+      <c r="H58" s="81"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="28"/>
+      <c r="E59" s="85"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
-      <c r="H59" s="89"/>
+      <c r="H59" s="81"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E60" s="90"/>
+      <c r="E60" s="28"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
-      <c r="H60" s="89"/>
+      <c r="H60" s="81"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="28"/>
+      <c r="E61" s="85"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
-      <c r="H61" s="89"/>
+      <c r="H61" s="81"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="90"/>
+      <c r="E62" s="28"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
-      <c r="H62" s="89"/>
+      <c r="H62" s="81"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="28"/>
+      <c r="E63" s="85"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
-      <c r="H63" s="89"/>
+      <c r="H63" s="81"/>
     </row>
     <row r="64" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E64" s="90"/>
+      <c r="E64" s="85"/>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
-      <c r="H64" s="89"/>
+      <c r="H64" s="81"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="89"/>
+      <c r="E65" s="85"/>
+      <c r="H65" s="81"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E66" s="90"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="89"/>
+      <c r="E66" s="85"/>
+      <c r="H66" s="81"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E67" s="90"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="89"/>
+      <c r="E67" s="85"/>
+      <c r="H67" s="81"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E68" s="90"/>
-      <c r="H68" s="89"/>
+      <c r="E68" s="85"/>
+      <c r="H68" s="81"/>
     </row>
     <row r="69" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E69" s="90"/>
-      <c r="H69" s="89"/>
+      <c r="E69" s="85"/>
+      <c r="H69" s="81"/>
     </row>
     <row r="70" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E70" s="90"/>
-      <c r="H70" s="89"/>
-    </row>
-    <row r="71" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E71" s="90"/>
-      <c r="H71" s="89"/>
-    </row>
-    <row r="72" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E72" s="90"/>
-      <c r="H72" s="89"/>
-    </row>
-    <row r="73" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E73" s="90"/>
-      <c r="H73" s="89"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="28"/>
-    </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="91"/>
+      <c r="E70" s="85"/>
+      <c r="H70" s="81"/>
+    </row>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="28"/>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="86"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -3290,126 +3101,110 @@
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="cellIs" dxfId="22" priority="53" operator="lessThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="54" operator="greaterThan">
-      <formula>100</formula>
+  <conditionalFormatting sqref="H18:H19">
+    <cfRule type="cellIs" dxfId="22" priority="49" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="50" operator="greaterThan">
+      <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19:H20">
-    <cfRule type="cellIs" dxfId="24" priority="49" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="50" operator="greaterThan">
-      <formula>400</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="cellIs" dxfId="24" priority="51" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="52" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21">
-    <cfRule type="cellIs" dxfId="26" priority="51" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="52" operator="equal">
-      <formula>0</formula>
+    <cfRule type="cellIs" dxfId="26" priority="47" operator="lessThan">
+      <formula>100</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="48" operator="greaterThan">
+      <formula>250</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="cellIs" dxfId="28" priority="47" operator="lessThan">
-      <formula>100</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="48" operator="greaterThan">
-      <formula>250</formula>
+  <conditionalFormatting sqref="H22:H23">
+    <cfRule type="cellIs" dxfId="28" priority="43" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="44" operator="greaterThan">
+      <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H24">
-    <cfRule type="cellIs" dxfId="30" priority="43" operator="lessThan">
+  <conditionalFormatting sqref="H24">
+    <cfRule type="cellIs" dxfId="30" priority="41" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="42" operator="greaterThan">
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="cellIs" dxfId="32" priority="41" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="37" operator="lessThan">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="38" operator="greaterThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="42" operator="greaterThan">
-      <formula>150</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="cellIs" dxfId="34" priority="37" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="38" operator="greaterThan">
-      <formula>50</formula>
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="cellIs" dxfId="34" priority="33" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="34" operator="greaterThan">
+      <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27:H28">
-    <cfRule type="cellIs" dxfId="36" priority="33" operator="lessThan">
+  <conditionalFormatting sqref="H28:H29">
+    <cfRule type="cellIs" dxfId="36" priority="7" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="34" operator="greaterThan">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="cellIs" dxfId="37" priority="32" operator="greaterThan">
       <formula>1500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H30">
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="lessThan">
-      <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="cellIs" dxfId="39" priority="32" operator="greaterThan">
-      <formula>1500</formula>
+    <cfRule type="cellIs" dxfId="38" priority="28" operator="greaterThan">
+      <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
+  <conditionalFormatting sqref="H30:H33">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="13" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H34">
-    <cfRule type="cellIs" dxfId="41" priority="12" operator="lessThan">
+  <conditionalFormatting sqref="H34:H35 H38:H43">
+    <cfRule type="cellIs" dxfId="41" priority="25" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="26" operator="greaterThan">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36:H37">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="6" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H36">
-    <cfRule type="cellIs" dxfId="43" priority="25" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="26" operator="greaterThan">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H38">
-    <cfRule type="cellIs" dxfId="45" priority="5" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="6" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39:H47">
-    <cfRule type="cellIs" dxfId="47" priority="17" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="18" operator="greaterThan">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J47">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J5:J43">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="51" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="62" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -372,16 +372,16 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="18"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -609,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -681,7 +681,8 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -694,7 +695,7 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -736,7 +737,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -751,7 +752,7 @@
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1579,7 +1580,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
+    <col min="2" max="2" width="51.42578125" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1600,7 +1601,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46278</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1613,7 +1614,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,23 +1667,23 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>8459+25760+30160</f>
-        <v>64379</v>
+        <f>14363+20720+22560</f>
+        <v>57643</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="25">
-        <f t="shared" ref="H5:H43" si="0">+E5/C5</f>
-        <v>804.7375</v>
+        <f>+E5/C5</f>
+        <v>720.5375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
-        <f t="shared" ref="J5:J43" si="1">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1</v>
+        <f>IFERROR(ROUND((+H5/I5),1),0)</f>
+        <v>0.9</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1698,23 +1699,23 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>115-2</f>
-        <v>113</v>
+        <f>83-2+6480</f>
+        <v>6561</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="35">
-        <f t="shared" si="0"/>
-        <v>1.4125</v>
+        <f>+E6/C6</f>
+        <v>82.0125</v>
       </c>
       <c r="I6" s="36">
         <v>111</v>
       </c>
       <c r="J6" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IFERROR(ROUND((+H6/I6),1),0)</f>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1729,22 +1730,22 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="35">
-        <v>14588</v>
+        <v>247</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="35">
-        <f t="shared" si="0"/>
-        <v>182.35</v>
+        <f>+E7/C7</f>
+        <v>3.0875</v>
       </c>
       <c r="I7" s="36">
         <v>240</v>
       </c>
       <c r="J7" s="37">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
+        <f>IFERROR(ROUND((+H7/I7),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1759,23 +1760,23 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="35">
-        <f>21739+15440</f>
-        <v>37179</v>
+        <f>34296+4226</f>
+        <v>38522</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="35">
-        <f t="shared" si="0"/>
-        <v>464.7375</v>
+        <f>+E8/C8</f>
+        <v>481.525</v>
       </c>
       <c r="I8" s="36">
         <v>83</v>
       </c>
       <c r="J8" s="37">
-        <f t="shared" si="1"/>
-        <v>5.6</v>
+        <f>IFERROR(ROUND((+H8/I8),1),0)</f>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1797,14 +1798,14 @@
         <v>16</v>
       </c>
       <c r="H9" s="35">
-        <f t="shared" si="0"/>
+        <f>+E9/C9</f>
         <v>0</v>
       </c>
       <c r="I9" s="36">
         <v>86</v>
       </c>
       <c r="J9" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H9/I9),1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1820,23 +1821,23 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="35">
-        <f>42174+16560</f>
-        <v>58734</v>
+        <f>43747+11760</f>
+        <v>55507</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="35">
-        <f t="shared" si="0"/>
-        <v>734.175</v>
+        <f>+E10/C10</f>
+        <v>693.8375</v>
       </c>
       <c r="I10" s="36">
         <v>261</v>
       </c>
       <c r="J10" s="37">
-        <f t="shared" si="1"/>
-        <v>2.8</v>
+        <f>IFERROR(ROUND((+H10/I10),1),0)</f>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1851,22 +1852,22 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="35">
-        <v>6025</v>
+        <v>5593</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="35">
-        <f t="shared" si="0"/>
-        <v>75.3125</v>
+        <f>+E11/C11</f>
+        <v>69.9125</v>
       </c>
       <c r="I11" s="36">
         <v>6</v>
       </c>
       <c r="J11" s="37">
-        <f t="shared" si="1"/>
-        <v>12.6</v>
+        <f>IFERROR(ROUND((+H11/I11),1),0)</f>
+        <v>11.7</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1881,23 +1882,23 @@
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="33">
-        <f>13135-1</f>
-        <v>13134</v>
+        <f>6532-1</f>
+        <v>6531</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H12" s="35">
-        <f t="shared" si="0"/>
-        <v>164.175</v>
+        <f>+E12/C12</f>
+        <v>81.6375</v>
       </c>
       <c r="I12" s="36">
         <v>60</v>
       </c>
       <c r="J12" s="37">
-        <f t="shared" si="1"/>
-        <v>2.7</v>
+        <f>IFERROR(ROUND((+H12/I12),1),0)</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1912,22 +1913,22 @@
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="35">
-        <v>238</v>
+        <v>46</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H13" s="35">
-        <f t="shared" si="0"/>
-        <v>2.975</v>
+        <f>+E13/C13</f>
+        <v>0.575</v>
       </c>
       <c r="I13" s="36">
         <v>6</v>
       </c>
       <c r="J13" s="37">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(ROUND((+H13/I13),1),0)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1942,22 +1943,22 @@
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="23">
-        <v>9087</v>
+        <v>2551</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44" t="s">
         <v>31</v>
       </c>
       <c r="H14" s="23">
-        <f t="shared" si="0"/>
-        <v>116.5</v>
+        <f>+E14/C14</f>
+        <v>32.705128205128204</v>
       </c>
       <c r="I14" s="45">
         <v>118</v>
       </c>
       <c r="J14" s="46">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IFERROR(ROUND((+H14/I14),1),0)</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1972,23 +1973,22 @@
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="35">
-        <f>8914+2730</f>
-        <v>11644</v>
+        <v>10909</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H15" s="35">
-        <f t="shared" si="0"/>
-        <v>149.28205128205127</v>
+        <f>+E15/C15</f>
+        <v>139.85897435897436</v>
       </c>
       <c r="I15" s="36">
         <v>14</v>
       </c>
       <c r="J15" s="37">
-        <f t="shared" si="1"/>
-        <v>10.7</v>
+        <f>IFERROR(ROUND((+H15/I15),1),0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,22 +2003,23 @@
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="35">
-        <v>10052</v>
+        <f>7113+8658</f>
+        <v>15771</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H16" s="35">
-        <f t="shared" si="0"/>
-        <v>128.87179487179486</v>
+        <f>+E16/C16</f>
+        <v>202.19230769230768</v>
       </c>
       <c r="I16" s="36">
         <v>49</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="1"/>
-        <v>2.6</v>
+        <f>IFERROR(ROUND((+H16/I16),1),0)</f>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,22 +2034,22 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="35">
-        <v>25895</v>
+        <v>22972</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H17" s="35">
-        <f t="shared" si="0"/>
-        <v>331.9871794871795</v>
+        <f>+E17/C17</f>
+        <v>294.5128205128205</v>
       </c>
       <c r="I17" s="36">
         <v>45</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="1"/>
-        <v>7.4</v>
+        <f>IFERROR(ROUND((+H17/I17),1),0)</f>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2063,23 +2064,23 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="35">
-        <f>6+9594</f>
-        <v>9600</v>
+        <f>10838+2280</f>
+        <v>13118</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H18" s="35">
-        <f t="shared" si="0"/>
-        <v>123.07692307692308</v>
+        <f>+E18/C18</f>
+        <v>168.17948717948718</v>
       </c>
       <c r="I18" s="36">
         <v>7</v>
       </c>
       <c r="J18" s="37">
-        <f t="shared" si="1"/>
-        <v>17.6</v>
+        <f>IFERROR(ROUND((+H18/I18),1),0)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2101,14 +2102,14 @@
         <v>31</v>
       </c>
       <c r="H19" s="35">
-        <f t="shared" si="0"/>
+        <f>+E19/C19</f>
         <v>0.01282051282051282</v>
       </c>
       <c r="I19" s="36">
         <v>8</v>
       </c>
       <c r="J19" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H19/I19),1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2123,23 +2124,24 @@
         <v>78</v>
       </c>
       <c r="D20" s="32"/>
-      <c r="E20" s="35">
-        <v>2439</v>
+      <c r="E20" s="47">
+        <f>1901+5</f>
+        <v>1906</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="35">
-        <f t="shared" si="0"/>
-        <v>31.26923076923077</v>
+        <f>+E20/C20</f>
+        <v>24.435897435897434</v>
       </c>
       <c r="I20" s="36">
         <v>9</v>
       </c>
       <c r="J20" s="37">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
+        <f>IFERROR(ROUND((+H20/I20),1),0)</f>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2154,22 +2156,22 @@
       </c>
       <c r="D21" s="43"/>
       <c r="E21" s="23">
-        <v>4995</v>
+        <v>335</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43" t="s">
         <v>31</v>
       </c>
       <c r="H21" s="23">
-        <f t="shared" si="0"/>
-        <v>31.21875</v>
+        <f>+E21/C21</f>
+        <v>2.09375</v>
       </c>
       <c r="I21" s="45">
         <v>46</v>
       </c>
       <c r="J21" s="46">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
+        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2184,22 +2186,22 @@
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="35">
-        <v>3486</v>
+        <v>2548</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H22" s="35">
-        <f t="shared" si="0"/>
-        <v>21.7875</v>
+        <f>+E22/C22</f>
+        <v>15.925</v>
       </c>
       <c r="I22" s="36">
         <v>6</v>
       </c>
       <c r="J22" s="37">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
+        <f>IFERROR(ROUND((+H22/I22),1),0)</f>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2214,22 +2216,22 @@
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="35">
-        <v>8377</v>
+        <v>6479</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="35">
-        <f t="shared" si="0"/>
-        <v>52.35625</v>
+        <f>+E23/C23</f>
+        <v>40.49375</v>
       </c>
       <c r="I23" s="36">
         <v>20</v>
       </c>
       <c r="J23" s="37">
-        <f t="shared" si="1"/>
-        <v>2.6</v>
+        <f>IFERROR(ROUND((+H23/I23),1),0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2244,23 +2246,23 @@
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="35">
-        <f>3992+15520</f>
-        <v>19512</v>
+        <f>18997+10400</f>
+        <v>29397</v>
       </c>
       <c r="F24" s="32"/>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="48" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="35">
-        <f t="shared" si="0"/>
-        <v>121.95</v>
+        <f>+E24/C24</f>
+        <v>183.73125</v>
       </c>
       <c r="I24" s="36">
         <v>20</v>
       </c>
       <c r="J24" s="37">
-        <f t="shared" si="1"/>
-        <v>6.1</v>
+        <f>IFERROR(ROUND((+H24/I24),1),0)</f>
+        <v>9.2</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2275,740 +2277,739 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="35">
-        <v>5775</v>
+        <v>5150</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="35">
-        <f t="shared" si="0"/>
-        <v>36.09375</v>
+        <f>+E25/C25</f>
+        <v>32.1875</v>
       </c>
       <c r="I25" s="36">
         <v>4</v>
       </c>
       <c r="J25" s="37">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>IFERROR(ROUND((+H25/I25),1),0)</f>
+        <v>8</v>
       </c>
       <c r="L25" s="28"/>
     </row>
     <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="50">
+      <c r="C26" s="51">
         <v>50</v>
       </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="52">
-        <v>43759</v>
-      </c>
-      <c r="F26" s="51"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="53">
+        <v>38916</v>
+      </c>
+      <c r="F26" s="52"/>
       <c r="G26" s="44" t="s">
         <v>16</v>
       </c>
       <c r="H26" s="23">
-        <f t="shared" si="0"/>
-        <v>875.18</v>
+        <f>+E26/C26</f>
+        <v>778.32</v>
       </c>
       <c r="I26" s="45">
         <v>108</v>
       </c>
       <c r="J26" s="46">
-        <f t="shared" si="1"/>
-        <v>8.1</v>
+        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
+        <v>7.2</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="56">
         <v>50</v>
       </c>
-      <c r="D27" s="56"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="35">
-        <f>26044+10800</f>
-        <v>36844</v>
-      </c>
-      <c r="F27" s="56"/>
+        <f>32679+6434</f>
+        <v>39113</v>
+      </c>
+      <c r="F27" s="57"/>
       <c r="G27" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H27" s="35">
-        <f t="shared" si="0"/>
-        <v>736.88</v>
+        <f>+E27/C27</f>
+        <v>782.26</v>
       </c>
       <c r="I27" s="36">
         <v>130</v>
       </c>
       <c r="J27" s="37">
-        <f t="shared" si="1"/>
-        <v>5.7</v>
+        <f>IFERROR(ROUND((+H27/I27),1),0)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="56">
         <v>50</v>
       </c>
-      <c r="D28" s="56"/>
+      <c r="D28" s="57"/>
       <c r="E28" s="35">
-        <v>2623</v>
-      </c>
-      <c r="F28" s="56"/>
+        <v>108</v>
+      </c>
+      <c r="F28" s="57"/>
       <c r="G28" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="35">
-        <f t="shared" si="0"/>
-        <v>52.46</v>
+        <f>+E28/C28</f>
+        <v>2.16</v>
       </c>
       <c r="I28" s="36">
         <v>46</v>
       </c>
       <c r="J28" s="37">
-        <f t="shared" si="1"/>
-        <v>1.1</v>
+        <f>IFERROR(ROUND((+H28/I28),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="56">
         <v>50</v>
       </c>
-      <c r="D29" s="56"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="35">
-        <v>2703</v>
-      </c>
-      <c r="F29" s="56"/>
+        <v>90</v>
+      </c>
+      <c r="F29" s="57"/>
       <c r="G29" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="35">
-        <f t="shared" si="0"/>
-        <v>54.06</v>
+        <f>+E29/C29</f>
+        <v>1.8</v>
       </c>
       <c r="I29" s="36">
         <v>80</v>
       </c>
       <c r="J29" s="37">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
+        <f>IFERROR(ROUND((+H29/I29),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="50">
+      <c r="C30" s="51">
         <v>160</v>
       </c>
-      <c r="D30" s="51"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="23">
-        <v>2</v>
-      </c>
-      <c r="F30" s="51"/>
+        <v>4472</v>
+      </c>
+      <c r="F30" s="52"/>
       <c r="G30" s="44" t="s">
         <v>31</v>
       </c>
       <c r="H30" s="23">
-        <f t="shared" si="0"/>
-        <v>0.0125</v>
+        <f>+E30/C30</f>
+        <v>27.95</v>
       </c>
       <c r="I30" s="45">
         <v>15</v>
       </c>
       <c r="J30" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IFERROR(ROUND((+H30/I30),1),0)</f>
+        <v>1.9</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="56">
         <v>160</v>
       </c>
-      <c r="D31" s="56"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="35">
-        <v>14082</v>
-      </c>
-      <c r="F31" s="56"/>
+        <v>12602</v>
+      </c>
+      <c r="F31" s="57"/>
       <c r="G31" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H31" s="35">
-        <f t="shared" si="0"/>
-        <v>88.0125</v>
+        <f>+E31/C31</f>
+        <v>78.7625</v>
       </c>
       <c r="I31" s="36">
         <v>24</v>
       </c>
       <c r="J31" s="37">
-        <f t="shared" si="1"/>
-        <v>3.7</v>
+        <f>IFERROR(ROUND((+H31/I31),1),0)</f>
+        <v>3.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="56">
         <v>160</v>
       </c>
-      <c r="D32" s="56"/>
+      <c r="D32" s="57"/>
       <c r="E32" s="35">
-        <v>18506</v>
-      </c>
-      <c r="F32" s="56"/>
+        <v>16536</v>
+      </c>
+      <c r="F32" s="57"/>
       <c r="G32" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H32" s="35">
-        <f t="shared" si="0"/>
-        <v>115.6625</v>
+        <f>+E32/C32</f>
+        <v>103.35</v>
       </c>
       <c r="I32" s="36">
         <v>21</v>
       </c>
       <c r="J32" s="37">
-        <f t="shared" si="1"/>
-        <v>5.5</v>
+        <f>IFERROR(ROUND((+H32/I32),1),0)</f>
+        <v>4.9</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="55">
+      <c r="C33" s="56">
         <v>160</v>
       </c>
-      <c r="D33" s="56"/>
+      <c r="D33" s="57"/>
       <c r="E33" s="35">
-        <v>5177</v>
-      </c>
-      <c r="F33" s="56"/>
+        <v>3612</v>
+      </c>
+      <c r="F33" s="57"/>
       <c r="G33" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H33" s="35">
-        <f t="shared" si="0"/>
-        <v>32.35625</v>
+        <f>+E33/C33</f>
+        <v>22.575</v>
       </c>
       <c r="I33" s="36">
         <v>15</v>
       </c>
       <c r="J33" s="37">
-        <f t="shared" si="1"/>
-        <v>2.2</v>
+        <f>IFERROR(ROUND((+H33/I33),1),0)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="50">
+      <c r="C34" s="51">
         <v>70</v>
       </c>
-      <c r="D34" s="51"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="23">
         <v>0</v>
       </c>
-      <c r="F34" s="51"/>
+      <c r="F34" s="52"/>
       <c r="G34" s="44" t="s">
         <v>16</v>
       </c>
       <c r="H34" s="23">
-        <f t="shared" si="0"/>
+        <f>+E34/C34</f>
         <v>0</v>
       </c>
       <c r="I34" s="45">
         <v>0</v>
       </c>
       <c r="J34" s="46">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H34/I34),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="56">
         <v>50</v>
       </c>
-      <c r="D35" s="56"/>
+      <c r="D35" s="57"/>
       <c r="E35" s="35">
         <v>0</v>
       </c>
-      <c r="F35" s="56"/>
+      <c r="F35" s="57"/>
       <c r="G35" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="35">
-        <f t="shared" si="0"/>
+        <f>+E35/C35</f>
         <v>0</v>
       </c>
       <c r="I35" s="36">
         <v>1</v>
       </c>
       <c r="J35" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H35/I35),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="56">
         <v>160</v>
       </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="33">
-        <f>363-1</f>
-        <v>362</v>
-      </c>
-      <c r="F36" s="56"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="35">
+        <v>325</v>
+      </c>
+      <c r="F36" s="57"/>
       <c r="G36" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="35">
-        <f t="shared" si="0"/>
-        <v>2.2625</v>
+        <f>+E36/C36</f>
+        <v>2.03125</v>
       </c>
       <c r="I36" s="36">
         <v>1</v>
       </c>
       <c r="J36" s="37">
-        <f t="shared" si="1"/>
-        <v>2.3</v>
+        <f>IFERROR(ROUND((+H36/I36),1),0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="56">
         <v>160</v>
       </c>
-      <c r="D37" s="56"/>
+      <c r="D37" s="57"/>
       <c r="E37" s="35">
         <v>0</v>
       </c>
-      <c r="F37" s="56"/>
+      <c r="F37" s="57"/>
       <c r="G37" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H37" s="35">
-        <f t="shared" si="0"/>
+        <f>+E37/C37</f>
         <v>0</v>
       </c>
       <c r="I37" s="36">
         <v>0</v>
       </c>
       <c r="J37" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H37/I37),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="57" t="s">
+      <c r="A38" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="60">
         <v>84</v>
       </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="61">
-        <f>3191-2</f>
-        <v>3189</v>
-      </c>
-      <c r="F38" s="60"/>
-      <c r="G38" s="62" t="s">
+      <c r="D38" s="61"/>
+      <c r="E38" s="62">
+        <f>2839-1</f>
+        <v>2838</v>
+      </c>
+      <c r="F38" s="61"/>
+      <c r="G38" s="63" t="s">
         <v>16</v>
       </c>
       <c r="H38" s="35">
-        <f t="shared" si="0"/>
-        <v>37.964285714285715</v>
+        <f>+E38/C38</f>
+        <v>33.785714285714285</v>
       </c>
       <c r="I38" s="36">
         <v>0</v>
       </c>
       <c r="J38" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H38/I38),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="59">
+      <c r="C39" s="60">
         <v>50</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="63">
-        <v>1715</v>
-      </c>
-      <c r="F39" s="60"/>
-      <c r="G39" s="62" t="s">
+      <c r="D39" s="61"/>
+      <c r="E39" s="64">
+        <v>1162</v>
+      </c>
+      <c r="F39" s="61"/>
+      <c r="G39" s="63" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="35">
-        <f t="shared" si="0"/>
-        <v>34.3</v>
+        <f>+E39/C39</f>
+        <v>23.24</v>
       </c>
       <c r="I39" s="36">
         <v>14</v>
       </c>
       <c r="J39" s="37">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
+        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
+        <v>1.7</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="59">
+      <c r="C40" s="60">
         <v>136</v>
       </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="64">
-        <f>11040+1</f>
-        <v>11041</v>
-      </c>
-      <c r="F40" s="60"/>
-      <c r="G40" s="62" t="s">
+      <c r="D40" s="61"/>
+      <c r="E40" s="65">
+        <f>10853+1</f>
+        <v>10854</v>
+      </c>
+      <c r="F40" s="61"/>
+      <c r="G40" s="63" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="35">
-        <f t="shared" si="0"/>
-        <v>81.18382352941177</v>
+        <f>+E40/C40</f>
+        <v>79.80882352941177</v>
       </c>
       <c r="I40" s="36">
         <v>27</v>
       </c>
       <c r="J40" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H40/I40),1),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="65" t="s">
+      <c r="A41" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="66" t="s">
+      <c r="B41" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="67">
+      <c r="C41" s="68">
         <v>160</v>
       </c>
-      <c r="D41" s="68"/>
+      <c r="D41" s="69"/>
       <c r="E41" s="35">
-        <v>6683</v>
-      </c>
-      <c r="F41" s="68"/>
-      <c r="G41" s="69" t="s">
+        <v>6508</v>
+      </c>
+      <c r="F41" s="69"/>
+      <c r="G41" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="70">
-        <f t="shared" si="0"/>
-        <v>41.76875</v>
+      <c r="H41" s="71">
+        <f>+E41/C41</f>
+        <v>40.675</v>
       </c>
       <c r="I41" s="36">
         <v>2</v>
       </c>
       <c r="J41" s="37">
-        <f t="shared" si="1"/>
-        <v>20.9</v>
+        <f>IFERROR(ROUND((+H41/I41),1),0)</f>
+        <v>20.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="66" t="s">
+      <c r="B42" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="67">
+      <c r="C42" s="68">
         <v>160</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="70">
-        <v>2257</v>
-      </c>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="s">
+      <c r="D42" s="69"/>
+      <c r="E42" s="71">
+        <v>2244</v>
+      </c>
+      <c r="F42" s="69"/>
+      <c r="G42" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="70">
-        <f t="shared" si="0"/>
-        <v>14.10625</v>
+      <c r="H42" s="71">
+        <f>+E42/C42</f>
+        <v>14.025</v>
       </c>
       <c r="I42" s="36">
         <v>0</v>
       </c>
       <c r="J42" s="37">
-        <f t="shared" si="1"/>
+        <f>IFERROR(ROUND((+H42/I42),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="71" t="s">
+      <c r="A43" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="73">
+      <c r="C43" s="74">
         <v>160</v>
       </c>
-      <c r="D43" s="74"/>
-      <c r="E43" s="75">
+      <c r="D43" s="75"/>
+      <c r="E43" s="76">
         <v>0</v>
       </c>
-      <c r="F43" s="74"/>
-      <c r="G43" s="76" t="s">
+      <c r="F43" s="75"/>
+      <c r="G43" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="77">
-        <f t="shared" si="0"/>
+      <c r="H43" s="78">
+        <f>+E43/C43</f>
         <v>0</v>
       </c>
-      <c r="I43" s="78">
+      <c r="I43" s="79">
         <v>0</v>
       </c>
-      <c r="J43" s="79">
-        <f t="shared" si="1"/>
+      <c r="J43" s="80">
+        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="81"/>
       <c r="E44" s="28"/>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
-      <c r="H44" s="81"/>
+      <c r="H44" s="82"/>
     </row>
     <row r="45" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="82"/>
-      <c r="B45" s="82"/>
-      <c r="C45" s="82"/>
-      <c r="D45" s="82"/>
-      <c r="E45" s="83">
+      <c r="A45" s="83"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="84">
         <f>SUM(E5:E44)</f>
-        <v>454196</v>
-      </c>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="84">
+        <v>421167</v>
+      </c>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="85">
         <f>SUM(H5:H44)</f>
-        <v>5740.490609243697</v>
+        <v>5260.196973712562</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="80"/>
-      <c r="B46" s="80"/>
+      <c r="A46" s="81"/>
+      <c r="B46" s="81"/>
       <c r="E46" s="28"/>
       <c r="F46" s="28"/>
       <c r="G46" s="28"/>
-      <c r="H46" s="81"/>
+      <c r="H46" s="82"/>
     </row>
     <row r="47" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="80"/>
-      <c r="B47" s="80"/>
+      <c r="A47" s="81"/>
+      <c r="B47" s="81"/>
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
-      <c r="H47" s="81"/>
+      <c r="H47" s="82"/>
     </row>
     <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E48" s="28"/>
       <c r="F48" s="28"/>
       <c r="G48" s="28"/>
-      <c r="H48" s="81"/>
+      <c r="H48" s="82"/>
     </row>
     <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
-      <c r="H49" s="81"/>
+      <c r="H49" s="82"/>
     </row>
     <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E50" s="28"/>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
-      <c r="H50" s="81"/>
+      <c r="H50" s="82"/>
     </row>
     <row r="51" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E51" s="28"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
-      <c r="H51" s="81"/>
+      <c r="H51" s="82"/>
     </row>
     <row r="52" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
-      <c r="H52" s="81"/>
+      <c r="H52" s="82"/>
     </row>
     <row r="53" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
-      <c r="H53" s="81"/>
+      <c r="H53" s="82"/>
     </row>
     <row r="54" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
-      <c r="H54" s="81"/>
+      <c r="H54" s="82"/>
     </row>
     <row r="55" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
-      <c r="H55" s="81"/>
+      <c r="H55" s="82"/>
     </row>
     <row r="56" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
-      <c r="H56" s="81"/>
+      <c r="H56" s="82"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="85"/>
+      <c r="E57" s="86"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
-      <c r="H57" s="81"/>
+      <c r="H57" s="82"/>
     </row>
     <row r="58" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
-      <c r="H58" s="81"/>
+      <c r="H58" s="82"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="85"/>
+      <c r="E59" s="86"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
-      <c r="H59" s="81"/>
+      <c r="H59" s="82"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E60" s="28"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
-      <c r="H60" s="81"/>
+      <c r="H60" s="82"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="85"/>
+      <c r="E61" s="86"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
-      <c r="H61" s="81"/>
+      <c r="H61" s="82"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E62" s="28"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
-      <c r="H62" s="81"/>
+      <c r="H62" s="82"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="85"/>
+      <c r="E63" s="86"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
-      <c r="H63" s="81"/>
+      <c r="H63" s="82"/>
     </row>
     <row r="64" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E64" s="85"/>
+      <c r="E64" s="86"/>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
-      <c r="H64" s="81"/>
+      <c r="H64" s="82"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="85"/>
-      <c r="H65" s="81"/>
+      <c r="E65" s="86"/>
+      <c r="H65" s="82"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E66" s="85"/>
-      <c r="H66" s="81"/>
+      <c r="E66" s="86"/>
+      <c r="H66" s="82"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E67" s="85"/>
-      <c r="H67" s="81"/>
+      <c r="E67" s="86"/>
+      <c r="H67" s="82"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E68" s="85"/>
-      <c r="H68" s="81"/>
+      <c r="E68" s="86"/>
+      <c r="H68" s="82"/>
     </row>
     <row r="69" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E69" s="85"/>
-      <c r="H69" s="81"/>
+      <c r="E69" s="86"/>
+      <c r="H69" s="82"/>
     </row>
     <row r="70" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E70" s="85"/>
-      <c r="H70" s="81"/>
+      <c r="E70" s="86"/>
+      <c r="H70" s="82"/>
     </row>
     <row r="72" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E72" s="28"/>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G75" s="86"/>
+      <c r="G75" s="87"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -10,14 +10,14 @@
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J51</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
@@ -157,6 +157,12 @@
     <t>GLUP! NARANJA CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
+    <t>PRODT-0106</t>
+  </si>
+  <si>
+    <t>GLUP! PIÑA PARCHITA CAJA X 12BOT X 1.0LTS</t>
+  </si>
+  <si>
     <t>PRODT-0107</t>
   </si>
   <si>
@@ -193,6 +199,12 @@
     <t>GLUP! MANZANA ROJA CAJA X 15BOT X 0.400LTS</t>
   </si>
   <si>
+    <t>PRODT-0013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUSTY MANGO DURAZNO 1,5 LTRS       </t>
+  </si>
+  <si>
     <t>PRODT-0014</t>
   </si>
   <si>
@@ -203,6 +215,24 @@
   </si>
   <si>
     <t>JUSTY DURAZNO CAJA X 12BOT X 1.5LTS</t>
+  </si>
+  <si>
+    <t>PRODT-0101</t>
+  </si>
+  <si>
+    <t>JUSTY SANDIA CAJA X 12BOT X 1.5LTS</t>
+  </si>
+  <si>
+    <t>PRODT-0102</t>
+  </si>
+  <si>
+    <t>JUSTY MANDARINA CAJA X 12BOT X 1.5LTS</t>
+  </si>
+  <si>
+    <t>PRODT-0103</t>
+  </si>
+  <si>
+    <t>JUSTY TAMARINDO CAJA X 12BOT X 1.5LTS</t>
   </si>
   <si>
     <t>PRODT-0115</t>
@@ -609,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -683,6 +713,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -723,7 +759,6 @@
     <xf numFmtId="3" fontId="12" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -768,7 +803,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="51">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1136,6 +1171,46 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1576,11 +1651,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="51.42578125" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1601,7 +1676,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1614,7 +1689,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.25</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1667,8 +1742,8 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>14363+20720+22560</f>
-        <v>57643</v>
+        <f>19786+33840+28720</f>
+        <v>82346</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -1676,14 +1751,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>720.5375</v>
+        <v>1029.325</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f>IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1699,8 +1774,8 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>83-2+6480</f>
-        <v>6561</v>
+        <f>2219-2+13840</f>
+        <v>16057</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -1708,14 +1783,14 @@
       </c>
       <c r="H6" s="35">
         <f>+E6/C6</f>
-        <v>82.0125</v>
+        <v>200.7125</v>
       </c>
       <c r="I6" s="36">
         <v>111</v>
       </c>
       <c r="J6" s="37">
         <f>IFERROR(ROUND((+H6/I6),1),0)</f>
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1730,7 +1805,8 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="35">
-        <v>247</v>
+        <f>119+14400</f>
+        <v>14519</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -1738,14 +1814,14 @@
       </c>
       <c r="H7" s="35">
         <f>+E7/C7</f>
-        <v>3.0875</v>
+        <v>181.4875</v>
       </c>
       <c r="I7" s="36">
         <v>240</v>
       </c>
       <c r="J7" s="37">
         <f>IFERROR(ROUND((+H7/I7),1),0)</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1760,8 +1836,7 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="35">
-        <f>34296+4226</f>
-        <v>38522</v>
+        <v>31347</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -1769,14 +1844,14 @@
       </c>
       <c r="H8" s="35">
         <f>+E8/C8</f>
-        <v>481.525</v>
+        <v>391.8375</v>
       </c>
       <c r="I8" s="36">
         <v>83</v>
       </c>
       <c r="J8" s="37">
         <f>IFERROR(ROUND((+H8/I8),1),0)</f>
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1821,8 +1896,7 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="35">
-        <f>43747+11760</f>
-        <v>55507</v>
+        <v>41477</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -1830,14 +1904,14 @@
       </c>
       <c r="H10" s="35">
         <f>+E10/C10</f>
-        <v>693.8375</v>
+        <v>518.4625</v>
       </c>
       <c r="I10" s="36">
         <v>261</v>
       </c>
       <c r="J10" s="37">
         <f>IFERROR(ROUND((+H10/I10),1),0)</f>
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1852,7 +1926,7 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="35">
-        <v>5593</v>
+        <v>5453</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -1860,14 +1934,14 @@
       </c>
       <c r="H11" s="35">
         <f>+E11/C11</f>
-        <v>69.9125</v>
+        <v>68.1625</v>
       </c>
       <c r="I11" s="36">
         <v>6</v>
       </c>
       <c r="J11" s="37">
         <f>IFERROR(ROUND((+H11/I11),1),0)</f>
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1881,9 +1955,8 @@
         <v>80</v>
       </c>
       <c r="D12" s="32"/>
-      <c r="E12" s="33">
-        <f>6532-1</f>
-        <v>6531</v>
+      <c r="E12" s="35">
+        <v>3071</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -1891,14 +1964,14 @@
       </c>
       <c r="H12" s="35">
         <f>+E12/C12</f>
-        <v>81.6375</v>
+        <v>38.3875</v>
       </c>
       <c r="I12" s="36">
         <v>60</v>
       </c>
       <c r="J12" s="37">
         <f>IFERROR(ROUND((+H12/I12),1),0)</f>
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1913,7 +1986,7 @@
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="35">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -1921,14 +1994,14 @@
       </c>
       <c r="H13" s="35">
         <f>+E13/C13</f>
-        <v>0.575</v>
+        <v>0.175</v>
       </c>
       <c r="I13" s="36">
         <v>6</v>
       </c>
       <c r="J13" s="37">
         <f>IFERROR(ROUND((+H13/I13),1),0)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1943,7 +2016,8 @@
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="23">
-        <v>2551</v>
+        <f>2011+2184</f>
+        <v>4195</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44" t="s">
@@ -1951,14 +2025,14 @@
       </c>
       <c r="H14" s="23">
         <f>+E14/C14</f>
-        <v>32.705128205128204</v>
+        <v>53.782051282051285</v>
       </c>
       <c r="I14" s="45">
         <v>118</v>
       </c>
       <c r="J14" s="46">
         <f>IFERROR(ROUND((+H14/I14),1),0)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1973,7 +2047,7 @@
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="35">
-        <v>10909</v>
+        <v>9581</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -1981,14 +2055,14 @@
       </c>
       <c r="H15" s="35">
         <f>+E15/C15</f>
-        <v>139.85897435897436</v>
+        <v>122.83333333333333</v>
       </c>
       <c r="I15" s="36">
         <v>14</v>
       </c>
       <c r="J15" s="37">
         <f>IFERROR(ROUND((+H15/I15),1),0)</f>
-        <v>10</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,8 +2077,8 @@
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="35">
-        <f>7113+8658</f>
-        <v>15771</v>
+        <f>12498+6452</f>
+        <v>18950</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -2012,14 +2086,14 @@
       </c>
       <c r="H16" s="35">
         <f>+E16/C16</f>
-        <v>202.19230769230768</v>
+        <v>242.94871794871796</v>
       </c>
       <c r="I16" s="36">
         <v>49</v>
       </c>
       <c r="J16" s="37">
         <f>IFERROR(ROUND((+H16/I16),1),0)</f>
-        <v>4.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2034,7 +2108,7 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="35">
-        <v>22972</v>
+        <v>19110</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -2042,14 +2116,14 @@
       </c>
       <c r="H17" s="35">
         <f>+E17/C17</f>
-        <v>294.5128205128205</v>
+        <v>245</v>
       </c>
       <c r="I17" s="36">
         <v>45</v>
       </c>
       <c r="J17" s="37">
         <f>IFERROR(ROUND((+H17/I17),1),0)</f>
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2064,8 +2138,7 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="35">
-        <f>10838+2280</f>
-        <v>13118</v>
+        <v>12650</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -2073,14 +2146,14 @@
       </c>
       <c r="H18" s="35">
         <f>+E18/C18</f>
-        <v>168.17948717948718</v>
+        <v>162.17948717948718</v>
       </c>
       <c r="I18" s="36">
         <v>7</v>
       </c>
       <c r="J18" s="37">
         <f>IFERROR(ROUND((+H18/I18),1),0)</f>
-        <v>24</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2113,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>46</v>
       </c>
@@ -2124,9 +2197,8 @@
         <v>78</v>
       </c>
       <c r="D20" s="32"/>
-      <c r="E20" s="47">
-        <f>1901+5</f>
-        <v>1906</v>
+      <c r="E20" s="35">
+        <v>0</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -2134,74 +2206,76 @@
       </c>
       <c r="H20" s="35">
         <f>+E20/C20</f>
-        <v>24.435897435897434</v>
+        <v>0</v>
       </c>
       <c r="I20" s="36">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="37">
         <f>IFERROR(ROUND((+H20/I20),1),0)</f>
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="31">
+        <v>78</v>
+      </c>
+      <c r="D21" s="32"/>
+      <c r="E21" s="47">
+        <f>912+5</f>
+        <v>917</v>
+      </c>
+      <c r="F21" s="34"/>
+      <c r="G21" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="35">
+        <f>+E21/C21</f>
+        <v>11.756410256410257</v>
+      </c>
+      <c r="I21" s="36">
+        <v>9</v>
+      </c>
+      <c r="J21" s="37">
+        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="42">
         <v>160</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="23">
-        <v>335</v>
-      </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43" t="s">
+      <c r="D22" s="43"/>
+      <c r="E22" s="23">
+        <f>235+11840+4480</f>
+        <v>16555</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="23">
-        <f>+E21/C21</f>
-        <v>2.09375</v>
-      </c>
-      <c r="I21" s="45">
+      <c r="H22" s="23">
+        <f>+E22/C22</f>
+        <v>103.46875</v>
+      </c>
+      <c r="I22" s="45">
         <v>46</v>
       </c>
-      <c r="J21" s="46">
-        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="31">
-        <v>160</v>
-      </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="35">
-        <v>2548</v>
-      </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="35">
-        <f>+E22/C22</f>
-        <v>15.925</v>
-      </c>
-      <c r="I22" s="36">
-        <v>6</v>
-      </c>
-      <c r="J22" s="37">
+      <c r="J22" s="46">
         <f>IFERROR(ROUND((+H22/I22),1),0)</f>
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2216,7 +2290,7 @@
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="35">
-        <v>6479</v>
+        <v>1843</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -2224,14 +2298,14 @@
       </c>
       <c r="H23" s="35">
         <f>+E23/C23</f>
-        <v>40.49375</v>
+        <v>11.51875</v>
       </c>
       <c r="I23" s="36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J23" s="37">
         <f>IFERROR(ROUND((+H23/I23),1),0)</f>
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2246,26 +2320,25 @@
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="35">
-        <f>18997+10400</f>
-        <v>29397</v>
+        <v>3679</v>
       </c>
       <c r="F24" s="32"/>
-      <c r="G24" s="48" t="s">
+      <c r="G24" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="35">
         <f>+E24/C24</f>
-        <v>183.73125</v>
+        <v>22.99375</v>
       </c>
       <c r="I24" s="36">
         <v>20</v>
       </c>
       <c r="J24" s="37">
         <f>IFERROR(ROUND((+H24/I24),1),0)</f>
-        <v>9.2</v>
-      </c>
-    </row>
-    <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="25" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>56</v>
       </c>
@@ -2277,529 +2350,529 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="35">
-        <v>5150</v>
+        <f>29767+572</f>
+        <v>30339</v>
       </c>
       <c r="F25" s="32"/>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="48" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="35">
         <f>+E25/C25</f>
-        <v>32.1875</v>
+        <v>189.61875</v>
       </c>
       <c r="I25" s="36">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J25" s="37">
         <f>IFERROR(ROUND((+H25/I25),1),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L25" s="28"/>
-    </row>
-    <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="26" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="51">
-        <v>50</v>
-      </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="53">
-        <v>38916</v>
-      </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="44" t="s">
+      <c r="C26" s="31">
+        <v>160</v>
+      </c>
+      <c r="D26" s="32"/>
+      <c r="E26" s="35">
+        <v>3575</v>
+      </c>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="35">
+        <f>+E26/C26</f>
+        <v>22.34375</v>
+      </c>
+      <c r="I26" s="36">
+        <v>4</v>
+      </c>
+      <c r="J26" s="37">
+        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
+        <v>5.6</v>
+      </c>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="42">
+        <v>70</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="23">
+        <v>0</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="23">
-        <f>+E26/C26</f>
-        <v>778.32</v>
-      </c>
-      <c r="I26" s="45">
-        <v>108</v>
-      </c>
-      <c r="J26" s="46">
-        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="56">
-        <v>50</v>
-      </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="35">
-        <f>32679+6434</f>
-        <v>39113</v>
-      </c>
-      <c r="F27" s="57"/>
-      <c r="G27" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="35">
+      <c r="H27" s="23">
         <f>+E27/C27</f>
-        <v>782.26</v>
+        <v>0</v>
       </c>
       <c r="I27" s="36">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="J27" s="37">
         <f>IFERROR(ROUND((+H27/I27),1),0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="53">
         <v>50</v>
       </c>
-      <c r="D28" s="57"/>
-      <c r="E28" s="35">
+      <c r="D28" s="54"/>
+      <c r="E28" s="55">
+        <v>35684</v>
+      </c>
+      <c r="F28" s="54"/>
+      <c r="G28" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="23">
+        <f>+E28/C28</f>
+        <v>713.68</v>
+      </c>
+      <c r="I28" s="45">
         <v>108</v>
       </c>
-      <c r="F28" s="57"/>
-      <c r="G28" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="35">
-        <f>+E28/C28</f>
-        <v>2.16</v>
-      </c>
-      <c r="I28" s="36">
-        <v>46</v>
-      </c>
-      <c r="J28" s="37">
+      <c r="J28" s="46">
         <f>IFERROR(ROUND((+H28/I28),1),0)</f>
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="58">
         <v>50</v>
       </c>
-      <c r="D29" s="57"/>
+      <c r="D29" s="59"/>
       <c r="E29" s="35">
-        <v>90</v>
-      </c>
-      <c r="F29" s="57"/>
+        <v>34305</v>
+      </c>
+      <c r="F29" s="59"/>
       <c r="G29" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="35">
         <f>+E29/C29</f>
-        <v>1.8</v>
+        <v>686.1</v>
       </c>
       <c r="I29" s="36">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="J29" s="37">
         <f>IFERROR(ROUND((+H29/I29),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="49" t="s">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="51">
-        <v>160</v>
-      </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="23">
-        <v>4472</v>
-      </c>
-      <c r="F30" s="52"/>
-      <c r="G30" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="23">
+      <c r="C30" s="58">
+        <v>70</v>
+      </c>
+      <c r="D30" s="59"/>
+      <c r="E30" s="35">
+        <v>0</v>
+      </c>
+      <c r="F30" s="59"/>
+      <c r="G30" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="35">
         <f>+E30/C30</f>
-        <v>27.95</v>
-      </c>
-      <c r="I30" s="45">
-        <v>15</v>
-      </c>
-      <c r="J30" s="46">
+        <v>0</v>
+      </c>
+      <c r="I30" s="36">
+        <v>0</v>
+      </c>
+      <c r="J30" s="37">
         <f>IFERROR(ROUND((+H30/I30),1),0)</f>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="54" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="56">
-        <v>160</v>
-      </c>
-      <c r="D31" s="57"/>
+      <c r="C31" s="58">
+        <v>50</v>
+      </c>
+      <c r="D31" s="59"/>
       <c r="E31" s="35">
-        <v>12602</v>
-      </c>
-      <c r="F31" s="57"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="59"/>
       <c r="G31" s="34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H31" s="35">
         <f>+E31/C31</f>
-        <v>78.7625</v>
+        <v>0</v>
       </c>
       <c r="I31" s="36">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J31" s="37">
         <f>IFERROR(ROUND((+H31/I31),1),0)</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="54" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="56">
-        <v>160</v>
-      </c>
-      <c r="D32" s="57"/>
+      <c r="C32" s="58">
+        <v>70</v>
+      </c>
+      <c r="D32" s="59"/>
       <c r="E32" s="35">
-        <v>16536</v>
-      </c>
-      <c r="F32" s="57"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="59"/>
       <c r="G32" s="34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H32" s="35">
         <f>+E32/C32</f>
-        <v>103.35</v>
+        <v>0</v>
       </c>
       <c r="I32" s="36">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J32" s="37">
         <f>IFERROR(ROUND((+H32/I32),1),0)</f>
-        <v>4.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="56">
-        <v>160</v>
-      </c>
-      <c r="D33" s="57"/>
+      <c r="C33" s="58">
+        <v>50</v>
+      </c>
+      <c r="D33" s="59"/>
       <c r="E33" s="35">
-        <v>3612</v>
-      </c>
-      <c r="F33" s="57"/>
+        <f>684+6100+1400+1400</f>
+        <v>9584</v>
+      </c>
+      <c r="F33" s="59"/>
       <c r="G33" s="34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H33" s="35">
         <f>+E33/C33</f>
-        <v>22.575</v>
+        <v>191.68</v>
       </c>
       <c r="I33" s="36">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J33" s="37">
         <f>IFERROR(ROUND((+H33/I33),1),0)</f>
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="51">
-        <v>70</v>
-      </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="23">
-        <v>0</v>
-      </c>
-      <c r="F34" s="52"/>
-      <c r="G34" s="44" t="s">
+      <c r="C34" s="58">
+        <v>50</v>
+      </c>
+      <c r="D34" s="59"/>
+      <c r="E34" s="35">
+        <f>20+1400+1400+1400</f>
+        <v>4220</v>
+      </c>
+      <c r="F34" s="59"/>
+      <c r="G34" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="35">
         <f>+E34/C34</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="45">
-        <v>0</v>
-      </c>
-      <c r="J34" s="46">
+        <v>84.4</v>
+      </c>
+      <c r="I34" s="36">
+        <v>80</v>
+      </c>
+      <c r="J34" s="37">
         <f>IFERROR(ROUND((+H34/I34),1),0)</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="56">
-        <v>50</v>
-      </c>
-      <c r="D35" s="57"/>
-      <c r="E35" s="35">
-        <v>0</v>
-      </c>
-      <c r="F35" s="57"/>
-      <c r="G35" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="35">
+      <c r="C35" s="53">
+        <v>160</v>
+      </c>
+      <c r="D35" s="54"/>
+      <c r="E35" s="23">
+        <v>8002</v>
+      </c>
+      <c r="F35" s="54"/>
+      <c r="G35" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="23">
         <f>+E35/C35</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="36">
-        <v>1</v>
-      </c>
-      <c r="J35" s="37">
+        <v>50.0125</v>
+      </c>
+      <c r="I35" s="45">
+        <v>15</v>
+      </c>
+      <c r="J35" s="46">
         <f>IFERROR(ROUND((+H35/I35),1),0)</f>
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="55" t="s">
+      <c r="B36" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="56">
+      <c r="C36" s="58">
         <v>160</v>
       </c>
-      <c r="D36" s="57"/>
+      <c r="D36" s="59"/>
       <c r="E36" s="35">
-        <v>325</v>
-      </c>
-      <c r="F36" s="57"/>
+        <v>10497</v>
+      </c>
+      <c r="F36" s="59"/>
       <c r="G36" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="35">
         <f>+E36/C36</f>
-        <v>2.03125</v>
+        <v>65.60625</v>
       </c>
       <c r="I36" s="36">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J36" s="37">
         <f>IFERROR(ROUND((+H36/I36),1),0)</f>
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="56">
+      <c r="C37" s="58">
         <v>160</v>
       </c>
-      <c r="D37" s="57"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="35">
-        <v>0</v>
-      </c>
-      <c r="F37" s="57"/>
+        <v>14476</v>
+      </c>
+      <c r="F37" s="59"/>
       <c r="G37" s="34" t="s">
         <v>31</v>
       </c>
       <c r="H37" s="35">
         <f>+E37/C37</f>
-        <v>0</v>
+        <v>90.475</v>
       </c>
       <c r="I37" s="36">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J37" s="37">
         <f>IFERROR(ROUND((+H37/I37),1),0)</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="s">
+      <c r="A38" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="60">
-        <v>84</v>
-      </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="62">
-        <f>2839-1</f>
-        <v>2838</v>
-      </c>
-      <c r="F38" s="61"/>
-      <c r="G38" s="63" t="s">
-        <v>16</v>
+      <c r="C38" s="58">
+        <v>160</v>
+      </c>
+      <c r="D38" s="59"/>
+      <c r="E38" s="35">
+        <v>10922</v>
+      </c>
+      <c r="F38" s="59"/>
+      <c r="G38" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="H38" s="35">
         <f>+E38/C38</f>
-        <v>33.785714285714285</v>
+        <v>68.2625</v>
       </c>
       <c r="I38" s="36">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J38" s="37">
         <f>IFERROR(ROUND((+H38/I38),1),0)</f>
-        <v>0</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="58" t="s">
+      <c r="A39" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="59" t="s">
+      <c r="B39" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="60">
+      <c r="C39" s="53">
+        <v>70</v>
+      </c>
+      <c r="D39" s="54"/>
+      <c r="E39" s="23">
+        <v>0</v>
+      </c>
+      <c r="F39" s="54"/>
+      <c r="G39" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="23">
+        <f>+E39/C39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="45">
+        <v>0</v>
+      </c>
+      <c r="J39" s="46">
+        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="58">
         <v>50</v>
       </c>
-      <c r="D39" s="61"/>
-      <c r="E39" s="64">
-        <v>1162</v>
-      </c>
-      <c r="F39" s="61"/>
-      <c r="G39" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="35">
-        <f>+E39/C39</f>
-        <v>23.24</v>
-      </c>
-      <c r="I39" s="36">
-        <v>14</v>
-      </c>
-      <c r="J39" s="37">
-        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="60">
-        <v>136</v>
-      </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="65">
-        <f>10853+1</f>
-        <v>10854</v>
-      </c>
-      <c r="F40" s="61"/>
-      <c r="G40" s="63" t="s">
+      <c r="D40" s="59"/>
+      <c r="E40" s="35">
+        <v>0</v>
+      </c>
+      <c r="F40" s="59"/>
+      <c r="G40" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="35">
         <f>+E40/C40</f>
-        <v>79.80882352941177</v>
+        <v>0</v>
       </c>
       <c r="I40" s="36">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J40" s="37">
         <f>IFERROR(ROUND((+H40/I40),1),0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="68">
+      <c r="C41" s="58">
         <v>160</v>
       </c>
-      <c r="D41" s="69"/>
+      <c r="D41" s="59"/>
       <c r="E41" s="35">
-        <v>6508</v>
-      </c>
-      <c r="F41" s="69"/>
-      <c r="G41" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="71">
+        <v>150</v>
+      </c>
+      <c r="F41" s="59"/>
+      <c r="G41" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41" s="35">
         <f>+E41/C41</f>
-        <v>40.675</v>
+        <v>0.9375</v>
       </c>
       <c r="I41" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="37">
         <f>IFERROR(ROUND((+H41/I41),1),0)</f>
-        <v>20.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="67" t="s">
+      <c r="B42" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="68">
+      <c r="C42" s="58">
         <v>160</v>
       </c>
-      <c r="D42" s="69"/>
-      <c r="E42" s="71">
-        <v>2244</v>
-      </c>
-      <c r="F42" s="69"/>
-      <c r="G42" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="71">
+      <c r="D42" s="59"/>
+      <c r="E42" s="35">
+        <v>0</v>
+      </c>
+      <c r="F42" s="59"/>
+      <c r="G42" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="35">
         <f>+E42/C42</f>
-        <v>14.025</v>
+        <v>0</v>
       </c>
       <c r="I42" s="36">
         <v>0</v>
@@ -2810,206 +2883,357 @@
       </c>
     </row>
     <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="73" t="s">
+      <c r="B43" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="74">
+      <c r="C43" s="62">
+        <v>84</v>
+      </c>
+      <c r="D43" s="63"/>
+      <c r="E43" s="64">
+        <f>2733-1</f>
+        <v>2732</v>
+      </c>
+      <c r="F43" s="63"/>
+      <c r="G43" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="35">
+        <f>+E43/C43</f>
+        <v>32.523809523809526</v>
+      </c>
+      <c r="I43" s="36">
+        <v>0</v>
+      </c>
+      <c r="J43" s="37">
+        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="62">
+        <v>50</v>
+      </c>
+      <c r="D44" s="63"/>
+      <c r="E44" s="66">
+        <v>626</v>
+      </c>
+      <c r="F44" s="63"/>
+      <c r="G44" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="35">
+        <f>+E44/C44</f>
+        <v>12.52</v>
+      </c>
+      <c r="I44" s="36">
+        <v>14</v>
+      </c>
+      <c r="J44" s="37">
+        <f>IFERROR(ROUND((+H44/I44),1),0)</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="62">
+        <v>136</v>
+      </c>
+      <c r="D45" s="63"/>
+      <c r="E45" s="66">
+        <v>9983</v>
+      </c>
+      <c r="F45" s="63"/>
+      <c r="G45" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="35">
+        <f>+E45/C45</f>
+        <v>73.40441176470588</v>
+      </c>
+      <c r="I45" s="36">
+        <v>27</v>
+      </c>
+      <c r="J45" s="37">
+        <f>IFERROR(ROUND((+H45/I45),1),0)</f>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="69">
         <v>160</v>
       </c>
-      <c r="D43" s="75"/>
-      <c r="E43" s="76">
-        <v>0</v>
-      </c>
-      <c r="F43" s="75"/>
-      <c r="G43" s="77" t="s">
+      <c r="D46" s="70"/>
+      <c r="E46" s="35">
+        <v>8280</v>
+      </c>
+      <c r="F46" s="70"/>
+      <c r="G46" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="78">
-        <f>+E43/C43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="79">
-        <v>0</v>
-      </c>
-      <c r="J43" s="80">
-        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="81"/>
-      <c r="B44" s="81"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="82"/>
-    </row>
-    <row r="45" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="83"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="84">
-        <f>SUM(E5:E44)</f>
-        <v>421167</v>
-      </c>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="85">
-        <f>SUM(H5:H44)</f>
-        <v>5260.196973712562</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="81"/>
-      <c r="B46" s="81"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="82"/>
-    </row>
-    <row r="47" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="81"/>
-      <c r="B47" s="81"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="82"/>
-    </row>
-    <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="82"/>
-    </row>
-    <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H46" s="72">
+        <f>+E46/C46</f>
+        <v>51.75</v>
+      </c>
+      <c r="I46" s="36">
+        <v>2</v>
+      </c>
+      <c r="J46" s="37">
+        <f>IFERROR(ROUND((+H46/I46),1),0)</f>
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="47" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="69">
+        <v>160</v>
+      </c>
+      <c r="D47" s="70"/>
+      <c r="E47" s="72">
+        <v>2140</v>
+      </c>
+      <c r="F47" s="70"/>
+      <c r="G47" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="72">
+        <f>+E47/C47</f>
+        <v>13.375</v>
+      </c>
+      <c r="I47" s="36">
+        <v>0</v>
+      </c>
+      <c r="J47" s="37">
+        <f>IFERROR(ROUND((+H47/I47),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="73" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="75">
+        <v>160</v>
+      </c>
+      <c r="D48" s="76"/>
+      <c r="E48" s="77">
+        <v>0</v>
+      </c>
+      <c r="F48" s="76"/>
+      <c r="G48" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="79">
+        <f>+E48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="80">
+        <v>0</v>
+      </c>
+      <c r="J48" s="81">
+        <f>IFERROR(ROUND((+H48/I48),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="82"/>
+      <c r="B49" s="82"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
-      <c r="H49" s="82"/>
-    </row>
-    <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="82"/>
-    </row>
-    <row r="51" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H49" s="83"/>
+    </row>
+    <row r="50" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="84"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="85">
+        <f>SUM(E5:E49)</f>
+        <v>467280</v>
+      </c>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="86">
+        <f>SUM(H5:H49)</f>
+        <v>5751.733541801337</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="82"/>
+      <c r="B51" s="82"/>
       <c r="E51" s="28"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
-      <c r="H51" s="82"/>
-    </row>
-    <row r="52" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H51" s="83"/>
+    </row>
+    <row r="52" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="82"/>
+      <c r="B52" s="82"/>
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
-      <c r="H52" s="82"/>
+      <c r="H52" s="83"/>
     </row>
     <row r="53" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
-      <c r="H53" s="82"/>
+      <c r="H53" s="83"/>
     </row>
     <row r="54" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
-      <c r="H54" s="82"/>
+      <c r="H54" s="83"/>
     </row>
     <row r="55" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
-      <c r="H55" s="82"/>
+      <c r="H55" s="83"/>
     </row>
     <row r="56" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
-      <c r="H56" s="82"/>
+      <c r="H56" s="83"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="86"/>
+      <c r="E57" s="28"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
-      <c r="H57" s="82"/>
+      <c r="H57" s="83"/>
     </row>
     <row r="58" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
-      <c r="H58" s="82"/>
+      <c r="H58" s="83"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="86"/>
+      <c r="E59" s="28"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
-      <c r="H59" s="82"/>
+      <c r="H59" s="83"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E60" s="28"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
-      <c r="H60" s="82"/>
+      <c r="H60" s="83"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="86"/>
+      <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
-      <c r="H61" s="82"/>
+      <c r="H61" s="83"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="28"/>
+      <c r="E62" s="87"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
-      <c r="H62" s="82"/>
+      <c r="H62" s="83"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="86"/>
+      <c r="E63" s="28"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
-      <c r="H63" s="82"/>
+      <c r="H63" s="83"/>
     </row>
     <row r="64" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E64" s="86"/>
+      <c r="E64" s="87"/>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
-      <c r="H64" s="82"/>
+      <c r="H64" s="83"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="86"/>
-      <c r="H65" s="82"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="83"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E66" s="86"/>
-      <c r="H66" s="82"/>
+      <c r="E66" s="87"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="83"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E67" s="86"/>
-      <c r="H67" s="82"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="83"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E68" s="86"/>
-      <c r="H68" s="82"/>
+      <c r="E68" s="87"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="83"/>
     </row>
     <row r="69" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E69" s="86"/>
-      <c r="H69" s="82"/>
+      <c r="E69" s="87"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="83"/>
     </row>
     <row r="70" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E70" s="86"/>
-      <c r="H70" s="82"/>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="28"/>
-    </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G75" s="87"/>
+      <c r="E70" s="87"/>
+      <c r="H70" s="83"/>
+    </row>
+    <row r="71" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E71" s="87"/>
+      <c r="H71" s="83"/>
+    </row>
+    <row r="72" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E72" s="87"/>
+      <c r="H72" s="83"/>
+    </row>
+    <row r="73" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E73" s="87"/>
+      <c r="H73" s="83"/>
+    </row>
+    <row r="74" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E74" s="87"/>
+      <c r="H74" s="83"/>
+    </row>
+    <row r="75" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E75" s="87"/>
+      <c r="H75" s="83"/>
+    </row>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="28"/>
+    </row>
+    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G80" s="88"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -3110,7 +3334,7 @@
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
+  <conditionalFormatting sqref="H20:H21">
     <cfRule type="cellIs" dxfId="24" priority="51" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3118,7 +3342,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="H22">
     <cfRule type="cellIs" dxfId="26" priority="47" operator="lessThan">
       <formula>100</formula>
     </cfRule>
@@ -3126,7 +3350,7 @@
       <formula>250</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H23">
+  <conditionalFormatting sqref="H23:H24">
     <cfRule type="cellIs" dxfId="28" priority="43" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -3134,7 +3358,7 @@
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
+  <conditionalFormatting sqref="H25">
     <cfRule type="cellIs" dxfId="30" priority="41" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -3142,7 +3366,7 @@
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
+  <conditionalFormatting sqref="H26">
     <cfRule type="cellIs" dxfId="32" priority="37" operator="lessThan">
       <formula>5</formula>
     </cfRule>
@@ -3150,7 +3374,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26:H27">
+  <conditionalFormatting sqref="H28:H29">
     <cfRule type="cellIs" dxfId="34" priority="33" operator="lessThan">
       <formula>500</formula>
     </cfRule>
@@ -3158,54 +3382,72 @@
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28:H29">
-    <cfRule type="cellIs" dxfId="36" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="H30">
+    <cfRule type="cellIs" dxfId="36" priority="23" operator="lessThan">
+      <formula>300</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="24" operator="greaterThan">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="cellIs" dxfId="38" priority="10" operator="greaterThan">
+      <formula>1500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31:H34">
+    <cfRule type="cellIs" dxfId="39" priority="7" operator="lessThan">
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="37" priority="32" operator="greaterThan">
+  <conditionalFormatting sqref="H32">
+    <cfRule type="cellIs" dxfId="40" priority="8" operator="greaterThan">
+      <formula>800</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="cellIs" dxfId="41" priority="32" operator="greaterThan">
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="cellIs" dxfId="38" priority="28" operator="greaterThan">
+  <conditionalFormatting sqref="H34">
+    <cfRule type="cellIs" dxfId="42" priority="28" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H33">
-    <cfRule type="cellIs" dxfId="39" priority="12" operator="lessThan">
+  <conditionalFormatting sqref="H35:H38">
+    <cfRule type="cellIs" dxfId="43" priority="12" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="13" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H35 H38:H43">
-    <cfRule type="cellIs" dxfId="41" priority="25" operator="lessThan">
+  <conditionalFormatting sqref="H39:H40 H43:H48">
+    <cfRule type="cellIs" dxfId="45" priority="25" operator="lessThan">
       <formula>200</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="26" operator="greaterThan">
       <formula>600</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H37">
-    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="H41:H42">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="6" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J43">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J5:J48">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="62" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="61" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
+    <sheet sheetId="29" name="Hoja1" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J49</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
@@ -100,12 +101,24 @@
     <t xml:space="preserve">GLUP! FRESH 6X2000ML </t>
   </si>
   <si>
+    <t>PRODT-0048</t>
+  </si>
+  <si>
+    <t>GLUP! PONCHE DE FRUTAS CAJA X 6BOT X 2LTS</t>
+  </si>
+  <si>
     <t>PRODT-0049</t>
   </si>
   <si>
     <t>GLUP! MANZANA VERDE CAJA X 6BOT X 2LTS</t>
   </si>
   <si>
+    <t>PRODT-0050</t>
+  </si>
+  <si>
+    <t>GLUP! CHICLE BOMBA CAJA X 6BOT X 2LTS</t>
+  </si>
+  <si>
     <t>PRODT-0097</t>
   </si>
   <si>
@@ -145,6 +158,12 @@
     <t>GLUP! KOLITA  CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
+    <t>PRODT-0090</t>
+  </si>
+  <si>
+    <t>GLUP! MANZANA VERDE CAJA X 12BOT X 1.0LTS</t>
+  </si>
+  <si>
     <t>PRODT-0104</t>
   </si>
   <si>
@@ -157,12 +176,6 @@
     <t>GLUP! NARANJA CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
-    <t>PRODT-0106</t>
-  </si>
-  <si>
-    <t>GLUP! PIÑA PARCHITA CAJA X 12BOT X 1.0LTS</t>
-  </si>
-  <si>
     <t>PRODT-0107</t>
   </si>
   <si>
@@ -199,12 +212,6 @@
     <t>GLUP! MANZANA ROJA CAJA X 15BOT X 0.400LTS</t>
   </si>
   <si>
-    <t>PRODT-0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUSTY MANGO DURAZNO 1,5 LTRS       </t>
-  </si>
-  <si>
     <t>PRODT-0014</t>
   </si>
   <si>
@@ -215,24 +222,6 @@
   </si>
   <si>
     <t>JUSTY DURAZNO CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0101</t>
-  </si>
-  <si>
-    <t>JUSTY SANDIA CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0102</t>
-  </si>
-  <si>
-    <t>JUSTY MANDARINA CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0103</t>
-  </si>
-  <si>
-    <t>JUSTY TAMARINDO CAJA X 12BOT X 1.5LTS</t>
   </si>
   <si>
     <t>PRODT-0115</t>
@@ -461,7 +450,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,12 +466,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -711,14 +694,8 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -772,7 +749,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -803,7 +779,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="49">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1186,31 +1162,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1651,11 +1607,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="2" max="2" width="53.5703125" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1676,7 +1632,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1689,7 +1645,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.3541666666678793</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1742,8 +1698,8 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>19786+33840+28720</f>
-        <v>82346</v>
+        <f>33022+24800+32640</f>
+        <v>90462</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -1751,14 +1707,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1029.325</v>
+        <v>1130.775</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
-        <f>IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.3</v>
+        <f t="shared" ref="J5:J46" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
+        <v>1.4</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1774,23 +1730,23 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>2219-2+13840</f>
-        <v>16057</v>
+        <f>10925-2</f>
+        <v>10923</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="35">
-        <f>+E6/C6</f>
-        <v>200.7125</v>
+        <f t="shared" ref="H6:H44" si="1">+E6/C6</f>
+        <v>136.5375</v>
       </c>
       <c r="I6" s="36">
         <v>111</v>
       </c>
       <c r="J6" s="37">
-        <f>IFERROR(ROUND((+H6/I6),1),0)</f>
-        <v>1.8</v>
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1805,23 +1761,23 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="35">
-        <f>119+14400</f>
-        <v>14519</v>
+        <f>2850+210+20080</f>
+        <v>23140</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="35">
-        <f>+E7/C7</f>
-        <v>181.4875</v>
+        <f t="shared" si="1"/>
+        <v>289.25</v>
       </c>
       <c r="I7" s="36">
         <v>240</v>
       </c>
       <c r="J7" s="37">
-        <f>IFERROR(ROUND((+H7/I7),1),0)</f>
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1836,22 +1792,22 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="35">
-        <v>31347</v>
+        <v>23296</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="35">
-        <f>+E8/C8</f>
-        <v>391.8375</v>
+        <f t="shared" si="1"/>
+        <v>291.2</v>
       </c>
       <c r="I8" s="36">
         <v>83</v>
       </c>
       <c r="J8" s="37">
-        <f>IFERROR(ROUND((+H8/I8),1),0)</f>
-        <v>4.7</v>
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1873,14 +1829,14 @@
         <v>16</v>
       </c>
       <c r="H9" s="35">
-        <f>+E9/C9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="36">
         <v>86</v>
       </c>
       <c r="J9" s="37">
-        <f>IFERROR(ROUND((+H9/I9),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1896,25 +1852,26 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="35">
-        <v>41477</v>
+        <f>14236+9280</f>
+        <v>23516</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="35">
-        <f>+E10/C10</f>
-        <v>518.4625</v>
+        <f t="shared" si="1"/>
+        <v>293.95</v>
       </c>
       <c r="I10" s="36">
         <v>261</v>
       </c>
       <c r="J10" s="37">
-        <f>IFERROR(ROUND((+H10/I10),1),0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
         <v>27</v>
       </c>
@@ -1926,22 +1883,22 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="35">
-        <v>5453</v>
+        <v>0</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="35">
-        <f>+E11/C11</f>
-        <v>68.1625</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I11" s="36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J11" s="37">
-        <f>IFERROR(ROUND((+H11/I11),1),0)</f>
-        <v>11.4</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1956,83 +1913,83 @@
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="35">
-        <v>3071</v>
-      </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32" t="s">
+        <v>4765</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="35">
+        <f t="shared" si="1"/>
+        <v>59.5625</v>
+      </c>
+      <c r="I12" s="36">
+        <v>6</v>
+      </c>
+      <c r="J12" s="37">
+        <f t="shared" si="0"/>
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="13" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="35">
-        <f>+E12/C12</f>
-        <v>38.3875</v>
-      </c>
-      <c r="I12" s="36">
-        <v>60</v>
-      </c>
-      <c r="J12" s="37">
-        <f>IFERROR(ROUND((+H12/I12),1),0)</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>33</v>
       </c>
       <c r="C13" s="31">
         <v>80</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="35">
-        <v>14</v>
-      </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="H13" s="35">
-        <f>+E13/C13</f>
-        <v>0.175</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I13" s="36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J13" s="37">
-        <f>IFERROR(ROUND((+H13/I13),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="C14" s="31">
+        <v>80</v>
+      </c>
+      <c r="D14" s="32"/>
+      <c r="E14" s="33">
+        <f>64-1</f>
+        <v>63</v>
+      </c>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="42">
-        <v>78</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="23">
-        <f>2011+2184</f>
-        <v>4195</v>
-      </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="23">
-        <f>+E14/C14</f>
-        <v>53.782051282051285</v>
-      </c>
-      <c r="I14" s="45">
-        <v>118</v>
-      </c>
-      <c r="J14" s="46">
-        <f>IFERROR(ROUND((+H14/I14),1),0)</f>
-        <v>0.5</v>
+      <c r="H14" s="35">
+        <f t="shared" si="1"/>
+        <v>0.7875</v>
+      </c>
+      <c r="I14" s="36">
+        <v>60</v>
+      </c>
+      <c r="J14" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2043,57 +2000,57 @@
         <v>37</v>
       </c>
       <c r="C15" s="31">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="35">
-        <v>9581</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32" t="s">
+        <v>35</v>
       </c>
       <c r="H15" s="35">
-        <f>+E15/C15</f>
-        <v>122.83333333333333</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I15" s="36">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J15" s="37">
-        <f>IFERROR(ROUND((+H15/I15),1),0)</f>
-        <v>8.8</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="42">
         <v>78</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="35">
-        <f>12498+6452</f>
-        <v>18950</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="35">
-        <f>+E16/C16</f>
-        <v>242.94871794871796</v>
-      </c>
-      <c r="I16" s="36">
-        <v>49</v>
-      </c>
-      <c r="J16" s="37">
-        <f>IFERROR(ROUND((+H16/I16),1),0)</f>
-        <v>5</v>
+      <c r="D16" s="43"/>
+      <c r="E16" s="23">
+        <f>1168+13650</f>
+        <v>14818</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="23">
+        <f t="shared" si="1"/>
+        <v>189.97435897435898</v>
+      </c>
+      <c r="I16" s="45">
+        <v>118</v>
+      </c>
+      <c r="J16" s="46">
+        <f t="shared" si="0"/>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2108,22 +2065,22 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="35">
-        <v>19110</v>
+        <v>7551</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H17" s="35">
-        <f>+E17/C17</f>
-        <v>245</v>
+        <f t="shared" si="1"/>
+        <v>96.8076923076923</v>
       </c>
       <c r="I17" s="36">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J17" s="37">
-        <f>IFERROR(ROUND((+H17/I17),1),0)</f>
-        <v>5.4</v>
+        <f t="shared" si="0"/>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2138,22 +2095,22 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="35">
-        <v>12650</v>
+        <v>14115</v>
       </c>
       <c r="F18" s="34"/>
-      <c r="G18" s="32" t="s">
-        <v>31</v>
+      <c r="G18" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H18" s="35">
-        <f>+E18/C18</f>
-        <v>162.17948717948718</v>
+        <f t="shared" si="1"/>
+        <v>180.96153846153845</v>
       </c>
       <c r="I18" s="36">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="J18" s="37">
-        <f>IFERROR(ROUND((+H18/I18),1),0)</f>
-        <v>23.2</v>
+        <f t="shared" si="0"/>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2168,22 +2125,22 @@
       </c>
       <c r="D19" s="32"/>
       <c r="E19" s="35">
-        <v>1</v>
+        <v>13600</v>
       </c>
       <c r="F19" s="34"/>
-      <c r="G19" s="32" t="s">
-        <v>31</v>
+      <c r="G19" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H19" s="35">
-        <f>+E19/C19</f>
-        <v>0.01282051282051282</v>
+        <f t="shared" si="1"/>
+        <v>174.35897435897436</v>
       </c>
       <c r="I19" s="36">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J19" s="37">
-        <f>IFERROR(ROUND((+H19/I19),1),0)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3.9</v>
       </c>
     </row>
     <row r="20" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2200,19 +2157,19 @@
       <c r="E20" s="35">
         <v>0</v>
       </c>
-      <c r="F20" s="34"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="32" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H20" s="35">
-        <f>+E20/C20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="36">
         <v>0</v>
       </c>
       <c r="J20" s="37">
-        <f>IFERROR(ROUND((+H20/I20),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2227,55 +2184,53 @@
         <v>78</v>
       </c>
       <c r="D21" s="32"/>
-      <c r="E21" s="47">
-        <f>912+5</f>
-        <v>917</v>
+      <c r="E21" s="35">
+        <v>10450</v>
       </c>
       <c r="F21" s="34"/>
       <c r="G21" s="32" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H21" s="35">
-        <f>+E21/C21</f>
-        <v>11.756410256410257</v>
+        <f t="shared" si="1"/>
+        <v>133.97435897435898</v>
       </c>
       <c r="I21" s="36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J21" s="37">
-        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
-        <v>1.3</v>
+        <f t="shared" si="0"/>
+        <v>19.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="42">
-        <v>160</v>
-      </c>
-      <c r="D22" s="43"/>
-      <c r="E22" s="23">
-        <f>235+11840+4480</f>
-        <v>16555</v>
-      </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="23">
-        <f>+E22/C22</f>
-        <v>103.46875</v>
-      </c>
-      <c r="I22" s="45">
-        <v>46</v>
-      </c>
-      <c r="J22" s="46">
-        <f>IFERROR(ROUND((+H22/I22),1),0)</f>
-        <v>2.2</v>
+      <c r="C22" s="31">
+        <v>78</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="35">
+        <v>1</v>
+      </c>
+      <c r="F22" s="34"/>
+      <c r="G22" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="35">
+        <f t="shared" si="1"/>
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="I22" s="36">
+        <v>8</v>
+      </c>
+      <c r="J22" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2286,56 +2241,57 @@
         <v>53</v>
       </c>
       <c r="C23" s="31">
+        <v>78</v>
+      </c>
+      <c r="D23" s="32"/>
+      <c r="E23" s="47">
+        <v>270</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="35">
+        <f t="shared" si="1"/>
+        <v>3.4615384615384617</v>
+      </c>
+      <c r="I23" s="36">
+        <v>9</v>
+      </c>
+      <c r="J23" s="37">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="42">
         <v>160</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="35">
-        <v>1843</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="35">
-        <f>+E23/C23</f>
-        <v>11.51875</v>
-      </c>
-      <c r="I23" s="36">
-        <v>6</v>
-      </c>
-      <c r="J23" s="37">
-        <f>IFERROR(ROUND((+H23/I23),1),0)</f>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="31">
-        <v>160</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="35">
-        <v>3679</v>
-      </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="35">
-        <f>+E24/C24</f>
-        <v>22.99375</v>
-      </c>
-      <c r="I24" s="36">
-        <v>20</v>
-      </c>
-      <c r="J24" s="37">
-        <f>IFERROR(ROUND((+H24/I24),1),0)</f>
-        <v>1.1</v>
+      <c r="D24" s="43"/>
+      <c r="E24" s="23">
+        <f>12595+13270</f>
+        <v>25865</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="23">
+        <f t="shared" si="1"/>
+        <v>161.65625</v>
+      </c>
+      <c r="I24" s="45">
+        <v>46</v>
+      </c>
+      <c r="J24" s="46">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2350,26 +2306,25 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="35">
-        <f>29767+572</f>
-        <v>30339</v>
+        <v>1088</v>
       </c>
       <c r="F25" s="32"/>
-      <c r="G25" s="48" t="s">
-        <v>31</v>
+      <c r="G25" s="32" t="s">
+        <v>35</v>
       </c>
       <c r="H25" s="35">
-        <f>+E25/C25</f>
-        <v>189.61875</v>
+        <f t="shared" si="1"/>
+        <v>6.8</v>
       </c>
       <c r="I25" s="36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J25" s="37">
-        <f>IFERROR(ROUND((+H25/I25),1),0)</f>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="26" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>58</v>
       </c>
@@ -2381,859 +2336,802 @@
       </c>
       <c r="D26" s="32"/>
       <c r="E26" s="35">
-        <v>3575</v>
+        <f>341+1600</f>
+        <v>1941</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="35">
-        <f>+E26/C26</f>
-        <v>22.34375</v>
+        <f t="shared" si="1"/>
+        <v>12.13125</v>
       </c>
       <c r="I26" s="36">
+        <v>20</v>
+      </c>
+      <c r="J26" s="37">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="31">
+        <v>160</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="35">
+        <v>27814</v>
+      </c>
+      <c r="F27" s="32"/>
+      <c r="G27" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="35">
+        <f t="shared" si="1"/>
+        <v>173.8375</v>
+      </c>
+      <c r="I27" s="36">
+        <v>20</v>
+      </c>
+      <c r="J27" s="37">
+        <f t="shared" si="0"/>
+        <v>8.7</v>
+      </c>
+    </row>
+    <row r="28" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="31">
+        <v>160</v>
+      </c>
+      <c r="D28" s="32"/>
+      <c r="E28" s="35">
+        <v>2960</v>
+      </c>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="35">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="I28" s="36">
         <v>4</v>
       </c>
-      <c r="J26" s="37">
-        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
-        <v>5.6</v>
-      </c>
-      <c r="L26" s="28"/>
-    </row>
-    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="42">
-        <v>70</v>
-      </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="23">
-        <v>0</v>
-      </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44" t="s">
+      <c r="J28" s="37">
+        <f t="shared" si="0"/>
+        <v>4.6</v>
+      </c>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="51">
+        <v>50</v>
+      </c>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53">
+        <v>29232</v>
+      </c>
+      <c r="F29" s="52"/>
+      <c r="G29" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="23">
-        <f>+E27/C27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="36">
-        <v>0</v>
-      </c>
-      <c r="J27" s="37">
-        <f>IFERROR(ROUND((+H27/I27),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="53">
+      <c r="H29" s="23">
+        <f t="shared" si="1"/>
+        <v>584.64</v>
+      </c>
+      <c r="I29" s="45">
+        <v>108</v>
+      </c>
+      <c r="J29" s="46">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="56">
         <v>50</v>
       </c>
-      <c r="D28" s="54"/>
-      <c r="E28" s="55">
-        <v>35684</v>
-      </c>
-      <c r="F28" s="54"/>
-      <c r="G28" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="23">
-        <f>+E28/C28</f>
-        <v>713.68</v>
-      </c>
-      <c r="I28" s="45">
-        <v>108</v>
-      </c>
-      <c r="J28" s="46">
-        <f>IFERROR(ROUND((+H28/I28),1),0)</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="58">
-        <v>50</v>
-      </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="35">
-        <v>34305</v>
-      </c>
-      <c r="F29" s="59"/>
-      <c r="G29" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="35">
-        <f>+E29/C29</f>
-        <v>686.1</v>
-      </c>
-      <c r="I29" s="36">
-        <v>130</v>
-      </c>
-      <c r="J29" s="37">
-        <f>IFERROR(ROUND((+H29/I29),1),0)</f>
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="30" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="58">
-        <v>70</v>
-      </c>
-      <c r="D30" s="59"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="35">
-        <v>0</v>
-      </c>
-      <c r="F30" s="59"/>
+        <v>27383</v>
+      </c>
+      <c r="F30" s="57"/>
       <c r="G30" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H30" s="35">
-        <f>+E30/C30</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>547.66</v>
       </c>
       <c r="I30" s="36">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="J30" s="37">
-        <f>IFERROR(ROUND((+H30/I30),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
+        <f t="shared" si="0"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="58">
+      <c r="C31" s="56">
         <v>50</v>
       </c>
-      <c r="D31" s="59"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="35">
-        <v>0</v>
-      </c>
-      <c r="F31" s="59"/>
+        <f>7159+10300</f>
+        <v>17459</v>
+      </c>
+      <c r="F31" s="57"/>
       <c r="G31" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="35">
-        <f>+E31/C31</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>349.18</v>
       </c>
       <c r="I31" s="36">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J31" s="37">
-        <f>IFERROR(ROUND((+H31/I31),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
+        <f t="shared" si="0"/>
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="58">
-        <v>70</v>
-      </c>
-      <c r="D32" s="59"/>
+      <c r="C32" s="56">
+        <v>50</v>
+      </c>
+      <c r="D32" s="57"/>
       <c r="E32" s="35">
-        <v>0</v>
-      </c>
-      <c r="F32" s="59"/>
+        <f>2905+1400+1400</f>
+        <v>5705</v>
+      </c>
+      <c r="F32" s="57"/>
       <c r="G32" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H32" s="35">
-        <f>+E32/C32</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>114.1</v>
       </c>
       <c r="I32" s="36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J32" s="37">
-        <f>IFERROR(ROUND((+H32/I32),1),0)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="58">
+      <c r="C33" s="51">
+        <v>160</v>
+      </c>
+      <c r="D33" s="52"/>
+      <c r="E33" s="23">
+        <v>6102</v>
+      </c>
+      <c r="F33" s="52"/>
+      <c r="G33" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="23">
+        <f t="shared" si="1"/>
+        <v>38.1375</v>
+      </c>
+      <c r="I33" s="45">
+        <v>15</v>
+      </c>
+      <c r="J33" s="46">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="56">
+        <v>160</v>
+      </c>
+      <c r="D34" s="57"/>
+      <c r="E34" s="35">
+        <v>4837</v>
+      </c>
+      <c r="F34" s="57"/>
+      <c r="G34" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="35">
+        <f t="shared" si="1"/>
+        <v>30.23125</v>
+      </c>
+      <c r="I34" s="36">
+        <v>24</v>
+      </c>
+      <c r="J34" s="37">
+        <f t="shared" si="0"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="56">
+        <v>160</v>
+      </c>
+      <c r="D35" s="57"/>
+      <c r="E35" s="35">
+        <v>14126</v>
+      </c>
+      <c r="F35" s="57"/>
+      <c r="G35" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35" s="35">
+        <f t="shared" si="1"/>
+        <v>88.2875</v>
+      </c>
+      <c r="I35" s="36">
+        <v>21</v>
+      </c>
+      <c r="J35" s="37">
+        <f t="shared" si="0"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="56">
+        <v>160</v>
+      </c>
+      <c r="D36" s="57"/>
+      <c r="E36" s="35">
+        <v>10797</v>
+      </c>
+      <c r="F36" s="57"/>
+      <c r="G36" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36" s="35">
+        <f t="shared" si="1"/>
+        <v>67.48125</v>
+      </c>
+      <c r="I36" s="36">
+        <v>15</v>
+      </c>
+      <c r="J36" s="37">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="51">
+        <v>70</v>
+      </c>
+      <c r="D37" s="52"/>
+      <c r="E37" s="23">
+        <v>0</v>
+      </c>
+      <c r="F37" s="52"/>
+      <c r="G37" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="45">
+        <v>0</v>
+      </c>
+      <c r="J37" s="46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="56">
         <v>50</v>
       </c>
-      <c r="D33" s="59"/>
-      <c r="E33" s="35">
-        <f>684+6100+1400+1400</f>
-        <v>9584</v>
-      </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="34" t="s">
+      <c r="D38" s="57"/>
+      <c r="E38" s="35">
+        <v>0</v>
+      </c>
+      <c r="F38" s="57"/>
+      <c r="G38" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="35">
-        <f>+E33/C33</f>
-        <v>191.68</v>
-      </c>
-      <c r="I33" s="36">
-        <v>46</v>
-      </c>
-      <c r="J33" s="37">
-        <f>IFERROR(ROUND((+H33/I33),1),0)</f>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="58">
-        <v>50</v>
-      </c>
-      <c r="D34" s="59"/>
-      <c r="E34" s="35">
-        <f>20+1400+1400+1400</f>
-        <v>4220</v>
-      </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="35">
-        <f>+E34/C34</f>
-        <v>84.4</v>
-      </c>
-      <c r="I34" s="36">
-        <v>80</v>
-      </c>
-      <c r="J34" s="37">
-        <f>IFERROR(ROUND((+H34/I34),1),0)</f>
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="53">
+      <c r="H38" s="35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="36">
+        <v>1</v>
+      </c>
+      <c r="J38" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="56">
         <v>160</v>
       </c>
-      <c r="D35" s="54"/>
-      <c r="E35" s="23">
-        <v>8002</v>
-      </c>
-      <c r="F35" s="54"/>
-      <c r="G35" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="23">
-        <f>+E35/C35</f>
-        <v>50.0125</v>
-      </c>
-      <c r="I35" s="45">
-        <v>15</v>
-      </c>
-      <c r="J35" s="46">
-        <f>IFERROR(ROUND((+H35/I35),1),0)</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="58">
+      <c r="D39" s="57"/>
+      <c r="E39" s="35">
+        <v>150</v>
+      </c>
+      <c r="F39" s="57"/>
+      <c r="G39" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39" s="35">
+        <f t="shared" si="1"/>
+        <v>0.9375</v>
+      </c>
+      <c r="I39" s="36">
+        <v>1</v>
+      </c>
+      <c r="J39" s="37">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="56">
         <v>160</v>
       </c>
-      <c r="D36" s="59"/>
-      <c r="E36" s="35">
-        <v>10497</v>
-      </c>
-      <c r="F36" s="59"/>
-      <c r="G36" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="35">
-        <f>+E36/C36</f>
-        <v>65.60625</v>
-      </c>
-      <c r="I36" s="36">
-        <v>24</v>
-      </c>
-      <c r="J36" s="37">
-        <f>IFERROR(ROUND((+H36/I36),1),0)</f>
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="58">
-        <v>160</v>
-      </c>
-      <c r="D37" s="59"/>
-      <c r="E37" s="35">
-        <v>14476</v>
-      </c>
-      <c r="F37" s="59"/>
-      <c r="G37" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="35">
-        <f>+E37/C37</f>
-        <v>90.475</v>
-      </c>
-      <c r="I37" s="36">
-        <v>21</v>
-      </c>
-      <c r="J37" s="37">
-        <f>IFERROR(ROUND((+H37/I37),1),0)</f>
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="58">
-        <v>160</v>
-      </c>
-      <c r="D38" s="59"/>
-      <c r="E38" s="35">
-        <v>10922</v>
-      </c>
-      <c r="F38" s="59"/>
-      <c r="G38" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" s="35">
-        <f>+E38/C38</f>
-        <v>68.2625</v>
-      </c>
-      <c r="I38" s="36">
-        <v>15</v>
-      </c>
-      <c r="J38" s="37">
-        <f>IFERROR(ROUND((+H38/I38),1),0)</f>
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="53">
-        <v>70</v>
-      </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="23">
-        <v>0</v>
-      </c>
-      <c r="F39" s="54"/>
-      <c r="G39" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="23">
-        <f>+E39/C39</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="45">
-        <v>0</v>
-      </c>
-      <c r="J39" s="46">
-        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="58">
-        <v>50</v>
-      </c>
-      <c r="D40" s="59"/>
+      <c r="D40" s="57"/>
       <c r="E40" s="35">
         <v>0</v>
       </c>
-      <c r="F40" s="59"/>
+      <c r="F40" s="57"/>
       <c r="G40" s="34" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H40" s="35">
         <f>+E40/C40</f>
         <v>0</v>
       </c>
       <c r="I40" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="37">
-        <f>IFERROR(ROUND((+H40/I40),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="58">
+      <c r="C41" s="60">
+        <v>84</v>
+      </c>
+      <c r="D41" s="61"/>
+      <c r="E41" s="62">
+        <f>2677-1</f>
+        <v>2676</v>
+      </c>
+      <c r="F41" s="61"/>
+      <c r="G41" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="35">
+        <f t="shared" si="1"/>
+        <v>31.857142857142858</v>
+      </c>
+      <c r="I41" s="36">
+        <v>0</v>
+      </c>
+      <c r="J41" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="60">
+        <v>50</v>
+      </c>
+      <c r="D42" s="61"/>
+      <c r="E42" s="64">
+        <f>17+1400</f>
+        <v>1417</v>
+      </c>
+      <c r="F42" s="61"/>
+      <c r="G42" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="35">
+        <f t="shared" si="1"/>
+        <v>28.34</v>
+      </c>
+      <c r="I42" s="36">
+        <v>14</v>
+      </c>
+      <c r="J42" s="37">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="60">
+        <v>136</v>
+      </c>
+      <c r="D43" s="61"/>
+      <c r="E43" s="64">
+        <v>9538</v>
+      </c>
+      <c r="F43" s="61"/>
+      <c r="G43" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="35">
+        <f t="shared" si="1"/>
+        <v>70.13235294117646</v>
+      </c>
+      <c r="I43" s="36">
+        <v>27</v>
+      </c>
+      <c r="J43" s="37">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="44" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="67">
         <v>160</v>
       </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="35">
-        <v>150</v>
-      </c>
-      <c r="F41" s="59"/>
-      <c r="G41" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41" s="35">
-        <f>+E41/C41</f>
-        <v>0.9375</v>
-      </c>
-      <c r="I41" s="36">
-        <v>1</v>
-      </c>
-      <c r="J41" s="37">
-        <f>IFERROR(ROUND((+H41/I41),1),0)</f>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="58">
+      <c r="D44" s="68"/>
+      <c r="E44" s="35">
+        <v>7974</v>
+      </c>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="47">
+        <f t="shared" si="1"/>
+        <v>49.8375</v>
+      </c>
+      <c r="I44" s="36">
+        <v>2</v>
+      </c>
+      <c r="J44" s="37">
+        <f t="shared" si="0"/>
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="67">
         <v>160</v>
       </c>
-      <c r="D42" s="59"/>
-      <c r="E42" s="35">
-        <v>0</v>
-      </c>
-      <c r="F42" s="59"/>
-      <c r="G42" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" s="35">
-        <f>+E42/C42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="36">
-        <v>0</v>
-      </c>
-      <c r="J42" s="37">
-        <f>IFERROR(ROUND((+H42/I42),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="62">
-        <v>84</v>
-      </c>
-      <c r="D43" s="63"/>
-      <c r="E43" s="64">
-        <f>2733-1</f>
-        <v>2732</v>
-      </c>
-      <c r="F43" s="63"/>
-      <c r="G43" s="65" t="s">
+      <c r="D45" s="68"/>
+      <c r="E45" s="47">
+        <f>2123+1920</f>
+        <v>4043</v>
+      </c>
+      <c r="F45" s="68"/>
+      <c r="G45" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="35">
-        <f>+E43/C43</f>
-        <v>32.523809523809526</v>
-      </c>
-      <c r="I43" s="36">
-        <v>0</v>
-      </c>
-      <c r="J43" s="37">
-        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="62">
-        <v>50</v>
-      </c>
-      <c r="D44" s="63"/>
-      <c r="E44" s="66">
-        <v>626</v>
-      </c>
-      <c r="F44" s="63"/>
-      <c r="G44" s="65" t="s">
+      <c r="H45" s="47">
+        <f>+E45/C45</f>
+        <v>25.26875</v>
+      </c>
+      <c r="I45" s="36">
+        <v>0</v>
+      </c>
+      <c r="J45" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="72">
+        <v>160</v>
+      </c>
+      <c r="D46" s="73"/>
+      <c r="E46" s="74">
+        <v>0</v>
+      </c>
+      <c r="F46" s="73"/>
+      <c r="G46" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="35">
-        <f>+E44/C44</f>
-        <v>12.52</v>
-      </c>
-      <c r="I44" s="36">
-        <v>14</v>
-      </c>
-      <c r="J44" s="37">
-        <f>IFERROR(ROUND((+H44/I44),1),0)</f>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="62">
-        <v>136</v>
-      </c>
-      <c r="D45" s="63"/>
-      <c r="E45" s="66">
-        <v>9983</v>
-      </c>
-      <c r="F45" s="63"/>
-      <c r="G45" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="35">
-        <f>+E45/C45</f>
-        <v>73.40441176470588</v>
-      </c>
-      <c r="I45" s="36">
-        <v>27</v>
-      </c>
-      <c r="J45" s="37">
-        <f>IFERROR(ROUND((+H45/I45),1),0)</f>
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="67" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="69">
-        <v>160</v>
-      </c>
-      <c r="D46" s="70"/>
-      <c r="E46" s="35">
-        <v>8280</v>
-      </c>
-      <c r="F46" s="70"/>
-      <c r="G46" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46" s="72">
+      <c r="H46" s="76">
         <f>+E46/C46</f>
-        <v>51.75</v>
-      </c>
-      <c r="I46" s="36">
-        <v>2</v>
-      </c>
-      <c r="J46" s="37">
-        <f>IFERROR(ROUND((+H46/I46),1),0)</f>
-        <v>25.9</v>
-      </c>
-    </row>
-    <row r="47" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="68" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="69">
-        <v>160</v>
-      </c>
-      <c r="D47" s="70"/>
-      <c r="E47" s="72">
-        <v>2140</v>
-      </c>
-      <c r="F47" s="70"/>
-      <c r="G47" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47" s="72">
-        <f>+E47/C47</f>
-        <v>13.375</v>
-      </c>
-      <c r="I47" s="36">
-        <v>0</v>
-      </c>
-      <c r="J47" s="37">
-        <f>IFERROR(ROUND((+H47/I47),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="73" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="75">
-        <v>160</v>
-      </c>
-      <c r="D48" s="76"/>
-      <c r="E48" s="77">
-        <v>0</v>
-      </c>
-      <c r="F48" s="76"/>
-      <c r="G48" s="78" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="79">
-        <f>+E48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="I48" s="80">
-        <v>0</v>
-      </c>
-      <c r="J48" s="81">
-        <f>IFERROR(ROUND((+H48/I48),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="82"/>
-      <c r="B49" s="82"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="77">
+        <v>0</v>
+      </c>
+      <c r="J46" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="79"/>
+      <c r="B47" s="79"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="80"/>
+    </row>
+    <row r="48" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="81"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="82">
+        <f>SUM(E5:E47)</f>
+        <v>438077</v>
+      </c>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="83">
+        <f>SUM(H5:H47)</f>
+        <v>5380.629527849603</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="79"/>
+      <c r="B49" s="79"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
-      <c r="H49" s="83"/>
-    </row>
-    <row r="50" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="84"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="84"/>
-      <c r="E50" s="85">
-        <f>SUM(E5:E49)</f>
-        <v>467280</v>
-      </c>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="86">
-        <f>SUM(H5:H49)</f>
-        <v>5751.733541801337</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="82"/>
+      <c r="H49" s="80"/>
+    </row>
+    <row r="50" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="79"/>
+      <c r="B50" s="79"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="80"/>
+    </row>
+    <row r="51" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E51" s="28"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
-      <c r="H51" s="83"/>
-    </row>
-    <row r="52" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="82"/>
-      <c r="B52" s="82"/>
+      <c r="H51" s="80"/>
+    </row>
+    <row r="52" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
-      <c r="H52" s="83"/>
+      <c r="H52" s="80"/>
     </row>
     <row r="53" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
-      <c r="H53" s="83"/>
+      <c r="H53" s="80"/>
     </row>
     <row r="54" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
-      <c r="H54" s="83"/>
+      <c r="H54" s="80"/>
     </row>
     <row r="55" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
-      <c r="H55" s="83"/>
+      <c r="H55" s="80"/>
     </row>
     <row r="56" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
-      <c r="H56" s="83"/>
+      <c r="H56" s="80"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E57" s="28"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
-      <c r="H57" s="83"/>
+      <c r="H57" s="80"/>
     </row>
     <row r="58" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
-      <c r="H58" s="83"/>
+      <c r="H58" s="80"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E59" s="28"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
-      <c r="H59" s="83"/>
+      <c r="H59" s="80"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E60" s="28"/>
+      <c r="E60" s="84"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
-      <c r="H60" s="83"/>
+      <c r="H60" s="80"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
-      <c r="H61" s="83"/>
+      <c r="H61" s="80"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="87"/>
+      <c r="E62" s="84"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
-      <c r="H62" s="83"/>
+      <c r="H62" s="80"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E63" s="28"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
-      <c r="H63" s="83"/>
+      <c r="H63" s="80"/>
     </row>
     <row r="64" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E64" s="87"/>
+      <c r="E64" s="84"/>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
-      <c r="H64" s="83"/>
+      <c r="H64" s="80"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E65" s="28"/>
       <c r="F65" s="28"/>
       <c r="G65" s="28"/>
-      <c r="H65" s="83"/>
+      <c r="H65" s="80"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E66" s="87"/>
+      <c r="E66" s="84"/>
       <c r="F66" s="28"/>
       <c r="G66" s="28"/>
-      <c r="H66" s="83"/>
+      <c r="H66" s="80"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E67" s="28"/>
+      <c r="E67" s="84"/>
       <c r="F67" s="28"/>
       <c r="G67" s="28"/>
-      <c r="H67" s="83"/>
+      <c r="H67" s="80"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E68" s="87"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="83"/>
+      <c r="E68" s="84"/>
+      <c r="H68" s="80"/>
     </row>
     <row r="69" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E69" s="87"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="83"/>
+      <c r="E69" s="84"/>
+      <c r="H69" s="80"/>
     </row>
     <row r="70" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E70" s="87"/>
-      <c r="H70" s="83"/>
+      <c r="E70" s="84"/>
+      <c r="H70" s="80"/>
     </row>
     <row r="71" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E71" s="87"/>
-      <c r="H71" s="83"/>
+      <c r="E71" s="84"/>
+      <c r="H71" s="80"/>
     </row>
     <row r="72" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E72" s="87"/>
-      <c r="H72" s="83"/>
+      <c r="E72" s="84"/>
+      <c r="H72" s="80"/>
     </row>
     <row r="73" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E73" s="87"/>
-      <c r="H73" s="83"/>
-    </row>
-    <row r="74" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E74" s="87"/>
-      <c r="H74" s="83"/>
-    </row>
-    <row r="75" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E75" s="87"/>
-      <c r="H75" s="83"/>
-    </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="28"/>
-    </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G80" s="88"/>
+      <c r="E73" s="84"/>
+      <c r="H73" s="80"/>
+    </row>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="28"/>
+    </row>
+    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="85"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -3286,7 +3184,7 @@
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+  <conditionalFormatting sqref="H12">
     <cfRule type="cellIs" dxfId="12" priority="65" operator="lessThan">
       <formula>10</formula>
     </cfRule>
@@ -3294,7 +3192,7 @@
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="H14">
     <cfRule type="cellIs" dxfId="14" priority="63" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3302,7 +3200,7 @@
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H15">
     <cfRule type="cellIs" dxfId="16" priority="61" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -3310,7 +3208,7 @@
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="H16">
     <cfRule type="cellIs" dxfId="18" priority="59" operator="lessThan">
       <formula>400</formula>
     </cfRule>
@@ -3318,7 +3216,7 @@
       <formula>1300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H17">
+  <conditionalFormatting sqref="H17:H19">
     <cfRule type="cellIs" dxfId="20" priority="55" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3326,128 +3224,127 @@
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="22" priority="49" operator="lessThan">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="cellIs" dxfId="22" priority="53" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="54" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H22">
+    <cfRule type="cellIs" dxfId="24" priority="49" operator="lessThan">
       <formula>200</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="50" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H21">
-    <cfRule type="cellIs" dxfId="24" priority="51" operator="lessThan">
+  <conditionalFormatting sqref="H23">
+    <cfRule type="cellIs" dxfId="26" priority="51" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="52" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="cellIs" dxfId="26" priority="47" operator="lessThan">
+  <conditionalFormatting sqref="H24">
+    <cfRule type="cellIs" dxfId="28" priority="47" operator="lessThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="48" operator="greaterThan">
       <formula>250</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H24">
-    <cfRule type="cellIs" dxfId="28" priority="43" operator="lessThan">
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="cellIs" dxfId="30" priority="43" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="44" operator="greaterThan">
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="cellIs" dxfId="30" priority="41" operator="lessThan">
+  <conditionalFormatting sqref="H27">
+    <cfRule type="cellIs" dxfId="32" priority="41" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="42" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="42" operator="greaterThan">
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="cellIs" dxfId="32" priority="37" operator="lessThan">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="cellIs" dxfId="34" priority="37" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="38" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="38" operator="greaterThan">
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28:H29">
-    <cfRule type="cellIs" dxfId="34" priority="33" operator="lessThan">
+  <conditionalFormatting sqref="H29:H30">
+    <cfRule type="cellIs" dxfId="36" priority="33" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="34" operator="greaterThan">
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="cellIs" dxfId="36" priority="23" operator="lessThan">
-      <formula>300</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="24" operator="greaterThan">
-      <formula>600</formula>
+  <conditionalFormatting sqref="H31:H32">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="lessThan">
+      <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="cellIs" dxfId="38" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="32" operator="greaterThan">
       <formula>1500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H34">
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="lessThan">
-      <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="cellIs" dxfId="40" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H33">
-    <cfRule type="cellIs" dxfId="41" priority="32" operator="greaterThan">
-      <formula>1500</formula>
+  <conditionalFormatting sqref="H33:H36">
+    <cfRule type="cellIs" dxfId="41" priority="12" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="13" operator="greaterThan">
+      <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34">
-    <cfRule type="cellIs" dxfId="42" priority="28" operator="greaterThan">
+  <conditionalFormatting sqref="H37:H38 H41:H46">
+    <cfRule type="cellIs" dxfId="43" priority="25" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="26" operator="greaterThan">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39:H40">
+    <cfRule type="cellIs" dxfId="45" priority="5" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="6" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H38">
-    <cfRule type="cellIs" dxfId="43" priority="12" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="13" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39:H40 H43:H48">
-    <cfRule type="cellIs" dxfId="45" priority="25" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="26" operator="greaterThan">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H41:H42">
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="6" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J48">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J5:J46">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="61" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -8,17 +8,16 @@
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
-    <sheet sheetId="29" name="Hoja1" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J46</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
@@ -101,24 +100,12 @@
     <t xml:space="preserve">GLUP! FRESH 6X2000ML </t>
   </si>
   <si>
-    <t>PRODT-0048</t>
-  </si>
-  <si>
-    <t>GLUP! PONCHE DE FRUTAS CAJA X 6BOT X 2LTS</t>
-  </si>
-  <si>
     <t>PRODT-0049</t>
   </si>
   <si>
     <t>GLUP! MANZANA VERDE CAJA X 6BOT X 2LTS</t>
   </si>
   <si>
-    <t>PRODT-0050</t>
-  </si>
-  <si>
-    <t>GLUP! CHICLE BOMBA CAJA X 6BOT X 2LTS</t>
-  </si>
-  <si>
     <t>PRODT-0097</t>
   </si>
   <si>
@@ -156,12 +143,6 @@
   </si>
   <si>
     <t>GLUP! KOLITA  CAJA X 12BOT X 1.0LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0090</t>
-  </si>
-  <si>
-    <t>GLUP! MANZANA VERDE CAJA X 12BOT X 1.0LTS</t>
   </si>
   <si>
     <t>PRODT-0104</t>
@@ -678,13 +659,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -779,27 +760,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="47">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1607,7 +1568,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1632,7 +1593,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46283</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1645,7 +1606,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3541666666678793</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1698,8 +1659,8 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>33022+24800+32640</f>
-        <v>90462</v>
+        <f>74507+27360+30160+11680+442</f>
+        <v>144149</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -1707,14 +1668,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1130.775</v>
+        <v>1801.8625</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
-        <f t="shared" ref="J5:J46" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.4</v>
+        <f>IFERROR(ROUND((+H5/I5),1),0)</f>
+        <v>2.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1730,23 +1691,23 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>10925-2</f>
-        <v>10923</v>
+        <f>1691+24319</f>
+        <v>26010</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="35">
-        <f t="shared" ref="H6:H44" si="1">+E6/C6</f>
-        <v>136.5375</v>
-      </c>
-      <c r="I6" s="36">
+      <c r="H6" s="33">
+        <f t="shared" ref="H6:H41" si="0">+E6/C6</f>
+        <v>325.125</v>
+      </c>
+      <c r="I6" s="35">
         <v>111</v>
       </c>
-      <c r="J6" s="37">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+      <c r="J6" s="36">
+        <f>IFERROR(ROUND((+H6/I6),1),0)</f>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1760,24 +1721,23 @@
         <v>80</v>
       </c>
       <c r="D7" s="32"/>
-      <c r="E7" s="35">
-        <f>2850+210+20080</f>
-        <v>23140</v>
+      <c r="E7" s="33">
+        <v>19306</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="35">
-        <f t="shared" si="1"/>
-        <v>289.25</v>
-      </c>
-      <c r="I7" s="36">
+      <c r="H7" s="33">
+        <f t="shared" si="0"/>
+        <v>241.325</v>
+      </c>
+      <c r="I7" s="35">
         <v>240</v>
       </c>
-      <c r="J7" s="37">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+      <c r="J7" s="36">
+        <f>IFERROR(ROUND((+H7/I7),1),0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1791,23 +1751,23 @@
         <v>80</v>
       </c>
       <c r="D8" s="32"/>
-      <c r="E8" s="35">
-        <v>23296</v>
+      <c r="E8" s="33">
+        <v>12908</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="35">
-        <f t="shared" si="1"/>
-        <v>291.2</v>
-      </c>
-      <c r="I8" s="36">
+      <c r="H8" s="33">
+        <f t="shared" si="0"/>
+        <v>161.35</v>
+      </c>
+      <c r="I8" s="35">
         <v>83</v>
       </c>
-      <c r="J8" s="37">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
+      <c r="J8" s="36">
+        <f>IFERROR(ROUND((+H8/I8),1),0)</f>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1821,22 +1781,22 @@
         <v>80</v>
       </c>
       <c r="D9" s="32"/>
-      <c r="E9" s="35">
+      <c r="E9" s="33">
         <v>0</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="35">
-        <f t="shared" si="1"/>
+      <c r="H9" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="35">
         <v>86</v>
       </c>
-      <c r="J9" s="37">
-        <f t="shared" si="0"/>
+      <c r="J9" s="36">
+        <f>IFERROR(ROUND((+H9/I9),1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1851,629 +1811,628 @@
         <v>80</v>
       </c>
       <c r="D10" s="32"/>
-      <c r="E10" s="35">
-        <f>14236+9280</f>
-        <v>23516</v>
+      <c r="E10" s="33">
+        <f>25204+12894</f>
+        <v>38098</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="35">
-        <f t="shared" si="1"/>
-        <v>293.95</v>
-      </c>
-      <c r="I10" s="36">
+      <c r="H10" s="33">
+        <f t="shared" si="0"/>
+        <v>476.225</v>
+      </c>
+      <c r="I10" s="35">
         <v>261</v>
       </c>
-      <c r="J10" s="37">
-        <f t="shared" si="0"/>
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="J10" s="36">
+        <f>IFERROR(ROUND((+H10/I10),1),0)</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="31">
         <v>80</v>
       </c>
       <c r="D11" s="32"/>
-      <c r="E11" s="35">
-        <v>0</v>
+      <c r="E11" s="33">
+        <v>4715</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="36">
-        <v>0</v>
-      </c>
-      <c r="J11" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H11" s="33">
+        <f t="shared" si="0"/>
+        <v>58.9375</v>
+      </c>
+      <c r="I11" s="35">
+        <v>6</v>
+      </c>
+      <c r="J11" s="36">
+        <f>IFERROR(ROUND((+H11/I11),1),0)</f>
+        <v>9.8</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="31">
         <v>80</v>
       </c>
       <c r="D12" s="32"/>
-      <c r="E12" s="35">
-        <v>4765</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="35">
-        <f t="shared" si="1"/>
-        <v>59.5625</v>
-      </c>
-      <c r="I12" s="36">
-        <v>6</v>
-      </c>
-      <c r="J12" s="37">
-        <f t="shared" si="0"/>
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="13" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="E12" s="39">
+        <f>16-1+1120+9920+661</f>
+        <v>11716</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="H12" s="33">
+        <f t="shared" si="0"/>
+        <v>146.45</v>
+      </c>
+      <c r="I12" s="35">
+        <v>60</v>
+      </c>
+      <c r="J12" s="36">
+        <f>IFERROR(ROUND((+H12/I12),1),0)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
         <v>32</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="C13" s="31">
         <v>80</v>
       </c>
       <c r="D13" s="32"/>
-      <c r="E13" s="35">
+      <c r="E13" s="33">
         <v>0</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="35">
-        <f t="shared" si="1"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="35">
+        <v>6</v>
+      </c>
+      <c r="J13" s="36">
+        <f>IFERROR(ROUND((+H13/I13),1),0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="39" t="s">
+      <c r="A14" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="31">
-        <v>80</v>
-      </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33">
-        <f>64-1</f>
-        <v>63</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32" t="s">
+      <c r="B14" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="35">
-        <f t="shared" si="1"/>
-        <v>0.7875</v>
-      </c>
-      <c r="I14" s="36">
-        <v>60</v>
-      </c>
-      <c r="J14" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C14" s="42">
+        <v>78</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="23">
+        <v>7764</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="23">
+        <f t="shared" si="0"/>
+        <v>99.53846153846153</v>
+      </c>
+      <c r="I14" s="45">
+        <v>118</v>
+      </c>
+      <c r="J14" s="46">
+        <f>IFERROR(ROUND((+H14/I14),1),0)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="38" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="31">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D15" s="32"/>
-      <c r="E15" s="35">
-        <v>0</v>
-      </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="36">
-        <v>6</v>
-      </c>
-      <c r="J15" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E15" s="33">
+        <v>5683</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="33">
+        <f t="shared" si="0"/>
+        <v>72.85897435897436</v>
+      </c>
+      <c r="I15" s="35">
+        <v>14</v>
+      </c>
+      <c r="J15" s="36">
+        <f>IFERROR(ROUND((+H15/I15),1),0)</f>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="31">
         <v>78</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="23">
-        <f>1168+13650</f>
-        <v>14818</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="23">
-        <f t="shared" si="1"/>
-        <v>189.97435897435898</v>
-      </c>
-      <c r="I16" s="45">
-        <v>118</v>
-      </c>
-      <c r="J16" s="46">
-        <f t="shared" si="0"/>
-        <v>1.6</v>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33">
+        <v>9530</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="33">
+        <f t="shared" si="0"/>
+        <v>122.17948717948718</v>
+      </c>
+      <c r="I16" s="35">
+        <v>49</v>
+      </c>
+      <c r="J16" s="36">
+        <f>IFERROR(ROUND((+H16/I16),1),0)</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>41</v>
       </c>
       <c r="C17" s="31">
         <v>78</v>
       </c>
       <c r="D17" s="32"/>
-      <c r="E17" s="35">
-        <v>7551</v>
+      <c r="E17" s="33">
+        <v>9791</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="35">
-        <f t="shared" si="1"/>
-        <v>96.8076923076923</v>
-      </c>
-      <c r="I17" s="36">
-        <v>14</v>
-      </c>
-      <c r="J17" s="37">
-        <f t="shared" si="0"/>
-        <v>6.9</v>
+        <v>31</v>
+      </c>
+      <c r="H17" s="33">
+        <f t="shared" si="0"/>
+        <v>125.52564102564102</v>
+      </c>
+      <c r="I17" s="35">
+        <v>45</v>
+      </c>
+      <c r="J17" s="36">
+        <f>IFERROR(ROUND((+H17/I17),1),0)</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="31">
         <v>78</v>
       </c>
       <c r="D18" s="32"/>
-      <c r="E18" s="35">
-        <v>14115</v>
+      <c r="E18" s="33">
+        <v>9695</v>
       </c>
       <c r="F18" s="34"/>
-      <c r="G18" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="35">
-        <f t="shared" si="1"/>
-        <v>180.96153846153845</v>
-      </c>
-      <c r="I18" s="36">
-        <v>49</v>
-      </c>
-      <c r="J18" s="37">
-        <f t="shared" si="0"/>
-        <v>3.7</v>
+      <c r="G18" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="33">
+        <f t="shared" si="0"/>
+        <v>124.2948717948718</v>
+      </c>
+      <c r="I18" s="35">
+        <v>7</v>
+      </c>
+      <c r="J18" s="36">
+        <f>IFERROR(ROUND((+H18/I18),1),0)</f>
+        <v>17.8</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="38" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="31">
         <v>78</v>
       </c>
       <c r="D19" s="32"/>
-      <c r="E19" s="35">
-        <v>13600</v>
+      <c r="E19" s="33">
+        <v>1</v>
       </c>
       <c r="F19" s="34"/>
-      <c r="G19" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="35">
-        <f t="shared" si="1"/>
-        <v>174.35897435897436</v>
-      </c>
-      <c r="I19" s="36">
-        <v>45</v>
-      </c>
-      <c r="J19" s="37">
-        <f t="shared" si="0"/>
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="20" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="G19" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="33">
+        <f t="shared" si="0"/>
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="I19" s="35">
+        <v>8</v>
+      </c>
+      <c r="J19" s="36">
+        <f>IFERROR(ROUND((+H19/I19),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="38" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="31">
         <v>78</v>
       </c>
       <c r="D20" s="32"/>
-      <c r="E20" s="35">
-        <v>0</v>
-      </c>
-      <c r="F20" s="32"/>
+      <c r="E20" s="47">
+        <v>15437</v>
+      </c>
+      <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="36">
-        <v>0</v>
-      </c>
-      <c r="J20" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="H20" s="33">
+        <f t="shared" si="0"/>
+        <v>197.9102564102564</v>
+      </c>
+      <c r="I20" s="35">
+        <v>9</v>
+      </c>
+      <c r="J20" s="36">
+        <f>IFERROR(ROUND((+H20/I20),1),0)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="31">
-        <v>78</v>
-      </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="35">
-        <v>10450</v>
-      </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="35">
-        <f t="shared" si="1"/>
-        <v>133.97435897435898</v>
-      </c>
-      <c r="I21" s="36">
-        <v>7</v>
-      </c>
-      <c r="J21" s="37">
-        <f t="shared" si="0"/>
-        <v>19.1</v>
+      <c r="C21" s="42">
+        <v>160</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="23">
+        <v>19605</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="23">
+        <f t="shared" si="0"/>
+        <v>122.53125</v>
+      </c>
+      <c r="I21" s="45">
+        <v>46</v>
+      </c>
+      <c r="J21" s="46">
+        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="31">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D22" s="32"/>
-      <c r="E22" s="35">
-        <v>1</v>
-      </c>
-      <c r="F22" s="34"/>
+      <c r="E22" s="33">
+        <v>833</v>
+      </c>
+      <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="35">
-        <f t="shared" si="1"/>
-        <v>0.01282051282051282</v>
-      </c>
-      <c r="I22" s="36">
-        <v>8</v>
-      </c>
-      <c r="J22" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="H22" s="33">
+        <f t="shared" si="0"/>
+        <v>5.20625</v>
+      </c>
+      <c r="I22" s="35">
+        <v>6</v>
+      </c>
+      <c r="J22" s="36">
+        <f>IFERROR(ROUND((+H22/I22),1),0)</f>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="38" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="31">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D23" s="32"/>
-      <c r="E23" s="47">
-        <v>270</v>
-      </c>
-      <c r="F23" s="34"/>
+      <c r="E23" s="33">
+        <f>16171+1512</f>
+        <v>17683</v>
+      </c>
+      <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="35">
-        <f t="shared" si="1"/>
-        <v>3.4615384615384617</v>
-      </c>
-      <c r="I23" s="36">
-        <v>9</v>
-      </c>
-      <c r="J23" s="37">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>31</v>
+      </c>
+      <c r="H23" s="33">
+        <f t="shared" si="0"/>
+        <v>110.51875</v>
+      </c>
+      <c r="I23" s="35">
+        <v>20</v>
+      </c>
+      <c r="J23" s="36">
+        <f>IFERROR(ROUND((+H23/I23),1),0)</f>
+        <v>5.5</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="31">
         <v>160</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="23">
-        <f>12595+13270</f>
-        <v>25865</v>
-      </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="23">
-        <f t="shared" si="1"/>
-        <v>161.65625</v>
-      </c>
-      <c r="I24" s="45">
-        <v>46</v>
-      </c>
-      <c r="J24" s="46">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="25" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+      <c r="D24" s="32"/>
+      <c r="E24" s="33">
+        <v>24689</v>
+      </c>
+      <c r="F24" s="32"/>
+      <c r="G24" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="33">
+        <f t="shared" si="0"/>
+        <v>154.30625</v>
+      </c>
+      <c r="I24" s="35">
+        <v>20</v>
+      </c>
+      <c r="J24" s="36">
+        <f>IFERROR(ROUND((+H24/I24),1),0)</f>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="38" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="31">
         <v>160</v>
       </c>
       <c r="D25" s="32"/>
-      <c r="E25" s="35">
-        <v>1088</v>
+      <c r="E25" s="33">
+        <v>2160</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="35">
-        <f t="shared" si="1"/>
-        <v>6.8</v>
-      </c>
-      <c r="I25" s="36">
-        <v>6</v>
-      </c>
-      <c r="J25" s="37">
-        <f t="shared" si="0"/>
-        <v>1.1</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H25" s="33">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="I25" s="35">
+        <v>4</v>
+      </c>
+      <c r="J25" s="36">
+        <f>IFERROR(ROUND((+H25/I25),1),0)</f>
+        <v>3.4</v>
+      </c>
+      <c r="L25" s="28"/>
     </row>
     <row r="26" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="51">
+        <v>50</v>
+      </c>
+      <c r="D26" s="52"/>
+      <c r="E26" s="53">
+        <v>23742</v>
+      </c>
+      <c r="F26" s="52"/>
+      <c r="G26" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="23">
+        <f t="shared" si="0"/>
+        <v>474.84</v>
+      </c>
+      <c r="I26" s="45">
+        <v>108</v>
+      </c>
+      <c r="J26" s="46">
+        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="56">
+        <v>50</v>
+      </c>
+      <c r="D27" s="57"/>
+      <c r="E27" s="33">
+        <v>22793</v>
+      </c>
+      <c r="F27" s="57"/>
+      <c r="G27" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="33">
+        <f t="shared" si="0"/>
+        <v>455.86</v>
+      </c>
+      <c r="I27" s="35">
+        <v>130</v>
+      </c>
+      <c r="J27" s="36">
+        <f>IFERROR(ROUND((+H27/I27),1),0)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="56">
+        <v>50</v>
+      </c>
+      <c r="D28" s="57"/>
+      <c r="E28" s="33">
+        <f>24994+9740</f>
+        <v>34734</v>
+      </c>
+      <c r="F28" s="57"/>
+      <c r="G28" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="33">
+        <f t="shared" si="0"/>
+        <v>694.68</v>
+      </c>
+      <c r="I28" s="35">
+        <v>46</v>
+      </c>
+      <c r="J28" s="36">
+        <f>IFERROR(ROUND((+H28/I28),1),0)</f>
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="56">
+        <v>50</v>
+      </c>
+      <c r="D29" s="57"/>
+      <c r="E29" s="33">
+        <v>5895</v>
+      </c>
+      <c r="F29" s="57"/>
+      <c r="G29" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="33">
+        <f t="shared" si="0"/>
+        <v>117.9</v>
+      </c>
+      <c r="I29" s="35">
+        <v>80</v>
+      </c>
+      <c r="J29" s="36">
+        <f>IFERROR(ROUND((+H29/I29),1),0)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="51">
         <v>160</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="35">
-        <f>341+1600</f>
-        <v>1941</v>
-      </c>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" s="35">
-        <f t="shared" si="1"/>
-        <v>12.13125</v>
-      </c>
-      <c r="I26" s="36">
-        <v>20</v>
-      </c>
-      <c r="J26" s="37">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="31">
-        <v>160</v>
-      </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="35">
-        <v>27814</v>
-      </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="H27" s="35">
-        <f t="shared" si="1"/>
-        <v>173.8375</v>
-      </c>
-      <c r="I27" s="36">
-        <v>20</v>
-      </c>
-      <c r="J27" s="37">
-        <f t="shared" si="0"/>
-        <v>8.7</v>
-      </c>
-    </row>
-    <row r="28" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="31">
-        <v>160</v>
-      </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="35">
-        <v>2960</v>
-      </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="35">
-        <f t="shared" si="1"/>
-        <v>18.5</v>
-      </c>
-      <c r="I28" s="36">
-        <v>4</v>
-      </c>
-      <c r="J28" s="37">
-        <f t="shared" si="0"/>
-        <v>4.6</v>
-      </c>
-      <c r="L28" s="28"/>
-    </row>
-    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="51">
-        <v>50</v>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53">
-        <v>29232</v>
-      </c>
-      <c r="F29" s="52"/>
-      <c r="G29" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="23">
-        <f t="shared" si="1"/>
-        <v>584.64</v>
-      </c>
-      <c r="I29" s="45">
-        <v>108</v>
-      </c>
-      <c r="J29" s="46">
-        <f t="shared" si="0"/>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="56">
-        <v>50</v>
-      </c>
-      <c r="D30" s="57"/>
-      <c r="E30" s="35">
-        <v>27383</v>
-      </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="35">
-        <f t="shared" si="1"/>
-        <v>547.66</v>
-      </c>
-      <c r="I30" s="36">
-        <v>130</v>
-      </c>
-      <c r="J30" s="37">
-        <f t="shared" si="0"/>
-        <v>4.2</v>
+      <c r="D30" s="52"/>
+      <c r="E30" s="23">
+        <v>3342</v>
+      </c>
+      <c r="F30" s="52"/>
+      <c r="G30" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="23">
+        <f t="shared" si="0"/>
+        <v>20.8875</v>
+      </c>
+      <c r="I30" s="45">
+        <v>15</v>
+      </c>
+      <c r="J30" s="46">
+        <f>IFERROR(ROUND((+H30/I30),1),0)</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2484,27 +2443,26 @@
         <v>69</v>
       </c>
       <c r="C31" s="56">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D31" s="57"/>
-      <c r="E31" s="35">
-        <f>7159+10300</f>
-        <v>17459</v>
+      <c r="E31" s="33">
+        <v>2932</v>
       </c>
       <c r="F31" s="57"/>
       <c r="G31" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="35">
-        <f t="shared" si="1"/>
-        <v>349.18</v>
-      </c>
-      <c r="I31" s="36">
-        <v>46</v>
-      </c>
-      <c r="J31" s="37">
-        <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>31</v>
+      </c>
+      <c r="H31" s="33">
+        <f t="shared" si="0"/>
+        <v>18.325</v>
+      </c>
+      <c r="I31" s="35">
+        <v>24</v>
+      </c>
+      <c r="J31" s="36">
+        <f>IFERROR(ROUND((+H31/I31),1),0)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2515,87 +2473,86 @@
         <v>71</v>
       </c>
       <c r="C32" s="56">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D32" s="57"/>
-      <c r="E32" s="35">
-        <f>2905+1400+1400</f>
-        <v>5705</v>
+      <c r="E32" s="33">
+        <v>14301</v>
       </c>
       <c r="F32" s="57"/>
       <c r="G32" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="33">
+        <f t="shared" si="0"/>
+        <v>89.38125</v>
+      </c>
+      <c r="I32" s="35">
+        <v>21</v>
+      </c>
+      <c r="J32" s="36">
+        <f>IFERROR(ROUND((+H32/I32),1),0)</f>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="56">
+        <v>160</v>
+      </c>
+      <c r="D33" s="57"/>
+      <c r="E33" s="33">
+        <v>19022</v>
+      </c>
+      <c r="F33" s="57"/>
+      <c r="G33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="33">
+        <f t="shared" si="0"/>
+        <v>118.8875</v>
+      </c>
+      <c r="I33" s="35">
+        <v>15</v>
+      </c>
+      <c r="J33" s="36">
+        <f>IFERROR(ROUND((+H33/I33),1),0)</f>
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="51">
+        <v>70</v>
+      </c>
+      <c r="D34" s="52"/>
+      <c r="E34" s="23">
+        <v>0</v>
+      </c>
+      <c r="F34" s="52"/>
+      <c r="G34" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="35">
-        <f t="shared" si="1"/>
-        <v>114.1</v>
-      </c>
-      <c r="I32" s="36">
-        <v>80</v>
-      </c>
-      <c r="J32" s="37">
-        <f t="shared" si="0"/>
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="51">
-        <v>160</v>
-      </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="23">
-        <v>6102</v>
-      </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="23">
-        <f t="shared" si="1"/>
-        <v>38.1375</v>
-      </c>
-      <c r="I33" s="45">
-        <v>15</v>
-      </c>
-      <c r="J33" s="46">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="56">
-        <v>160</v>
-      </c>
-      <c r="D34" s="57"/>
-      <c r="E34" s="35">
-        <v>4837</v>
-      </c>
-      <c r="F34" s="57"/>
-      <c r="G34" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="35">
-        <f t="shared" si="1"/>
-        <v>30.23125</v>
-      </c>
-      <c r="I34" s="36">
-        <v>24</v>
-      </c>
-      <c r="J34" s="37">
-        <f t="shared" si="0"/>
-        <v>1.3</v>
+      <c r="H34" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="45">
+        <v>0</v>
+      </c>
+      <c r="J34" s="46">
+        <f>IFERROR(ROUND((+H34/I34),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2606,26 +2563,26 @@
         <v>77</v>
       </c>
       <c r="C35" s="56">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="D35" s="57"/>
-      <c r="E35" s="35">
-        <v>14126</v>
+      <c r="E35" s="33">
+        <v>0</v>
       </c>
       <c r="F35" s="57"/>
       <c r="G35" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H35" s="35">
-        <f t="shared" si="1"/>
-        <v>88.2875</v>
-      </c>
-      <c r="I35" s="36">
-        <v>21</v>
-      </c>
-      <c r="J35" s="37">
-        <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>16</v>
+      </c>
+      <c r="H35" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="36">
+        <f>IFERROR(ROUND((+H35/I35),1),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2639,329 +2596,269 @@
         <v>160</v>
       </c>
       <c r="D36" s="57"/>
-      <c r="E36" s="35">
-        <v>10797</v>
+      <c r="E36" s="33">
+        <v>145</v>
       </c>
       <c r="F36" s="57"/>
       <c r="G36" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="35">
-        <f t="shared" si="1"/>
-        <v>67.48125</v>
-      </c>
-      <c r="I36" s="36">
-        <v>15</v>
-      </c>
-      <c r="J36" s="37">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>31</v>
+      </c>
+      <c r="H36" s="33">
+        <f t="shared" si="0"/>
+        <v>0.90625</v>
+      </c>
+      <c r="I36" s="35">
+        <v>1</v>
+      </c>
+      <c r="J36" s="36">
+        <f>IFERROR(ROUND((+H36/I36),1),0)</f>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="51">
-        <v>70</v>
-      </c>
-      <c r="D37" s="52"/>
-      <c r="E37" s="23">
+      <c r="C37" s="56">
+        <v>160</v>
+      </c>
+      <c r="D37" s="57"/>
+      <c r="E37" s="33">
         <v>0</v>
       </c>
-      <c r="F37" s="52"/>
-      <c r="G37" s="44" t="s">
+      <c r="F37" s="57"/>
+      <c r="G37" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="33">
+        <f>+E37/C37</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="35">
+        <v>0</v>
+      </c>
+      <c r="J37" s="36">
+        <f>IFERROR(ROUND((+H37/I37),1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="60">
+        <v>84</v>
+      </c>
+      <c r="D38" s="61"/>
+      <c r="E38" s="62">
+        <f>2543-1</f>
+        <v>2542</v>
+      </c>
+      <c r="F38" s="61"/>
+      <c r="G38" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H37" s="23">
-        <f t="shared" si="1"/>
+      <c r="H38" s="33">
+        <f t="shared" si="0"/>
+        <v>30.261904761904763</v>
+      </c>
+      <c r="I38" s="35">
         <v>0</v>
       </c>
-      <c r="I37" s="45">
+      <c r="J38" s="36">
+        <f>IFERROR(ROUND((+H38/I38),1),0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="46">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="60">
+        <v>50</v>
+      </c>
+      <c r="D39" s="61"/>
+      <c r="E39" s="64">
+        <v>2492</v>
+      </c>
+      <c r="F39" s="61"/>
+      <c r="G39" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="33">
+        <f t="shared" si="0"/>
+        <v>49.84</v>
+      </c>
+      <c r="I39" s="35">
+        <v>14</v>
+      </c>
+      <c r="J39" s="36">
+        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="60">
+        <v>136</v>
+      </c>
+      <c r="D40" s="61"/>
+      <c r="E40" s="64">
+        <v>12838</v>
+      </c>
+      <c r="F40" s="61"/>
+      <c r="G40" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="33">
+        <f t="shared" si="0"/>
+        <v>94.3970588235294</v>
+      </c>
+      <c r="I40" s="35">
+        <v>27</v>
+      </c>
+      <c r="J40" s="36">
+        <f>IFERROR(ROUND((+H40/I40),1),0)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="67">
+        <v>160</v>
+      </c>
+      <c r="D41" s="68"/>
+      <c r="E41" s="33">
+        <v>7608</v>
+      </c>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="47">
+        <f t="shared" si="0"/>
+        <v>47.55</v>
+      </c>
+      <c r="I41" s="35">
+        <v>2</v>
+      </c>
+      <c r="J41" s="36">
+        <f>IFERROR(ROUND((+H41/I41),1),0)</f>
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="67">
+        <v>160</v>
+      </c>
+      <c r="D42" s="68"/>
+      <c r="E42" s="47">
+        <v>3932</v>
+      </c>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="47">
+        <f>+E42/C42</f>
+        <v>24.575</v>
+      </c>
+      <c r="I42" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="56">
-        <v>50</v>
-      </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="35">
+      <c r="J42" s="36">
+        <f>IFERROR(ROUND((+H42/I42),1),0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="57"/>
-      <c r="G38" s="34" t="s">
+    </row>
+    <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="71" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="72">
+        <v>160</v>
+      </c>
+      <c r="D43" s="73"/>
+      <c r="E43" s="74">
+        <v>0</v>
+      </c>
+      <c r="F43" s="73"/>
+      <c r="G43" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="35">
-        <f t="shared" si="1"/>
+      <c r="H43" s="76">
+        <f>+E43/C43</f>
         <v>0</v>
       </c>
-      <c r="I38" s="36">
-        <v>1</v>
-      </c>
-      <c r="J38" s="37">
-        <f t="shared" si="0"/>
+      <c r="I43" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="56">
-        <v>160</v>
-      </c>
-      <c r="D39" s="57"/>
-      <c r="E39" s="35">
-        <v>150</v>
-      </c>
-      <c r="F39" s="57"/>
-      <c r="G39" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="35">
-        <f t="shared" si="1"/>
-        <v>0.9375</v>
-      </c>
-      <c r="I39" s="36">
-        <v>1</v>
-      </c>
-      <c r="J39" s="37">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="56">
-        <v>160</v>
-      </c>
-      <c r="D40" s="57"/>
-      <c r="E40" s="35">
+      <c r="J43" s="78">
+        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="57"/>
-      <c r="G40" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="35">
-        <f>+E40/C40</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="36">
-        <v>0</v>
-      </c>
-      <c r="J40" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="60">
-        <v>84</v>
-      </c>
-      <c r="D41" s="61"/>
-      <c r="E41" s="62">
-        <f>2677-1</f>
-        <v>2676</v>
-      </c>
-      <c r="F41" s="61"/>
-      <c r="G41" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="35">
-        <f t="shared" si="1"/>
-        <v>31.857142857142858</v>
-      </c>
-      <c r="I41" s="36">
-        <v>0</v>
-      </c>
-      <c r="J41" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="58" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="60">
-        <v>50</v>
-      </c>
-      <c r="D42" s="61"/>
-      <c r="E42" s="64">
-        <f>17+1400</f>
-        <v>1417</v>
-      </c>
-      <c r="F42" s="61"/>
-      <c r="G42" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="35">
-        <f t="shared" si="1"/>
-        <v>28.34</v>
-      </c>
-      <c r="I42" s="36">
-        <v>14</v>
-      </c>
-      <c r="J42" s="37">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="60">
-        <v>136</v>
-      </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="64">
-        <v>9538</v>
-      </c>
-      <c r="F43" s="61"/>
-      <c r="G43" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="35">
-        <f t="shared" si="1"/>
-        <v>70.13235294117646</v>
-      </c>
-      <c r="I43" s="36">
-        <v>27</v>
-      </c>
-      <c r="J43" s="37">
-        <f t="shared" si="0"/>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="44" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="67">
-        <v>160</v>
-      </c>
-      <c r="D44" s="68"/>
-      <c r="E44" s="35">
-        <v>7974</v>
-      </c>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="47">
-        <f t="shared" si="1"/>
-        <v>49.8375</v>
-      </c>
-      <c r="I44" s="36">
-        <v>2</v>
-      </c>
-      <c r="J44" s="37">
-        <f t="shared" si="0"/>
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="67">
-        <v>160</v>
-      </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="47">
-        <f>2123+1920</f>
-        <v>4043</v>
-      </c>
-      <c r="F45" s="68"/>
-      <c r="G45" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="47">
-        <f>+E45/C45</f>
-        <v>25.26875</v>
-      </c>
-      <c r="I45" s="36">
-        <v>0</v>
-      </c>
-      <c r="J45" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="72">
-        <v>160</v>
-      </c>
-      <c r="D46" s="73"/>
-      <c r="E46" s="74">
-        <v>0</v>
-      </c>
-      <c r="F46" s="73"/>
-      <c r="G46" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46" s="76">
-        <f>+E46/C46</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="77">
-        <v>0</v>
-      </c>
-      <c r="J46" s="78">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="79"/>
+      <c r="B44" s="79"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="80"/>
+    </row>
+    <row r="45" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="81"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="82">
+        <f>SUM(E5:E44)</f>
+        <v>536091</v>
+      </c>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="83">
+        <f>SUM(H5:H44)</f>
+        <v>6597.9494764059455</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="79"/>
+      <c r="B46" s="79"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="80"/>
+    </row>
+    <row r="47" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="79"/>
       <c r="B47" s="79"/>
       <c r="E47" s="28"/>
@@ -2969,33 +2866,19 @@
       <c r="G47" s="28"/>
       <c r="H47" s="80"/>
     </row>
-    <row r="48" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="81"/>
-      <c r="B48" s="81"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="82">
-        <f>SUM(E5:E47)</f>
-        <v>438077</v>
-      </c>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="83">
-        <f>SUM(H5:H47)</f>
-        <v>5380.629527849603</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="79"/>
-      <c r="B49" s="79"/>
+    <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="80"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
       <c r="H49" s="80"/>
     </row>
-    <row r="50" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="79"/>
-      <c r="B50" s="79"/>
+    <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E50" s="28"/>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
@@ -3038,7 +2921,7 @@
       <c r="H56" s="80"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="28"/>
+      <c r="E57" s="84"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
       <c r="H57" s="80"/>
@@ -3050,31 +2933,31 @@
       <c r="H58" s="80"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="28"/>
+      <c r="E59" s="84"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
       <c r="H59" s="80"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E60" s="84"/>
+      <c r="E60" s="28"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
       <c r="H60" s="80"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="28"/>
+      <c r="E61" s="84"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
       <c r="H61" s="80"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="84"/>
+      <c r="E62" s="28"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
       <c r="H62" s="80"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="28"/>
+      <c r="E63" s="84"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="80"/>
@@ -3086,21 +2969,15 @@
       <c r="H64" s="80"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
+      <c r="E65" s="84"/>
       <c r="H65" s="80"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E66" s="84"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
       <c r="H66" s="80"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E67" s="84"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
       <c r="H67" s="80"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
@@ -3115,23 +2992,11 @@
       <c r="E70" s="84"/>
       <c r="H70" s="80"/>
     </row>
-    <row r="71" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E71" s="84"/>
-      <c r="H71" s="80"/>
-    </row>
-    <row r="72" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E72" s="84"/>
-      <c r="H72" s="80"/>
-    </row>
-    <row r="73" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E73" s="84"/>
-      <c r="H73" s="80"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="28"/>
-    </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="85"/>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="28"/>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="85"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -3184,7 +3049,7 @@
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="H11">
     <cfRule type="cellIs" dxfId="12" priority="65" operator="lessThan">
       <formula>10</formula>
     </cfRule>
@@ -3192,7 +3057,7 @@
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="H12">
     <cfRule type="cellIs" dxfId="14" priority="63" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3200,7 +3065,7 @@
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H13">
     <cfRule type="cellIs" dxfId="16" priority="61" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -3208,7 +3073,7 @@
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H14">
     <cfRule type="cellIs" dxfId="18" priority="59" operator="lessThan">
       <formula>400</formula>
     </cfRule>
@@ -3216,7 +3081,7 @@
       <formula>1300</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H19">
+  <conditionalFormatting sqref="H15:H17">
     <cfRule type="cellIs" dxfId="20" priority="55" operator="lessThan">
       <formula>200</formula>
     </cfRule>
@@ -3224,127 +3089,110 @@
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H18:H19">
+    <cfRule type="cellIs" dxfId="22" priority="49" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="50" operator="greaterThan">
+      <formula>400</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H20">
-    <cfRule type="cellIs" dxfId="22" priority="53" operator="lessThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="51" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="52" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21">
+    <cfRule type="cellIs" dxfId="26" priority="47" operator="lessThan">
       <formula>100</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="48" operator="greaterThan">
+      <formula>250</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="cellIs" dxfId="24" priority="49" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="50" operator="greaterThan">
-      <formula>400</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="cellIs" dxfId="26" priority="51" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="52" operator="equal">
-      <formula>0</formula>
+  <conditionalFormatting sqref="H22:H23">
+    <cfRule type="cellIs" dxfId="28" priority="43" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="44" operator="greaterThan">
+      <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="cellIs" dxfId="28" priority="47" operator="lessThan">
-      <formula>100</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="48" operator="greaterThan">
-      <formula>250</formula>
+    <cfRule type="cellIs" dxfId="30" priority="41" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="42" operator="greaterThan">
+      <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="cellIs" dxfId="30" priority="43" operator="lessThan">
+  <conditionalFormatting sqref="H25">
+    <cfRule type="cellIs" dxfId="32" priority="37" operator="lessThan">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="38" operator="greaterThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="44" operator="greaterThan">
-      <formula>150</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="cellIs" dxfId="32" priority="41" operator="lessThan">
-      <formula>50</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="42" operator="greaterThan">
-      <formula>150</formula>
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="cellIs" dxfId="34" priority="33" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="34" operator="greaterThan">
+      <formula>1500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:H29">
+    <cfRule type="cellIs" dxfId="36" priority="7" operator="lessThan">
+      <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="34" priority="37" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="38" operator="greaterThan">
-      <formula>50</formula>
+    <cfRule type="cellIs" dxfId="37" priority="32" operator="greaterThan">
+      <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H30">
-    <cfRule type="cellIs" dxfId="36" priority="33" operator="lessThan">
+  <conditionalFormatting sqref="H29">
+    <cfRule type="cellIs" dxfId="38" priority="28" operator="greaterThan">
+      <formula>800</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H33">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="lessThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="34" operator="greaterThan">
-      <formula>1500</formula>
+    <cfRule type="cellIs" dxfId="40" priority="13" operator="greaterThan">
+      <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H32">
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="H34:H35 H38:H43">
+    <cfRule type="cellIs" dxfId="41" priority="25" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="26" operator="greaterThan">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36:H37">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
       <formula>500</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="6" operator="greaterThan">
+      <formula>800</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="cellIs" dxfId="39" priority="32" operator="greaterThan">
-      <formula>1500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33:H36">
-    <cfRule type="cellIs" dxfId="41" priority="12" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="13" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H38 H41:H46">
-    <cfRule type="cellIs" dxfId="43" priority="25" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="26" operator="greaterThan">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39:H40">
-    <cfRule type="cellIs" dxfId="45" priority="5" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="6" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J46">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J5:J43">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="61" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="51" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -1572,7 +1572,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.42578125" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1659,8 +1659,8 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>74507+27360+30160+11680+442</f>
-        <v>144149</v>
+        <f>88090+21360</f>
+        <v>109450</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1801.8625</v>
+        <v>1368.125</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f>IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1691,8 +1691,8 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <f>1691+24319</f>
-        <v>26010</v>
+        <f>22859+14800</f>
+        <v>37659</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="0">+E6/C6</f>
-        <v>325.125</v>
+        <v>470.7375</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f>IFERROR(ROUND((+H6/I6),1),0)</f>
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="33">
-        <v>19306</v>
+        <v>186</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -1730,14 +1730,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="0"/>
-        <v>241.325</v>
+        <v>2.325</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f>IFERROR(ROUND((+H7/I7),1),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="33">
-        <v>12908</v>
+        <v>3443</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="0"/>
-        <v>161.35</v>
+        <v>43.0375</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f>IFERROR(ROUND((+H8/I8),1),0)</f>
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1812,8 +1812,8 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="33">
-        <f>25204+12894</f>
-        <v>38098</v>
+        <f>19827+15120</f>
+        <v>34947</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="0"/>
-        <v>476.225</v>
+        <v>436.8375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f>IFERROR(ROUND((+H10/I10),1),0)</f>
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="33">
-        <v>4715</v>
+        <v>4388</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -1851,14 +1851,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="0"/>
-        <v>58.9375</v>
+        <v>54.85</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f>IFERROR(ROUND((+H11/I11),1),0)</f>
-        <v>9.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1873,8 +1873,8 @@
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="39">
-        <f>16-1+1120+9920+661</f>
-        <v>11716</v>
+        <f>20368-1-1+15600</f>
+        <v>35966</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="0"/>
-        <v>146.45</v>
+        <v>449.575</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f>IFERROR(ROUND((+H12/I12),1),0)</f>
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,8 @@
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="23">
-        <v>7764</v>
+        <f>1382+8346</f>
+        <v>9728</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44" t="s">
@@ -1942,14 +1943,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="0"/>
-        <v>99.53846153846153</v>
+        <v>124.71794871794872</v>
       </c>
       <c r="I14" s="45">
         <v>118</v>
       </c>
       <c r="J14" s="46">
         <f>IFERROR(ROUND((+H14/I14),1),0)</f>
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1963,8 +1964,9 @@
         <v>78</v>
       </c>
       <c r="D15" s="32"/>
-      <c r="E15" s="33">
-        <v>5683</v>
+      <c r="E15" s="39">
+        <f>4641-1</f>
+        <v>4640</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -1972,14 +1974,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="0"/>
-        <v>72.85897435897436</v>
+        <v>59.48717948717949</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f>IFERROR(ROUND((+H15/I15),1),0)</f>
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1994,7 +1996,7 @@
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="33">
-        <v>9530</v>
+        <v>5520</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -2002,14 +2004,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="0"/>
-        <v>122.17948717948718</v>
+        <v>70.76923076923077</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f>IFERROR(ROUND((+H16/I16),1),0)</f>
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2024,7 +2026,7 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="33">
-        <v>9791</v>
+        <v>6295</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -2032,14 +2034,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="0"/>
-        <v>125.52564102564102</v>
+        <v>80.7051282051282</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f>IFERROR(ROUND((+H17/I17),1),0)</f>
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2054,7 +2056,7 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="33">
-        <v>9695</v>
+        <v>8824</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -2062,14 +2064,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="0"/>
-        <v>124.2948717948718</v>
+        <v>113.12820512820512</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f>IFERROR(ROUND((+H18/I18),1),0)</f>
-        <v>17.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2114,7 +2116,7 @@
       </c>
       <c r="D20" s="32"/>
       <c r="E20" s="47">
-        <v>15437</v>
+        <v>14423</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -2122,14 +2124,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="0"/>
-        <v>197.9102564102564</v>
+        <v>184.9102564102564</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f>IFERROR(ROUND((+H20/I20),1),0)</f>
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2144,7 +2146,8 @@
       </c>
       <c r="D21" s="43"/>
       <c r="E21" s="23">
-        <v>19605</v>
+        <f>15727+4480</f>
+        <v>20207</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43" t="s">
@@ -2152,7 +2155,7 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="0"/>
-        <v>122.53125</v>
+        <v>126.29375</v>
       </c>
       <c r="I21" s="45">
         <v>46</v>
@@ -2174,7 +2177,7 @@
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="33">
-        <v>833</v>
+        <v>443</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -2182,14 +2185,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="0"/>
-        <v>5.20625</v>
+        <v>2.76875</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f>IFERROR(ROUND((+H22/I22),1),0)</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2204,8 +2207,8 @@
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="33">
-        <f>16171+1512</f>
-        <v>17683</v>
+        <f>20030+9600</f>
+        <v>29630</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -2213,14 +2216,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="0"/>
-        <v>110.51875</v>
+        <v>185.1875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f>IFERROR(ROUND((+H23/I23),1),0)</f>
-        <v>5.5</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2235,7 +2238,7 @@
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="33">
-        <v>24689</v>
+        <v>22121</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="48" t="s">
@@ -2243,14 +2246,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="0"/>
-        <v>154.30625</v>
+        <v>138.25625</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f>IFERROR(ROUND((+H24/I24),1),0)</f>
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2265,7 +2268,7 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="33">
-        <v>2160</v>
+        <v>3240</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -2273,14 +2276,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="0"/>
-        <v>13.5</v>
+        <v>20.25</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f>IFERROR(ROUND((+H25/I25),1),0)</f>
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -2296,7 +2299,7 @@
       </c>
       <c r="D26" s="52"/>
       <c r="E26" s="53">
-        <v>23742</v>
+        <v>19974</v>
       </c>
       <c r="F26" s="52"/>
       <c r="G26" s="44" t="s">
@@ -2304,14 +2307,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="0"/>
-        <v>474.84</v>
+        <v>399.48</v>
       </c>
       <c r="I26" s="45">
         <v>108</v>
       </c>
       <c r="J26" s="46">
         <f>IFERROR(ROUND((+H26/I26),1),0)</f>
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2326,7 +2329,8 @@
       </c>
       <c r="D27" s="57"/>
       <c r="E27" s="33">
-        <v>22793</v>
+        <f>19595+9750</f>
+        <v>29345</v>
       </c>
       <c r="F27" s="57"/>
       <c r="G27" s="34" t="s">
@@ -2334,14 +2338,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="0"/>
-        <v>455.86</v>
+        <v>586.9</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f>IFERROR(ROUND((+H27/I27),1),0)</f>
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2356,8 +2360,8 @@
       </c>
       <c r="D28" s="57"/>
       <c r="E28" s="33">
-        <f>24994+9740</f>
-        <v>34734</v>
+        <f>32066</f>
+        <v>32066</v>
       </c>
       <c r="F28" s="57"/>
       <c r="G28" s="34" t="s">
@@ -2365,14 +2369,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="0"/>
-        <v>694.68</v>
+        <v>641.32</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f>IFERROR(ROUND((+H28/I28),1),0)</f>
-        <v>15.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2387,7 +2391,8 @@
       </c>
       <c r="D29" s="57"/>
       <c r="E29" s="33">
-        <v>5895</v>
+        <f>10912+1400+1400</f>
+        <v>13712</v>
       </c>
       <c r="F29" s="57"/>
       <c r="G29" s="34" t="s">
@@ -2395,14 +2400,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="0"/>
-        <v>117.9</v>
+        <v>274.24</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f>IFERROR(ROUND((+H29/I29),1),0)</f>
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2417,7 +2422,8 @@
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="23">
-        <v>3342</v>
+        <f>1987+4480</f>
+        <v>6467</v>
       </c>
       <c r="F30" s="52"/>
       <c r="G30" s="44" t="s">
@@ -2425,14 +2431,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="0"/>
-        <v>20.8875</v>
+        <v>40.41875</v>
       </c>
       <c r="I30" s="45">
         <v>15</v>
       </c>
       <c r="J30" s="46">
         <f>IFERROR(ROUND((+H30/I30),1),0)</f>
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2447,7 +2453,7 @@
       </c>
       <c r="D31" s="57"/>
       <c r="E31" s="33">
-        <v>2932</v>
+        <v>460</v>
       </c>
       <c r="F31" s="57"/>
       <c r="G31" s="34" t="s">
@@ -2455,14 +2461,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="0"/>
-        <v>18.325</v>
+        <v>2.875</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f>IFERROR(ROUND((+H31/I31),1),0)</f>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2477,7 +2483,7 @@
       </c>
       <c r="D32" s="57"/>
       <c r="E32" s="33">
-        <v>14301</v>
+        <v>25314</v>
       </c>
       <c r="F32" s="57"/>
       <c r="G32" s="34" t="s">
@@ -2485,14 +2491,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="0"/>
-        <v>89.38125</v>
+        <v>158.2125</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f>IFERROR(ROUND((+H32/I32),1),0)</f>
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2507,7 +2513,7 @@
       </c>
       <c r="D33" s="57"/>
       <c r="E33" s="33">
-        <v>19022</v>
+        <v>17027</v>
       </c>
       <c r="F33" s="57"/>
       <c r="G33" s="34" t="s">
@@ -2515,14 +2521,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="0"/>
-        <v>118.8875</v>
+        <v>106.41875</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f>IFERROR(ROUND((+H33/I33),1),0)</f>
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2597,7 +2603,7 @@
       </c>
       <c r="D36" s="57"/>
       <c r="E36" s="33">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F36" s="57"/>
       <c r="G36" s="34" t="s">
@@ -2605,14 +2611,14 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.8375</v>
       </c>
       <c r="I36" s="35">
         <v>1</v>
       </c>
       <c r="J36" s="36">
         <f>IFERROR(ROUND((+H36/I36),1),0)</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2657,8 +2663,8 @@
       </c>
       <c r="D38" s="61"/>
       <c r="E38" s="62">
-        <f>2543-1</f>
-        <v>2542</v>
+        <f>3714-1</f>
+        <v>3713</v>
       </c>
       <c r="F38" s="61"/>
       <c r="G38" s="63" t="s">
@@ -2666,7 +2672,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="0"/>
-        <v>30.261904761904763</v>
+        <v>44.20238095238095</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -2688,7 +2694,7 @@
       </c>
       <c r="D39" s="61"/>
       <c r="E39" s="64">
-        <v>2492</v>
+        <v>4186</v>
       </c>
       <c r="F39" s="61"/>
       <c r="G39" s="63" t="s">
@@ -2696,14 +2702,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="0"/>
-        <v>49.84</v>
+        <v>83.72</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f>IFERROR(ROUND((+H39/I39),1),0)</f>
-        <v>3.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2718,7 +2724,7 @@
       </c>
       <c r="D40" s="61"/>
       <c r="E40" s="64">
-        <v>12838</v>
+        <v>20122</v>
       </c>
       <c r="F40" s="61"/>
       <c r="G40" s="63" t="s">
@@ -2726,14 +2732,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="0"/>
-        <v>94.3970588235294</v>
+        <v>147.9558823529412</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f>IFERROR(ROUND((+H40/I40),1),0)</f>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2748,7 +2754,7 @@
       </c>
       <c r="D41" s="68"/>
       <c r="E41" s="33">
-        <v>7608</v>
+        <v>6987</v>
       </c>
       <c r="F41" s="68"/>
       <c r="G41" s="69" t="s">
@@ -2756,14 +2762,14 @@
       </c>
       <c r="H41" s="47">
         <f t="shared" si="0"/>
-        <v>47.55</v>
+        <v>43.66875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f>IFERROR(ROUND((+H41/I41),1),0)</f>
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2841,13 +2847,13 @@
       <c r="D45" s="81"/>
       <c r="E45" s="82">
         <f>SUM(E5:E44)</f>
-        <v>536091</v>
+        <v>534550</v>
       </c>
       <c r="F45" s="81"/>
       <c r="G45" s="81"/>
       <c r="H45" s="83">
         <f>SUM(H5:H44)</f>
-        <v>6597.9494764059455</v>
+        <v>6486.799032536089</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -10,14 +10,14 @@
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Existencia Sistema'!$A1:$J46</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
   <si>
     <t>MULTINACIONAL DE SABORES C.A.</t>
   </si>
@@ -203,24 +203,6 @@
   </si>
   <si>
     <t>JUSTY DURAZNO CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0101</t>
-  </si>
-  <si>
-    <t>JUSTY SANDIA CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0102</t>
-  </si>
-  <si>
-    <t>JUSTY MANDARINA CAJA X 12BOT X 1.5LTS</t>
-  </si>
-  <si>
-    <t>PRODT-0103</t>
-  </si>
-  <si>
-    <t>JUSTY TAMARINDO CAJA X 12BOT X 1.5LTS</t>
   </si>
   <si>
     <t>PRODT-0115</t>
@@ -785,7 +767,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="47">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1153,46 +1135,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1633,11 +1575,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="58.42578125" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="2.7109375" customWidth="1"/>
@@ -1658,7 +1600,7 @@
       </c>
       <c r="F1" s="3"/>
       <c r="J1" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1724,8 +1666,8 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23">
-        <f>3110+5981+10640</f>
-        <v>19731</v>
+        <f>951+17680+15440+13680+2720+3760</f>
+        <v>54231</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -1733,14 +1675,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>246.6375</v>
+        <v>677.8875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f>IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -1756,22 +1698,22 @@
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33">
-        <v>22096</v>
+        <v>16996</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="33">
-        <f t="shared" ref="H6:H44" si="0">+E6/C6</f>
-        <v>276.2</v>
+        <f t="shared" ref="H6:H41" si="0">+E6/C6</f>
+        <v>212.45</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f>IFERROR(ROUND((+H6/I6),1),0)</f>
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1786,8 +1728,7 @@
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="33">
-        <f>4558+19440</f>
-        <v>23998</v>
+        <v>24127</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -1795,14 +1736,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="0"/>
-        <v>299.975</v>
+        <v>301.5875</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f>IFERROR(ROUND((+H7/I7),1),0)</f>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1817,7 +1758,8 @@
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="33">
-        <v>16562</v>
+        <f>11502+480+2400</f>
+        <v>14382</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -1825,14 +1767,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="0"/>
-        <v>207.025</v>
+        <v>179.775</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f>IFERROR(ROUND((+H8/I8),1),0)</f>
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1877,8 +1819,8 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="33">
-        <f>1976+15760</f>
-        <v>17736</v>
+        <f>13196+16633</f>
+        <v>29829</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -1886,14 +1828,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="0"/>
-        <v>221.7</v>
+        <v>372.8625</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f>IFERROR(ROUND((+H10/I10),1),0)</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1908,7 +1850,7 @@
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="33">
-        <v>3424</v>
+        <v>3104</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -1916,14 +1858,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="0"/>
-        <v>42.8</v>
+        <v>38.8</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f>IFERROR(ROUND((+H11/I11),1),0)</f>
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1938,8 +1880,8 @@
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="39">
-        <f>33300-1-1</f>
-        <v>33298</v>
+        <f>30820-1-1</f>
+        <v>30818</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -1947,14 +1889,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="0"/>
-        <v>416.225</v>
+        <v>385.225</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f>IFERROR(ROUND((+H12/I12),1),0)</f>
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1969,7 +1911,7 @@
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33">
-        <v>5822</v>
+        <v>5247</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -1977,14 +1919,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="0"/>
-        <v>72.775</v>
+        <v>65.5875</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f>IFERROR(ROUND((+H13/I13),1),0)</f>
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1999,8 +1941,7 @@
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="23">
-        <f>4525+5343</f>
-        <v>9868</v>
+        <v>4094</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44" t="s">
@@ -2008,14 +1949,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="0"/>
-        <v>126.51282051282051</v>
+        <v>52.48717948717949</v>
       </c>
       <c r="I14" s="45">
         <v>118</v>
       </c>
       <c r="J14" s="46">
         <f>IFERROR(ROUND((+H14/I14),1),0)</f>
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2030,8 +1971,8 @@
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="39">
-        <f>309-1</f>
-        <v>308</v>
+        <f>64-1</f>
+        <v>63</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -2039,14 +1980,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="0"/>
-        <v>3.948717948717949</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f>IFERROR(ROUND((+H15/I15),1),0)</f>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2061,7 +2002,8 @@
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="33">
-        <v>235</v>
+        <f>40+5382+2340</f>
+        <v>7762</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -2069,14 +2011,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="0"/>
-        <v>3.0128205128205128</v>
+        <v>99.51282051282051</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f>IFERROR(ROUND((+H16/I16),1),0)</f>
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2091,8 +2033,8 @@
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="47">
-        <f>38+1+156</f>
-        <v>195</v>
+        <f>194+1+455</f>
+        <v>650</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -2100,14 +2042,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f>IFERROR(ROUND((+H17/I17),1),0)</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2122,7 +2064,7 @@
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="33">
-        <v>6054</v>
+        <v>5370</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -2130,14 +2072,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="0"/>
-        <v>77.61538461538461</v>
+        <v>68.84615384615384</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f>IFERROR(ROUND((+H18/I18),1),0)</f>
-        <v>11.1</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2182,7 +2124,7 @@
       </c>
       <c r="D20" s="32"/>
       <c r="E20" s="48">
-        <v>11742</v>
+        <v>11362</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -2190,14 +2132,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="0"/>
-        <v>150.53846153846155</v>
+        <v>145.66666666666666</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f>IFERROR(ROUND((+H20/I20),1),0)</f>
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2212,8 +2154,8 @@
       </c>
       <c r="D21" s="43"/>
       <c r="E21" s="23">
-        <f>8409+5280</f>
-        <v>13689</v>
+        <f>9064+7449</f>
+        <v>16513</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43" t="s">
@@ -2221,14 +2163,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="0"/>
-        <v>85.55625</v>
+        <v>103.20625</v>
       </c>
       <c r="I21" s="45">
         <v>46</v>
       </c>
       <c r="J21" s="46">
         <f>IFERROR(ROUND((+H21/I21),1),0)</f>
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2243,7 +2185,7 @@
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="33">
-        <v>11953</v>
+        <v>11238</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -2251,14 +2193,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="0"/>
-        <v>74.70625</v>
+        <v>70.2375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f>IFERROR(ROUND((+H22/I22),1),0)</f>
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2273,7 +2215,7 @@
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="33">
-        <v>18508</v>
+        <v>16853</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -2281,14 +2223,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="0"/>
-        <v>115.675</v>
+        <v>105.33125</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f>IFERROR(ROUND((+H23/I23),1),0)</f>
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2303,7 +2245,7 @@
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="33">
-        <v>13619</v>
+        <v>11389</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -2311,14 +2253,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="0"/>
-        <v>85.11875</v>
+        <v>71.18125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f>IFERROR(ROUND((+H24/I24),1),0)</f>
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2333,7 +2275,7 @@
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="33">
-        <v>1260</v>
+        <v>1170</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -2341,14 +2283,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="0"/>
-        <v>7.875</v>
+        <v>7.3125</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f>IFERROR(ROUND((+H25/I25),1),0)</f>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -2364,7 +2306,7 @@
       </c>
       <c r="D26" s="53"/>
       <c r="E26" s="54">
-        <v>8241</v>
+        <v>1516</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="44" t="s">
@@ -2372,14 +2314,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="0"/>
-        <v>164.82</v>
+        <v>30.32</v>
       </c>
       <c r="I26" s="45">
         <v>108</v>
       </c>
       <c r="J26" s="46">
         <f>IFERROR(ROUND((+H26/I26),1),0)</f>
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2394,8 +2336,8 @@
       </c>
       <c r="D27" s="58"/>
       <c r="E27" s="33">
-        <f>30339+4100</f>
-        <v>34439</v>
+        <f>29749+5639+1400</f>
+        <v>36788</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -2403,17 +2345,17 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="0"/>
-        <v>688.78</v>
+        <v>735.76</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f>IFERROR(ROUND((+H27/I27),1),0)</f>
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="28" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="55" t="s">
         <v>62</v>
       </c>
@@ -2421,11 +2363,12 @@
         <v>63</v>
       </c>
       <c r="C28" s="57">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D28" s="58"/>
-      <c r="E28" s="33">
-        <v>0</v>
+      <c r="E28" s="47">
+        <f>21061+50</f>
+        <v>21111</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -2433,17 +2376,17 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>422.22</v>
       </c>
       <c r="I28" s="35">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J28" s="36">
         <f>IFERROR(ROUND((+H28/I28),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9.2</v>
+      </c>
+    </row>
+    <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
         <v>64</v>
       </c>
@@ -2455,7 +2398,7 @@
       </c>
       <c r="D29" s="58"/>
       <c r="E29" s="33">
-        <v>0</v>
+        <v>6016</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -2463,44 +2406,44 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120.32</v>
       </c>
       <c r="I29" s="35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J29" s="36">
         <f>IFERROR(ROUND((+H29/I29),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="27.95" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="55" t="s">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="57">
-        <v>70</v>
-      </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="33">
-        <v>0</v>
-      </c>
-      <c r="F30" s="58"/>
-      <c r="G30" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="35">
-        <v>0</v>
-      </c>
-      <c r="J30" s="36">
+      <c r="C30" s="52">
+        <v>160</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="23">
+        <v>20526</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="23">
+        <f t="shared" si="0"/>
+        <v>128.2875</v>
+      </c>
+      <c r="I30" s="45">
+        <v>15</v>
+      </c>
+      <c r="J30" s="46">
         <f>IFERROR(ROUND((+H30/I30),1),0)</f>
-        <v>0</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2511,27 +2454,27 @@
         <v>69</v>
       </c>
       <c r="C31" s="57">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D31" s="58"/>
-      <c r="E31" s="47">
-        <f>23107+50-1</f>
-        <v>23156</v>
+      <c r="E31" s="33">
+        <f>13480+4480+4480+4480</f>
+        <v>26920</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="0"/>
-        <v>463.12</v>
+        <v>168.25</v>
       </c>
       <c r="I31" s="35">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J31" s="36">
         <f>IFERROR(ROUND((+H31/I31),1),0)</f>
-        <v>10.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2542,88 +2485,88 @@
         <v>71</v>
       </c>
       <c r="C32" s="57">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D32" s="58"/>
       <c r="E32" s="33">
-        <v>9811</v>
+        <f>18648+4480</f>
+        <v>23128</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H32" s="33">
         <f t="shared" si="0"/>
-        <v>196.22</v>
+        <v>144.55</v>
       </c>
       <c r="I32" s="35">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="J32" s="36">
         <f>IFERROR(ROUND((+H32/I32),1),0)</f>
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
+      <c r="A33" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="52">
+      <c r="C33" s="57">
         <v>160</v>
       </c>
-      <c r="D33" s="53"/>
-      <c r="E33" s="23">
-        <f>18471+4480</f>
-        <v>22951</v>
-      </c>
-      <c r="F33" s="53"/>
-      <c r="G33" s="44" t="s">
+      <c r="D33" s="58"/>
+      <c r="E33" s="39">
+        <f>8451-160</f>
+        <v>8291</v>
+      </c>
+      <c r="F33" s="58"/>
+      <c r="G33" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="23">
-        <f t="shared" si="0"/>
-        <v>143.44375</v>
-      </c>
-      <c r="I33" s="45">
+      <c r="H33" s="33">
+        <f t="shared" si="0"/>
+        <v>51.81875</v>
+      </c>
+      <c r="I33" s="35">
         <v>15</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J33" s="36">
         <f>IFERROR(ROUND((+H33/I33),1),0)</f>
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="57">
-        <v>160</v>
-      </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="33">
-        <f>4520+1920+4480</f>
-        <v>10920</v>
-      </c>
-      <c r="F34" s="58"/>
-      <c r="G34" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="33">
-        <f t="shared" si="0"/>
-        <v>68.25</v>
-      </c>
-      <c r="I34" s="35">
-        <v>24</v>
-      </c>
-      <c r="J34" s="36">
+      <c r="C34" s="52">
+        <v>70</v>
+      </c>
+      <c r="D34" s="53"/>
+      <c r="E34" s="23">
+        <v>0</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="45">
+        <v>0</v>
+      </c>
+      <c r="J34" s="46">
         <f>IFERROR(ROUND((+H34/I34),1),0)</f>
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2634,27 +2577,26 @@
         <v>77</v>
       </c>
       <c r="C35" s="57">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="33">
-        <f>17053+4480</f>
-        <v>21533</v>
+        <v>0</v>
       </c>
       <c r="F35" s="58"/>
       <c r="G35" s="34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H35" s="33">
         <f t="shared" si="0"/>
-        <v>134.58125</v>
+        <v>0</v>
       </c>
       <c r="I35" s="35">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J35" s="36">
         <f>IFERROR(ROUND((+H35/I35),1),0)</f>
-        <v>6.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2668,9 +2610,8 @@
         <v>160</v>
       </c>
       <c r="D36" s="58"/>
-      <c r="E36" s="39">
-        <f>11006-160</f>
-        <v>10846</v>
+      <c r="E36" s="33">
+        <v>134</v>
       </c>
       <c r="F36" s="58"/>
       <c r="G36" s="34" t="s">
@@ -2678,70 +2619,71 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="0"/>
-        <v>67.7875</v>
+        <v>0.8375</v>
       </c>
       <c r="I36" s="35">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J36" s="36">
         <f>IFERROR(ROUND((+H36/I36),1),0)</f>
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="52">
-        <v>70</v>
-      </c>
-      <c r="D37" s="53"/>
-      <c r="E37" s="23">
+      <c r="C37" s="57">
+        <v>160</v>
+      </c>
+      <c r="D37" s="58"/>
+      <c r="E37" s="33">
         <v>0</v>
       </c>
-      <c r="F37" s="53"/>
-      <c r="G37" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="23">
-        <f t="shared" si="0"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="33">
+        <f>+E37/C37</f>
         <v>0</v>
       </c>
-      <c r="I37" s="45">
+      <c r="I37" s="35">
         <v>0</v>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="36">
         <f>IFERROR(ROUND((+H37/I37),1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="57">
-        <v>50</v>
-      </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="33">
+      <c r="C38" s="61">
+        <v>84</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63">
+        <f>7188-1+2352</f>
+        <v>9539</v>
+      </c>
+      <c r="F38" s="62"/>
+      <c r="G38" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="33">
+        <f t="shared" si="0"/>
+        <v>113.55952380952381</v>
+      </c>
+      <c r="I38" s="35">
         <v>0</v>
-      </c>
-      <c r="F38" s="58"/>
-      <c r="G38" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="35">
-        <v>1</v>
       </c>
       <c r="J38" s="36">
         <f>IFERROR(ROUND((+H38/I38),1),0)</f>
@@ -2749,249 +2691,190 @@
       </c>
     </row>
     <row r="39" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="57">
-        <v>160</v>
-      </c>
-      <c r="D39" s="58"/>
-      <c r="E39" s="33">
-        <v>134</v>
-      </c>
-      <c r="F39" s="58"/>
-      <c r="G39" s="34" t="s">
-        <v>31</v>
+      <c r="C39" s="61">
+        <v>50</v>
+      </c>
+      <c r="D39" s="62"/>
+      <c r="E39" s="65">
+        <f>12062+1400</f>
+        <v>13462</v>
+      </c>
+      <c r="F39" s="62"/>
+      <c r="G39" s="64" t="s">
+        <v>16</v>
       </c>
       <c r="H39" s="33">
         <f t="shared" si="0"/>
-        <v>0.8375</v>
+        <v>269.24</v>
       </c>
       <c r="I39" s="35">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J39" s="36">
         <f>IFERROR(ROUND((+H39/I39),1),0)</f>
-        <v>0.8</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="57">
-        <v>160</v>
-      </c>
-      <c r="D40" s="58"/>
-      <c r="E40" s="33">
-        <v>0</v>
-      </c>
-      <c r="F40" s="58"/>
-      <c r="G40" s="34" t="s">
-        <v>31</v>
+      <c r="C40" s="61">
+        <v>136</v>
+      </c>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63">
+        <f>23278-1</f>
+        <v>23277</v>
+      </c>
+      <c r="F40" s="62"/>
+      <c r="G40" s="64" t="s">
+        <v>16</v>
       </c>
       <c r="H40" s="33">
-        <f>+E40/C40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>171.15441176470588</v>
       </c>
       <c r="I40" s="35">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J40" s="36">
         <f>IFERROR(ROUND((+H40/I40),1),0)</f>
-        <v>0</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="59" t="s">
+      <c r="A41" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="61">
-        <v>84</v>
-      </c>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63">
-        <f>5049-1+2352</f>
-        <v>7400</v>
-      </c>
-      <c r="F41" s="62"/>
-      <c r="G41" s="64" t="s">
+      <c r="C41" s="68">
+        <v>160</v>
+      </c>
+      <c r="D41" s="69"/>
+      <c r="E41" s="33">
+        <v>5488</v>
+      </c>
+      <c r="F41" s="69"/>
+      <c r="G41" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="33">
-        <f t="shared" si="0"/>
-        <v>88.0952380952381</v>
+      <c r="H41" s="48">
+        <f t="shared" si="0"/>
+        <v>34.3</v>
       </c>
       <c r="I41" s="35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="36">
         <f>IFERROR(ROUND((+H41/I41),1),0)</f>
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="68">
+        <v>160</v>
+      </c>
+      <c r="D42" s="69"/>
+      <c r="E42" s="48">
+        <v>3663</v>
+      </c>
+      <c r="F42" s="69"/>
+      <c r="G42" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="48">
+        <f>+E42/C42</f>
+        <v>22.89375</v>
+      </c>
+      <c r="I42" s="35">
         <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="61">
-        <v>50</v>
-      </c>
-      <c r="D42" s="62"/>
-      <c r="E42" s="65">
-        <f>6738+1400+1400+1400+1400</f>
-        <v>12338</v>
-      </c>
-      <c r="F42" s="62"/>
-      <c r="G42" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="33">
-        <f t="shared" si="0"/>
-        <v>246.76</v>
-      </c>
-      <c r="I42" s="35">
-        <v>14</v>
       </c>
       <c r="J42" s="36">
         <f>IFERROR(ROUND((+H42/I42),1),0)</f>
-        <v>17.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="59" t="s">
+      <c r="A43" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="61">
-        <v>136</v>
-      </c>
-      <c r="D43" s="62"/>
-      <c r="E43" s="63">
-        <f>19495-1+3808</f>
-        <v>23302</v>
-      </c>
-      <c r="F43" s="62"/>
-      <c r="G43" s="64" t="s">
+      <c r="C43" s="73">
+        <v>160</v>
+      </c>
+      <c r="D43" s="74"/>
+      <c r="E43" s="75">
+        <v>0</v>
+      </c>
+      <c r="F43" s="74"/>
+      <c r="G43" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="33">
-        <f t="shared" si="0"/>
-        <v>171.33823529411765</v>
-      </c>
-      <c r="I43" s="35">
-        <v>27</v>
-      </c>
-      <c r="J43" s="36">
+      <c r="H43" s="77">
+        <f>+E43/C43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="78">
+        <v>0</v>
+      </c>
+      <c r="J43" s="79">
         <f>IFERROR(ROUND((+H43/I43),1),0)</f>
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="44" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="68">
-        <v>160</v>
-      </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="33">
-        <v>5603</v>
-      </c>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="48">
-        <f t="shared" si="0"/>
-        <v>35.01875</v>
-      </c>
-      <c r="I44" s="35">
-        <v>2</v>
-      </c>
-      <c r="J44" s="36">
-        <f>IFERROR(ROUND((+H44/I44),1),0)</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="45" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="68">
-        <v>160</v>
-      </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="48">
-        <v>3663</v>
-      </c>
-      <c r="F45" s="69"/>
-      <c r="G45" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="48">
-        <f>+E45/C45</f>
-        <v>22.89375</v>
-      </c>
-      <c r="I45" s="35">
         <v>0</v>
       </c>
-      <c r="J45" s="36">
-        <f>IFERROR(ROUND((+H45/I45),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="72" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="73">
-        <v>160</v>
-      </c>
-      <c r="D46" s="74"/>
-      <c r="E46" s="75">
-        <v>0</v>
-      </c>
-      <c r="F46" s="74"/>
-      <c r="G46" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46" s="77">
-        <f>+E46/C46</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="78">
-        <v>0</v>
-      </c>
-      <c r="J46" s="79">
-        <f>IFERROR(ROUND((+H46/I46),1),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" ht="3.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="81"/>
+    </row>
+    <row r="45" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="82"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83">
+        <f>SUM(E5:E44)</f>
+        <v>465058</v>
+      </c>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="84">
+        <f>SUM(H5:H44)</f>
+        <v>5380.621852240898</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="80"/>
+      <c r="B46" s="80"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="81"/>
+    </row>
+    <row r="47" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="80"/>
       <c r="B47" s="80"/>
       <c r="E47" s="28"/>
@@ -2999,33 +2882,19 @@
       <c r="G47" s="28"/>
       <c r="H47" s="81"/>
     </row>
-    <row r="48" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="82"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="82"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="83">
-        <f>SUM(E5:E47)</f>
-        <v>424436</v>
-      </c>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="84">
-        <f>SUM(H5:H47)</f>
-        <v>5008.355749030384</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="80"/>
-      <c r="B49" s="80"/>
+    <row r="48" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="81"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
       <c r="H49" s="81"/>
     </row>
-    <row r="50" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="80"/>
-      <c r="B50" s="80"/>
+    <row r="50" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E50" s="28"/>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
@@ -3068,7 +2937,7 @@
       <c r="H56" s="81"/>
     </row>
     <row r="57" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E57" s="28"/>
+      <c r="E57" s="85"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
       <c r="H57" s="81"/>
@@ -3080,31 +2949,31 @@
       <c r="H58" s="81"/>
     </row>
     <row r="59" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E59" s="28"/>
+      <c r="E59" s="85"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
       <c r="H59" s="81"/>
     </row>
     <row r="60" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E60" s="85"/>
+      <c r="E60" s="28"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
       <c r="H60" s="81"/>
     </row>
     <row r="61" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E61" s="28"/>
+      <c r="E61" s="85"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
       <c r="H61" s="81"/>
     </row>
     <row r="62" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E62" s="85"/>
+      <c r="E62" s="28"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
       <c r="H62" s="81"/>
     </row>
     <row r="63" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E63" s="28"/>
+      <c r="E63" s="85"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="81"/>
@@ -3116,21 +2985,15 @@
       <c r="H64" s="81"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
+      <c r="E65" s="85"/>
       <c r="H65" s="81"/>
     </row>
     <row r="66" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E66" s="85"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
       <c r="H66" s="81"/>
     </row>
     <row r="67" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E67" s="85"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
       <c r="H67" s="81"/>
     </row>
     <row r="68" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
@@ -3145,23 +3008,11 @@
       <c r="E70" s="85"/>
       <c r="H70" s="81"/>
     </row>
-    <row r="71" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E71" s="85"/>
-      <c r="H71" s="81"/>
-    </row>
-    <row r="72" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E72" s="85"/>
-      <c r="H72" s="81"/>
-    </row>
-    <row r="73" ht="21" customHeight="1" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E73" s="85"/>
-      <c r="H73" s="81"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="28"/>
-    </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="86"/>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="28"/>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="86"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -3310,72 +3161,54 @@
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H28:H29">
+    <cfRule type="cellIs" dxfId="36" priority="7" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="36" priority="23" operator="lessThan">
-      <formula>300</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="24" operator="greaterThan">
-      <formula>600</formula>
+    <cfRule type="cellIs" dxfId="37" priority="32" operator="greaterThan">
+      <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="cellIs" dxfId="38" priority="10" operator="greaterThan">
-      <formula>1500</formula>
+    <cfRule type="cellIs" dxfId="38" priority="28" operator="greaterThan">
+      <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H32">
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="H30:H33">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="lessThan">
       <formula>500</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="13" operator="greaterThan">
+      <formula>800</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="cellIs" dxfId="40" priority="8" operator="greaterThan">
+  <conditionalFormatting sqref="H34:H35 H38:H43">
+    <cfRule type="cellIs" dxfId="41" priority="25" operator="lessThan">
+      <formula>200</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="26" operator="greaterThan">
+      <formula>600</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36:H37">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="6" operator="greaterThan">
       <formula>800</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="cellIs" dxfId="41" priority="32" operator="greaterThan">
-      <formula>1500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="cellIs" dxfId="42" priority="28" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33:H36">
-    <cfRule type="cellIs" dxfId="43" priority="12" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="13" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H38 H41:H46">
-    <cfRule type="cellIs" dxfId="45" priority="25" operator="lessThan">
-      <formula>200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="26" operator="greaterThan">
-      <formula>600</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39:H40">
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="6" operator="greaterThan">
-      <formula>800</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J46">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J5:J43">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="59" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967295" scale="51" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -3055,7 +3055,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>71331</v>
+        <v>77491</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>891.6375</v>
+        <v>968.6375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
-        <f>IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.1</v>
+        <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
+        <v>1.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3094,14 +3094,14 @@
         <v>16</v>
       </c>
       <c r="H6" s="33">
-        <f t="shared" ref="H6:H41" si="0">+E6/C6</f>
+        <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
         <v>147.7</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
-        <f>IFERROR(ROUND((+H6/I6),1),0)</f>
+        <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
     </row>
@@ -3118,22 +3118,22 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>44258</v>
+        <v>49322</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="33">
-        <f t="shared" si="0"/>
-        <v>553.225</v>
+        <f t="shared" si="1"/>
+        <v>616.525</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
-        <f>IFERROR(ROUND((+H7/I7),1),0)</f>
-        <v>2.3</v>
+        <f t="shared" si="0"/>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3156,14 +3156,14 @@
         <v>16</v>
       </c>
       <c r="H8" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>179.7125</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
-        <f>IFERROR(ROUND((+H8/I8),1),0)</f>
+        <f t="shared" si="0"/>
         <v>2.2</v>
       </c>
     </row>
@@ -3187,14 +3187,14 @@
         <v>16</v>
       </c>
       <c r="H9" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="35">
         <v>86</v>
       </c>
       <c r="J9" s="36">
-        <f>IFERROR(ROUND((+H9/I9),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3211,22 +3211,22 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32559</v>
+        <v>38719</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="33">
-        <f t="shared" si="0"/>
-        <v>406.9875</v>
+        <f t="shared" si="1"/>
+        <v>483.9875</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
-        <f>IFERROR(ROUND((+H10/I10),1),0)</f>
-        <v>1.6</v>
+        <f t="shared" si="0"/>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3249,14 +3249,14 @@
         <v>16</v>
       </c>
       <c r="H11" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36.4875</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
-        <f>IFERROR(ROUND((+H11/I11),1),0)</f>
+        <f t="shared" si="0"/>
         <v>6.1</v>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         <v>31</v>
       </c>
       <c r="H12" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>359.35</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
-        <f>IFERROR(ROUND((+H12/I12),1),0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -3311,14 +3311,14 @@
         <v>31</v>
       </c>
       <c r="H13" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63.2125</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
-        <f>IFERROR(ROUND((+H13/I13),1),0)</f>
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
     </row>
@@ -3342,14 +3342,14 @@
         <v>31</v>
       </c>
       <c r="H14" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.333333333333334</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
-        <f>IFERROR(ROUND((+H14/I14),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
@@ -3373,14 +3373,14 @@
         <v>31</v>
       </c>
       <c r="H15" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.5512820512820513</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
-        <f>IFERROR(ROUND((+H15/I15),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3404,14 +3404,14 @@
         <v>31</v>
       </c>
       <c r="H16" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>195</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
-        <f>IFERROR(ROUND((+H16/I16),1),0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -3435,14 +3435,14 @@
         <v>31</v>
       </c>
       <c r="H17" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
-        <f>IFERROR(ROUND((+H17/I17),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
@@ -3466,14 +3466,14 @@
         <v>31</v>
       </c>
       <c r="H18" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66.84615384615384</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
-        <f>IFERROR(ROUND((+H18/I18),1),0)</f>
+        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
     </row>
@@ -3497,14 +3497,14 @@
         <v>31</v>
       </c>
       <c r="H19" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.01282051282051282</v>
       </c>
       <c r="I19" s="35">
         <v>8</v>
       </c>
       <c r="J19" s="36">
-        <f>IFERROR(ROUND((+H19/I19),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3528,14 +3528,14 @@
         <v>31</v>
       </c>
       <c r="H20" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>140.66666666666666</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
-        <f>IFERROR(ROUND((+H20/I20),1),0)</f>
+        <f t="shared" si="0"/>
         <v>15.6</v>
       </c>
     </row>
@@ -3559,14 +3559,14 @@
         <v>31</v>
       </c>
       <c r="H21" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>126.86875</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
-        <f>IFERROR(ROUND((+H21/I21),1),0)</f>
+        <f t="shared" si="0"/>
         <v>2.8</v>
       </c>
     </row>
@@ -3590,14 +3590,14 @@
         <v>31</v>
       </c>
       <c r="H22" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60.425</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
-        <f>IFERROR(ROUND((+H22/I22),1),0)</f>
+        <f t="shared" si="0"/>
         <v>10.1</v>
       </c>
     </row>
@@ -3621,14 +3621,14 @@
         <v>31</v>
       </c>
       <c r="H23" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>94.19375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
-        <f>IFERROR(ROUND((+H23/I23),1),0)</f>
+        <f t="shared" si="0"/>
         <v>4.7</v>
       </c>
     </row>
@@ -3652,14 +3652,14 @@
         <v>31</v>
       </c>
       <c r="H24" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.54375</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
-        <f>IFERROR(ROUND((+H24/I24),1),0)</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
     </row>
@@ -3683,14 +3683,14 @@
         <v>31</v>
       </c>
       <c r="H25" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.6875</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
-        <f>IFERROR(ROUND((+H25/I25),1),0)</f>
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="L25" s="28"/>
@@ -3715,14 +3715,14 @@
         <v>16</v>
       </c>
       <c r="H26" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.22</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
-        <f>IFERROR(ROUND((+H26/I26),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3746,14 +3746,14 @@
         <v>16</v>
       </c>
       <c r="H27" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>730.22</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
-        <f>IFERROR(ROUND((+H27/I27),1),0)</f>
+        <f t="shared" si="0"/>
         <v>5.6</v>
       </c>
     </row>
@@ -3777,14 +3777,14 @@
         <v>16</v>
       </c>
       <c r="H28" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>399.52</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
-        <f>IFERROR(ROUND((+H28/I28),1),0)</f>
+        <f t="shared" si="0"/>
         <v>8.7</v>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         <v>16</v>
       </c>
       <c r="H29" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>81.32</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
-        <f>IFERROR(ROUND((+H29/I29),1),0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3839,14 +3839,14 @@
         <v>31</v>
       </c>
       <c r="H30" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112.2875</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
-        <f>IFERROR(ROUND((+H30/I30),1),0)</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
     </row>
@@ -3870,14 +3870,14 @@
         <v>31</v>
       </c>
       <c r="H31" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>183.25</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
-        <f>IFERROR(ROUND((+H31/I31),1),0)</f>
+        <f t="shared" si="0"/>
         <v>7.6</v>
       </c>
     </row>
@@ -3901,14 +3901,14 @@
         <v>31</v>
       </c>
       <c r="H32" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>135.05</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
-        <f>IFERROR(ROUND((+H32/I32),1),0)</f>
+        <f t="shared" si="0"/>
         <v>6.4</v>
       </c>
     </row>
@@ -3932,14 +3932,14 @@
         <v>31</v>
       </c>
       <c r="H33" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43.06875</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
-        <f>IFERROR(ROUND((+H33/I33),1),0)</f>
+        <f t="shared" si="0"/>
         <v>2.9</v>
       </c>
     </row>
@@ -3963,14 +3963,14 @@
         <v>16</v>
       </c>
       <c r="H34" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="46">
+        <v>0</v>
+      </c>
+      <c r="J34" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="46">
-        <v>0</v>
-      </c>
-      <c r="J34" s="47">
-        <f>IFERROR(ROUND((+H34/I34),1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -3994,14 +3994,14 @@
         <v>16</v>
       </c>
       <c r="H35" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="35">
         <v>1</v>
       </c>
       <c r="J35" s="36">
-        <f>IFERROR(ROUND((+H35/I35),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4025,14 +4025,14 @@
         <v>31</v>
       </c>
       <c r="H36" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.8375</v>
       </c>
       <c r="I36" s="35">
         <v>1</v>
       </c>
       <c r="J36" s="36">
-        <f>IFERROR(ROUND((+H36/I36),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="36">
-        <f>IFERROR(ROUND((+H37/I37),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4087,14 +4087,14 @@
         <v>16</v>
       </c>
       <c r="H38" s="33">
+        <f t="shared" si="1"/>
+        <v>108.78571428571429</v>
+      </c>
+      <c r="I38" s="35">
+        <v>0</v>
+      </c>
+      <c r="J38" s="36">
         <f t="shared" si="0"/>
-        <v>108.78571428571429</v>
-      </c>
-      <c r="I38" s="35">
-        <v>0</v>
-      </c>
-      <c r="J38" s="36">
-        <f>IFERROR(ROUND((+H38/I38),1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -4118,14 +4118,14 @@
         <v>16</v>
       </c>
       <c r="H39" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>252.44</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
-        <f>IFERROR(ROUND((+H39/I39),1),0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
@@ -4149,14 +4149,14 @@
         <v>16</v>
       </c>
       <c r="H40" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>170.56617647058823</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
-        <f>IFERROR(ROUND((+H40/I40),1),0)</f>
+        <f t="shared" si="0"/>
         <v>6.3</v>
       </c>
     </row>
@@ -4180,14 +4180,14 @@
         <v>16</v>
       </c>
       <c r="H41" s="48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32.9875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
-        <f>IFERROR(ROUND((+H41/I41),1),0)</f>
+        <f t="shared" si="0"/>
         <v>16.5</v>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="36">
-        <f>IFERROR(ROUND((+H42/I42),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="79">
-        <f>IFERROR(ROUND((+H43/I43),1),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4268,13 +4268,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>488317</v>
+        <v>505701</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5671.034230499894</v>
+        <v>5888.334230499893</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>16691+24000+30640</f>
-        <v>71331</v>
+        <f>16691+24000+30640+6160</f>
+        <v>77491</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>71331</v>
+        <v>77491</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-20123</v>
+        <v>-26283</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>90931</v>
+        <v>97091</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>891.6375</v>
+        <v>968.6375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="37">
-        <f>19697+1+24560</f>
-        <v>44258</v>
+        <f>19697+1+24560+5064</f>
+        <v>49322</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>20842</v>
+        <v>25906</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-35809</v>
+        <v>-40873</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>25962</v>
+        <v>31026</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>553.225</v>
+        <v>616.525</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>22079+10480</f>
-        <v>32559</v>
+        <f>22079+10480+6160</f>
+        <v>38719</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>29083</v>
+        <v>35243</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-23202</v>
+        <v>-29362</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>29723</v>
+        <v>35883</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>406.9875</v>
+        <v>483.9875</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -9213,7 +9213,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10081,26 +10081,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>488317</v>
+        <v>505701</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>185370</v>
+        <v>202754</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>694015</v>
+        <v>676631</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>283342</v>
+        <v>300726</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5671.034230499894</v>
+        <v>5888.334230499893</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>82874</v>
+        <v>99689</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1035.925</v>
+        <v>1246.1125</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7</v>
+        <v>6994</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>0.0875</v>
+        <v>87.425</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>799</v>
+        <v>6157</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>9.9875</v>
+        <v>76.9625</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>40351</v>
+        <v>45940</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>504.3875</v>
+        <v>574.25</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9222</v>
+        <v>10730</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>118.23076923076923</v>
+        <v>137.56410256410257</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23419</v>
+        <v>40100</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>146.36875</v>
+        <v>250.625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6992</v>
+        <v>8396</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>43.7</v>
+        <v>52.475</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20548</v>
+        <v>23614</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>410.96</v>
+        <v>472.28</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10</v>
+        <v>4210</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>84.2</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21343</v>
+        <v>23263</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>133.39375</v>
+        <v>145.39375</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2257</v>
+        <v>3857</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>14.10625</v>
+        <v>24.10625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>468034</v>
+        <v>533162</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5527.2973693708245</v>
+        <v>6261.344452704158</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4634,7 +4634,6 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="4.28515625" customWidth="1"/>
     <col min="10" max="10" width="19.28515625" customWidth="1"/>
     <col min="11" max="11" width="2.7109375" customWidth="1"/>
@@ -4680,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4693,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.75</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5238,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>23354+29760+29760</f>
-        <v>82874</v>
+        <f>23354+29760+29760+7807+9008</f>
+        <v>99689</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5247,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>82874</v>
+        <v>99689</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5255,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-31666</v>
+        <v>-48481</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>102474</v>
+        <v>119289</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1035.925</v>
+        <v>1246.1125</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5315,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5339,7 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>7</v>
+        <f>7+6987</f>
+        <v>6994</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6994</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>197</v>
+        <v>-6790</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>7</v>
+        <v>6994</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>0.0875</v>
+        <v>87.425</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5535,7 +5535,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>799</v>
+        <f>799+5358</f>
+        <v>6157</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5544,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>796</v>
+        <v>6154</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5552,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>4806</v>
+        <v>-552</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>5516</v>
+        <v>10874</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>9.9875</v>
+        <v>76.9625</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5612,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,8 +5730,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>25071+15280</f>
-        <v>40351</v>
+        <f>25071+15280+5589</f>
+        <v>45940</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5739,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>36875</v>
+        <v>42464</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5747,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-30994</v>
+        <v>-36583</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>37515</v>
+        <v>43104</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>504.3875</v>
+        <v>574.25</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5807,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6333,8 +6334,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>19-1+9204</f>
-        <v>9222</v>
+        <f>19-1+9204+1508</f>
+        <v>10730</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6343,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-8329</v>
+        <v>-6821</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6351,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>42672</v>
+        <v>41164</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-6223</v>
+        <v>-4715</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>118.23076923076923</v>
+        <v>137.56410256410257</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6399,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>8.4</v>
+        <v>9.8</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6937,7 +6938,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <v>23419</v>
+        <f>23419+13440+3241</f>
+        <v>40100</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6945,7 +6947,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-24376</v>
+        <v>-7695</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6953,15 +6955,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>29939</v>
+        <v>13258</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-19096</v>
+        <v>-2415</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>146.36875</v>
+        <v>250.625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7001,7 +7003,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7022,7 +7024,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>6992</v>
+        <f>6992+1404</f>
+        <v>8396</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7030,7 +7033,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-4111</v>
+        <v>-2707</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7038,15 +7041,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>13116</v>
+        <v>11712</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-3151</v>
+        <v>-1747</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>43.7</v>
+        <v>52.475</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7074,7 +7077,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>7.3</v>
+        <v>8.7</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -8193,8 +8196,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="54">
-        <f>8380+12168</f>
-        <v>20548</v>
+        <f>8380+12168+3066</f>
+        <v>23614</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8202,7 +8205,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-20082</v>
+        <v>-17016</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8210,15 +8213,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>32058</v>
+        <v>28992</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-13932</v>
+        <v>-10866</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>410.96</v>
+        <v>472.28</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8242,7 +8245,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8610,7 +8613,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>10</v>
+        <f>10+1400+1400+1400</f>
+        <v>4210</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8618,7 +8622,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>4210</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8626,15 +8630,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52596</v>
+        <v>48396</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6160</v>
+        <v>10360</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>0.2</v>
+        <v>84.2</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8658,7 +8662,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -9009,7 +9013,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="33">
-        <v>21343</v>
+        <f>21343+1920</f>
+        <v>23263</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9017,7 +9022,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>21343</v>
+        <v>23263</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9026,11 +9031,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>21343</v>
+        <v>23263</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>133.39375</v>
+        <v>145.39375</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9054,7 +9059,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9141,7 +9146,8 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>2257</v>
+        <f>2257+1600</f>
+        <v>3857</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9149,7 +9155,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>2257</v>
+        <v>3857</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9158,11 +9164,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>2257</v>
+        <v>3857</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>14.10625</v>
+        <v>24.10625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9186,7 +9192,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9214,7 +9220,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10082,26 +10088,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>468034</v>
+        <v>533162</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>165971</v>
+        <v>231099</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>702572</v>
+        <v>640964</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>263943</v>
+        <v>329071</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5527.2973693708245</v>
+        <v>6261.344452704158</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>99689</v>
+        <v>39747</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1246.1125</v>
+        <v>496.8375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6994</v>
+        <v>12202</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>87.425</v>
+        <v>152.525</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>58461</v>
+        <v>38546</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>730.7625</v>
+        <v>481.825</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6157</v>
+        <v>5611</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>76.9625</v>
+        <v>70.1375</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>45940</v>
+        <v>27186</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>574.25</v>
+        <v>339.825</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1724</v>
+        <v>1129</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>21.55</v>
+        <v>14.1125</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17117</v>
+        <v>11438</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>213.9625</v>
+        <v>142.975</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3780</v>
+        <v>3185</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>47.25</v>
+        <v>39.8125</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5130</v>
+        <v>60</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>65.76923076923077</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10730</v>
+        <v>14358</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>137.56410256410257</v>
+        <v>184.07692307692307</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>9.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9311</v>
+        <v>5948</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>119.37179487179488</v>
+        <v>76.25641025641026</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14574</v>
+        <v>11689</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>186.84615384615384</v>
+        <v>149.85897435897436</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1397</v>
+        <v>995</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>17.91025641025641</v>
+        <v>12.756410256410257</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9133</v>
+        <v>8319</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>117.08974358974359</v>
+        <v>106.65384615384616</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>40100</v>
+        <v>32050</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>250.625</v>
+        <v>200.3125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8396</v>
+        <v>5832</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>52.475</v>
+        <v>36.45</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>8.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8281</v>
+        <v>5121</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>51.75625</v>
+        <v>32.00625</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1044</v>
+        <v>124</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>6.525</v>
+        <v>0.775</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23614</v>
+        <v>17504</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>472.28</v>
+        <v>350.08</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21532</v>
+        <v>14887</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>430.64</v>
+        <v>297.74</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13356</v>
+        <v>9621</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>267.12</v>
+        <v>192.42</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4210</v>
+        <v>2155</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>84.2</v>
+        <v>43.1</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17296</v>
+        <v>15136</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>108.1</v>
+        <v>94.6</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23263</v>
+        <v>19859</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>145.39375</v>
+        <v>124.11875</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24498</v>
+        <v>20993</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>153.1125</v>
+        <v>131.20625</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3857</v>
+        <v>1262</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>24.10625</v>
+        <v>7.8875</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8707</v>
+        <v>8445</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>103.6547619047619</v>
+        <v>100.53571428571429</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11857</v>
+        <v>11385</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>237.14</v>
+        <v>227.7</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22708</v>
+        <v>22048</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>166.97058823529412</v>
+        <v>162.11764705882354</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6495</v>
+        <v>6335</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>40.59375</v>
+        <v>39.59375</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.4</v>
+        <v>22.3875</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>533162</v>
+        <v>376979</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>6261.344452704158</v>
+        <v>4332.877976729153</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>23354+29760+29760+7807+9008</f>
-        <v>99689</v>
+        <f>22932+9008+7807</f>
+        <v>39747</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>99689</v>
+        <v>39747</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-48481</v>
+        <v>11461</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>119289</v>
+        <v>59347</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1246.1125</v>
+        <v>496.8375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>7+6987</f>
-        <v>6994</v>
+        <f>5215+6987</f>
+        <v>12202</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>6994</v>
+        <v>12202</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-6790</v>
+        <v>-11998</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>6994</v>
+        <v>12202</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>87.425</v>
+        <v>152.525</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>43741+14720</f>
-        <v>58461</v>
+        <v>38546</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>35045</v>
+        <v>15130</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-50012</v>
+        <v>-30097</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>40165</v>
+        <v>20250</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>730.7625</v>
+        <v>481.825</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5514,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5535,8 +5534,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>799+5358</f>
-        <v>6157</v>
+        <f>253+5358</f>
+        <v>5611</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5544,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>6154</v>
+        <v>5608</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5552,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-552</v>
+        <v>-6</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>10874</v>
+        <v>10328</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>76.9625</v>
+        <v>70.1375</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5612,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5730,8 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>25071+15280+5589</f>
-        <v>45940</v>
+        <f>21607+5579</f>
+        <v>27186</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5739,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>42464</v>
+        <v>23710</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5747,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-36583</v>
+        <v>-17829</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>43104</v>
+        <v>24350</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>574.25</v>
+        <v>339.825</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5807,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5910,7 +5909,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>1724</v>
+        <v>1129</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5918,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>1723</v>
+        <v>1128</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5926,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-1199</v>
+        <v>-604</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>1723</v>
+        <v>1128</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>21.55</v>
+        <v>14.1125</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5974,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,9 +6075,8 @@
         <v>80</v>
       </c>
       <c r="I33" s="32"/>
-      <c r="J33" s="40">
-        <f>17119-2</f>
-        <v>17117</v>
+      <c r="J33" s="33">
+        <v>11438</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6086,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>17117</v>
+        <v>11438</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6094,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-17117</v>
+        <v>-11438</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>17117</v>
+        <v>11438</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>213.9625</v>
+        <v>142.975</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6142,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6164,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>3780</v>
+        <v>3185</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6172,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-47150</v>
+        <v>-47745</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6180,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-3780</v>
+        <v>-3185</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-47150</v>
+        <v>-47745</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>47.25</v>
+        <v>39.8125</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6228,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6249,7 +6247,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>5130</v>
+        <v>60</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6257,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-23180</v>
+        <v>-28250</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6265,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>127811</v>
+        <v>132881</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-19982</v>
+        <v>-25052</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>65.76923076923077</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6313,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6333,9 +6331,9 @@
         <v>78</v>
       </c>
       <c r="I36" s="32"/>
-      <c r="J36" s="40">
-        <f>19-1+9204+1508</f>
-        <v>10730</v>
+      <c r="J36" s="33">
+        <f>12850+1508</f>
+        <v>14358</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6343,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-6821</v>
+        <v>-3193</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6351,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>41164</v>
+        <v>37536</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-4715</v>
+        <v>-1087</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>137.56410256410257</v>
+        <v>184.07692307692307</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6399,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>9.8</v>
+        <v>13.1</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6420,7 +6418,7 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>9311</v>
+        <v>5948</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6426,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>1466</v>
+        <v>-1897</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6434,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>8151</v>
+        <v>11514</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>3962</v>
+        <v>599</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>119.37179487179488</v>
+        <v>76.25641025641026</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6482,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6504,9 +6502,8 @@
         <v>78</v>
       </c>
       <c r="I38" s="32"/>
-      <c r="J38" s="37">
-        <f>8059+1+6514</f>
-        <v>14574</v>
+      <c r="J38" s="33">
+        <v>11689</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-8705</v>
+        <v>-11590</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>25023</v>
+        <v>27908</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-6053</v>
+        <v>-8938</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>186.84615384615384</v>
+        <v>149.85897435897436</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6570,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6660,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>1397</v>
+        <v>995</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6668,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>1397</v>
+        <v>995</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6676,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>49569</v>
+        <v>49971</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>2099</v>
+        <v>1697</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>17.91025641025641</v>
+        <v>12.756410256410257</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6708,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6866,9 +6863,8 @@
         <v>78</v>
       </c>
       <c r="I43" s="32"/>
-      <c r="J43" s="40">
-        <f>9134-1</f>
-        <v>9133</v>
+      <c r="J43" s="33">
+        <v>8319</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6876,7 +6872,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>9133</v>
+        <v>8319</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6884,15 +6880,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>41833</v>
+        <v>42647</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>9835</v>
+        <v>9021</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>117.08974358974359</v>
+        <v>106.65384615384616</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6916,7 +6912,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>11.9</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6938,8 +6934,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <f>23419+13440+3241</f>
-        <v>40100</v>
+        <f>28809+3241</f>
+        <v>32050</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6947,7 +6943,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-7695</v>
+        <v>-15745</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6955,15 +6951,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>13258</v>
+        <v>21308</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-2415</v>
+        <v>-10465</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>250.625</v>
+        <v>200.3125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7003,7 +6999,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7024,8 +7020,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <f>6992+1404</f>
-        <v>8396</v>
+        <v>5832</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7033,7 +7028,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-2707</v>
+        <v>-5271</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7041,15 +7036,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>11712</v>
+        <v>14276</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-1747</v>
+        <v>-4311</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>52.475</v>
+        <v>36.45</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7077,7 +7072,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>8.7</v>
+        <v>6.1</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7099,7 +7094,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>8281</v>
+        <v>5121</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7107,7 +7102,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>5319</v>
+        <v>2159</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7115,15 +7110,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-2037</v>
+        <v>1123</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>7079</v>
+        <v>3919</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>51.75625</v>
+        <v>32.00625</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7147,7 +7142,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7237,7 +7232,7 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <v>1044</v>
+        <v>124</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7245,7 +7240,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>1038</v>
+        <v>118</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7253,15 +7248,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>29446</v>
+        <v>30366</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>3918</v>
+        <v>2998</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>6.525</v>
+        <v>0.775</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7285,7 +7280,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -8196,8 +8191,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="54">
-        <f>8380+12168+3066</f>
-        <v>23614</v>
+        <f>14438+3066</f>
+        <v>17504</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8205,7 +8200,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-17016</v>
+        <v>-23126</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8213,15 +8208,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>28992</v>
+        <v>35102</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-10866</v>
+        <v>-16976</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>472.28</v>
+        <v>350.08</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8245,7 +8240,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8266,7 +8261,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>21532</v>
+        <v>14887</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8274,7 +8269,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>21532</v>
+        <v>14887</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8282,15 +8277,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>31074</v>
+        <v>37719</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>27682</v>
+        <v>21037</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>430.64</v>
+        <v>297.74</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8314,7 +8309,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8544,7 +8539,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>13356</v>
+        <v>9621</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8552,7 +8547,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>13356</v>
+        <v>9621</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8560,15 +8555,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>39250</v>
+        <v>42985</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>19506</v>
+        <v>15771</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>267.12</v>
+        <v>192.42</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8592,7 +8587,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8613,8 +8608,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <f>10+1400+1400+1400</f>
-        <v>4210</v>
+        <v>2155</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8622,7 +8616,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>4210</v>
+        <v>2155</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8630,15 +8624,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>48396</v>
+        <v>50451</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>10360</v>
+        <v>8305</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>84.2</v>
+        <v>43.1</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8662,7 +8656,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8947,7 +8941,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>17296</v>
+        <v>15136</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8955,7 +8949,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>17296</v>
+        <v>15136</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8964,11 +8958,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>17296</v>
+        <v>15136</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>108.1</v>
+        <v>94.6</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8992,7 +8986,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9013,8 +9007,7 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="33">
-        <f>21343+1920</f>
-        <v>23263</v>
+        <v>19859</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9022,7 +9015,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>23263</v>
+        <v>19859</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9031,11 +9024,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>23263</v>
+        <v>19859</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>145.39375</v>
+        <v>124.11875</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9059,7 +9052,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9080,7 +9073,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>24498</v>
+        <v>20993</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9088,7 +9081,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>24498</v>
+        <v>20993</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9097,11 +9090,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>24498</v>
+        <v>20993</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>153.1125</v>
+        <v>131.20625</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9125,7 +9118,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9146,8 +9139,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <f>2257+1600</f>
-        <v>3857</v>
+        <v>1262</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9155,7 +9147,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>3857</v>
+        <v>1262</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9164,11 +9156,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>3857</v>
+        <v>1262</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>24.10625</v>
+        <v>7.8875</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9192,7 +9184,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9476,9 +9468,8 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="63">
-        <f>8709-2</f>
-        <v>8707</v>
+      <c r="J82" s="65">
+        <v>8445</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9486,7 +9477,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>8707</v>
+        <v>8445</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9495,11 +9486,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>8707</v>
+        <v>8445</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>103.6547619047619</v>
+        <v>100.53571428571429</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9544,7 +9535,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>11857</v>
+        <v>11385</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9556,7 +9547,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>237.14</v>
+        <v>227.7</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9580,7 +9571,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9600,9 +9591,8 @@
         <v>136</v>
       </c>
       <c r="I84" s="62"/>
-      <c r="J84" s="63">
-        <f>22709-1</f>
-        <v>22708</v>
+      <c r="J84" s="65">
+        <v>22048</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9614,7 +9604,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>166.97058823529412</v>
+        <v>162.11764705882354</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9638,7 +9628,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9830,7 +9820,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>6495</v>
+        <v>6335</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9842,7 +9832,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>40.59375</v>
+        <v>39.59375</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9866,7 +9856,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9887,7 +9877,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9899,7 +9889,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.4</v>
+        <v>22.3875</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10088,26 +10078,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>533162</v>
+        <v>376979</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>231099</v>
+        <v>76210</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>640964</v>
+        <v>783927</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>329071</v>
+        <v>174182</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>6261.344452704158</v>
+        <v>4332.877976729153</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39747</v>
+        <v>37767</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>496.8375</v>
+        <v>472.0875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12202</v>
+        <v>35395</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>152.525</v>
+        <v>442.4375</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>38546</v>
+        <v>23680</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>481.825</v>
+        <v>296</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5611</v>
+        <v>551</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>70.1375</v>
+        <v>6.8875</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27186</v>
+        <v>33638</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>339.825</v>
+        <v>420.475</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1129</v>
+        <v>1080</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>14.1125</v>
+        <v>13.5</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11438</v>
+        <v>7953</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>142.975</v>
+        <v>99.4125</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3185</v>
+        <v>2906</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>39.8125</v>
+        <v>36.325</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>60</v>
+        <v>24214</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>0.7692307692307693</v>
+        <v>310.43589743589746</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14358</v>
+        <v>14035</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>184.07692307692307</v>
+        <v>179.93589743589743</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5948</v>
+        <v>3031</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>76.25641025641026</v>
+        <v>38.85897435897436</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11689</v>
+        <v>9099</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>149.85897435897436</v>
+        <v>116.65384615384616</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>995</v>
+        <v>673</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>12.756410256410257</v>
+        <v>8.628205128205128</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8319</v>
+        <v>7642</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>106.65384615384616</v>
+        <v>97.97435897435898</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32050</v>
+        <v>28605</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>200.3125</v>
+        <v>178.78125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5832</v>
+        <v>5152</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>36.45</v>
+        <v>32.2</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5121</v>
+        <v>3151</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>32.00625</v>
+        <v>19.69375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>124</v>
+        <v>844</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>0.775</v>
+        <v>5.275</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>112</v>
+        <v>15388</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>96.175</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>24</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17504</v>
+        <v>29164</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>350.08</v>
+        <v>583.28</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14887</v>
+        <v>11052</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>297.74</v>
+        <v>221.04</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9621</v>
+        <v>7381</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>192.42</v>
+        <v>147.62</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2155</v>
+        <v>8024</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>43.1</v>
+        <v>160.48</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15136</v>
+        <v>13481</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>94.6</v>
+        <v>84.25625</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19859</v>
+        <v>25713</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>124.11875</v>
+        <v>160.70625</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20993</v>
+        <v>27128</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>131.20625</v>
+        <v>169.55</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1262</v>
+        <v>11281</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>7.8875</v>
+        <v>70.50625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
       <c r="D36" s="58"/>
       <c r="E36" s="33">
         <f>VLOOKUP(A36,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F36" s="58"/>
       <c r="G36" s="34" t="s">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="1"/>
-        <v>0.7125</v>
+        <v>0.5875</v>
       </c>
       <c r="I36" s="35">
         <v>1</v>
       </c>
       <c r="J36" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8445</v>
+        <v>8340</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>100.53571428571429</v>
+        <v>99.28571428571429</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11385</v>
+        <v>11094</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>227.7</v>
+        <v>221.88</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22048</v>
+        <v>21783</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>162.11764705882354</v>
+        <v>160.1691176470588</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6335</v>
+        <v>6273</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>39.59375</v>
+        <v>39.20625</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.3875</v>
+        <v>22.375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>376979</v>
+        <v>439193</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4332.877976729153</v>
+        <v>5012.692331932773</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>22932+9008+7807</f>
-        <v>39747</v>
+        <f>887+5440+31440</f>
+        <v>37767</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>39747</v>
+        <v>37767</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>11461</v>
+        <v>13441</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>59347</v>
+        <v>57367</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>496.8375</v>
+        <v>472.0875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>5215+6987</f>
-        <v>12202</v>
+        <f>16355+19040</f>
+        <v>35395</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>12202</v>
+        <v>35395</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-11998</v>
+        <v>-35191</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>12202</v>
+        <v>35395</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>152.525</v>
+        <v>442.4375</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>38546</v>
+        <v>23680</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>15130</v>
+        <v>264</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-30097</v>
+        <v>-15231</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>20250</v>
+        <v>5384</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>481.825</v>
+        <v>296</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,8 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>253+5358</f>
-        <v>5611</v>
+        <v>551</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>5608</v>
+        <v>548</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-6</v>
+        <v>5054</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>10328</v>
+        <v>5268</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>70.1375</v>
+        <v>6.8875</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>21607+5579</f>
-        <v>27186</v>
+        <f>15158+18480</f>
+        <v>33638</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>23710</v>
+        <v>30162</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-17829</v>
+        <v>-24281</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>24350</v>
+        <v>30802</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>339.825</v>
+        <v>420.475</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>1129</v>
+        <v>1080</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>1128</v>
+        <v>1079</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-604</v>
+        <v>-555</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>1128</v>
+        <v>1079</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>14.1125</v>
+        <v>13.5</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>11438</v>
+        <v>7953</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>11438</v>
+        <v>7953</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-11438</v>
+        <v>-7953</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>11438</v>
+        <v>7953</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>142.975</v>
+        <v>99.4125</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>3185</v>
+        <v>2906</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-47745</v>
+        <v>-48024</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-3185</v>
+        <v>-2906</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-47745</v>
+        <v>-48024</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>39.8125</v>
+        <v>36.325</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,7 +6246,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>60</v>
+        <f>1828+22386</f>
+        <v>24214</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-28250</v>
+        <v>-4096</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6263,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>132881</v>
+        <v>108727</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-25052</v>
+        <v>-898</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>0.7692307692307693</v>
+        <v>310.43589743589746</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,9 +6331,9 @@
         <v>78</v>
       </c>
       <c r="I36" s="32"/>
-      <c r="J36" s="33">
-        <f>12850+1508</f>
-        <v>14358</v>
+      <c r="J36" s="40">
+        <f>14036-1</f>
+        <v>14035</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-3193</v>
+        <v>-3516</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6349,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>37536</v>
+        <v>37859</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-1087</v>
+        <v>-1410</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>184.07692307692307</v>
+        <v>179.93589743589743</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>5948</v>
+        <v>3031</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-1897</v>
+        <v>-4814</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6434,15 +6434,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>11514</v>
+        <v>14431</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>599</v>
+        <v>-2318</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>76.25641025641026</v>
+        <v>38.85897435897436</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>11689</v>
+        <v>9099</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-11590</v>
+        <v>-14180</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>27908</v>
+        <v>30498</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-8938</v>
+        <v>-11528</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>149.85897435897436</v>
+        <v>116.65384615384616</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>995</v>
+        <v>673</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>995</v>
+        <v>673</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6673,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>49971</v>
+        <v>50293</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>1697</v>
+        <v>1375</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>12.756410256410257</v>
+        <v>8.628205128205128</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>8319</v>
+        <v>7642</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>8319</v>
+        <v>7642</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6880,15 +6880,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>42647</v>
+        <v>43324</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>9021</v>
+        <v>8344</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>106.65384615384616</v>
+        <v>97.97435897435898</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6934,8 +6934,7 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <f>28809+3241</f>
-        <v>32050</v>
+        <v>28605</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6943,7 +6942,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-15745</v>
+        <v>-19190</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6951,15 +6950,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>21308</v>
+        <v>24753</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-10465</v>
+        <v>-13910</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>200.3125</v>
+        <v>178.78125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6999,7 +6998,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7020,7 +7019,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>5832</v>
+        <v>5152</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7028,7 +7027,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-5271</v>
+        <v>-5951</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7036,15 +7035,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>14276</v>
+        <v>14956</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-4311</v>
+        <v>-4991</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>36.45</v>
+        <v>32.2</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7072,7 +7071,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7094,7 +7093,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>5121</v>
+        <v>3151</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7102,7 +7101,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>2159</v>
+        <v>189</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7110,15 +7109,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>1123</v>
+        <v>3093</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>3919</v>
+        <v>1949</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>32.00625</v>
+        <v>19.69375</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7142,7 +7141,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7232,7 +7231,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <v>124</v>
+        <f>44+800</f>
+        <v>844</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>838</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7248,15 +7248,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>30366</v>
+        <v>29646</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>2998</v>
+        <v>3718</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>0.775</v>
+        <v>5.275</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7473,7 +7473,8 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>112</v>
+        <f>2192+13196</f>
+        <v>15388</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7485,7 +7486,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>0.7</v>
+        <v>96.175</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7509,7 +7510,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>24</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8190,9 +8191,9 @@
         <v>50</v>
       </c>
       <c r="I63" s="53"/>
-      <c r="J63" s="54">
-        <f>14438+3066</f>
-        <v>17504</v>
+      <c r="J63" s="23">
+        <f>16964+12200</f>
+        <v>29164</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8200,7 +8201,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-23126</v>
+        <v>-11466</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8208,15 +8209,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>35102</v>
+        <v>23442</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-16976</v>
+        <v>-5316</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>350.08</v>
+        <v>583.28</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8240,7 +8241,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8261,7 +8262,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>14887</v>
+        <f>11052</f>
+        <v>11052</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8269,7 +8271,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>14887</v>
+        <v>11052</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8277,15 +8279,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>37719</v>
+        <v>41554</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>21037</v>
+        <v>17202</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>297.74</v>
+        <v>221.04</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8309,7 +8311,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8539,7 +8541,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>9621</v>
+        <v>7381</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8547,7 +8549,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>9621</v>
+        <v>7381</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8555,15 +8557,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>42985</v>
+        <v>45225</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>15771</v>
+        <v>13531</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>192.42</v>
+        <v>147.62</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8587,7 +8589,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8608,7 +8610,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>2155</v>
+        <f>6624+1400</f>
+        <v>8024</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8616,7 +8619,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>2155</v>
+        <v>8024</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8624,15 +8627,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>50451</v>
+        <v>44582</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>8305</v>
+        <v>14174</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>43.1</v>
+        <v>160.48</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8656,7 +8659,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8941,7 +8944,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>15136</v>
+        <v>13481</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8949,7 +8952,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>15136</v>
+        <v>13481</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8958,11 +8961,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>15136</v>
+        <v>13481</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>94.6</v>
+        <v>84.25625</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8986,7 +8989,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9006,8 +9009,9 @@
         <v>160</v>
       </c>
       <c r="I75" s="58"/>
-      <c r="J75" s="33">
-        <v>19859</v>
+      <c r="J75" s="40">
+        <f>21234-1+4480</f>
+        <v>25713</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9015,7 +9019,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>19859</v>
+        <v>25713</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9024,11 +9028,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>19859</v>
+        <v>25713</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>124.11875</v>
+        <v>160.70625</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9052,7 +9056,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9073,7 +9077,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>20993</v>
+        <f>22648+4480</f>
+        <v>27128</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9081,7 +9086,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>20993</v>
+        <v>27128</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9090,11 +9095,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>20993</v>
+        <v>27128</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>131.20625</v>
+        <v>169.55</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9118,7 +9123,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9139,7 +9144,8 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>1262</v>
+        <f>401+1920+4480+4480</f>
+        <v>11281</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9147,7 +9153,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>1262</v>
+        <v>11281</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9156,11 +9162,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>1262</v>
+        <v>11281</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>7.8875</v>
+        <v>70.50625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9184,7 +9190,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9337,7 +9343,7 @@
       </c>
       <c r="I80" s="58"/>
       <c r="J80" s="33">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="K80" s="58"/>
       <c r="L80" s="34" t="s">
@@ -9345,7 +9351,7 @@
       </c>
       <c r="M80" s="115">
         <f t="shared" si="13"/>
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N80" s="116">
         <f t="shared" si="8"/>
@@ -9354,11 +9360,11 @@
       <c r="O80" s="117"/>
       <c r="P80" s="118">
         <f t="shared" si="12"/>
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="Q80" s="33">
         <f t="shared" si="5"/>
-        <v>0.7125</v>
+        <v>0.5875</v>
       </c>
       <c r="R80" s="32"/>
       <c r="S80" s="32"/>
@@ -9382,7 +9388,7 @@
       </c>
       <c r="AJ80" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AN80" s="114"/>
     </row>
@@ -9469,7 +9475,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>8445</v>
+        <v>8340</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9477,7 +9483,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>8445</v>
+        <v>8340</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9486,11 +9492,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>8445</v>
+        <v>8340</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>100.53571428571429</v>
+        <v>99.28571428571429</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9535,7 +9541,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>11385</v>
+        <v>11094</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9547,7 +9553,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>227.7</v>
+        <v>221.88</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9571,7 +9577,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9592,7 +9598,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>22048</v>
+        <v>21783</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9604,7 +9610,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>162.11764705882354</v>
+        <v>160.1691176470588</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9628,7 +9634,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9820,7 +9826,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>6335</v>
+        <v>6273</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9832,7 +9838,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>39.59375</v>
+        <v>39.20625</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9856,7 +9862,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9877,7 +9883,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9889,7 +9895,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.3875</v>
+        <v>22.375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10078,26 +10084,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>376979</v>
+        <v>439193</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>76210</v>
+        <v>123768</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>783927</v>
+        <v>756597</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>174182</v>
+        <v>221740</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4332.877976729153</v>
+        <v>5012.692331932773</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46297</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>37767</v>
+        <v>10258</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>472.0875</v>
+        <v>128.225</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>35395</v>
+        <v>44657</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>442.4375</v>
+        <v>558.2125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23680</v>
+        <v>6856</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>296</v>
+        <v>85.7</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>551</v>
+        <v>7</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>6.8875</v>
+        <v>0.0875</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33638</v>
+        <v>33045</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>420.475</v>
+        <v>413.0625</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1080</v>
+        <v>574</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>13.5</v>
+        <v>7.175</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7953</v>
+        <v>2679</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>99.4125</v>
+        <v>33.4875</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2906</v>
+        <v>2424</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>36.325</v>
+        <v>30.3</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24214</v>
+        <v>24898</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>310.43589743589746</v>
+        <v>319.20512820512823</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14035</v>
+        <v>13205</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>179.93589743589743</v>
+        <v>169.2948717948718</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3031</v>
+        <v>662</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>38.85897435897436</v>
+        <v>8.487179487179487</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9099</v>
+        <v>5067</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>116.65384615384616</v>
+        <v>64.96153846153847</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>673</v>
+        <v>491</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>8.628205128205128</v>
+        <v>6.294871794871795</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7642</v>
+        <v>6624</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>97.97435897435898</v>
+        <v>84.92307692307692</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28605</v>
+        <v>23485</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>178.78125</v>
+        <v>146.78125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5152</v>
+        <v>4682</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>32.2</v>
+        <v>29.2625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3151</v>
+        <v>1121</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>19.69375</v>
+        <v>7.00625</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>844</v>
+        <v>3237</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>5.275</v>
+        <v>20.23125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15388</v>
+        <v>15348</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>96.175</v>
+        <v>95.925</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29164</v>
+        <v>30808</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>583.28</v>
+        <v>616.16</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11052</v>
+        <v>7282</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>221.04</v>
+        <v>145.64</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7381</v>
+        <v>5546</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>147.62</v>
+        <v>110.92</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8024</v>
+        <v>6854</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>160.48</v>
+        <v>137.08</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13481</v>
+        <v>11936</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>84.25625</v>
+        <v>74.6</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25713</v>
+        <v>26698</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>160.70625</v>
+        <v>166.8625</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27128</v>
+        <v>25143</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>169.55</v>
+        <v>157.14375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11281</v>
+        <v>20016</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>70.50625</v>
+        <v>125.1</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
       <c r="D36" s="58"/>
       <c r="E36" s="33">
         <f>VLOOKUP(A36,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F36" s="58"/>
       <c r="G36" s="34" t="s">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="1"/>
-        <v>0.5875</v>
+        <v>0.5125</v>
       </c>
       <c r="I36" s="35">
         <v>1</v>
       </c>
       <c r="J36" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8340</v>
+        <v>8210</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>99.28571428571429</v>
+        <v>97.73809523809524</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11094</v>
+        <v>10683</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>221.88</v>
+        <v>213.66</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21783</v>
+        <v>21466</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>160.1691176470588</v>
+        <v>157.83823529411765</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6273</v>
+        <v>6025</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>39.20625</v>
+        <v>37.65625</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3580</v>
+        <v>3574</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.375</v>
+        <v>22.3375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>439193</v>
+        <v>383644</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5012.692331932773</v>
+        <v>4271.8845677117</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>887+5440+31440</f>
-        <v>37767</v>
+        <f>18+10240</f>
+        <v>10258</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>37767</v>
+        <v>10258</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>13441</v>
+        <v>40950</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>57367</v>
+        <v>29858</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>472.0875</v>
+        <v>128.225</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>16355+19040</f>
-        <v>35395</v>
+        <f>38433+6224</f>
+        <v>44657</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>35395</v>
+        <v>44657</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-35191</v>
+        <v>-44453</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>35395</v>
+        <v>44657</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>442.4375</v>
+        <v>558.2125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>23680</v>
+        <v>6856</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>264</v>
+        <v>-16560</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-15231</v>
+        <v>1593</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>5384</v>
+        <v>-11440</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>296</v>
+        <v>85.7</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>551</v>
+        <v>7</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>548</v>
+        <v>4</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>5054</v>
+        <v>5598</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>5268</v>
+        <v>4724</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>6.8875</v>
+        <v>0.0875</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>15158+18480</f>
-        <v>33638</v>
+        <f>19205+13840</f>
+        <v>33045</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>30162</v>
+        <v>29569</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-24281</v>
+        <v>-23688</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>30802</v>
+        <v>30209</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>420.475</v>
+        <v>413.0625</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>1080</v>
+        <v>574</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>1079</v>
+        <v>573</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-555</v>
+        <v>-49</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>1079</v>
+        <v>573</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>13.5</v>
+        <v>7.175</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>7953</v>
+        <v>2679</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>7953</v>
+        <v>2679</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-7953</v>
+        <v>-2679</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>7953</v>
+        <v>2679</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>99.4125</v>
+        <v>33.4875</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>2906</v>
+        <v>2424</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-48024</v>
+        <v>-48506</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-2906</v>
+        <v>-2424</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-48024</v>
+        <v>-48506</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>36.325</v>
+        <v>30.3</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,8 +6246,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>1828+22386</f>
-        <v>24214</v>
+        <f>23180+1718</f>
+        <v>24898</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-4096</v>
+        <v>-3412</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6263,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>108727</v>
+        <v>108043</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-898</v>
+        <v>-214</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>310.43589743589746</v>
+        <v>319.20512820512823</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6332,8 +6332,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>14036-1</f>
-        <v>14035</v>
+        <f>13206-1</f>
+        <v>13205</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-3516</v>
+        <v>-4346</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6349,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>37859</v>
+        <v>38689</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-1410</v>
+        <v>-2240</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>179.93589743589743</v>
+        <v>169.2948717948718</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>3031</v>
+        <v>662</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-4814</v>
+        <v>-7183</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6434,15 +6434,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>14431</v>
+        <v>16800</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-2318</v>
+        <v>-4687</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>38.85897435897436</v>
+        <v>8.487179487179487</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>9099</v>
+        <v>5067</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-14180</v>
+        <v>-18212</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>30498</v>
+        <v>34530</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-11528</v>
+        <v>-15560</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>116.65384615384616</v>
+        <v>64.96153846153847</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>673</v>
+        <v>491</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>673</v>
+        <v>491</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6673,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>50293</v>
+        <v>50475</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>1375</v>
+        <v>1193</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>8.628205128205128</v>
+        <v>6.294871794871795</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>7642</v>
+        <v>6624</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>7642</v>
+        <v>6624</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6880,15 +6880,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>43324</v>
+        <v>44342</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>8344</v>
+        <v>7326</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>97.97435897435898</v>
+        <v>84.92307692307692</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <v>28605</v>
+        <v>23485</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-19190</v>
+        <v>-24310</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6950,15 +6950,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>24753</v>
+        <v>29873</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-13910</v>
+        <v>-19030</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>178.78125</v>
+        <v>146.78125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>5152</v>
+        <v>4682</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-5951</v>
+        <v>-6421</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7035,15 +7035,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>14956</v>
+        <v>15426</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-4991</v>
+        <v>-5461</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>32.2</v>
+        <v>29.2625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>3151</v>
+        <v>1121</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>189</v>
+        <v>-1841</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7109,15 +7109,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>3093</v>
+        <v>5123</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>1949</v>
+        <v>-81</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>19.69375</v>
+        <v>7.00625</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7231,8 +7231,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <f>44+800</f>
-        <v>844</v>
+        <f>584+2653</f>
+        <v>3237</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>838</v>
+        <v>3231</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7248,15 +7248,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>29646</v>
+        <v>27253</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>3718</v>
+        <v>6111</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>5.275</v>
+        <v>20.23125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7473,8 +7473,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <f>2192+13196</f>
-        <v>15388</v>
+        <v>15348</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7486,7 +7485,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>96.175</v>
+        <v>95.925</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -8192,8 +8191,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>16964+12200</f>
-        <v>29164</v>
+        <f>28697+2111</f>
+        <v>30808</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8201,7 +8200,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-11466</v>
+        <v>-9822</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8209,15 +8208,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>23442</v>
+        <v>21798</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-5316</v>
+        <v>-3672</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>583.28</v>
+        <v>616.16</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8241,7 +8240,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8262,8 +8261,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>11052</f>
-        <v>11052</v>
+        <v>7282</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8271,7 +8269,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>11052</v>
+        <v>7282</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8279,15 +8277,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>41554</v>
+        <v>45324</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>17202</v>
+        <v>13432</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>221.04</v>
+        <v>145.64</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8311,7 +8309,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8541,7 +8539,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>7381</v>
+        <v>5546</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8549,7 +8547,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>7381</v>
+        <v>5546</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8557,15 +8555,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>45225</v>
+        <v>47060</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>13531</v>
+        <v>11696</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>147.62</v>
+        <v>110.92</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8589,7 +8587,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8610,8 +8608,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <f>6624+1400</f>
-        <v>8024</v>
+        <f>5454+1400</f>
+        <v>6854</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8619,7 +8617,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>8024</v>
+        <v>6854</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8627,15 +8625,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>44582</v>
+        <v>45752</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>14174</v>
+        <v>13004</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>160.48</v>
+        <v>137.08</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8659,7 +8657,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8944,7 +8942,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>13481</v>
+        <v>11936</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8952,7 +8950,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>13481</v>
+        <v>11936</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8961,11 +8959,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>13481</v>
+        <v>11936</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>84.25625</v>
+        <v>74.6</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8989,7 +8987,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9010,8 +9008,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>21234-1+4480</f>
-        <v>25713</v>
+        <f>26699-1</f>
+        <v>26698</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9019,7 +9017,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>25713</v>
+        <v>26698</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9028,11 +9026,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>25713</v>
+        <v>26698</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>160.70625</v>
+        <v>166.8625</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9056,7 +9054,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9077,8 +9075,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <f>22648+4480</f>
-        <v>27128</v>
+        <v>25143</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9086,7 +9083,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>27128</v>
+        <v>25143</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9095,11 +9092,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>27128</v>
+        <v>25143</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>169.55</v>
+        <v>157.14375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9123,7 +9120,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9144,8 +9141,8 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <f>401+1920+4480+4480</f>
-        <v>11281</v>
+        <f>11056+4480+4480</f>
+        <v>20016</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9153,7 +9150,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>11281</v>
+        <v>20016</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9162,11 +9159,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>11281</v>
+        <v>20016</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>70.50625</v>
+        <v>125.1</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9190,7 +9187,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>4.7</v>
+        <v>8.3</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9343,7 +9340,7 @@
       </c>
       <c r="I80" s="58"/>
       <c r="J80" s="33">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" s="58"/>
       <c r="L80" s="34" t="s">
@@ -9351,7 +9348,7 @@
       </c>
       <c r="M80" s="115">
         <f t="shared" si="13"/>
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="N80" s="116">
         <f t="shared" si="8"/>
@@ -9360,11 +9357,11 @@
       <c r="O80" s="117"/>
       <c r="P80" s="118">
         <f t="shared" si="12"/>
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="Q80" s="33">
         <f t="shared" si="5"/>
-        <v>0.5875</v>
+        <v>0.5125</v>
       </c>
       <c r="R80" s="32"/>
       <c r="S80" s="32"/>
@@ -9388,7 +9385,7 @@
       </c>
       <c r="AJ80" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN80" s="114"/>
     </row>
@@ -9475,7 +9472,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>8340</v>
+        <v>8210</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9483,7 +9480,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>8340</v>
+        <v>8210</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9492,11 +9489,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>8340</v>
+        <v>8210</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>99.28571428571429</v>
+        <v>97.73809523809524</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9541,7 +9538,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>11094</v>
+        <v>10683</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9553,7 +9550,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>221.88</v>
+        <v>213.66</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9577,7 +9574,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9598,7 +9595,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>21783</v>
+        <v>21466</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9610,7 +9607,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>160.1691176470588</v>
+        <v>157.83823529411765</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9634,7 +9631,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9826,7 +9823,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>6273</v>
+        <v>6025</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9838,7 +9835,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>39.20625</v>
+        <v>37.65625</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9862,7 +9859,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9883,7 +9880,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3580</v>
+        <v>3574</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9895,7 +9892,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.375</v>
+        <v>22.3375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10084,26 +10081,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>439193</v>
+        <v>383644</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>123768</v>
+        <v>69241</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>756597</v>
+        <v>817172</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>221740</v>
+        <v>167213</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5012.692331932773</v>
+        <v>4271.8845677117</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46298</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10258</v>
+        <v>39358</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>128.225</v>
+        <v>491.975</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>44657</v>
+        <v>39997</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>558.2125</v>
+        <v>499.9625</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6856</v>
+        <v>18561</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>85.7</v>
+        <v>232.0125</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7</v>
+        <v>16647</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>0.0875</v>
+        <v>208.0875</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33045</v>
+        <v>27917</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>413.0625</v>
+        <v>348.9625</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>574</v>
+        <v>334</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>7.175</v>
+        <v>4.175</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2679</v>
+        <v>1354</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>33.4875</v>
+        <v>16.925</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2424</v>
+        <v>2072</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>30.3</v>
+        <v>25.9</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24898</v>
+        <v>20593</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>319.20512820512823</v>
+        <v>264.0128205128205</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13205</v>
+        <v>12581</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>169.2948717948718</v>
+        <v>161.2948717948718</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>662</v>
+        <v>38</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>8.487179487179487</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5067</v>
+        <v>2717</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>64.96153846153847</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6624</v>
+        <v>5454</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>84.92307692307692</v>
+        <v>69.92307692307692</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23485</v>
+        <v>21089</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>146.78125</v>
+        <v>131.80625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4682</v>
+        <v>4332</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>29.2625</v>
+        <v>27.075</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1121</v>
+        <v>851</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>7.00625</v>
+        <v>5.31875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3237</v>
+        <v>2673</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>20.23125</v>
+        <v>16.70625</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15348</v>
+        <v>14808</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>95.925</v>
+        <v>92.55</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>30808</v>
+        <v>29468</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>616.16</v>
+        <v>589.36</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7282</v>
+        <v>5512</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>145.64</v>
+        <v>110.24</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5546</v>
+        <v>4516</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>110.92</v>
+        <v>90.32</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6854</v>
+        <v>5594</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>137.08</v>
+        <v>111.88</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11936</v>
+        <v>11366</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>74.6</v>
+        <v>71.0375</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26698</v>
+        <v>25558</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>166.8625</v>
+        <v>159.7375</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25143</v>
+        <v>23983</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>157.14375</v>
+        <v>149.89375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20016</v>
+        <v>19416</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>125.1</v>
+        <v>121.35</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>8.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8210</v>
+        <v>7528</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>97.73809523809524</v>
+        <v>89.61904761904762</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10683</v>
+        <v>10398</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>213.66</v>
+        <v>207.96</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21466</v>
+        <v>21315</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>157.83823529411765</v>
+        <v>156.72794117647058</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6025</v>
+        <v>5535</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>37.65625</v>
+        <v>34.59375</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>18.8</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3574</v>
+        <v>3569</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.3375</v>
+        <v>22.30625</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>383644</v>
+        <v>405708</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4271.8845677117</v>
+        <v>4553.853463154492</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>18+10240</f>
-        <v>10258</v>
+        <f>3198+15760+20400</f>
+        <v>39358</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>10258</v>
+        <v>39358</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>40950</v>
+        <v>11850</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>29858</v>
+        <v>58958</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>128.225</v>
+        <v>491.975</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>38433+6224</f>
-        <v>44657</v>
+        <v>39997</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>44657</v>
+        <v>39997</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-44453</v>
+        <v>-39793</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>44657</v>
+        <v>39997</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>558.2125</v>
+        <v>499.9625</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>6856</v>
+        <f>1041+17520</f>
+        <v>18561</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-16560</v>
+        <v>-4855</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>1593</v>
+        <v>-10112</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>-11440</v>
+        <v>265</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>85.7</v>
+        <v>232.0125</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5534,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>7</v>
+        <f>1927+14720</f>
+        <v>16647</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>16644</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>5598</v>
+        <v>-11042</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>4724</v>
+        <v>21364</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>0.0875</v>
+        <v>208.0875</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5729,7 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>19205+13840</f>
-        <v>33045</v>
+        <v>27917</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>29569</v>
+        <v>24441</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-23688</v>
+        <v>-18560</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>30209</v>
+        <v>25081</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>413.0625</v>
+        <v>348.9625</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>574</v>
+        <v>334</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>573</v>
+        <v>333</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-49</v>
+        <v>191</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>573</v>
+        <v>333</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>7.175</v>
+        <v>4.175</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>2679</v>
+        <v>1354</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>2679</v>
+        <v>1354</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-2679</v>
+        <v>-1354</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>2679</v>
+        <v>1354</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>33.4875</v>
+        <v>16.925</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>2424</v>
+        <v>2072</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-48506</v>
+        <v>-48858</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-2424</v>
+        <v>-2072</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-48506</v>
+        <v>-48858</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>30.3</v>
+        <v>25.9</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,8 +6246,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>23180+1718</f>
-        <v>24898</v>
+        <v>20593</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6255,7 +6254,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-3412</v>
+        <v>-7717</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6263,15 +6262,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>108043</v>
+        <v>112348</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-214</v>
+        <v>-4519</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>319.20512820512823</v>
+        <v>264.0128205128205</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6311,7 +6310,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6332,8 +6331,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>13206-1</f>
-        <v>13205</v>
+        <f>12582-1</f>
+        <v>12581</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6341,7 +6340,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-4346</v>
+        <v>-4970</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6349,15 +6348,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>38689</v>
+        <v>39313</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-2240</v>
+        <v>-2864</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>169.2948717948718</v>
+        <v>161.2948717948718</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6397,7 +6396,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6418,7 +6417,7 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>662</v>
+        <v>38</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6426,7 +6425,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-7183</v>
+        <v>-7807</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6434,15 +6433,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>16800</v>
+        <v>17424</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-4687</v>
+        <v>-5311</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>8.487179487179487</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6482,7 +6481,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6503,7 +6502,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>5067</v>
+        <v>2717</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6510,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-18212</v>
+        <v>-20562</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6518,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>34530</v>
+        <v>36880</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-15560</v>
+        <v>-17910</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>64.96153846153847</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6566,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6864,7 +6863,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>6624</v>
+        <v>5454</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6872,7 +6871,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>6624</v>
+        <v>5454</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6880,15 +6879,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>44342</v>
+        <v>45512</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>7326</v>
+        <v>6156</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>84.92307692307692</v>
+        <v>69.92307692307692</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6912,7 +6911,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6934,7 +6933,7 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <v>23485</v>
+        <v>21089</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6942,7 +6941,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-24310</v>
+        <v>-26706</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6950,15 +6949,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>29873</v>
+        <v>32269</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-19030</v>
+        <v>-21426</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>146.78125</v>
+        <v>131.80625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6998,7 +6997,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7019,7 +7018,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>4682</v>
+        <v>4332</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7027,7 +7026,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-6421</v>
+        <v>-6771</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7035,15 +7034,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>15426</v>
+        <v>15776</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-5461</v>
+        <v>-5811</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>29.2625</v>
+        <v>27.075</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7071,7 +7070,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7093,7 +7092,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>1121</v>
+        <v>851</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7101,7 +7100,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-1841</v>
+        <v>-2111</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7109,15 +7108,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>5123</v>
+        <v>5393</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>-81</v>
+        <v>-351</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>7.00625</v>
+        <v>5.31875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7141,7 +7140,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7231,8 +7230,7 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <f>584+2653</f>
-        <v>3237</v>
+        <v>2673</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7240,7 +7238,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>3231</v>
+        <v>2667</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7248,15 +7246,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>27253</v>
+        <v>27817</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>6111</v>
+        <v>5547</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>20.23125</v>
+        <v>16.70625</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7280,7 +7278,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7473,7 +7471,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>15348</v>
+        <v>14808</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7485,7 +7483,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>95.925</v>
+        <v>92.55</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7509,7 +7507,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8191,8 +8189,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>28697+2111</f>
-        <v>30808</v>
+        <v>29468</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8200,7 +8197,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-9822</v>
+        <v>-11162</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8208,15 +8205,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>21798</v>
+        <v>23138</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-3672</v>
+        <v>-5012</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>616.16</v>
+        <v>589.36</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8240,7 +8237,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8261,7 +8258,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>7282</v>
+        <v>5512</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8269,7 +8266,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>7282</v>
+        <v>5512</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8277,15 +8274,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>45324</v>
+        <v>47094</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>13432</v>
+        <v>11662</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>145.64</v>
+        <v>110.24</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8309,7 +8306,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8539,7 +8536,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>5546</v>
+        <v>4516</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8547,7 +8544,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>5546</v>
+        <v>4516</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8555,15 +8552,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>47060</v>
+        <v>48090</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>11696</v>
+        <v>10666</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>110.92</v>
+        <v>90.32</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8587,7 +8584,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8608,8 +8605,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <f>5454+1400</f>
-        <v>6854</v>
+        <v>5594</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8617,7 +8613,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>6854</v>
+        <v>5594</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8625,15 +8621,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>45752</v>
+        <v>47012</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>13004</v>
+        <v>11744</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>137.08</v>
+        <v>111.88</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8657,7 +8653,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8942,7 +8938,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>11936</v>
+        <v>11366</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8950,7 +8946,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>11936</v>
+        <v>11366</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8959,11 +8955,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>11936</v>
+        <v>11366</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>74.6</v>
+        <v>71.0375</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8987,7 +8983,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9008,8 +9004,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>26699-1</f>
-        <v>26698</v>
+        <f>25559-1</f>
+        <v>25558</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9017,7 +9013,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>26698</v>
+        <v>25558</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9026,11 +9022,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>26698</v>
+        <v>25558</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>166.8625</v>
+        <v>159.7375</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9054,7 +9050,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9075,7 +9071,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>25143</v>
+        <v>23983</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9083,7 +9079,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>25143</v>
+        <v>23983</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9092,11 +9088,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>25143</v>
+        <v>23983</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>157.14375</v>
+        <v>149.89375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9120,7 +9116,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9141,8 +9137,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <f>11056+4480+4480</f>
-        <v>20016</v>
+        <v>19416</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9150,7 +9145,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>20016</v>
+        <v>19416</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9159,11 +9154,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>20016</v>
+        <v>19416</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>125.1</v>
+        <v>121.35</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9187,7 +9182,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>8.3</v>
+        <v>8.1</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9472,7 +9467,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>8210</v>
+        <v>7528</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9480,7 +9475,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>8210</v>
+        <v>7528</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9489,11 +9484,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>8210</v>
+        <v>7528</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>97.73809523809524</v>
+        <v>89.61904761904762</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9538,7 +9533,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>10683</v>
+        <v>10398</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9550,7 +9545,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>213.66</v>
+        <v>207.96</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9574,7 +9569,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9595,7 +9590,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>21466</v>
+        <v>21315</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9607,7 +9602,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>157.83823529411765</v>
+        <v>156.72794117647058</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9823,7 +9818,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>6025</v>
+        <v>5535</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9835,7 +9830,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>37.65625</v>
+        <v>34.59375</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9859,7 +9854,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>18.8</v>
+        <v>17.3</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9880,7 +9875,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3574</v>
+        <v>3569</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9892,7 +9887,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.3375</v>
+        <v>22.30625</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10081,26 +10076,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>383644</v>
+        <v>405708</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>69241</v>
+        <v>92776</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>817172</v>
+        <v>789485</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>167213</v>
+        <v>190748</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4271.8845677117</v>
+        <v>4553.853463154492</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39358</v>
+        <v>56663</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>491.975</v>
+        <v>708.2875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18561</v>
+        <v>31441</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>232.0125</v>
+        <v>393.0125</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16647</v>
+        <v>29728</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>208.0875</v>
+        <v>371.6</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>405708</v>
+        <v>448974</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4553.853463154492</v>
+        <v>5094.678463154493</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>3198+15760+20400</f>
-        <v>39358</v>
+        <f>3198+15760+20400+17305</f>
+        <v>56663</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>39358</v>
+        <v>56663</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>11850</v>
+        <v>-5455</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>58958</v>
+        <v>76263</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>491.975</v>
+        <v>708.2875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>1041+17520</f>
-        <v>18561</v>
+        <f>1041+17520+12880</f>
+        <v>31441</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-4855</v>
+        <v>8025</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-10112</v>
+        <v>-22992</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>265</v>
+        <v>13145</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>232.0125</v>
+        <v>393.0125</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,8 +5534,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>1927+14720</f>
-        <v>16647</v>
+        <f>1927+14720+13081</f>
+        <v>29728</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>16644</v>
+        <v>29725</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-11042</v>
+        <v>-24123</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>21364</v>
+        <v>34445</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>208.0875</v>
+        <v>371.6</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -9210,7 +9210,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10076,26 +10076,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>405708</v>
+        <v>448974</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>92776</v>
+        <v>136042</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>789485</v>
+        <v>746219</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>190748</v>
+        <v>234014</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4553.853463154492</v>
+        <v>5094.678463154493</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46299</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>56663</v>
+        <v>33234</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>708.2875</v>
+        <v>415.425</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39997</v>
+        <v>18447</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>499.9625</v>
+        <v>230.5875</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31441</v>
+        <v>18324</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>393.0125</v>
+        <v>229.05</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29728</v>
+        <v>18101</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>371.6</v>
+        <v>226.2625</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27917</v>
+        <v>22398</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>348.9625</v>
+        <v>279.975</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>334</v>
+        <v>10</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>4.175</v>
+        <v>0.125</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1354</v>
+        <v>22562</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>16.925</v>
+        <v>282.025</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2072</v>
+        <v>1033</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>25.9</v>
+        <v>12.9125</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20593</v>
+        <v>100</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>264.0128205128205</v>
+        <v>1.2820512820512822</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12581</v>
+        <v>9060</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>161.2948717948718</v>
+        <v>116.15384615384616</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>38</v>
+        <v>39358</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>0.48717948717948717</v>
+        <v>504.5897435897436</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2717</v>
+        <v>1185</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>34.833333333333336</v>
+        <v>15.192307692307692</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>491</v>
+        <v>296</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>6.294871794871795</v>
+        <v>3.7948717948717947</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5454</v>
+        <v>3118</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>69.92307692307692</v>
+        <v>39.97435897435897</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21089</v>
+        <v>10966</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>131.80625</v>
+        <v>68.5375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4332</v>
+        <v>1367</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>27.075</v>
+        <v>8.54375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>5.31875</v>
+        <v>0</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2673</v>
+        <v>24424</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>16.70625</v>
+        <v>152.65</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14808</v>
+        <v>12428</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>92.55</v>
+        <v>77.675</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>23.1</v>
+        <v>19.4</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29468</v>
+        <v>22720</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>589.36</v>
+        <v>454.4</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5512</v>
+        <v>13193</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>110.24</v>
+        <v>263.86</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4516</v>
+        <v>121</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>90.32</v>
+        <v>2.42</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5594</v>
+        <v>5774</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>111.88</v>
+        <v>115.48</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11366</v>
+        <v>10866</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>71.0375</v>
+        <v>67.9125</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25558</v>
+        <v>15572</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>159.7375</v>
+        <v>97.325</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23983</v>
+        <v>18564</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>149.89375</v>
+        <v>116.025</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19416</v>
+        <v>23946</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>121.35</v>
+        <v>149.6625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>8.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7528</v>
+        <v>6168</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>89.61904761904762</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10398</v>
+        <v>8875</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>207.96</v>
+        <v>177.5</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>14.9</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21315</v>
+        <v>27744</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>156.72794117647058</v>
+        <v>204</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5535</v>
+        <v>6822</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>34.59375</v>
+        <v>42.6375</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>17.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3569</v>
+        <v>3561</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.30625</v>
+        <v>22.25625</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>448974</v>
+        <v>400420</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5094.678463154493</v>
+        <v>4452.188571428572</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46299</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5236,9 +5236,9 @@
         <v>80</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="23">
-        <f>3198+15760+20400+17305</f>
-        <v>56663</v>
+      <c r="J24" s="40">
+        <f>11315-1+9520+12400</f>
+        <v>33234</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>56663</v>
+        <v>33234</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-5455</v>
+        <v>17974</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>76263</v>
+        <v>52834</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>708.2875</v>
+        <v>415.425</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>39997</v>
+        <v>18447</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>39997</v>
+        <v>18447</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-39793</v>
+        <v>-18243</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>39997</v>
+        <v>18447</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>499.9625</v>
+        <v>230.5875</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5436,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>1041+17520+12880</f>
-        <v>31441</v>
+        <v>18324</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5444,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>8025</v>
+        <v>-5092</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5452,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-22992</v>
+        <v>-9875</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>13145</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>393.0125</v>
+        <v>229.05</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5512,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,8 +5533,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>1927+14720+13081</f>
-        <v>29728</v>
+        <v>18101</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5541,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>29725</v>
+        <v>18098</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5549,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-24123</v>
+        <v>-12496</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>34445</v>
+        <v>22818</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>371.6</v>
+        <v>226.2625</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5609,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,7 +5727,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <v>27917</v>
+        <f>15278+7120</f>
+        <v>22398</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5736,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>24441</v>
+        <v>18922</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5744,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-18560</v>
+        <v>-13041</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>25081</v>
+        <v>19562</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>348.9625</v>
+        <v>279.975</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5804,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5907,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>334</v>
+        <v>10</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5915,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>333</v>
+        <v>9</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5923,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>191</v>
+        <v>515</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>333</v>
+        <v>9</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>4.175</v>
+        <v>0.125</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5971,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6074,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>1354</v>
+        <f>6882+15680</f>
+        <v>22562</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>1354</v>
+        <v>22562</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-1354</v>
+        <v>-22562</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>1354</v>
+        <v>22562</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>16.925</v>
+        <v>282.025</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>2072</v>
+        <v>1033</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-48858</v>
+        <v>-49897</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-2072</v>
+        <v>-1033</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-48858</v>
+        <v>-49897</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>25.9</v>
+        <v>12.9125</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>20593</v>
+        <v>100</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-7717</v>
+        <v>-28210</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6262,15 +6262,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>112348</v>
+        <v>132841</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-4519</v>
+        <v>-25012</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>264.0128205128205</v>
+        <v>1.2820512820512822</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,8 +6331,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>12582-1</f>
-        <v>12581</v>
+        <f>9061-1</f>
+        <v>9060</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-4970</v>
+        <v>-8491</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6348,15 +6348,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>39313</v>
+        <v>42834</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-2864</v>
+        <v>-6385</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>161.2948717948718</v>
+        <v>116.15384615384616</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>11.5</v>
+        <v>8.3</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6416,8 +6416,9 @@
         <v>78</v>
       </c>
       <c r="I37" s="32"/>
-      <c r="J37" s="33">
-        <v>38</v>
+      <c r="J37" s="37">
+        <f>32028+1+7329</f>
+        <v>39358</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6425,7 +6426,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-7807</v>
+        <v>31513</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6433,15 +6434,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>17424</v>
+        <v>-21896</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-5311</v>
+        <v>34009</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>0.48717948717948717</v>
+        <v>504.5897435897436</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6481,7 +6482,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6501,8 +6502,9 @@
         <v>78</v>
       </c>
       <c r="I38" s="32"/>
-      <c r="J38" s="33">
-        <v>2717</v>
+      <c r="J38" s="37">
+        <f>1184+1</f>
+        <v>1185</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6510,7 +6512,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-20562</v>
+        <v>-22094</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6518,15 +6520,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>36880</v>
+        <v>38412</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-17910</v>
+        <v>-19442</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>34.833333333333336</v>
+        <v>15.192307692307692</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6566,7 +6568,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6656,7 +6658,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>491</v>
+        <v>296</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6664,7 +6666,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>491</v>
+        <v>296</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6672,15 +6674,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>50475</v>
+        <v>50670</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>1193</v>
+        <v>998</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>6.294871794871795</v>
+        <v>3.7948717948717947</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6704,7 +6706,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6863,7 +6865,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>5454</v>
+        <v>3118</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6871,7 +6873,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>5454</v>
+        <v>3118</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6879,15 +6881,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>45512</v>
+        <v>47848</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>6156</v>
+        <v>3820</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>69.92307692307692</v>
+        <v>39.97435897435897</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6911,7 +6913,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6932,8 +6934,9 @@
         <v>160</v>
       </c>
       <c r="I44" s="44"/>
-      <c r="J44" s="23">
-        <v>21089</v>
+      <c r="J44" s="40">
+        <f>5048-2+5920</f>
+        <v>10966</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6941,7 +6944,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-26706</v>
+        <v>-36829</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6949,15 +6952,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>32269</v>
+        <v>42392</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-21426</v>
+        <v>-31549</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>131.80625</v>
+        <v>68.5375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6997,7 +7000,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7018,7 +7021,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>4332</v>
+        <v>1367</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7026,7 +7029,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-6771</v>
+        <v>-9736</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7034,15 +7037,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>15776</v>
+        <v>18741</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-5811</v>
+        <v>-8776</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>27.075</v>
+        <v>8.54375</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7070,7 +7073,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7092,7 +7095,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7100,7 +7103,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-2111</v>
+        <v>-2962</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7108,15 +7111,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>5393</v>
+        <v>6244</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>-351</v>
+        <v>-1202</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>5.31875</v>
+        <v>0</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7140,7 +7143,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7229,8 +7232,9 @@
         <v>160</v>
       </c>
       <c r="I48" s="32"/>
-      <c r="J48" s="33">
-        <v>2673</v>
+      <c r="J48" s="37">
+        <f>24423+1</f>
+        <v>24424</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7238,7 +7242,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>2667</v>
+        <v>24418</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7246,15 +7250,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>27817</v>
+        <v>6066</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>5547</v>
+        <v>27298</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>16.70625</v>
+        <v>152.65</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7278,7 +7282,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7471,7 +7475,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>14808</v>
+        <v>12428</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7483,7 +7487,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>92.55</v>
+        <v>77.675</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7507,7 +7511,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>23.1</v>
+        <v>19.4</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8189,7 +8193,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>29468</v>
+        <v>22720</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8197,7 +8201,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-11162</v>
+        <v>-17910</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8205,15 +8209,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>23138</v>
+        <v>29886</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-5012</v>
+        <v>-11760</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>589.36</v>
+        <v>454.4</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8237,7 +8241,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8258,7 +8262,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>5512</v>
+        <f>9493+3700</f>
+        <v>13193</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8266,7 +8271,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>5512</v>
+        <v>13193</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8274,15 +8279,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>47094</v>
+        <v>39413</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>11662</v>
+        <v>19343</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>110.24</v>
+        <v>263.86</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8306,7 +8311,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8536,7 +8541,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>4516</v>
+        <v>121</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8544,7 +8549,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>4516</v>
+        <v>121</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8552,15 +8557,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>48090</v>
+        <v>52485</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>10666</v>
+        <v>6271</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>90.32</v>
+        <v>2.42</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8604,8 +8609,9 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="33">
-        <v>5594</v>
+      <c r="J69" s="40">
+        <f>5775-1</f>
+        <v>5774</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8613,7 +8619,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>5594</v>
+        <v>5774</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8621,15 +8627,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>47012</v>
+        <v>46832</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>11744</v>
+        <v>11924</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>111.88</v>
+        <v>115.48</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8938,7 +8944,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>11366</v>
+        <v>10866</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8946,7 +8952,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>11366</v>
+        <v>10866</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8955,11 +8961,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>11366</v>
+        <v>10866</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>71.0375</v>
+        <v>67.9125</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8983,7 +8989,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9004,8 +9010,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>25559-1</f>
-        <v>25558</v>
+        <f>15573-1</f>
+        <v>15572</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9013,7 +9019,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>25558</v>
+        <v>15572</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9022,11 +9028,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>25558</v>
+        <v>15572</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>159.7375</v>
+        <v>97.325</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9050,7 +9056,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9071,7 +9077,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>23983</v>
+        <v>18564</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9079,7 +9085,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>23983</v>
+        <v>18564</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9088,11 +9094,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>23983</v>
+        <v>18564</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>149.89375</v>
+        <v>116.025</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9116,7 +9122,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9137,7 +9143,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>19416</v>
+        <v>23946</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9145,7 +9151,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>19416</v>
+        <v>23946</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9154,11 +9160,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>19416</v>
+        <v>23946</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>121.35</v>
+        <v>149.6625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9182,7 +9188,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9210,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9467,7 +9473,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>7528</v>
+        <v>6168</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9475,7 +9481,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>7528</v>
+        <v>6168</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9484,11 +9490,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>7528</v>
+        <v>6168</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>89.61904761904762</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9533,7 +9539,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>10398</v>
+        <v>8875</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9545,7 +9551,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>207.96</v>
+        <v>177.5</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9569,7 +9575,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>14.9</v>
+        <v>12.7</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9590,7 +9596,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>21315</v>
+        <v>27744</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9602,7 +9608,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>156.72794117647058</v>
+        <v>204</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9626,7 +9632,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9818,7 +9824,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>5535</v>
+        <v>6822</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9830,7 +9836,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>34.59375</v>
+        <v>42.6375</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9854,7 +9860,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>17.3</v>
+        <v>21.3</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9875,7 +9881,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3569</v>
+        <v>3561</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9887,7 +9893,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.30625</v>
+        <v>22.25625</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10076,26 +10082,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>448974</v>
+        <v>400420</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>136042</v>
+        <v>83683</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>746219</v>
+        <v>785843</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>234014</v>
+        <v>181655</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5094.678463154493</v>
+        <v>4452.188571428572</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.25</v>
+        <v>0.4583333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33234</v>
+        <v>44434</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>415.425</v>
+        <v>555.425</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22398</v>
+        <v>24878</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>279.975</v>
+        <v>310.975</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22562</v>
+        <v>26882</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>282.025</v>
+        <v>336.025</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10966</v>
+        <v>15126</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>68.5375</v>
+        <v>94.5375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13193</v>
+        <v>16193</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>263.86</v>
+        <v>323.86</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>400420</v>
+        <v>425580</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4452.188571428572</v>
+        <v>4763.188571428572</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>11315-1+9520+12400</f>
-        <v>33234</v>
+        <f>11315-1+9520+12400+4800+6400</f>
+        <v>44434</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>33234</v>
+        <v>44434</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>17974</v>
+        <v>6774</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>52834</v>
+        <v>64034</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>415.425</v>
+        <v>555.425</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5727,8 +5727,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>15278+7120</f>
-        <v>22398</v>
+        <f>15278+7120+2480</f>
+        <v>24878</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>18922</v>
+        <v>21402</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5744,15 +5744,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-13041</v>
+        <v>-15521</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>19562</v>
+        <v>22042</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>279.975</v>
+        <v>310.975</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6074,8 +6074,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>6882+15680</f>
-        <v>22562</v>
+        <f>6882+15680+4320</f>
+        <v>26882</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>22562</v>
+        <v>26882</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-22562</v>
+        <v>-26882</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>22562</v>
+        <v>26882</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>282.025</v>
+        <v>336.025</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6935,8 +6935,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>5048-2+5920</f>
-        <v>10966</v>
+        <f>5048-2+5920+4160</f>
+        <v>15126</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-36829</v>
+        <v>-32669</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6952,15 +6952,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>42392</v>
+        <v>38232</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-31549</v>
+        <v>-27389</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>68.5375</v>
+        <v>94.5375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -8262,8 +8262,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>9493+3700</f>
-        <v>13193</v>
+        <f>9493+3700+3000</f>
+        <v>16193</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>13193</v>
+        <v>16193</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8279,15 +8279,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>39413</v>
+        <v>36413</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>19343</v>
+        <v>22343</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>263.86</v>
+        <v>323.86</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -9216,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10082,26 +10082,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>400420</v>
+        <v>425580</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>83683</v>
+        <v>108843</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>785843</v>
+        <v>760683</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>181655</v>
+        <v>206815</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4452.188571428572</v>
+        <v>4763.188571428572</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.4583333333321207</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>44434</v>
+        <v>46367</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>555.425</v>
+        <v>579.5875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18447</v>
+        <v>7219</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>230.5875</v>
+        <v>90.2375</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18324</v>
+        <v>2941</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>229.05</v>
+        <v>36.7625</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18101</v>
+        <v>10348</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>226.2625</v>
+        <v>129.35</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24878</v>
+        <v>15486</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>310.975</v>
+        <v>193.575</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26882</v>
+        <v>43431</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>336.025</v>
+        <v>542.8875</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>5.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1033</v>
+        <v>383</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>12.9125</v>
+        <v>4.7875</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>100</v>
+        <v>9294</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>1.2820512820512822</v>
+        <v>119.15384615384616</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9060</v>
+        <v>6914</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>116.15384615384616</v>
+        <v>88.64102564102564</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>8.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39358</v>
+        <v>34306</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>504.5897435897436</v>
+        <v>439.8205128205128</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>10.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1185</v>
+        <v>322</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>15.192307692307692</v>
+        <v>4.128205128205129</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>296</v>
+        <v>140</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>3.7948717948717947</v>
+        <v>1.794871794871795</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3118</v>
+        <v>1745</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>39.97435897435897</v>
+        <v>22.371794871794872</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15126</v>
+        <v>20367</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>94.5375</v>
+        <v>127.29375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1367</v>
+        <v>732</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>8.54375</v>
+        <v>4.575</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24424</v>
+        <v>22514</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>152.65</v>
+        <v>140.7125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12428</v>
+        <v>11418</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>77.675</v>
+        <v>71.3625</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>19.4</v>
+        <v>17.8</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22720</v>
+        <v>17035</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>454.4</v>
+        <v>340.7</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16193</v>
+        <v>23163</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>323.86</v>
+        <v>463.26</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5774</v>
+        <v>1285</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>115.48</v>
+        <v>25.7</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10866</v>
+        <v>21830</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>67.9125</v>
+        <v>136.4375</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15572</v>
+        <v>23221</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>97.325</v>
+        <v>145.13125</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18564</v>
+        <v>14923</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>116.025</v>
+        <v>93.26875</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23946</v>
+        <v>20995</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>149.6625</v>
+        <v>131.21875</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6168</v>
+        <v>5805</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>73.42857142857143</v>
+        <v>69.10714285714286</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8875</v>
+        <v>8507</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>177.5</v>
+        <v>170.14</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27744</v>
+        <v>31174</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>204</v>
+        <v>229.22058823529412</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6822</v>
+        <v>8311</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>42.6375</v>
+        <v>51.94375</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>21.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3561</v>
+        <v>3396</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>22.25625</v>
+        <v>21.225</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>425580</v>
+        <v>416526</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4763.188571428572</v>
+        <v>4494.939558015513</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5236,9 +5236,9 @@
         <v>80</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="40">
-        <f>11315-1+9520+12400+4800+6400</f>
-        <v>44434</v>
+      <c r="J24" s="23">
+        <f>9407+18320+18640</f>
+        <v>46367</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>44434</v>
+        <v>46367</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>6774</v>
+        <v>4841</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>64034</v>
+        <v>65967</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>555.425</v>
+        <v>579.5875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>18447</v>
+        <v>7219</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>18447</v>
+        <v>7219</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-18243</v>
+        <v>-7015</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>18447</v>
+        <v>7219</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>230.5875</v>
+        <v>90.2375</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,7 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>18324</v>
+        <f>61+2880</f>
+        <v>2941</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5444,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-5092</v>
+        <v>-20475</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5452,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-9875</v>
+        <v>5508</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>28</v>
+        <v>-15355</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>229.05</v>
+        <v>36.7625</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5512,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5533,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>18101</v>
+        <v>10348</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5541,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>18098</v>
+        <v>10345</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5549,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-12496</v>
+        <v>-4743</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>22818</v>
+        <v>15065</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>226.2625</v>
+        <v>129.35</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5609,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5727,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>15278+7120+2480</f>
-        <v>24878</v>
+        <f>6766+8720</f>
+        <v>15486</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5736,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>21402</v>
+        <v>12010</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5744,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-15521</v>
+        <v>-6129</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>22042</v>
+        <v>12650</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>310.975</v>
+        <v>193.575</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5804,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5907,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5915,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5923,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -6074,8 +6075,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>6882+15680+4320</f>
-        <v>26882</v>
+        <f>30863+12568</f>
+        <v>43431</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>26882</v>
+        <v>43431</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-26882</v>
+        <v>-43431</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>26882</v>
+        <v>43431</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>336.025</v>
+        <v>542.8875</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>1033</v>
+        <v>383</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-49897</v>
+        <v>-50547</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-1033</v>
+        <v>-383</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-49897</v>
+        <v>-50547</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>12.9125</v>
+        <v>4.7875</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,7 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>100</v>
+        <f>12+9282</f>
+        <v>9294</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6254,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-28210</v>
+        <v>-19016</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6262,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>132841</v>
+        <v>123647</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-25012</v>
+        <v>-15818</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>1.2820512820512822</v>
+        <v>119.15384615384616</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6310,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,8 +6333,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>9061-1</f>
-        <v>9060</v>
+        <f>6915-1</f>
+        <v>6914</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6340,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-8491</v>
+        <v>-10637</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6348,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>42834</v>
+        <v>44980</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-6385</v>
+        <v>-8531</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>116.15384615384616</v>
+        <v>88.64102564102564</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6396,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>8.3</v>
+        <v>6.3</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6417,8 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="37">
-        <f>32028+1+7329</f>
-        <v>39358</v>
+        <f>34305+1</f>
+        <v>34306</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6426,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>31513</v>
+        <v>26461</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6434,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-21896</v>
+        <v>-16844</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>34009</v>
+        <v>28957</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>504.5897435897436</v>
+        <v>439.8205128205128</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6482,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6503,8 +6505,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>1184+1</f>
-        <v>1185</v>
+        <f>321+1</f>
+        <v>322</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6512,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-22094</v>
+        <v>-22957</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6520,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>38412</v>
+        <v>39275</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-19442</v>
+        <v>-20305</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>15.192307692307692</v>
+        <v>4.128205128205129</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6568,7 +6570,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6658,7 +6660,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>296</v>
+        <v>140</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6666,7 +6668,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>296</v>
+        <v>140</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6674,15 +6676,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>50670</v>
+        <v>50826</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>998</v>
+        <v>842</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>3.7948717948717947</v>
+        <v>1.794871794871795</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6706,7 +6708,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6865,7 +6867,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>3118</v>
+        <v>1745</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6873,7 +6875,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>3118</v>
+        <v>1745</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6881,15 +6883,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>47848</v>
+        <v>49221</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>3820</v>
+        <v>2447</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>39.97435897435897</v>
+        <v>22.371794871794872</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6913,7 +6915,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6935,8 +6937,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>5048-2+5920+4160</f>
-        <v>15126</v>
+        <f>15303-2+5066</f>
+        <v>20367</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6944,7 +6946,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-32669</v>
+        <v>-27428</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6952,15 +6954,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>38232</v>
+        <v>32991</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-27389</v>
+        <v>-22148</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>94.5375</v>
+        <v>127.29375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7000,7 +7002,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7021,7 +7023,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>1367</v>
+        <v>732</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7029,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-9736</v>
+        <v>-10371</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7037,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>18741</v>
+        <v>19376</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-8776</v>
+        <v>-9411</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>8.54375</v>
+        <v>4.575</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7073,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7095,7 +7097,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7103,7 +7105,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-2962</v>
+        <v>-242</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7111,15 +7113,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>6244</v>
+        <v>3524</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>-1202</v>
+        <v>1518</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7143,7 +7145,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7233,8 +7235,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>24423+1</f>
-        <v>24424</v>
+        <f>22513+1</f>
+        <v>22514</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7242,7 +7244,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>24418</v>
+        <v>22508</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7250,15 +7252,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>6066</v>
+        <v>7976</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>27298</v>
+        <v>25388</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>152.65</v>
+        <v>140.7125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7282,7 +7284,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7475,7 +7477,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>12428</v>
+        <v>11418</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7487,7 +7489,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>77.675</v>
+        <v>71.3625</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7511,7 +7513,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>19.4</v>
+        <v>17.8</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8193,7 +8195,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>22720</v>
+        <v>17035</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8201,7 +8203,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-17910</v>
+        <v>-23595</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8209,15 +8211,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>29886</v>
+        <v>35571</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-11760</v>
+        <v>-17445</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>454.4</v>
+        <v>340.7</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8241,7 +8243,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8262,8 +8264,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>9493+3700+3000</f>
-        <v>16193</v>
+        <f>16263+6900</f>
+        <v>23163</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8271,7 +8273,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>16193</v>
+        <v>23163</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8279,15 +8281,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>36413</v>
+        <v>29443</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>22343</v>
+        <v>29313</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>323.86</v>
+        <v>463.26</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8311,7 +8313,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8541,7 +8543,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8549,7 +8551,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8557,15 +8559,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52485</v>
+        <v>52455</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6271</v>
+        <v>6301</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8609,9 +8611,8 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="40">
-        <f>5775-1</f>
-        <v>5774</v>
+      <c r="J69" s="33">
+        <v>1285</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8619,7 +8620,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>5774</v>
+        <v>1285</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8627,15 +8628,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>46832</v>
+        <v>51321</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>11924</v>
+        <v>7435</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>115.48</v>
+        <v>25.7</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8659,7 +8660,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8944,7 +8945,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>10866</v>
+        <v>21830</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8952,7 +8953,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>10866</v>
+        <v>21830</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8961,11 +8962,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>10866</v>
+        <v>21830</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>67.9125</v>
+        <v>136.4375</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8989,7 +8990,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9010,8 +9011,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>15573-1</f>
-        <v>15572</v>
+        <f>23222-1</f>
+        <v>23221</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9019,7 +9020,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>15572</v>
+        <v>23221</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9028,11 +9029,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>15572</v>
+        <v>23221</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>97.325</v>
+        <v>145.13125</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9056,7 +9057,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9077,7 +9078,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>18564</v>
+        <v>14923</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9085,7 +9086,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>18564</v>
+        <v>14923</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9094,11 +9095,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>18564</v>
+        <v>14923</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>116.025</v>
+        <v>93.26875</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9122,7 +9123,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9143,7 +9144,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>23946</v>
+        <v>20995</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9151,7 +9152,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>23946</v>
+        <v>20995</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9160,11 +9161,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>23946</v>
+        <v>20995</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>149.6625</v>
+        <v>131.21875</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9188,7 +9189,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>8.7</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9216,7 +9217,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9473,7 +9474,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>6168</v>
+        <v>5805</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9481,7 +9482,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>6168</v>
+        <v>5805</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9490,11 +9491,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>6168</v>
+        <v>5805</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>73.42857142857143</v>
+        <v>69.10714285714286</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9539,7 +9540,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>8875</v>
+        <v>8507</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9551,7 +9552,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>177.5</v>
+        <v>170.14</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9575,7 +9576,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9596,7 +9597,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>27744</v>
+        <v>31174</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9608,7 +9609,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>204</v>
+        <v>229.22058823529412</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9632,7 +9633,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9824,7 +9825,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>6822</v>
+        <v>8311</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9836,7 +9837,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>42.6375</v>
+        <v>51.94375</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9860,7 +9861,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>21.3</v>
+        <v>26</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9881,7 +9882,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3561</v>
+        <v>3396</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9893,7 +9894,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>22.25625</v>
+        <v>21.225</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10082,26 +10083,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>425580</v>
+        <v>416526</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>108843</v>
+        <v>96413</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>760683</v>
+        <v>784771</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>206815</v>
+        <v>194385</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4763.188571428572</v>
+        <v>4494.939558015513</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>46367</v>
+        <v>60767</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>579.5875</v>
+        <v>759.5875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2941</v>
+        <v>10141</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>36.7625</v>
+        <v>126.7625</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15486</v>
+        <v>22206</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>193.575</v>
+        <v>277.575</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9294</v>
+        <v>12648</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>119.15384615384616</v>
+        <v>162.15384615384616</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2720</v>
+        <v>7680</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23163</v>
+        <v>26495</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>463.26</v>
+        <v>529.9</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>416526</v>
+        <v>456492</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4494.939558015513</v>
+        <v>4989.5795580155145</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>9407+18320+18640</f>
-        <v>46367</v>
+        <f>9407+18320+18640+4000+6560+3840</f>
+        <v>60767</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>46367</v>
+        <v>60767</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>4841</v>
+        <v>-9559</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>65967</v>
+        <v>80367</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>579.5875</v>
+        <v>759.5875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>61+2880</f>
-        <v>2941</v>
+        <f>61+2880+3680+1760+1760</f>
+        <v>10141</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-20475</v>
+        <v>-13275</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>5508</v>
+        <v>-1692</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>-15355</v>
+        <v>-8155</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>36.7625</v>
+        <v>126.7625</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>6766+8720</f>
-        <v>15486</v>
+        <f>6766+8720+2400+4320</f>
+        <v>22206</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>12010</v>
+        <v>18730</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-6129</v>
+        <v>-12849</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>12650</v>
+        <v>19370</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>193.575</v>
+        <v>277.575</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6247,8 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>12+9282</f>
-        <v>9294</v>
+        <f>12+9282+780+2574</f>
+        <v>12648</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-19016</v>
+        <v>-15662</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>123647</v>
+        <v>120293</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-15818</v>
+        <v>-12464</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>119.15384615384616</v>
+        <v>162.15384615384616</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -7097,7 +7097,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>2720</v>
+        <f>2720+1280+2240+1440</f>
+        <v>7680</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7105,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-242</v>
+        <v>4718</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7113,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>3524</v>
+        <v>-1436</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>1518</v>
+        <v>6478</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7145,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -8264,8 +8265,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>16263+6900</f>
-        <v>23163</v>
+        <f>16263+6900+1782+750+800</f>
+        <v>26495</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8273,7 +8274,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>23163</v>
+        <v>26495</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8281,15 +8282,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>29443</v>
+        <v>26111</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>29313</v>
+        <v>32645</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>463.26</v>
+        <v>529.9</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8313,7 +8314,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -9217,7 +9218,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10083,26 +10084,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>416526</v>
+        <v>456492</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>96413</v>
+        <v>136379</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>784771</v>
+        <v>744805</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>194385</v>
+        <v>234351</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4494.939558015513</v>
+        <v>4989.5795580155145</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.5625</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>60767</v>
+        <v>38710</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>759.5875</v>
+        <v>483.875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7219</v>
+        <v>161</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>90.2375</v>
+        <v>2.0125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10141</v>
+        <v>22205</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>126.7625</v>
+        <v>277.5625</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10348</v>
+        <v>2606</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>129.35</v>
+        <v>32.575</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22206</v>
+        <v>14219</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>277.575</v>
+        <v>177.7375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>43431</v>
+        <v>39359</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>542.8875</v>
+        <v>491.9875</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>383</v>
+        <v>223</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>4.7875</v>
+        <v>2.7875</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12648</v>
+        <v>17321</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>162.15384615384616</v>
+        <v>222.06410256410257</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6914</v>
+        <v>4887</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>88.64102564102564</v>
+        <v>62.65384615384615</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34306</v>
+        <v>29342</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>439.8205128205128</v>
+        <v>376.1794871794872</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>4.128205128205129</v>
+        <v>1.0128205128205128</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1745</v>
+        <v>807</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>22.371794871794872</v>
+        <v>10.346153846153847</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20367</v>
+        <v>12621</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>127.29375</v>
+        <v>78.88125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>732</v>
+        <v>232</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>4.575</v>
+        <v>1.45</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7680</v>
+        <v>17392</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>108.7</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22514</v>
+        <v>17629</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>140.7125</v>
+        <v>110.18125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11418</v>
+        <v>9708</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>71.3625</v>
+        <v>60.675</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>15.2</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17035</v>
+        <v>12190</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>340.7</v>
+        <v>243.8</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26495</v>
+        <v>27215</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>529.9</v>
+        <v>544.3</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>3.02</v>
+        <v>2.42</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1285</v>
+        <v>145</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>25.7</v>
+        <v>2.9</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21830</v>
+        <v>19432</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>136.4375</v>
+        <v>121.45</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23221</v>
+        <v>29006</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>145.13125</v>
+        <v>181.2875</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14923</v>
+        <v>12481</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>93.26875</v>
+        <v>78.00625</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20995</v>
+        <v>17965</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>131.21875</v>
+        <v>112.28125</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>8.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5805</v>
+        <v>5159</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>69.10714285714286</v>
+        <v>61.416666666666664</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8507</v>
+        <v>9614</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>170.14</v>
+        <v>192.28</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31174</v>
+        <v>38157</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>229.22058823529412</v>
+        <v>280.56617647058823</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8311</v>
+        <v>8197</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>51.94375</v>
+        <v>51.23125</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>21.225</v>
+        <v>21.2125</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>456492</v>
+        <v>414800</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4989.5795580155145</v>
+        <v>4446.153195701356</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5236,9 +5236,9 @@
         <v>80</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="23">
-        <f>9407+18320+18640+4000+6560+3840</f>
-        <v>60767</v>
+      <c r="J24" s="40">
+        <f>1431-1+16480+20800</f>
+        <v>38710</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>60767</v>
+        <v>38710</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-9559</v>
+        <v>12498</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>80367</v>
+        <v>58310</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>759.5875</v>
+        <v>483.875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>7219</v>
+        <v>161</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>7219</v>
+        <v>161</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-7015</v>
+        <v>43</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>7219</v>
+        <v>161</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>90.2375</v>
+        <v>2.0125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>61+2880+3680+1760+1760</f>
-        <v>10141</v>
+        <f>2045+20160</f>
+        <v>22205</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-13275</v>
+        <v>-1211</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-1692</v>
+        <v>-13756</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>-8155</v>
+        <v>3909</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>126.7625</v>
+        <v>277.5625</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>10348</v>
+        <v>2606</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>10345</v>
+        <v>2603</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-4743</v>
+        <v>2999</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>15065</v>
+        <v>7323</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>129.35</v>
+        <v>32.575</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>6766+8720+2400+4320</f>
-        <v>22206</v>
+        <f>4866+9353</f>
+        <v>14219</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>18730</v>
+        <v>10743</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-12849</v>
+        <v>-4862</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>19370</v>
+        <v>11383</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>277.575</v>
+        <v>177.7375</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5908,8 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>0</v>
+        <f>0+4000</f>
+        <v>4000</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>3999</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>525</v>
+        <v>-3475</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>-1</v>
+        <v>3999</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,8 +6076,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>30863+12568</f>
-        <v>43431</v>
+        <v>39359</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>43431</v>
+        <v>39359</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-43431</v>
+        <v>-39359</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>43431</v>
+        <v>39359</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>542.8875</v>
+        <v>491.9875</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>8.2</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>383</v>
+        <v>223</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-50547</v>
+        <v>-50707</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-383</v>
+        <v>-223</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-50547</v>
+        <v>-50707</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>4.7875</v>
+        <v>2.7875</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,8 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>12+9282+780+2574</f>
-        <v>12648</v>
+        <f>551+16770</f>
+        <v>17321</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-15662</v>
+        <v>-10989</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>120293</v>
+        <v>115620</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-12464</v>
+        <v>-7791</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>162.15384615384616</v>
+        <v>222.06410256410257</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6333,8 +6333,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>6915-1</f>
-        <v>6914</v>
+        <f>4888-1</f>
+        <v>4887</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-10637</v>
+        <v>-12664</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>44980</v>
+        <v>47007</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-8531</v>
+        <v>-10558</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>88.64102564102564</v>
+        <v>62.65384615384615</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,8 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="37">
-        <f>34305+1</f>
-        <v>34306</v>
+        <f>29341+1</f>
+        <v>29342</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>26461</v>
+        <v>21497</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-16844</v>
+        <v>-11880</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>28957</v>
+        <v>23993</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>439.8205128205128</v>
+        <v>376.1794871794872</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6505,8 +6505,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>321+1</f>
-        <v>322</v>
+        <f>78+1</f>
+        <v>79</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-22957</v>
+        <v>-23200</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>39275</v>
+        <v>39518</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-20305</v>
+        <v>-20548</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>4.128205128205129</v>
+        <v>1.0128205128205128</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>1745</v>
+        <v>807</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>1745</v>
+        <v>807</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6883,15 +6883,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>49221</v>
+        <v>50159</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>2447</v>
+        <v>1509</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>22.371794871794872</v>
+        <v>10.346153846153847</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6937,8 +6937,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>15303-2+5066</f>
-        <v>20367</v>
+        <f>12623-2</f>
+        <v>12621</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-27428</v>
+        <v>-35174</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6954,15 +6954,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>32991</v>
+        <v>40737</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-22148</v>
+        <v>-29894</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>127.29375</v>
+        <v>78.88125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>732</v>
+        <v>232</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-10371</v>
+        <v>-10871</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7039,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>19376</v>
+        <v>19876</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-9411</v>
+        <v>-9911</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>4.575</v>
+        <v>1.45</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7097,8 +7097,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <f>2720+1280+2240+1440</f>
-        <v>7680</v>
+        <f>6810+10582</f>
+        <v>17392</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>4718</v>
+        <v>14430</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-1436</v>
+        <v>-11148</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>6478</v>
+        <v>16190</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>108.7</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,8 +7236,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>22513+1</f>
-        <v>22514</v>
+        <f>17628+1</f>
+        <v>17629</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>22508</v>
+        <v>17623</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7253,15 +7253,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>7976</v>
+        <v>12861</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>25388</v>
+        <v>20503</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>140.7125</v>
+        <v>110.18125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>11418</v>
+        <v>9708</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7490,7 +7490,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>71.3625</v>
+        <v>60.675</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>17.8</v>
+        <v>15.2</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>17035</v>
+        <v>12190</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-23595</v>
+        <v>-28440</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8212,15 +8212,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>35571</v>
+        <v>40416</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-17445</v>
+        <v>-22290</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>340.7</v>
+        <v>243.8</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8265,8 +8265,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>16263+6900+1782+750+800</f>
-        <v>26495</v>
+        <f>19015+8200</f>
+        <v>27215</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>26495</v>
+        <v>27215</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8282,15 +8282,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>26111</v>
+        <v>25391</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>32645</v>
+        <v>33365</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>529.9</v>
+        <v>544.3</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8560,15 +8560,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52455</v>
+        <v>52485</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6301</v>
+        <v>6271</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>3.02</v>
+        <v>2.42</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>1285</v>
+        <v>145</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>1285</v>
+        <v>145</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8629,15 +8629,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>51321</v>
+        <v>52461</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>7435</v>
+        <v>6295</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>25.7</v>
+        <v>2.9</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8945,8 +8945,9 @@
         <v>160</v>
       </c>
       <c r="I74" s="53"/>
-      <c r="J74" s="23">
-        <v>21830</v>
+      <c r="J74" s="37">
+        <f>19430+2</f>
+        <v>19432</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8954,7 +8955,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>21830</v>
+        <v>19432</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8963,11 +8964,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>21830</v>
+        <v>19432</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>136.4375</v>
+        <v>121.45</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8991,7 +8992,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9012,8 +9013,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>23222-1</f>
-        <v>23221</v>
+        <f>29007-1</f>
+        <v>29006</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9021,7 +9022,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>23221</v>
+        <v>29006</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9030,11 +9031,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>23221</v>
+        <v>29006</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>145.13125</v>
+        <v>181.2875</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9058,7 +9059,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9078,8 +9079,9 @@
         <v>160</v>
       </c>
       <c r="I76" s="58"/>
-      <c r="J76" s="33">
-        <v>14923</v>
+      <c r="J76" s="40">
+        <f>12483-2</f>
+        <v>12481</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9087,7 +9089,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>14923</v>
+        <v>12481</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9096,11 +9098,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>14923</v>
+        <v>12481</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>93.26875</v>
+        <v>78.00625</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9124,7 +9126,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9145,7 +9147,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>20995</v>
+        <v>17965</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9153,7 +9155,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>20995</v>
+        <v>17965</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9162,11 +9164,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>20995</v>
+        <v>17965</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>131.21875</v>
+        <v>112.28125</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9190,7 +9192,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>8.7</v>
+        <v>7.5</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9218,7 +9220,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9475,7 +9477,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>5805</v>
+        <v>5159</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9483,7 +9485,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>5805</v>
+        <v>5159</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9492,11 +9494,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>5805</v>
+        <v>5159</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>69.10714285714286</v>
+        <v>61.416666666666664</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9541,7 +9543,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>8507</v>
+        <v>9614</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9553,7 +9555,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>170.14</v>
+        <v>192.28</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9577,7 +9579,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9598,7 +9600,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>31174</v>
+        <v>38157</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9610,7 +9612,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>229.22058823529412</v>
+        <v>280.56617647058823</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9634,7 +9636,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>8.5</v>
+        <v>10.4</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9826,7 +9828,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>8311</v>
+        <v>8197</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9838,7 +9840,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>51.94375</v>
+        <v>51.23125</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9862,7 +9864,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9883,7 +9885,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9895,7 +9897,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>21.225</v>
+        <v>21.2125</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10084,26 +10086,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>456492</v>
+        <v>414800</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>136379</v>
+        <v>88423</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>744805</v>
+        <v>790030</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>234351</v>
+        <v>186395</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4989.5795580155145</v>
+        <v>4446.153195701356</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>38710</v>
+        <v>59412</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>483.875</v>
+        <v>742.65</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>2.0125</v>
+        <v>0.1125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22205</v>
+        <v>34456</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>277.5625</v>
+        <v>430.7</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2606</v>
+        <v>193</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>32.575</v>
+        <v>2.4125</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14219</v>
+        <v>8137</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>177.7375</v>
+        <v>101.7125</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4000</v>
+        <v>7538</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>94.225</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>8.3</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39359</v>
+        <v>33466</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>491.9875</v>
+        <v>418.325</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>8.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>223</v>
+        <v>6450</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>2.7875</v>
+        <v>80.625</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17321</v>
+        <v>7868</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>222.06410256410257</v>
+        <v>100.87179487179488</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4887</v>
+        <v>2671</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>62.65384615384615</v>
+        <v>34.243589743589745</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29342</v>
+        <v>23489</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>376.1794871794872</v>
+        <v>301.14102564102564</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>1.0128205128205128</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>140</v>
+        <v>11986</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>1.794871794871795</v>
+        <v>153.66666666666666</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>807</v>
+        <v>43</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>10.346153846153847</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12621</v>
+        <v>4767</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>78.88125</v>
+        <v>29.79375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>232</v>
+        <v>5343</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>1.45</v>
+        <v>33.39375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17392</v>
+        <v>20364</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>108.7</v>
+        <v>127.275</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17629</v>
+        <v>13129</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>110.18125</v>
+        <v>82.05625</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9708</v>
+        <v>8528</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>60.675</v>
+        <v>53.3</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12190</v>
+        <v>7744</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>243.8</v>
+        <v>154.88</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27215</v>
+        <v>31840</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>544.3</v>
+        <v>636.8</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>121</v>
+        <v>4688</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>2.42</v>
+        <v>93.76</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>2.9</v>
+        <v>0.64</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19432</v>
+        <v>21118</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>121.45</v>
+        <v>131.9875</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>8.1</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29006</v>
+        <v>29827</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>181.2875</v>
+        <v>186.41875</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12481</v>
+        <v>9157</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>78.00625</v>
+        <v>57.23125</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17965</v>
+        <v>33725</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>112.28125</v>
+        <v>210.78125</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
       <c r="D36" s="58"/>
       <c r="E36" s="33">
         <f>VLOOKUP(A36,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F36" s="58"/>
       <c r="G36" s="34" t="s">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="1"/>
-        <v>0.5125</v>
+        <v>0.50625</v>
       </c>
       <c r="I36" s="35">
         <v>1</v>
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5159</v>
+        <v>4917</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>61.416666666666664</v>
+        <v>58.535714285714285</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9614</v>
+        <v>8698</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>192.28</v>
+        <v>173.96</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>38157</v>
+        <v>33339</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>280.56617647058823</v>
+        <v>245.13970588235293</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8197</v>
+        <v>12445</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>51.23125</v>
+        <v>77.78125</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>25.6</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3394</v>
+        <v>3366</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>21.2125</v>
+        <v>21.0375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>414800</v>
+        <v>448867</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4446.153195701356</v>
+        <v>4837.0404201680685</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>1431-1+16480+20800</f>
-        <v>38710</v>
+        <f>4133-1+24880+30400</f>
+        <v>59412</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>38710</v>
+        <v>59412</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>12498</v>
+        <v>-8204</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>58310</v>
+        <v>79012</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>483.875</v>
+        <v>742.65</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>2.0125</v>
+        <v>0.1125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>2045+20160</f>
-        <v>22205</v>
+        <f>9864+24592</f>
+        <v>34456</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-1211</v>
+        <v>11040</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-13756</v>
+        <v>-26007</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>3909</v>
+        <v>16160</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>277.5625</v>
+        <v>430.7</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>2606</v>
+        <v>193</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>2603</v>
+        <v>190</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>2999</v>
+        <v>5412</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>7323</v>
+        <v>4910</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>32.575</v>
+        <v>2.4125</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>4866+9353</f>
-        <v>14219</v>
+        <f>57+8080</f>
+        <v>8137</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>10743</v>
+        <v>4661</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-4862</v>
+        <v>1220</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>11383</v>
+        <v>5301</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>177.7375</v>
+        <v>101.7125</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,8 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <f>0+4000</f>
-        <v>4000</v>
+        <v>7538</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>3999</v>
+        <v>7537</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-3475</v>
+        <v>-7013</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>3999</v>
+        <v>7537</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>94.225</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>8.3</v>
+        <v>15.7</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>39359</v>
+        <v>33466</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>39359</v>
+        <v>33466</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-39359</v>
+        <v>-33466</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>39359</v>
+        <v>33466</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>491.9875</v>
+        <v>418.325</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6161,8 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>223</v>
+        <f>3625+2825</f>
+        <v>6450</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-50707</v>
+        <v>-44480</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-223</v>
+        <v>-6450</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-50707</v>
+        <v>-44480</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>2.7875</v>
+        <v>80.625</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>13.4</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,8 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>551+16770</f>
-        <v>17321</v>
+        <f>7307+561</f>
+        <v>7868</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-10989</v>
+        <v>-20442</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>115620</v>
+        <v>125073</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-7791</v>
+        <v>-17244</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>222.06410256410257</v>
+        <v>100.87179487179488</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6333,8 +6333,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>4888-1</f>
-        <v>4887</v>
+        <f>2672-1</f>
+        <v>2671</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-12664</v>
+        <v>-14880</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>47007</v>
+        <v>49223</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-10558</v>
+        <v>-12774</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>62.65384615384615</v>
+        <v>34.243589743589745</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,8 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="37">
-        <f>29341+1</f>
-        <v>29342</v>
+        <f>23488+1</f>
+        <v>23489</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>21497</v>
+        <v>15644</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-11880</v>
+        <v>-6027</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>23993</v>
+        <v>18140</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>376.1794871794872</v>
+        <v>301.14102564102564</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6505,8 +6505,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>78+1</f>
-        <v>79</v>
+        <f>39+1</f>
+        <v>40</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-23200</v>
+        <v>-23239</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>39518</v>
+        <v>39557</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-20548</v>
+        <v>-20587</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>1.0128205128205128</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6660,7 +6660,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>140</v>
+        <f>130+11856</f>
+        <v>11986</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6668,7 +6669,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>140</v>
+        <v>11986</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6676,15 +6677,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>50826</v>
+        <v>38980</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>842</v>
+        <v>12688</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>1.794871794871795</v>
+        <v>153.66666666666666</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6708,7 +6709,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>22</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6867,7 +6868,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>807</v>
+        <v>43</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6875,7 +6876,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>807</v>
+        <v>43</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6883,15 +6884,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>50159</v>
+        <v>50923</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>1509</v>
+        <v>745</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>10.346153846153847</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6915,7 +6916,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6937,8 +6938,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>12623-2</f>
-        <v>12621</v>
+        <f>4769-2</f>
+        <v>4767</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6946,7 +6947,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-35174</v>
+        <v>-43028</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6954,15 +6955,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>40737</v>
+        <v>48591</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-29894</v>
+        <v>-37748</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>78.88125</v>
+        <v>29.79375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7002,7 +7003,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7023,7 +7024,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>232</v>
+        <f>222+5121</f>
+        <v>5343</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7031,7 +7033,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-10871</v>
+        <v>-5760</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7039,15 +7041,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>19876</v>
+        <v>14765</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-9911</v>
+        <v>-4800</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>1.45</v>
+        <v>33.39375</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7075,7 +7077,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7097,8 +7099,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <f>6810+10582</f>
-        <v>17392</v>
+        <f>15756+4608</f>
+        <v>20364</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7108,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>14430</v>
+        <v>17402</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7116,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-11148</v>
+        <v>-14120</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>16190</v>
+        <v>19162</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>108.7</v>
+        <v>127.275</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7148,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,8 +7238,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>17628+1</f>
-        <v>17629</v>
+        <f>13128+1</f>
+        <v>13129</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7245,7 +7247,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>17623</v>
+        <v>13123</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7253,15 +7255,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>12861</v>
+        <v>17361</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>20503</v>
+        <v>16003</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>110.18125</v>
+        <v>82.05625</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7285,7 +7287,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7478,7 +7480,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>9708</v>
+        <v>8528</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7490,7 +7492,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>60.675</v>
+        <v>53.3</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7514,7 +7516,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8196,7 +8198,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>12190</v>
+        <v>7744</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8204,7 +8206,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-28440</v>
+        <v>-32886</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8212,15 +8214,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>40416</v>
+        <v>44862</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-22290</v>
+        <v>-26736</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>243.8</v>
+        <v>154.88</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8244,7 +8246,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8265,8 +8267,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>19015+8200</f>
-        <v>27215</v>
+        <f>22084+9756</f>
+        <v>31840</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8274,7 +8276,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>27215</v>
+        <v>31840</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8282,15 +8284,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>25391</v>
+        <v>20766</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>33365</v>
+        <v>37990</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>544.3</v>
+        <v>636.8</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8314,7 +8316,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8544,7 +8546,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>121</v>
+        <v>4688</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8552,7 +8554,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>121</v>
+        <v>4688</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8560,15 +8562,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52485</v>
+        <v>47918</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6271</v>
+        <v>10838</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>2.42</v>
+        <v>93.76</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8592,7 +8594,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8613,7 +8615,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8621,7 +8623,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8629,15 +8631,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52461</v>
+        <v>52574</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6295</v>
+        <v>6182</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>2.9</v>
+        <v>0.64</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8946,8 +8948,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>19430+2</f>
-        <v>19432</v>
+        <f>21116+2</f>
+        <v>21118</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8955,7 +8957,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>19432</v>
+        <v>21118</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8964,11 +8966,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>19432</v>
+        <v>21118</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>121.45</v>
+        <v>131.9875</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8992,7 +8994,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>8.1</v>
+        <v>8.8</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9013,8 +9015,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>29007-1</f>
-        <v>29006</v>
+        <f>29828-1</f>
+        <v>29827</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9022,7 +9024,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>29006</v>
+        <v>29827</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9031,11 +9033,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>29006</v>
+        <v>29827</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>181.2875</v>
+        <v>186.41875</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9059,7 +9061,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9080,8 +9082,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>12483-2</f>
-        <v>12481</v>
+        <f>9159-2</f>
+        <v>9157</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9089,7 +9091,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>12481</v>
+        <v>9157</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9098,11 +9100,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>12481</v>
+        <v>9157</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>78.00625</v>
+        <v>57.23125</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9126,7 +9128,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9147,7 +9149,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>17965</v>
+        <v>33725</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9155,7 +9157,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>17965</v>
+        <v>33725</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9164,11 +9166,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>17965</v>
+        <v>33725</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>112.28125</v>
+        <v>210.78125</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9192,7 +9194,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>7.5</v>
+        <v>14.1</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9345,7 +9347,7 @@
       </c>
       <c r="I80" s="58"/>
       <c r="J80" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K80" s="58"/>
       <c r="L80" s="34" t="s">
@@ -9353,7 +9355,7 @@
       </c>
       <c r="M80" s="115">
         <f t="shared" si="13"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N80" s="116">
         <f t="shared" si="8"/>
@@ -9362,11 +9364,11 @@
       <c r="O80" s="117"/>
       <c r="P80" s="118">
         <f t="shared" si="12"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q80" s="33">
         <f t="shared" si="5"/>
-        <v>0.5125</v>
+        <v>0.50625</v>
       </c>
       <c r="R80" s="32"/>
       <c r="S80" s="32"/>
@@ -9477,7 +9479,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>5159</v>
+        <v>4917</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9485,7 +9487,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>5159</v>
+        <v>4917</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9494,11 +9496,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>5159</v>
+        <v>4917</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>61.416666666666664</v>
+        <v>58.535714285714285</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9543,7 +9545,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>9614</v>
+        <v>8698</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9555,7 +9557,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>192.28</v>
+        <v>173.96</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9579,7 +9581,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9600,7 +9602,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>38157</v>
+        <v>33339</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9612,7 +9614,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>280.56617647058823</v>
+        <v>245.13970588235293</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9636,7 +9638,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9828,7 +9830,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>8197</v>
+        <v>12445</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9840,7 +9842,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>51.23125</v>
+        <v>77.78125</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9864,7 +9866,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>25.6</v>
+        <v>38.9</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9885,7 +9887,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3394</v>
+        <v>3366</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9897,7 +9899,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>21.2125</v>
+        <v>21.0375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10086,26 +10088,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>414800</v>
+        <v>448867</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>88423</v>
+        <v>125184</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>790030</v>
+        <v>767969</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>186395</v>
+        <v>223156</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4446.153195701356</v>
+        <v>4837.0404201680685</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>59412</v>
+        <v>80224</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>742.65</v>
+        <v>1002.8</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9</v>
+        <v>28015</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>0.1125</v>
+        <v>350.1875</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34456</v>
+        <v>31677</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>430.7</v>
+        <v>395.9625</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8137</v>
+        <v>21348</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>101.7125</v>
+        <v>266.85</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7538</v>
+        <v>7198</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>94.225</v>
+        <v>89.975</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>15.7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33466</v>
+        <v>31354</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>418.325</v>
+        <v>391.925</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6450</v>
+        <v>6355</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>80.625</v>
+        <v>79.4375</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7868</v>
+        <v>3723</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>100.87179487179488</v>
+        <v>47.73076923076923</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2671</v>
+        <v>1764</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>34.243589743589745</v>
+        <v>22.615384615384617</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23489</v>
+        <v>21892</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>301.14102564102564</v>
+        <v>280.6666666666667</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>0.5128205128205128</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11986</v>
+        <v>13782</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>153.66666666666666</v>
+        <v>176.69230769230768</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4767</v>
+        <v>2757</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>29.79375</v>
+        <v>17.23125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5343</v>
+        <v>5993</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>33.39375</v>
+        <v>37.45625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20364</v>
+        <v>18115</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>127.275</v>
+        <v>113.21875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13129</v>
+        <v>11759</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>82.05625</v>
+        <v>73.49375</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8528</v>
+        <v>7863</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>53.3</v>
+        <v>49.14375</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7744</v>
+        <v>5334</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>154.88</v>
+        <v>106.68</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31840</v>
+        <v>29829</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>636.8</v>
+        <v>596.58</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4688</v>
+        <v>5023</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>93.76</v>
+        <v>100.46</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21118</v>
+        <v>20348</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>131.9875</v>
+        <v>127.175</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29827</v>
+        <v>37437</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>186.41875</v>
+        <v>233.98125</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9157</v>
+        <v>20722</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>57.23125</v>
+        <v>129.5125</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33725</v>
+        <v>41871</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>210.78125</v>
+        <v>261.69375</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4917</v>
+        <v>4688</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>58.535714285714285</v>
+        <v>55.80952380952381</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8698</v>
+        <v>9862</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>173.96</v>
+        <v>197.24</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33339</v>
+        <v>33052</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>245.13970588235293</v>
+        <v>243.02941176470588</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12445</v>
+        <v>12236</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>77.78125</v>
+        <v>76.475</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3366</v>
+        <v>3226</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>21.0375</v>
+        <v>20.1625</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>448867</v>
+        <v>517798</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4837.0404201680685</v>
+        <v>5548.320986856283</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46304</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>4133-1+24880+30400</f>
-        <v>59412</v>
+        <f>50004-1+15144+15077</f>
+        <v>80224</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>59412</v>
+        <v>80224</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-8204</v>
+        <v>-29016</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>79012</v>
+        <v>99824</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>742.65</v>
+        <v>1002.8</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>9</v>
+        <f>13849+14166</f>
+        <v>28015</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>28015</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>195</v>
+        <v>-27811</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>9</v>
+        <v>28015</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>0.1125</v>
+        <v>350.1875</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>9864+24592</f>
-        <v>34456</v>
+        <f>26593+5084</f>
+        <v>31677</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>11040</v>
+        <v>8261</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-26007</v>
+        <v>-23228</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>16160</v>
+        <v>13381</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>430.7</v>
+        <v>395.9625</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5728,8 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>57+8080</f>
-        <v>8137</v>
+        <f>5195+16153</f>
+        <v>21348</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>4661</v>
+        <v>17872</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>1220</v>
+        <v>-11991</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>5301</v>
+        <v>18512</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>101.7125</v>
+        <v>266.85</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>7538</v>
+        <v>7198</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>7537</v>
+        <v>7197</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-7013</v>
+        <v>-6673</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>7537</v>
+        <v>7197</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>94.225</v>
+        <v>89.975</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>15.7</v>
+        <v>15</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6076,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>33466</v>
+        <v>31354</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>33466</v>
+        <v>31354</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-33466</v>
+        <v>-31354</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>33466</v>
+        <v>31354</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>418.325</v>
+        <v>391.925</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,8 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <f>3625+2825</f>
-        <v>6450</v>
+        <v>6355</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-44480</v>
+        <v>-44575</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-6450</v>
+        <v>-6355</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-44480</v>
+        <v>-44575</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>80.625</v>
+        <v>79.4375</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,8 +6247,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>7307+561</f>
-        <v>7868</v>
+        <v>3723</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-20442</v>
+        <v>-24587</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>125073</v>
+        <v>129218</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-17244</v>
+        <v>-21389</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>100.87179487179488</v>
+        <v>47.73076923076923</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6333,8 +6332,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>2672-1</f>
-        <v>2671</v>
+        <f>1765-1</f>
+        <v>1764</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-14880</v>
+        <v>-15787</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>49223</v>
+        <v>50130</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-12774</v>
+        <v>-13681</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>34.243589743589745</v>
+        <v>22.615384615384617</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,8 +6418,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="37">
-        <f>23488+1</f>
-        <v>23489</v>
+        <f>21891+1</f>
+        <v>21892</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6427,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>15644</v>
+        <v>14047</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6435,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-6027</v>
+        <v>-4430</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>18140</v>
+        <v>16543</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>301.14102564102564</v>
+        <v>280.6666666666667</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6483,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6505,8 +6504,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>39+1</f>
-        <v>40</v>
+        <f>0+1</f>
+        <v>1</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6513,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-23239</v>
+        <v>-23278</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6521,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>39557</v>
+        <v>39596</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-20587</v>
+        <v>-20626</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>0.5128205128205128</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6660,8 +6659,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <f>130+11856</f>
-        <v>11986</v>
+        <v>13782</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6669,7 +6667,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>11986</v>
+        <v>13782</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6677,15 +6675,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>38980</v>
+        <v>37184</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>12688</v>
+        <v>14484</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>153.66666666666666</v>
+        <v>176.69230769230768</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6709,7 +6707,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6938,8 +6936,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>4769-2</f>
-        <v>4767</v>
+        <f>2759-2</f>
+        <v>2757</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6947,7 +6945,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-43028</v>
+        <v>-45038</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6955,15 +6953,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>48591</v>
+        <v>50601</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-37748</v>
+        <v>-39758</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>29.79375</v>
+        <v>17.23125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7003,7 +7001,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7023,9 +7021,9 @@
         <v>160</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="33">
-        <f>222+5121</f>
-        <v>5343</v>
+      <c r="J45" s="40">
+        <f>5498-1+496</f>
+        <v>5993</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7033,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-5760</v>
+        <v>-5110</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7041,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>14765</v>
+        <v>14115</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-4800</v>
+        <v>-4150</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>33.39375</v>
+        <v>37.45625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7077,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7098,9 +7096,9 @@
         <v>160</v>
       </c>
       <c r="I46" s="32"/>
-      <c r="J46" s="33">
-        <f>15756+4608</f>
-        <v>20364</v>
+      <c r="J46" s="37">
+        <f>18114+1</f>
+        <v>18115</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7108,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>17402</v>
+        <v>15153</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7116,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-14120</v>
+        <v>-11871</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>19162</v>
+        <v>16913</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>127.275</v>
+        <v>113.21875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7148,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7238,8 +7236,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>13128+1</f>
-        <v>13129</v>
+        <f>11758+1</f>
+        <v>11759</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7247,7 +7245,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>13123</v>
+        <v>11753</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7255,15 +7253,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>17361</v>
+        <v>18731</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>16003</v>
+        <v>14633</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>82.05625</v>
+        <v>73.49375</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7287,7 +7285,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7480,7 +7478,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>8528</v>
+        <v>7863</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7492,7 +7490,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>53.3</v>
+        <v>49.14375</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7516,7 +7514,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8198,7 +8196,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>7744</v>
+        <v>5334</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8206,7 +8204,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-32886</v>
+        <v>-35296</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8214,15 +8212,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>44862</v>
+        <v>47272</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-26736</v>
+        <v>-29146</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>154.88</v>
+        <v>106.68</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8246,7 +8244,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8267,8 +8265,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>22084+9756</f>
-        <v>31840</v>
+        <v>29829</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8276,7 +8273,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>31840</v>
+        <v>29829</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8284,15 +8281,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>20766</v>
+        <v>22777</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>37990</v>
+        <v>35979</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>636.8</v>
+        <v>596.58</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8316,7 +8313,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8546,7 +8543,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>4688</v>
+        <v>5023</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8554,7 +8551,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>4688</v>
+        <v>5023</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8562,15 +8559,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>47918</v>
+        <v>47583</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>10838</v>
+        <v>11173</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>93.76</v>
+        <v>100.46</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8594,7 +8591,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8948,8 +8945,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>21116+2</f>
-        <v>21118</v>
+        <f>20346+2</f>
+        <v>20348</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8957,7 +8954,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>21118</v>
+        <v>20348</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8966,11 +8963,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>21118</v>
+        <v>20348</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>131.9875</v>
+        <v>127.175</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8994,7 +8991,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9015,8 +9012,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>29828-1</f>
-        <v>29827</v>
+        <f>37438-1</f>
+        <v>37437</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9024,7 +9021,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>29827</v>
+        <v>37437</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9033,11 +9030,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>29827</v>
+        <v>37437</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>186.41875</v>
+        <v>233.98125</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9061,7 +9058,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>7.8</v>
+        <v>9.7</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9082,8 +9079,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>9159-2</f>
-        <v>9157</v>
+        <f>20724-2</f>
+        <v>20722</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9091,7 +9088,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>9157</v>
+        <v>20722</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9100,11 +9097,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>9157</v>
+        <v>20722</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>57.23125</v>
+        <v>129.5125</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9128,7 +9125,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9149,7 +9146,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>33725</v>
+        <v>41871</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9157,7 +9154,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>33725</v>
+        <v>41871</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9166,11 +9163,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>33725</v>
+        <v>41871</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>210.78125</v>
+        <v>261.69375</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9194,7 +9191,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9479,7 +9476,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>4917</v>
+        <v>4688</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9487,7 +9484,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>4917</v>
+        <v>4688</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9496,11 +9493,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>4917</v>
+        <v>4688</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>58.535714285714285</v>
+        <v>55.80952380952381</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9545,7 +9542,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>8698</v>
+        <v>9862</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9557,7 +9554,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>173.96</v>
+        <v>197.24</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9581,7 +9578,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,7 +9599,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>33339</v>
+        <v>33052</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9614,7 +9611,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>245.13970588235293</v>
+        <v>243.02941176470588</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9638,7 +9635,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9830,7 +9827,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>12445</v>
+        <v>12236</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9842,7 +9839,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>77.78125</v>
+        <v>76.475</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9866,7 +9863,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9887,7 +9884,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3366</v>
+        <v>3226</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9899,7 +9896,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>21.0375</v>
+        <v>20.1625</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10088,26 +10085,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>448867</v>
+        <v>517798</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>125184</v>
+        <v>194252</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>767969</v>
+        <v>725223</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>223156</v>
+        <v>292224</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4837.0404201680685</v>
+        <v>5548.320986856283</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>80224</v>
+        <v>132808</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1002.8</v>
+        <v>1660.1</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28015</v>
+        <v>51465</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>350.1875</v>
+        <v>643.3125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31677</v>
+        <v>22608</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>395.9625</v>
+        <v>282.6</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21348</v>
+        <v>34750</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>266.85</v>
+        <v>434.375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7198</v>
+        <v>7018</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>89.975</v>
+        <v>87.725</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31354</v>
+        <v>29174</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>391.925</v>
+        <v>364.675</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6355</v>
+        <v>6163</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>79.4375</v>
+        <v>77.0375</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3723</v>
+        <v>34504</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>47.73076923076923</v>
+        <v>442.35897435897436</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1764</v>
+        <v>1218</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>22.615384615384617</v>
+        <v>15.615384615384615</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21892</v>
+        <v>16912</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>280.6666666666667</v>
+        <v>216.82051282051282</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13782</v>
+        <v>13158</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>176.69230769230768</v>
+        <v>168.69230769230768</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>0.5512820512820513</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2757</v>
+        <v>23157</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>17.23125</v>
+        <v>144.73125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5993</v>
+        <v>5533</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>37.45625</v>
+        <v>34.58125</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18115</v>
+        <v>16455</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>113.21875</v>
+        <v>102.84375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11759</v>
+        <v>9959</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>73.49375</v>
+        <v>62.24375</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7863</v>
+        <v>7543</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>49.14375</v>
+        <v>47.14375</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5334</v>
+        <v>20564</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>106.68</v>
+        <v>411.28</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29829</v>
+        <v>26444</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>596.58</v>
+        <v>528.88</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5023</v>
+        <v>7260</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>100.46</v>
+        <v>145.2</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32</v>
+        <v>10833</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>0.64</v>
+        <v>216.66</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20348</v>
+        <v>24388</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>127.175</v>
+        <v>152.425</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>37437</v>
+        <v>34772</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>233.98125</v>
+        <v>217.325</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>9.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20722</v>
+        <v>18287</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>129.5125</v>
+        <v>114.29375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>41871</v>
+        <v>39687</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>261.69375</v>
+        <v>248.04375</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4688</v>
+        <v>4608</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>55.80952380952381</v>
+        <v>54.857142857142854</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9862</v>
+        <v>13752</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>197.24</v>
+        <v>275.04</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>14.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>33052</v>
+        <v>32957</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>243.02941176470588</v>
+        <v>242.3308823529412</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12236</v>
+        <v>12126</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>76.475</v>
+        <v>75.7875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>517798</v>
+        <v>661609</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5548.320986856283</v>
+        <v>7490.137127774186</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46306</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>50004-1+15144+15077</f>
-        <v>80224</v>
+        <f>85209-1+22320+25280</f>
+        <v>132808</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>80224</v>
+        <v>132808</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-29016</v>
+        <v>-81600</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>99824</v>
+        <v>152408</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1002.8</v>
+        <v>1660.1</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>13849+14166</f>
-        <v>28015</v>
+        <f>36985+14480</f>
+        <v>51465</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>28015</v>
+        <v>51465</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-27811</v>
+        <v>-51261</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>28015</v>
+        <v>51465</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>350.1875</v>
+        <v>643.3125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>26593+5084</f>
-        <v>31677</v>
+        <v>22608</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>8261</v>
+        <v>-808</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-23228</v>
+        <v>-14159</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>13381</v>
+        <v>4312</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>395.9625</v>
+        <v>282.6</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5514,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5729,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>5195+16153</f>
-        <v>21348</v>
+        <f>19390+15360</f>
+        <v>34750</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>17872</v>
+        <v>31274</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-11991</v>
+        <v>-25393</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>18512</v>
+        <v>31914</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>266.85</v>
+        <v>434.375</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>7198</v>
+        <v>7018</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>7197</v>
+        <v>7017</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-6673</v>
+        <v>-6493</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>7197</v>
+        <v>7017</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>89.975</v>
+        <v>87.725</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>31354</v>
+        <v>29174</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>31354</v>
+        <v>29174</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-31354</v>
+        <v>-29174</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>31354</v>
+        <v>29174</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>391.925</v>
+        <v>364.675</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>6355</v>
+        <v>6163</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-44575</v>
+        <v>-44767</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-6355</v>
+        <v>-6163</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-44575</v>
+        <v>-44767</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>79.4375</v>
+        <v>77.0375</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,7 +6246,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>3723</v>
+        <f>15160+19344</f>
+        <v>34504</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-24587</v>
+        <v>6194</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6263,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>129218</v>
+        <v>98437</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-21389</v>
+        <v>9392</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>47.73076923076923</v>
+        <v>442.35897435897436</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6332,8 +6332,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>1765-1</f>
-        <v>1764</v>
+        <f>1219-1</f>
+        <v>1218</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-15787</v>
+        <v>-16333</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6349,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>50130</v>
+        <v>50676</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-13681</v>
+        <v>-14227</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>22.615384615384617</v>
+        <v>15.615384615384615</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6418,8 +6418,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="37">
-        <f>21891+1</f>
-        <v>21892</v>
+        <f>16911+1</f>
+        <v>16912</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>14047</v>
+        <v>9067</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6435,15 +6435,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-4430</v>
+        <v>550</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>16543</v>
+        <v>11563</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>280.6666666666667</v>
+        <v>216.82051282051282</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>13782</v>
+        <v>13158</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>13782</v>
+        <v>13158</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>37184</v>
+        <v>37808</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>14484</v>
+        <v>13860</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>176.69230769230768</v>
+        <v>168.69230769230768</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6882,15 +6882,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>50923</v>
+        <v>50962</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>0.5512820512820513</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6936,8 +6936,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>2759-2</f>
-        <v>2757</v>
+        <f>9719-2+13440</f>
+        <v>23157</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-45038</v>
+        <v>-24638</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6953,15 +6953,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>50601</v>
+        <v>30201</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-39758</v>
+        <v>-19358</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>17.23125</v>
+        <v>144.73125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7022,8 +7022,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>5498-1+496</f>
-        <v>5993</v>
+        <f>5534-1</f>
+        <v>5533</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-5110</v>
+        <v>-5570</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7039,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>14115</v>
+        <v>14575</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-4150</v>
+        <v>-4610</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>37.45625</v>
+        <v>34.58125</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7097,8 +7097,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>18114+1</f>
-        <v>18115</v>
+        <f>16454+1</f>
+        <v>16455</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>15153</v>
+        <v>13493</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-11871</v>
+        <v>-10211</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>16913</v>
+        <v>15253</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>113.21875</v>
+        <v>102.84375</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,8 +7236,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>11758+1</f>
-        <v>11759</v>
+        <f>9958+1</f>
+        <v>9959</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>11753</v>
+        <v>9953</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7253,15 +7253,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>18731</v>
+        <v>20531</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>14633</v>
+        <v>12833</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>73.49375</v>
+        <v>62.24375</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>7863</v>
+        <v>7543</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7490,7 +7490,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>49.14375</v>
+        <v>47.14375</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8196,7 +8196,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>5334</v>
+        <f>10514+10050</f>
+        <v>20564</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8204,7 +8205,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-35296</v>
+        <v>-20066</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8212,15 +8213,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>47272</v>
+        <v>32042</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-29146</v>
+        <v>-13916</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>106.68</v>
+        <v>411.28</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8244,7 +8245,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8265,7 +8266,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>29829</v>
+        <v>26444</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8273,7 +8274,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>29829</v>
+        <v>26444</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8281,15 +8282,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>22777</v>
+        <v>26162</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>35979</v>
+        <v>32594</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>596.58</v>
+        <v>528.88</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8313,7 +8314,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8543,7 +8544,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>5023</v>
+        <v>7260</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8551,7 +8552,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>5023</v>
+        <v>7260</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8559,15 +8560,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>47583</v>
+        <v>45346</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>11173</v>
+        <v>13410</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>100.46</v>
+        <v>145.2</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8591,7 +8592,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8612,7 +8613,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>32</v>
+        <v>10833</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8620,7 +8621,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>10833</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8628,15 +8629,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52574</v>
+        <v>41773</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6182</v>
+        <v>16983</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>0.64</v>
+        <v>216.66</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8660,7 +8661,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8945,8 +8946,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>20346+2</f>
-        <v>20348</v>
+        <f>24386+2</f>
+        <v>24388</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8954,7 +8955,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>20348</v>
+        <v>24388</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8963,11 +8964,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>20348</v>
+        <v>24388</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>127.175</v>
+        <v>152.425</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8991,7 +8992,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9012,8 +9013,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>37438-1</f>
-        <v>37437</v>
+        <f>34773-1</f>
+        <v>34772</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9021,7 +9022,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>37437</v>
+        <v>34772</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9030,11 +9031,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>37437</v>
+        <v>34772</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>233.98125</v>
+        <v>217.325</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9058,7 +9059,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>9.7</v>
+        <v>9.1</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9079,8 +9080,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>20724-2</f>
-        <v>20722</v>
+        <f>18290-2-1</f>
+        <v>18287</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9088,7 +9089,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>20722</v>
+        <v>18287</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9097,11 +9098,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>20722</v>
+        <v>18287</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>129.5125</v>
+        <v>114.29375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9125,7 +9126,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9146,7 +9147,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>41871</v>
+        <v>39687</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9154,7 +9155,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>41871</v>
+        <v>39687</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9163,11 +9164,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>41871</v>
+        <v>39687</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>261.69375</v>
+        <v>248.04375</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9191,7 +9192,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9476,7 +9477,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>4688</v>
+        <v>4608</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9484,7 +9485,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>4688</v>
+        <v>4608</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9493,11 +9494,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>4688</v>
+        <v>4608</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>55.80952380952381</v>
+        <v>54.857142857142854</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9542,7 +9543,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>9862</v>
+        <v>13752</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9554,7 +9555,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>197.24</v>
+        <v>275.04</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9578,7 +9579,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>14.1</v>
+        <v>19.6</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9599,7 +9600,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>33052</v>
+        <v>32957</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9611,7 +9612,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>243.02941176470588</v>
+        <v>242.3308823529412</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9827,7 +9828,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>12236</v>
+        <v>12126</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9839,7 +9840,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>76.475</v>
+        <v>75.7875</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9863,7 +9864,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -10085,26 +10086,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>517798</v>
+        <v>661609</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>194252</v>
+        <v>334698</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>725223</v>
+        <v>581453</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>292224</v>
+        <v>432670</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5548.320986856283</v>
+        <v>7490.137127774186</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>132808</v>
+        <v>152008</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1660.1</v>
+        <v>1900.1</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>51465</v>
+        <v>55065</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>643.3125</v>
+        <v>688.3125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22608</v>
+        <v>27408</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>282.6</v>
+        <v>342.6</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>193</v>
+        <v>4193</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>2.4125</v>
+        <v>52.4125</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34750</v>
+        <v>37774</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>434.375</v>
+        <v>472.175</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1</v>
+        <v>3121</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>0.01282051282051282</v>
+        <v>40.01282051282051</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23157</v>
+        <v>27637</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>144.73125</v>
+        <v>172.73125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20564</v>
+        <v>25564</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>411.28</v>
+        <v>511.28</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>661609</v>
+        <v>708833</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>7490.137127774186</v>
+        <v>8090.937127774187</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>85209-1+22320+25280</f>
-        <v>132808</v>
+        <f>85209-1+22320+25280+9600+9600</f>
+        <v>152008</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>132808</v>
+        <v>152008</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-81600</v>
+        <v>-100800</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>152408</v>
+        <v>171608</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1660.1</v>
+        <v>1900.1</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>36985+14480</f>
-        <v>51465</v>
+        <f>36985+14480+3600</f>
+        <v>55065</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>51465</v>
+        <v>55065</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-51261</v>
+        <v>-54861</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>51465</v>
+        <v>55065</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>643.3125</v>
+        <v>688.3125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>22608</v>
+        <f>22608+4800</f>
+        <v>27408</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-808</v>
+        <v>3992</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-14159</v>
+        <v>-18959</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>4312</v>
+        <v>9112</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>282.6</v>
+        <v>342.6</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5535,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>193</v>
+        <f>193+1600+2400</f>
+        <v>4193</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5544,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>4190</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5552,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>5412</v>
+        <v>1412</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>4910</v>
+        <v>8910</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>2.4125</v>
+        <v>52.4125</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5612,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5730,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>19390+15360</f>
-        <v>34750</v>
+        <f>19390+15360+3024</f>
+        <v>37774</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5739,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>31274</v>
+        <v>34298</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5747,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-25393</v>
+        <v>-28417</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>31914</v>
+        <v>34938</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>434.375</v>
+        <v>472.175</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5807,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6504,8 +6506,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>0+1</f>
-        <v>1</v>
+        <f>0+1+3120</f>
+        <v>3121</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6513,7 +6515,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-23278</v>
+        <v>-20158</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6521,15 +6523,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>39596</v>
+        <v>36476</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-20626</v>
+        <v>-17506</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>0.01282051282051282</v>
+        <v>40.01282051282051</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6569,7 +6571,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6936,8 +6938,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>9719-2+13440</f>
-        <v>23157</v>
+        <f>9719-2+13440+4480</f>
+        <v>27637</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6945,7 +6947,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-24638</v>
+        <v>-20158</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6953,15 +6955,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>30201</v>
+        <v>25721</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-19358</v>
+        <v>-14878</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>144.73125</v>
+        <v>172.73125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7001,7 +7003,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -8196,8 +8198,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>10514+10050</f>
-        <v>20564</v>
+        <f>10514+10050+5000</f>
+        <v>25564</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8205,7 +8207,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-20066</v>
+        <v>-15066</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8213,15 +8215,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>32042</v>
+        <v>27042</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-13916</v>
+        <v>-8916</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>411.28</v>
+        <v>511.28</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8245,7 +8247,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -9220,7 +9222,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10086,26 +10088,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>661609</v>
+        <v>708833</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>334698</v>
+        <v>381922</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>581453</v>
+        <v>534229</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>432670</v>
+        <v>479894</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>7490.137127774186</v>
+        <v>8090.937127774187</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>152008</v>
+        <v>146371</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1900.1</v>
+        <v>1829.6375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>55065</v>
+        <v>44814</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>688.3125</v>
+        <v>560.175</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27408</v>
+        <v>26012</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>342.6</v>
+        <v>325.15</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4193</v>
+        <v>22667</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>52.4125</v>
+        <v>283.3375</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>37774</v>
+        <v>17758</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>472.175</v>
+        <v>221.975</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7018</v>
+        <v>6628</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>87.725</v>
+        <v>82.85</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29174</v>
+        <v>23343</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>364.675</v>
+        <v>291.7875</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6163</v>
+        <v>5658</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>77.0375</v>
+        <v>70.725</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34504</v>
+        <v>23595</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>442.35897435897436</v>
+        <v>302.5</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1218</v>
+        <v>339</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>15.615384615384615</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16912</v>
+        <v>11882</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>216.82051282051282</v>
+        <v>152.33333333333334</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3121</v>
+        <v>7838</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>40.01282051282051</v>
+        <v>100.48717948717949</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13158</v>
+        <v>18859</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>168.69230769230768</v>
+        <v>241.78205128205127</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>24.1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27637</v>
+        <v>24530</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>172.73125</v>
+        <v>153.3125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5533</v>
+        <v>4958</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>34.58125</v>
+        <v>30.9875</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16455</v>
+        <v>13745</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>102.84375</v>
+        <v>85.90625</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9959</v>
+        <v>5229</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>62.24375</v>
+        <v>32.68125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7543</v>
+        <v>6378</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>47.14375</v>
+        <v>39.8625</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25564</v>
+        <v>29812</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>511.28</v>
+        <v>596.24</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26444</v>
+        <v>19259</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>528.88</v>
+        <v>385.18</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7260</v>
+        <v>3143</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>145.2</v>
+        <v>62.86</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10833</v>
+        <v>7030</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>216.66</v>
+        <v>140.6</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24388</v>
+        <v>20743</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>152.425</v>
+        <v>129.64375</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34772</v>
+        <v>31837</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>217.325</v>
+        <v>198.98125</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>9.1</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18287</v>
+        <v>12922</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>114.29375</v>
+        <v>80.7625</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39687</v>
+        <v>32967</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>248.04375</v>
+        <v>206.04375</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4608</v>
+        <v>4114</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>54.857142857142854</v>
+        <v>48.976190476190474</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13752</v>
+        <v>13254</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>275.04</v>
+        <v>265.08</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>19.6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32957</v>
+        <v>32197</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>242.3308823529412</v>
+        <v>236.74264705882354</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12126</v>
+        <v>11933</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>75.7875</v>
+        <v>74.58125</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3226</v>
+        <v>3181</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>20.1625</v>
+        <v>19.88125</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>708833</v>
+        <v>633082</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>8090.937127774187</v>
+        <v>7255.979158047835</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>85209-1+22320+25280+9600+9600</f>
-        <v>152008</v>
+        <f>111764-1+16560+18048</f>
+        <v>146371</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>152008</v>
+        <v>146371</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-100800</v>
+        <v>-95163</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>171608</v>
+        <v>165971</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1900.1</v>
+        <v>1829.6375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>36985+14480+3600</f>
-        <v>55065</v>
+        <v>44814</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>55065</v>
+        <v>44814</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-54861</v>
+        <v>-44610</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>55065</v>
+        <v>44814</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>688.3125</v>
+        <v>560.175</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>22608+4800</f>
-        <v>27408</v>
+        <f>11452+14560</f>
+        <v>26012</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>3992</v>
+        <v>2596</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-18959</v>
+        <v>-17563</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>9112</v>
+        <v>7716</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>342.6</v>
+        <v>325.15</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5535,8 +5534,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>193+1600+2400</f>
-        <v>4193</v>
+        <f>6987+15680</f>
+        <v>22667</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5544,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>4190</v>
+        <v>22664</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5552,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>1412</v>
+        <v>-17062</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>8910</v>
+        <v>27384</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>52.4125</v>
+        <v>283.3375</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5612,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5730,8 +5729,7 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>19390+15360+3024</f>
-        <v>37774</v>
+        <v>17758</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5739,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>34298</v>
+        <v>14282</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5747,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-28417</v>
+        <v>-8401</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>34938</v>
+        <v>14922</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>472.175</v>
+        <v>221.975</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5807,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5910,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>7018</v>
+        <v>6628</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5918,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>7017</v>
+        <v>6627</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5926,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-6493</v>
+        <v>-6103</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>7017</v>
+        <v>6627</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>87.725</v>
+        <v>82.85</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5974,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6077,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>29174</v>
+        <v>23343</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6085,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>29174</v>
+        <v>23343</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6093,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-29174</v>
+        <v>-23343</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>29174</v>
+        <v>23343</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>364.675</v>
+        <v>291.7875</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6141,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6163,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>6163</v>
+        <v>5658</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6171,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-44767</v>
+        <v>-45272</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6179,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-6163</v>
+        <v>-5658</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-44767</v>
+        <v>-45272</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>77.0375</v>
+        <v>70.725</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6227,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6248,8 +6246,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <f>15160+19344</f>
-        <v>34504</v>
+        <v>23595</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6257,7 +6254,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>6194</v>
+        <v>-4715</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6265,15 +6262,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>98437</v>
+        <v>109346</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>9392</v>
+        <v>-1517</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>442.35897435897436</v>
+        <v>302.5</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6313,7 +6310,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6334,8 +6331,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>1219-1</f>
-        <v>1218</v>
+        <f>340-1</f>
+        <v>339</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6343,7 +6340,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-16333</v>
+        <v>-17212</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6351,15 +6348,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>50676</v>
+        <v>51555</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-14227</v>
+        <v>-15106</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>15.615384615384615</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6399,7 +6396,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,9 +6416,8 @@
         <v>78</v>
       </c>
       <c r="I37" s="32"/>
-      <c r="J37" s="37">
-        <f>16911+1</f>
-        <v>16912</v>
+      <c r="J37" s="33">
+        <v>11882</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6429,7 +6425,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>9067</v>
+        <v>4037</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6437,15 +6433,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>550</v>
+        <v>5580</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>11563</v>
+        <v>6533</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>216.82051282051282</v>
+        <v>152.33333333333334</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6485,7 +6481,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6506,8 +6502,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>0+1+3120</f>
-        <v>3121</v>
+        <f>7447+1+390</f>
+        <v>7838</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6515,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-20158</v>
+        <v>-15441</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6523,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>36476</v>
+        <v>31759</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-17506</v>
+        <v>-12789</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>40.01282051282051</v>
+        <v>100.48717948717949</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6571,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6661,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>13158</v>
+        <v>18859</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6669,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>13158</v>
+        <v>18859</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6677,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>37808</v>
+        <v>32107</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>13860</v>
+        <v>19561</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>168.69230769230768</v>
+        <v>241.78205128205127</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6709,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>24.1</v>
+        <v>34.5</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6938,8 +6934,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>9719-2+13440+4480</f>
-        <v>27637</v>
+        <f>24532-2</f>
+        <v>24530</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6947,7 +6943,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-20158</v>
+        <v>-23265</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6955,15 +6951,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>25721</v>
+        <v>28828</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-14878</v>
+        <v>-17985</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>172.73125</v>
+        <v>153.3125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7003,7 +6999,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7024,8 +7020,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>5534-1</f>
-        <v>5533</v>
+        <f>4959-1</f>
+        <v>4958</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7033,7 +7029,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-5570</v>
+        <v>-6145</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7041,15 +7037,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>14575</v>
+        <v>15150</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-4610</v>
+        <v>-5185</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>34.58125</v>
+        <v>30.9875</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7077,7 +7073,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7099,8 +7095,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>16454+1</f>
-        <v>16455</v>
+        <f>13744+1</f>
+        <v>13745</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7108,7 +7104,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>13493</v>
+        <v>10783</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7116,15 +7112,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-10211</v>
+        <v>-7501</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>15253</v>
+        <v>12543</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>102.84375</v>
+        <v>85.90625</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7148,7 +7144,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7238,8 +7234,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>9958+1</f>
-        <v>9959</v>
+        <f>5228+1</f>
+        <v>5229</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7247,7 +7243,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>9953</v>
+        <v>5223</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7255,15 +7251,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>20531</v>
+        <v>25261</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>12833</v>
+        <v>8103</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>62.24375</v>
+        <v>32.68125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7287,7 +7283,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7480,7 +7476,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>7543</v>
+        <v>6378</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7492,7 +7488,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>47.14375</v>
+        <v>39.8625</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7516,7 +7512,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8198,8 +8194,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>10514+10050+5000</f>
-        <v>25564</v>
+        <f>23662+6150</f>
+        <v>29812</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8207,7 +8203,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-15066</v>
+        <v>-10818</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8215,15 +8211,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>27042</v>
+        <v>22794</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-8916</v>
+        <v>-4668</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>511.28</v>
+        <v>596.24</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8247,7 +8243,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8268,7 +8264,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>26444</v>
+        <v>19259</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8276,7 +8272,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>26444</v>
+        <v>19259</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8284,15 +8280,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>26162</v>
+        <v>33347</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>32594</v>
+        <v>25409</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>528.88</v>
+        <v>385.18</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8316,7 +8312,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8546,7 +8542,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>7260</v>
+        <v>3143</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8554,7 +8550,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>7260</v>
+        <v>3143</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8562,15 +8558,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>45346</v>
+        <v>49463</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>13410</v>
+        <v>9293</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>145.2</v>
+        <v>62.86</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8594,7 +8590,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8614,8 +8610,9 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="33">
-        <v>10833</v>
+      <c r="J69" s="40">
+        <f>7031-1</f>
+        <v>7030</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8623,7 +8620,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>10833</v>
+        <v>7030</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8631,15 +8628,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>41773</v>
+        <v>45576</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>16983</v>
+        <v>13180</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>216.66</v>
+        <v>140.6</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8663,7 +8660,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8948,8 +8945,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>24386+2</f>
-        <v>24388</v>
+        <f>20741+2</f>
+        <v>20743</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8957,7 +8954,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>24388</v>
+        <v>20743</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8966,11 +8963,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>24388</v>
+        <v>20743</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>152.425</v>
+        <v>129.64375</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8994,7 +8991,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9015,8 +9012,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>34773-1</f>
-        <v>34772</v>
+        <f>31838-1</f>
+        <v>31837</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9024,7 +9021,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>34772</v>
+        <v>31837</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9033,11 +9030,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>34772</v>
+        <v>31837</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>217.325</v>
+        <v>198.98125</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9061,7 +9058,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>9.1</v>
+        <v>8.3</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9082,8 +9079,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>18290-2-1</f>
-        <v>18287</v>
+        <f>12925-2-1</f>
+        <v>12922</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9091,7 +9088,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>18287</v>
+        <v>12922</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9100,11 +9097,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>18287</v>
+        <v>12922</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>114.29375</v>
+        <v>80.7625</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9128,7 +9125,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9149,7 +9146,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>39687</v>
+        <v>32967</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9157,7 +9154,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>39687</v>
+        <v>32967</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9166,11 +9163,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>39687</v>
+        <v>32967</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>248.04375</v>
+        <v>206.04375</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9194,7 +9191,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>16.5</v>
+        <v>13.7</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9222,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9479,7 +9476,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>4608</v>
+        <v>4114</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9487,7 +9484,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>4608</v>
+        <v>4114</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9496,11 +9493,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>4608</v>
+        <v>4114</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>54.857142857142854</v>
+        <v>48.976190476190474</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9545,7 +9542,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>13752</v>
+        <v>13254</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9557,7 +9554,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>275.04</v>
+        <v>265.08</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9581,7 +9578,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>19.6</v>
+        <v>18.9</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,7 +9599,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>32957</v>
+        <v>32197</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9614,7 +9611,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>242.3308823529412</v>
+        <v>236.74264705882354</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9638,7 +9635,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>8.8</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9830,7 +9827,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>12126</v>
+        <v>11933</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9842,7 +9839,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>75.7875</v>
+        <v>74.58125</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9866,7 +9863,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9887,7 +9884,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3226</v>
+        <v>3181</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9899,7 +9896,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>20.1625</v>
+        <v>19.88125</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10088,26 +10085,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>708833</v>
+        <v>633082</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>381922</v>
+        <v>308832</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>534229</v>
+        <v>588160</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>479894</v>
+        <v>406804</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>8090.937127774187</v>
+        <v>7255.979158047835</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -417,7 +417,7 @@
     <t>USD 173.202,960</t>
   </si>
   <si>
-    <t>ACTUALIZADO    AGOSTO  2026</t>
+    <t>ACTUALIZADO    SEPTIEMBRE  2026</t>
   </si>
   <si>
     <t>GLUP! UVA  CAJA X 6BOT X 2.0LTS</t>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>146371</v>
+        <v>127083</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1829.6375</v>
+        <v>1588.5375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>44814</v>
+        <v>36155</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>560.175</v>
+        <v>451.9375</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26012</v>
+        <v>50078</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>325.15</v>
+        <v>625.975</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22667</v>
+        <v>44655</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>283.3375</v>
+        <v>558.1875</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17758</v>
+        <v>5463</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>221.975</v>
+        <v>68.2875</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6628</v>
+        <v>6127</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>82.85</v>
+        <v>76.5875</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23343</v>
+        <v>13032</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>291.7875</v>
+        <v>162.9</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5658</v>
+        <v>5573</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>70.725</v>
+        <v>69.6625</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23595</v>
+        <v>13743</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>302.5</v>
+        <v>176.19230769230768</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>339</v>
+        <v>128</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>4.346153846153846</v>
+        <v>1.641025641025641</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11882</v>
+        <v>6484</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>152.33333333333334</v>
+        <v>83.12820512820512</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7838</v>
+        <v>14050</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>100.48717948717949</v>
+        <v>180.12820512820514</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18859</v>
+        <v>17834</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>241.78205128205127</v>
+        <v>228.64102564102564</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4</v>
+        <v>2184</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>0.05128205128205128</v>
+        <v>28</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24530</v>
+        <v>17530</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>153.3125</v>
+        <v>109.5625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4958</v>
+        <v>4225</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>30.9875</v>
+        <v>26.40625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13745</v>
+        <v>10750</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>85.90625</v>
+        <v>67.1875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5229</v>
+        <v>2079</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>32.68125</v>
+        <v>12.99375</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6378</v>
+        <v>5550</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>39.8625</v>
+        <v>34.6875</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8.7</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29812</v>
+        <v>32184</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>596.24</v>
+        <v>643.68</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19259</v>
+        <v>12499</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>385.18</v>
+        <v>249.98</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3143</v>
+        <v>571</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>62.86</v>
+        <v>11.42</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7030</v>
+        <v>3540</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>140.6</v>
+        <v>70.8</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20743</v>
+        <v>16838</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>129.64375</v>
+        <v>105.2375</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>8.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31837</v>
+        <v>26836</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>198.98125</v>
+        <v>167.725</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>8.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12922</v>
+        <v>10447</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>80.7625</v>
+        <v>65.29375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32967</v>
+        <v>31202</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>206.04375</v>
+        <v>195.0125</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>13.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4114</v>
+        <v>3937</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>48.976190476190474</v>
+        <v>46.86904761904762</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13254</v>
+        <v>11562</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>265.08</v>
+        <v>231.24</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>18.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32197</v>
+        <v>31750</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>236.74264705882354</v>
+        <v>233.4558823529412</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>8.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11933</v>
+        <v>11827</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>74.58125</v>
+        <v>73.91875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>37.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3181</v>
+        <v>3163</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>19.88125</v>
+        <v>19.76875</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>633082</v>
+        <v>579161</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>7255.979158047835</v>
+        <v>6665.563519715579</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5236,9 +5236,9 @@
         <v>80</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="40">
-        <f>111764-1+16560+18048</f>
-        <v>146371</v>
+      <c r="J24" s="23">
+        <f>95003+12960+19120</f>
+        <v>127083</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>146371</v>
+        <v>127083</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-95163</v>
+        <v>-75875</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>165971</v>
+        <v>146683</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1829.6375</v>
+        <v>1588.5375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>44814</v>
+        <v>36155</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>44814</v>
+        <v>36155</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-44610</v>
+        <v>-35951</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>44814</v>
+        <v>36155</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>560.175</v>
+        <v>451.9375</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>11452+14560</f>
-        <v>26012</v>
+        <f>23118+26960</f>
+        <v>50078</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>2596</v>
+        <v>26662</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-17563</v>
+        <v>-41629</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>7716</v>
+        <v>31782</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>325.15</v>
+        <v>625.975</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,8 +5534,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>6987+15680</f>
-        <v>22667</v>
+        <f>32935+11720</f>
+        <v>44655</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>22664</v>
+        <v>44652</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-17062</v>
+        <v>-39050</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>27384</v>
+        <v>49372</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>283.3375</v>
+        <v>558.1875</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,7 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <v>17758</v>
+        <f>423+5040</f>
+        <v>5463</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>14282</v>
+        <v>1987</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-8401</v>
+        <v>3894</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>14922</v>
+        <v>2627</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>221.975</v>
+        <v>68.2875</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>6628</v>
+        <v>6127</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>6627</v>
+        <v>6126</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-6103</v>
+        <v>-5602</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>6627</v>
+        <v>6126</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>82.85</v>
+        <v>76.5875</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6076,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>23343</v>
+        <v>13032</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>23343</v>
+        <v>13032</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-23343</v>
+        <v>-13032</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>23343</v>
+        <v>13032</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>291.7875</v>
+        <v>162.9</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>5658</v>
+        <v>5573</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-45272</v>
+        <v>-45357</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-5658</v>
+        <v>-5573</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-45272</v>
+        <v>-45357</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>70.725</v>
+        <v>69.6625</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,7 +6247,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>23595</v>
+        <v>13743</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6254,7 +6255,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-4715</v>
+        <v>-14567</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6262,15 +6263,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>109346</v>
+        <v>119198</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-1517</v>
+        <v>-11369</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>302.5</v>
+        <v>176.19230769230768</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6310,7 +6311,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,8 +6332,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>340-1</f>
-        <v>339</v>
+        <f>129-1</f>
+        <v>128</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6340,7 +6341,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-17212</v>
+        <v>-17423</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6348,15 +6349,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>51555</v>
+        <v>51766</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-15106</v>
+        <v>-15317</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>4.346153846153846</v>
+        <v>1.641025641025641</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6396,7 +6397,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6416,8 +6417,9 @@
         <v>78</v>
       </c>
       <c r="I37" s="32"/>
-      <c r="J37" s="33">
-        <v>11882</v>
+      <c r="J37" s="40">
+        <f>6487-3</f>
+        <v>6484</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6425,7 +6427,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>4037</v>
+        <v>-1361</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6433,15 +6435,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>5580</v>
+        <v>10978</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>6533</v>
+        <v>1135</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>152.33333333333334</v>
+        <v>83.12820512820512</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6481,7 +6483,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6502,8 +6504,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>7447+1+390</f>
-        <v>7838</v>
+        <f>6639+1+7410</f>
+        <v>14050</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6513,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-15441</v>
+        <v>-9229</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6521,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>31759</v>
+        <v>25547</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-12789</v>
+        <v>-6577</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>100.48717948717949</v>
+        <v>180.12820512820514</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6569,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6657,7 +6659,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>18859</v>
+        <v>17834</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6665,7 +6667,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>18859</v>
+        <v>17834</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6673,15 +6675,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>32107</v>
+        <v>33132</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>19561</v>
+        <v>18536</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>241.78205128205127</v>
+        <v>228.64102564102564</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6705,7 +6707,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>34.5</v>
+        <v>32.7</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6864,7 +6866,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>4</v>
+        <v>2184</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6872,7 +6874,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>4</v>
+        <v>2184</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6880,15 +6882,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>50962</v>
+        <v>48782</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>706</v>
+        <v>2886</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>0.05128205128205128</v>
+        <v>28</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6912,7 +6914,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6934,8 +6936,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>24532-2</f>
-        <v>24530</v>
+        <f>17532-2</f>
+        <v>17530</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6943,7 +6945,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-23265</v>
+        <v>-30265</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6951,15 +6953,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>28828</v>
+        <v>35828</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-17985</v>
+        <v>-24985</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>153.3125</v>
+        <v>109.5625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6999,7 +7001,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7020,8 +7022,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>4959-1</f>
-        <v>4958</v>
+        <f>4226-1</f>
+        <v>4225</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7029,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-6145</v>
+        <v>-6878</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7037,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>15150</v>
+        <v>15883</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-5185</v>
+        <v>-5918</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>30.9875</v>
+        <v>26.40625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7073,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7095,8 +7097,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>13744+1</f>
-        <v>13745</v>
+        <f>10749+1</f>
+        <v>10750</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7104,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>10783</v>
+        <v>7788</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7112,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-7501</v>
+        <v>-4506</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>12543</v>
+        <v>9548</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>85.90625</v>
+        <v>67.1875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7144,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7234,8 +7236,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>5228+1</f>
-        <v>5229</v>
+        <f>2078+1</f>
+        <v>2079</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7243,7 +7245,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>5223</v>
+        <v>2073</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7251,15 +7253,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>25261</v>
+        <v>28411</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>8103</v>
+        <v>4953</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>32.68125</v>
+        <v>12.99375</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7283,7 +7285,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7476,7 +7478,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>6378</v>
+        <v>5550</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7488,7 +7490,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>39.8625</v>
+        <v>34.6875</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7512,7 +7514,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>8.7</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8194,8 +8196,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>23662+6150</f>
-        <v>29812</v>
+        <f>25606+6578</f>
+        <v>32184</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8203,7 +8205,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-10818</v>
+        <v>-8446</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8211,15 +8213,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>22794</v>
+        <v>20422</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-4668</v>
+        <v>-2296</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>596.24</v>
+        <v>643.68</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8243,7 +8245,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8264,7 +8266,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>19259</v>
+        <v>12499</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8272,7 +8274,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>19259</v>
+        <v>12499</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8280,15 +8282,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>33347</v>
+        <v>40107</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>25409</v>
+        <v>18649</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>385.18</v>
+        <v>249.98</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8312,7 +8314,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8542,7 +8544,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>3143</v>
+        <v>571</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8550,7 +8552,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>3143</v>
+        <v>571</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8558,15 +8560,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>49463</v>
+        <v>52035</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>9293</v>
+        <v>6721</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>62.86</v>
+        <v>11.42</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8590,7 +8592,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8611,8 +8613,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="40">
-        <f>7031-1</f>
-        <v>7030</v>
+        <f>3541-1</f>
+        <v>3540</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8620,7 +8622,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>7030</v>
+        <v>3540</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8628,15 +8630,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>45576</v>
+        <v>49066</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>13180</v>
+        <v>9690</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>140.6</v>
+        <v>70.8</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8660,7 +8662,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8945,8 +8947,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>20741+2</f>
-        <v>20743</v>
+        <f>16836+2</f>
+        <v>16838</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8954,7 +8956,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>20743</v>
+        <v>16838</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8963,11 +8965,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>20743</v>
+        <v>16838</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>129.64375</v>
+        <v>105.2375</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8991,7 +8993,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9012,8 +9014,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>31838-1</f>
-        <v>31837</v>
+        <f>26838-1-1</f>
+        <v>26836</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9021,7 +9023,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>31837</v>
+        <v>26836</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9030,11 +9032,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>31837</v>
+        <v>26836</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>198.98125</v>
+        <v>167.725</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9058,7 +9060,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>8.3</v>
+        <v>7</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9079,8 +9081,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>12925-2-1</f>
-        <v>12922</v>
+        <f>10450-2-1</f>
+        <v>10447</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9088,7 +9090,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>12922</v>
+        <v>10447</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9097,11 +9099,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>12922</v>
+        <v>10447</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>80.7625</v>
+        <v>65.29375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9125,7 +9127,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9146,7 +9148,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>32967</v>
+        <v>31202</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9154,7 +9156,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>32967</v>
+        <v>31202</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9163,11 +9165,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>32967</v>
+        <v>31202</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>206.04375</v>
+        <v>195.0125</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9191,7 +9193,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9475,8 +9477,9 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="65">
-        <v>4114</v>
+      <c r="J82" s="37">
+        <f>3936+1</f>
+        <v>3937</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9484,7 +9487,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>4114</v>
+        <v>3937</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9493,11 +9496,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>4114</v>
+        <v>3937</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>48.976190476190474</v>
+        <v>46.86904761904762</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9542,7 +9545,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>13254</v>
+        <v>11562</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9554,7 +9557,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>265.08</v>
+        <v>231.24</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9578,7 +9581,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>18.9</v>
+        <v>16.5</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9599,7 +9602,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>32197</v>
+        <v>31750</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9611,7 +9614,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>236.74264705882354</v>
+        <v>233.4558823529412</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9635,7 +9638,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>8.8</v>
+        <v>8.6</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9827,7 +9830,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>11933</v>
+        <v>11827</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9839,7 +9842,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>74.58125</v>
+        <v>73.91875</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9863,7 +9866,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9884,7 +9887,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3181</v>
+        <v>3163</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9896,7 +9899,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>19.88125</v>
+        <v>19.76875</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10085,26 +10088,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>633082</v>
+        <v>579161</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>308832</v>
+        <v>258002</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>588160</v>
+        <v>625667</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>406804</v>
+        <v>355974</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>7255.979158047835</v>
+        <v>6665.563519715579</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>127083</v>
+        <v>88048</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1588.5375</v>
+        <v>1100.6</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>36155</v>
+        <v>25251</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>451.9375</v>
+        <v>315.6375</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>50078</v>
+        <v>59447</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>625.975</v>
+        <v>743.0875</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>44655</v>
+        <v>39578</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>558.1875</v>
+        <v>494.725</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5463</v>
+        <v>15396</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>68.2875</v>
+        <v>192.45</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6127</v>
+        <v>5398</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>76.5875</v>
+        <v>67.475</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13032</v>
+        <v>6696</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>162.9</v>
+        <v>83.7</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5573</v>
+        <v>5377</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>69.6625</v>
+        <v>67.2125</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13743</v>
+        <v>2884</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>176.19230769230768</v>
+        <v>36.97435897435897</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>1.641025641025641</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6484</v>
+        <v>605</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>83.12820512820512</v>
+        <v>7.756410256410256</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14050</v>
+        <v>19098</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>180.12820512820514</v>
+        <v>244.84615384615384</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17834</v>
+        <v>16541</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>228.64102564102564</v>
+        <v>212.06410256410257</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>32.7</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2184</v>
+        <v>6630</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>17530</v>
+        <v>10210</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>109.5625</v>
+        <v>63.8125</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4225</v>
+        <v>3100</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>26.40625</v>
+        <v>19.375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10750</v>
+        <v>7415</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>67.1875</v>
+        <v>46.34375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2079</v>
+        <v>204</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>12.99375</v>
+        <v>1.275</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5550</v>
+        <v>5010</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>34.6875</v>
+        <v>31.3125</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>8.7</v>
+        <v>7.8</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32184</v>
+        <v>26765</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>643.68</v>
+        <v>535.3</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12499</v>
+        <v>6317</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>249.98</v>
+        <v>126.34</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>571</v>
+        <v>5184</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>11.42</v>
+        <v>103.68</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3540</v>
+        <v>78</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>70.8</v>
+        <v>1.56</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16838</v>
+        <v>14676</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>105.2375</v>
+        <v>91.725</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26836</v>
+        <v>22814</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>167.725</v>
+        <v>142.5875</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10447</v>
+        <v>7420</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>65.29375</v>
+        <v>46.375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31202</v>
+        <v>39505</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>195.0125</v>
+        <v>246.90625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3937</v>
+        <v>3877</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>46.86904761904762</v>
+        <v>46.154761904761905</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11562</v>
+        <v>10853</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>231.24</v>
+        <v>217.06</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31750</v>
+        <v>31709</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>233.4558823529412</v>
+        <v>233.15441176470588</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11827</v>
+        <v>11560</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>73.91875</v>
+        <v>72.25</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3163</v>
+        <v>3126</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>19.76875</v>
+        <v>19.5375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>579161</v>
+        <v>500860</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>6665.563519715579</v>
+        <v>5696.873692900238</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>95003+12960+19120</f>
-        <v>127083</v>
+        <f>67408+7360+13280</f>
+        <v>88048</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>127083</v>
+        <v>88048</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-75875</v>
+        <v>-36840</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>146683</v>
+        <v>107648</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1588.5375</v>
+        <v>1100.6</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>36155</v>
+        <v>25251</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>36155</v>
+        <v>25251</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-35951</v>
+        <v>-25047</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>36155</v>
+        <v>25251</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>451.9375</v>
+        <v>315.6375</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>23118+26960</f>
-        <v>50078</v>
+        <f>41927+17520</f>
+        <v>59447</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>26662</v>
+        <v>36031</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-41629</v>
+        <v>-50998</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>31782</v>
+        <v>41151</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>625.975</v>
+        <v>743.0875</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,8 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>32935+11720</f>
-        <v>44655</v>
+        <v>39578</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>44652</v>
+        <v>39575</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-39050</v>
+        <v>-33973</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>49372</v>
+        <v>44295</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>558.1875</v>
+        <v>494.725</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>423+5040</f>
-        <v>5463</v>
+        <f>1556+13840</f>
+        <v>15396</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>1987</v>
+        <v>11920</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>3894</v>
+        <v>-6039</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>2627</v>
+        <v>12560</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>68.2875</v>
+        <v>192.45</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>6127</v>
+        <v>5398</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>6126</v>
+        <v>5397</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-5602</v>
+        <v>-4873</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>6126</v>
+        <v>5397</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>76.5875</v>
+        <v>67.475</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6075,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>13032</v>
+        <v>6696</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6083,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>13032</v>
+        <v>6696</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6091,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-13032</v>
+        <v>-6696</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>13032</v>
+        <v>6696</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>162.9</v>
+        <v>83.7</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6139,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6161,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>5573</v>
+        <v>5377</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6169,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-45357</v>
+        <v>-45553</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6177,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-5573</v>
+        <v>-5377</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-45357</v>
+        <v>-45553</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>69.6625</v>
+        <v>67.2125</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6225,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,7 +6246,7 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>13743</v>
+        <v>2884</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6255,7 +6254,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-14567</v>
+        <v>-25426</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6263,15 +6262,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>119198</v>
+        <v>130057</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-11369</v>
+        <v>-22228</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>176.19230769230768</v>
+        <v>36.97435897435897</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6311,7 +6310,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6332,8 +6331,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>129-1</f>
-        <v>128</v>
+        <f>7-1</f>
+        <v>6</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6341,7 +6340,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-17423</v>
+        <v>-17545</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6349,15 +6348,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>51766</v>
+        <v>51888</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-15317</v>
+        <v>-15439</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>1.641025641025641</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6397,7 +6396,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6417,9 +6416,8 @@
         <v>78</v>
       </c>
       <c r="I37" s="32"/>
-      <c r="J37" s="40">
-        <f>6487-3</f>
-        <v>6484</v>
+      <c r="J37" s="33">
+        <v>605</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6427,7 +6425,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-1361</v>
+        <v>-7240</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6435,15 +6433,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>10978</v>
+        <v>16857</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>1135</v>
+        <v>-4744</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>83.12820512820512</v>
+        <v>7.756410256410256</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6483,7 +6481,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6504,8 +6502,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>6639+1+7410</f>
-        <v>14050</v>
+        <f>14075+1+5022</f>
+        <v>19098</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6513,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-9229</v>
+        <v>-4181</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6521,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>25547</v>
+        <v>20499</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-6577</v>
+        <v>-1529</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>180.12820512820514</v>
+        <v>244.84615384615384</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6569,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6659,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>17834</v>
+        <v>16541</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6667,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>17834</v>
+        <v>16541</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6675,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>33132</v>
+        <v>34425</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>18536</v>
+        <v>17243</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>228.64102564102564</v>
+        <v>212.06410256410257</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6707,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>32.7</v>
+        <v>30.3</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6866,7 +6864,8 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>2184</v>
+        <f>2028+4602</f>
+        <v>6630</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6874,7 +6873,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>2184</v>
+        <v>6630</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6882,15 +6881,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>48782</v>
+        <v>44336</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>2886</v>
+        <v>7332</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6914,7 +6913,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6936,8 +6935,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>17532-2</f>
-        <v>17530</v>
+        <f>10212-2</f>
+        <v>10210</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6945,7 +6944,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-30265</v>
+        <v>-37585</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6953,15 +6952,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>35828</v>
+        <v>43148</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-24985</v>
+        <v>-32305</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>109.5625</v>
+        <v>63.8125</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7001,7 +7000,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7022,8 +7021,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>4226-1</f>
-        <v>4225</v>
+        <f>3101-1</f>
+        <v>3100</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7031,7 +7030,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-6878</v>
+        <v>-8003</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7039,15 +7038,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>15883</v>
+        <v>17008</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-5918</v>
+        <v>-7043</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>26.40625</v>
+        <v>19.375</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7075,7 +7074,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7097,8 +7096,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>10749+1</f>
-        <v>10750</v>
+        <f>7414+1</f>
+        <v>7415</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7105,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>7788</v>
+        <v>4453</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7113,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-4506</v>
+        <v>-1171</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>9548</v>
+        <v>6213</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>67.1875</v>
+        <v>46.34375</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7145,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,8 +7235,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>2078+1</f>
-        <v>2079</v>
+        <f>203+1</f>
+        <v>204</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7245,7 +7244,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>2073</v>
+        <v>198</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7253,15 +7252,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>28411</v>
+        <v>30286</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>4953</v>
+        <v>3078</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>12.99375</v>
+        <v>1.275</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7285,7 +7284,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7478,7 +7477,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>5550</v>
+        <v>5010</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7490,7 +7489,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>34.6875</v>
+        <v>31.3125</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7514,7 +7513,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>8.7</v>
+        <v>7.8</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8196,8 +8195,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <f>25606+6578</f>
-        <v>32184</v>
+        <v>26765</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8205,7 +8203,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-8446</v>
+        <v>-13865</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8213,15 +8211,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>20422</v>
+        <v>25841</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-2296</v>
+        <v>-7715</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>643.68</v>
+        <v>535.3</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8245,7 +8243,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8266,7 +8264,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>12499</v>
+        <v>6317</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8274,7 +8272,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>12499</v>
+        <v>6317</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8282,15 +8280,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>40107</v>
+        <v>46289</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>18649</v>
+        <v>12467</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>249.98</v>
+        <v>126.34</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8314,7 +8312,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8544,7 +8542,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>571</v>
+        <v>5184</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8552,7 +8550,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>571</v>
+        <v>5184</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8560,15 +8558,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52035</v>
+        <v>47422</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6721</v>
+        <v>11334</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>11.42</v>
+        <v>103.68</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8592,7 +8590,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8613,8 +8611,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="40">
-        <f>3541-1</f>
-        <v>3540</v>
+        <f>79-1</f>
+        <v>78</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8622,7 +8620,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>3540</v>
+        <v>78</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8630,15 +8628,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>49066</v>
+        <v>52528</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>9690</v>
+        <v>6228</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>70.8</v>
+        <v>1.56</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8662,7 +8660,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8947,8 +8945,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>16836+2</f>
-        <v>16838</v>
+        <f>14674+2</f>
+        <v>14676</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8956,7 +8954,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>16838</v>
+        <v>14676</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8965,11 +8963,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>16838</v>
+        <v>14676</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>105.2375</v>
+        <v>91.725</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8993,7 +8991,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9014,8 +9012,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>26838-1-1</f>
-        <v>26836</v>
+        <f>22816-1-1</f>
+        <v>22814</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9023,7 +9021,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>26836</v>
+        <v>22814</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9032,11 +9030,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>26836</v>
+        <v>22814</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>167.725</v>
+        <v>142.5875</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9060,7 +9058,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9081,8 +9079,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>10450-2-1</f>
-        <v>10447</v>
+        <f>7423-2-1</f>
+        <v>7420</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9090,7 +9088,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>10447</v>
+        <v>7420</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9099,11 +9097,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>10447</v>
+        <v>7420</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>65.29375</v>
+        <v>46.375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9127,7 +9125,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9148,7 +9146,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>31202</v>
+        <v>39505</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9156,7 +9154,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>31202</v>
+        <v>39505</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9165,11 +9163,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>31202</v>
+        <v>39505</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>195.0125</v>
+        <v>246.90625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9193,7 +9191,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9477,9 +9475,8 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="37">
-        <f>3936+1</f>
-        <v>3937</v>
+      <c r="J82" s="33">
+        <v>3877</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9487,7 +9484,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>3937</v>
+        <v>3877</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9496,11 +9493,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>3937</v>
+        <v>3877</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>46.86904761904762</v>
+        <v>46.154761904761905</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9545,7 +9542,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>11562</v>
+        <v>10853</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9557,7 +9554,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>231.24</v>
+        <v>217.06</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9581,7 +9578,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,7 +9599,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>31750</v>
+        <v>31709</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9614,7 +9611,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>233.4558823529412</v>
+        <v>233.15441176470588</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9830,7 +9827,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>11827</v>
+        <v>11560</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9842,7 +9839,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>73.91875</v>
+        <v>72.25</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9866,7 +9863,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>36.1</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9887,7 +9884,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3163</v>
+        <v>3126</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9899,7 +9896,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>19.76875</v>
+        <v>19.5375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10088,26 +10085,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>579161</v>
+        <v>500860</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>258002</v>
+        <v>181295</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>625667</v>
+        <v>701406</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>355974</v>
+        <v>279267</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>6665.563519715579</v>
+        <v>5696.873692900238</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.47222222222262644</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>88048</v>
+        <v>99568</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1100.6</v>
+        <v>1244.6</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>59447</v>
+        <v>62787</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>743.0875</v>
+        <v>784.8375</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15396</v>
+        <v>18916</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>192.45</v>
+        <v>236.45</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6630</v>
+        <v>8970</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>500860</v>
+        <v>521580</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5696.873692900238</v>
+        <v>5956.623692900238</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.75</v>
+        <v>0.47222222222262644</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>67408+7360+13280</f>
-        <v>88048</v>
+        <f>67408+7360+13280+5440+6080</f>
+        <v>99568</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>88048</v>
+        <v>99568</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-36840</v>
+        <v>-48360</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>107648</v>
+        <v>119168</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1100.6</v>
+        <v>1244.6</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5436,8 +5436,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>41927+17520</f>
-        <v>59447</v>
+        <f>41927+17520+3340</f>
+        <v>62787</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>36031</v>
+        <v>39371</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-50998</v>
+        <v>-54338</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>41151</v>
+        <v>44491</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>743.0875</v>
+        <v>784.8375</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5728,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>1556+13840</f>
-        <v>15396</v>
+        <f>1556+13840+3520</f>
+        <v>18916</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>11920</v>
+        <v>15440</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-6039</v>
+        <v>-9559</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>12560</v>
+        <v>16080</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>192.45</v>
+        <v>236.45</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6864,8 +6864,8 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <f>2028+4602</f>
-        <v>6630</v>
+        <f>2028+4602+2340</f>
+        <v>8970</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>6630</v>
+        <v>8970</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6881,15 +6881,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>44336</v>
+        <v>41996</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>7332</v>
+        <v>9672</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -9219,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10085,26 +10085,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>500860</v>
+        <v>521580</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>181295</v>
+        <v>202015</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>701406</v>
+        <v>680686</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>279267</v>
+        <v>299987</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5696.873692900238</v>
+        <v>5956.623692900238</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46311</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.47222222222262644</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>99568</v>
+        <v>179748</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1244.6</v>
+        <v>2246.85</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25251</v>
+        <v>9025</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>315.6375</v>
+        <v>112.8125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>62787</v>
+        <v>32137</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>784.8375</v>
+        <v>401.7125</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39578</v>
+        <v>28273</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>494.725</v>
+        <v>353.4125</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18916</v>
+        <v>61507</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>236.45</v>
+        <v>768.8375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5398</v>
+        <v>4812</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>67.475</v>
+        <v>60.15</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>11.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6696</v>
+        <v>112</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>83.7</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5377</v>
+        <v>4995</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>67.2125</v>
+        <v>62.4375</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2884</v>
+        <v>13456</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>36.97435897435897</v>
+        <v>172.51282051282053</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6</v>
+        <v>26422</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>0.07692307692307693</v>
+        <v>338.7435897435897</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>605</v>
+        <v>6557</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>7.756410256410256</v>
+        <v>84.06410256410257</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19098</v>
+        <v>11855</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>244.84615384615384</v>
+        <v>151.98717948717947</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16541</v>
+        <v>13419</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>212.06410256410257</v>
+        <v>172.03846153846155</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>30.3</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8970</v>
+        <v>16369</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>115</v>
+        <v>209.85897435897436</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10210</v>
+        <v>1446</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>63.8125</v>
+        <v>9.0375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3100</v>
+        <v>2303</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>19.375</v>
+        <v>14.39375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7415</v>
+        <v>2360</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>46.34375</v>
+        <v>14.75</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>1.275</v>
+        <v>0.0125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5010</v>
+        <v>4125</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>31.3125</v>
+        <v>25.78125</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26765</v>
+        <v>18251</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>535.3</v>
+        <v>365.02</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6317</v>
+        <v>98</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>126.34</v>
+        <v>1.96</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5184</v>
+        <v>11389</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>103.68</v>
+        <v>227.78</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>2.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>1.56</v>
+        <v>0.56</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14676</v>
+        <v>10526</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>91.725</v>
+        <v>65.7875</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>22814</v>
+        <v>20519</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>142.5875</v>
+        <v>128.24375</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7420</v>
+        <v>1775</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>46.375</v>
+        <v>11.09375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>39505</v>
+        <v>34625</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>246.90625</v>
+        <v>216.40625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3877</v>
+        <v>2659</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>46.154761904761905</v>
+        <v>31.654761904761905</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10853</v>
+        <v>9827</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>217.06</v>
+        <v>196.54</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31709</v>
+        <v>31554</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>233.15441176470588</v>
+        <v>232.01470588235293</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11560</v>
+        <v>11165</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>72.25</v>
+        <v>69.78125</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>36.1</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3126</v>
+        <v>3026</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>19.5375</v>
+        <v>18.9125</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>521580</v>
+        <v>574447</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5956.623692900238</v>
+        <v>6767.066166505065</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46310</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.47222222222262644</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>67408+7360+13280+5440+6080</f>
-        <v>99568</v>
+        <f>120619+30676+28453</f>
+        <v>179748</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>99568</v>
+        <v>179748</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-48360</v>
+        <v>-128540</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>119168</v>
+        <v>199348</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1244.6</v>
+        <v>2246.85</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>25251</v>
+        <v>9025</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>25251</v>
+        <v>9025</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-25047</v>
+        <v>-8821</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>25251</v>
+        <v>9025</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>315.6375</v>
+        <v>112.8125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,8 +5436,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>41927+17520+3340</f>
-        <v>62787</v>
+        <v>32137</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5444,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>39371</v>
+        <v>8721</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5452,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-54338</v>
+        <v>-23688</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>44491</v>
+        <v>13841</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>784.8375</v>
+        <v>401.7125</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5512,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5533,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>39578</v>
+        <v>28273</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5541,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>39575</v>
+        <v>28270</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5549,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-33973</v>
+        <v>-22668</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>44295</v>
+        <v>32990</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>494.725</v>
+        <v>353.4125</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5609,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5727,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>1556+13840+3520</f>
-        <v>18916</v>
+        <f>29097+19200+13210</f>
+        <v>61507</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5736,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>15440</v>
+        <v>58031</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5744,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-9559</v>
+        <v>-52150</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>16080</v>
+        <v>58671</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>236.45</v>
+        <v>768.8375</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5804,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5907,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>5398</v>
+        <v>4812</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5915,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>5397</v>
+        <v>4811</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5923,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-4873</v>
+        <v>-4287</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>5397</v>
+        <v>4811</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>67.475</v>
+        <v>60.15</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5971,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,7 +6074,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>6696</v>
+        <v>112</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6083,7 +6082,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>6696</v>
+        <v>112</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6091,15 +6090,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-6696</v>
+        <v>-112</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>6696</v>
+        <v>112</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>83.7</v>
+        <v>1.4</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6139,7 +6138,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6161,7 +6160,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>5377</v>
+        <v>4995</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6169,7 +6168,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-45553</v>
+        <v>-45935</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6177,15 +6176,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-5377</v>
+        <v>-4995</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-45553</v>
+        <v>-45935</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>67.2125</v>
+        <v>62.4375</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6225,7 +6224,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6246,7 +6245,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="23">
-        <v>2884</v>
+        <f>31+13425</f>
+        <v>13456</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-25426</v>
+        <v>-14854</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6262,15 +6262,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>130057</v>
+        <v>119485</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-22228</v>
+        <v>-11656</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>36.97435897435897</v>
+        <v>172.51282051282053</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,8 +6331,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>7-1</f>
-        <v>6</v>
+        <f>26423-1</f>
+        <v>26422</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-17545</v>
+        <v>8871</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6348,15 +6348,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>51888</v>
+        <v>25472</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-15439</v>
+        <v>10977</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>0.07692307692307693</v>
+        <v>338.7435897435897</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>605</v>
+        <v>6557</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-7240</v>
+        <v>-1288</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6433,15 +6433,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>16857</v>
+        <v>10905</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-4744</v>
+        <v>1208</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>7.756410256410256</v>
+        <v>84.06410256410257</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6502,8 +6502,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>14075+1+5022</f>
-        <v>19098</v>
+        <f>11854+1</f>
+        <v>11855</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-4181</v>
+        <v>-11424</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6519,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>20499</v>
+        <v>27742</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-1529</v>
+        <v>-8772</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>244.84615384615384</v>
+        <v>151.98717948717947</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>16541</v>
+        <v>13419</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>16541</v>
+        <v>13419</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6673,15 +6673,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>34425</v>
+        <v>37547</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>17243</v>
+        <v>14121</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>212.06410256410257</v>
+        <v>172.03846153846155</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>30.3</v>
+        <v>24.6</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6864,8 +6864,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <f>2028+4602+2340</f>
-        <v>8970</v>
+        <v>16369</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6873,7 +6872,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>8970</v>
+        <v>16369</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6881,15 +6880,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>41996</v>
+        <v>34597</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>9672</v>
+        <v>17071</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>209.85897435897436</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6913,7 +6912,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>12.8</v>
+        <v>23.3</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6935,8 +6934,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>10212-2</f>
-        <v>10210</v>
+        <f>1448-2</f>
+        <v>1446</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6944,7 +6943,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-37585</v>
+        <v>-46349</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6952,15 +6951,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>43148</v>
+        <v>51912</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-32305</v>
+        <v>-41069</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>63.8125</v>
+        <v>9.0375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7000,7 +6999,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7021,8 +7020,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>3101-1</f>
-        <v>3100</v>
+        <f>2304-1</f>
+        <v>2303</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7030,7 +7029,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-8003</v>
+        <v>-8800</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7038,15 +7037,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>17008</v>
+        <v>17805</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-7043</v>
+        <v>-7840</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>19.375</v>
+        <v>14.39375</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7074,7 +7073,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7096,8 +7095,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>7414+1</f>
-        <v>7415</v>
+        <f>2359+1</f>
+        <v>2360</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7105,7 +7104,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>4453</v>
+        <v>-602</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7113,15 +7112,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-1171</v>
+        <v>3884</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>6213</v>
+        <v>1158</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>46.34375</v>
+        <v>14.75</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7145,7 +7144,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7235,8 +7234,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>203+1</f>
-        <v>204</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7244,7 +7243,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>-4</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7252,15 +7251,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>30286</v>
+        <v>30488</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>3078</v>
+        <v>2876</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>1.275</v>
+        <v>0.0125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7284,7 +7283,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7477,7 +7476,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>5010</v>
+        <v>4125</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7489,7 +7488,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>31.3125</v>
+        <v>25.78125</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7513,7 +7512,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8195,7 +8194,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>26765</v>
+        <v>18251</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8203,7 +8202,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-13865</v>
+        <v>-22379</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8211,15 +8210,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>25841</v>
+        <v>34355</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-7715</v>
+        <v>-16229</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>535.3</v>
+        <v>365.02</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8243,7 +8242,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8264,7 +8263,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>6317</v>
+        <v>98</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8272,7 +8271,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>6317</v>
+        <v>98</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8280,15 +8279,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>46289</v>
+        <v>52508</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>12467</v>
+        <v>6248</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>126.34</v>
+        <v>1.96</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8312,7 +8311,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8542,7 +8541,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>5184</v>
+        <v>11389</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8550,7 +8549,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>5184</v>
+        <v>11389</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8558,15 +8557,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>47422</v>
+        <v>41217</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>11334</v>
+        <v>17539</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>103.68</v>
+        <v>227.78</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8590,7 +8589,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8611,8 +8610,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="40">
-        <f>79-1</f>
-        <v>78</v>
+        <f>29-1</f>
+        <v>28</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8620,7 +8619,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8628,15 +8627,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52528</v>
+        <v>52578</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6228</v>
+        <v>6178</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>1.56</v>
+        <v>0.56</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8945,8 +8944,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>14674+2</f>
-        <v>14676</v>
+        <f>10524+2</f>
+        <v>10526</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8954,7 +8953,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>14676</v>
+        <v>10526</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8963,11 +8962,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>14676</v>
+        <v>10526</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>91.725</v>
+        <v>65.7875</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8991,7 +8990,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9012,8 +9011,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>22816-1-1</f>
-        <v>22814</v>
+        <f>20521-1-1</f>
+        <v>20519</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9021,7 +9020,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>22814</v>
+        <v>20519</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9030,11 +9029,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>22814</v>
+        <v>20519</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>142.5875</v>
+        <v>128.24375</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9058,7 +9057,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9079,8 +9078,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>7423-2-1</f>
-        <v>7420</v>
+        <f>1778-2-1</f>
+        <v>1775</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9088,7 +9087,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>7420</v>
+        <v>1775</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9097,11 +9096,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>7420</v>
+        <v>1775</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>46.375</v>
+        <v>11.09375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9125,7 +9124,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9146,7 +9145,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>39505</v>
+        <v>34625</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9154,7 +9153,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>39505</v>
+        <v>34625</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9163,11 +9162,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>39505</v>
+        <v>34625</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>246.90625</v>
+        <v>216.40625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9191,7 +9190,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9476,7 +9475,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="33">
-        <v>3877</v>
+        <v>2659</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9484,7 +9483,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>3877</v>
+        <v>2659</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9493,11 +9492,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>3877</v>
+        <v>2659</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>46.154761904761905</v>
+        <v>31.654761904761905</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9542,7 +9541,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>10853</v>
+        <v>9827</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9554,7 +9553,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>217.06</v>
+        <v>196.54</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9578,7 +9577,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9599,7 +9598,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>31709</v>
+        <v>31554</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9611,7 +9610,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>233.15441176470588</v>
+        <v>232.01470588235293</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9827,7 +9826,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>11560</v>
+        <v>11165</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9839,7 +9838,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>72.25</v>
+        <v>69.78125</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9863,7 +9862,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>36.1</v>
+        <v>34.9</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9884,7 +9883,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3126</v>
+        <v>3026</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9896,7 +9895,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>19.5375</v>
+        <v>18.9125</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10085,26 +10084,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>521580</v>
+        <v>574447</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>202015</v>
+        <v>257443</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>680686</v>
+        <v>607070</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>299987</v>
+        <v>355415</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5956.623692900238</v>
+        <v>6767.066166505065</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46313</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>179748</v>
+        <v>174134</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>2246.85</v>
+        <v>2176.675</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9025</v>
+        <v>2433</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>112.8125</v>
+        <v>30.4125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32137</v>
+        <v>8307</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>401.7125</v>
+        <v>103.8375</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28273</v>
+        <v>16105</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>353.4125</v>
+        <v>201.3125</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>61507</v>
+        <v>58564</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>768.8375</v>
+        <v>732.05</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4812</v>
+        <v>3362</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>60.15</v>
+        <v>42.025</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>112</v>
+        <v>20240</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>1.4</v>
+        <v>253</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4995</v>
+        <v>3375</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>62.4375</v>
+        <v>42.1875</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>10.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13456</v>
+        <v>116</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>172.51282051282053</v>
+        <v>1.4871794871794872</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26422</v>
+        <v>24895</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>338.7435897435897</v>
+        <v>319.1666666666667</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6557</v>
+        <v>25077</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>84.06410256410257</v>
+        <v>321.5</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11855</v>
+        <v>5370</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>151.98717948717947</v>
+        <v>68.84615384615384</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13419</v>
+        <v>11363</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>172.03846153846155</v>
+        <v>145.67948717948718</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>24.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16369</v>
+        <v>15028</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>209.85897435897436</v>
+        <v>192.66666666666666</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1446</v>
+        <v>966</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>9.0375</v>
+        <v>6.0375</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2303</v>
+        <v>1593</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>14.39375</v>
+        <v>9.95625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2360</v>
+        <v>650</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>14.75</v>
+        <v>4.0625</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2</v>
+        <v>16892</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>0.0125</v>
+        <v>105.575</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4125</v>
+        <v>3255</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>25.78125</v>
+        <v>20.34375</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18251</v>
+        <v>12986</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>365.02</v>
+        <v>259.72</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>98</v>
+        <v>1418</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>1.96</v>
+        <v>28.36</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11389</v>
+        <v>11919</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>227.78</v>
+        <v>238.38</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10526</v>
+        <v>8484</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>65.7875</v>
+        <v>53.025</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20519</v>
+        <v>16517</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>128.24375</v>
+        <v>103.23125</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1775</v>
+        <v>230</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>11.09375</v>
+        <v>1.4375</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>34625</v>
+        <v>32609</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>216.40625</v>
+        <v>203.80625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2659</v>
+        <v>2265</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>31.654761904761905</v>
+        <v>26.964285714285715</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9827</v>
+        <v>9405</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>196.54</v>
+        <v>188.1</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31554</v>
+        <v>31380</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>232.01470588235293</v>
+        <v>230.73529411764707</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11165</v>
+        <v>10835</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>69.78125</v>
+        <v>67.71875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3026</v>
+        <v>3011</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>18.9125</v>
+        <v>18.81875</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>574447</v>
+        <v>532894</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>6767.066166505065</v>
+        <v>6198.197304190909</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>120619+30676+28453</f>
-        <v>179748</v>
+        <f>118374+29040+26720</f>
+        <v>174134</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>179748</v>
+        <v>174134</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-128540</v>
+        <v>-122926</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>199348</v>
+        <v>193734</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>2246.85</v>
+        <v>2176.675</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,7 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <v>9025</v>
+        <f>113+2320</f>
+        <v>2433</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5346,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>9025</v>
+        <v>2433</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5354,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-8821</v>
+        <v>-2229</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>9025</v>
+        <v>2433</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>112.8125</v>
+        <v>30.4125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5414,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5436,7 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>32137</v>
+        <v>8307</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5444,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>8721</v>
+        <v>-15109</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5452,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-23688</v>
+        <v>142</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>13841</v>
+        <v>-9989</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>401.7125</v>
+        <v>103.8375</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5512,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5533,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>28273</v>
+        <v>16105</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5541,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>28270</v>
+        <v>16102</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5549,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-22668</v>
+        <v>-10500</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>32990</v>
+        <v>20822</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>353.4125</v>
+        <v>201.3125</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5609,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5727,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>29097+19200+13210</f>
-        <v>61507</v>
+        <f>40164+18400</f>
+        <v>58564</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5736,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>58031</v>
+        <v>55088</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5744,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-52150</v>
+        <v>-49207</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>58671</v>
+        <v>55728</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>768.8375</v>
+        <v>732.05</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5804,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5907,7 +5908,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>4812</v>
+        <v>3362</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5915,7 +5916,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>4811</v>
+        <v>3361</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5923,15 +5924,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-4287</v>
+        <v>-2837</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>4811</v>
+        <v>3361</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>60.15</v>
+        <v>42.025</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5971,7 +5972,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6074,7 +6075,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>112</v>
+        <f>4400+15840</f>
+        <v>20240</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6082,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>20240</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6090,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-112</v>
+        <v>-20240</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>112</v>
+        <v>20240</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>1.4</v>
+        <v>253</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6138,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6160,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>4995</v>
+        <v>3375</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6168,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-45935</v>
+        <v>-47555</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6176,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-4995</v>
+        <v>-3375</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-45935</v>
+        <v>-47555</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>62.4375</v>
+        <v>42.1875</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6224,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>10.4</v>
+        <v>7</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6244,9 +6246,9 @@
         <v>78</v>
       </c>
       <c r="I35" s="44"/>
-      <c r="J35" s="23">
-        <f>31+13425</f>
-        <v>13456</v>
+      <c r="J35" s="40">
+        <f>117-1</f>
+        <v>116</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6254,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-14854</v>
+        <v>-28194</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6262,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>119485</v>
+        <v>132825</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-11656</v>
+        <v>-24996</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>172.51282051282053</v>
+        <v>1.4871794871794872</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6310,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6331,8 +6333,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>26423-1</f>
-        <v>26422</v>
+        <f>24896-1</f>
+        <v>24895</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6340,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>8871</v>
+        <v>7344</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6348,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>25472</v>
+        <v>26999</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>10977</v>
+        <v>9450</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>338.7435897435897</v>
+        <v>319.1666666666667</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6396,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6417,7 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <v>6557</v>
+        <f>2613+22464</f>
+        <v>25077</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6425,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-1288</v>
+        <v>17232</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6433,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>10905</v>
+        <v>-7615</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>1208</v>
+        <v>19728</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>84.06410256410257</v>
+        <v>321.5</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6481,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6502,8 +6505,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="37">
-        <f>11854+1</f>
-        <v>11855</v>
+        <f>5369+1</f>
+        <v>5370</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6511,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-11424</v>
+        <v>-17909</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6519,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>27742</v>
+        <v>34227</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-8772</v>
+        <v>-15257</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>151.98717948717947</v>
+        <v>68.84615384615384</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6567,7 +6570,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6657,7 +6660,7 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33">
-        <v>13419</v>
+        <v>11363</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6665,7 +6668,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>13419</v>
+        <v>11363</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6673,15 +6676,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>37547</v>
+        <v>39603</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>14121</v>
+        <v>12065</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>172.03846153846155</v>
+        <v>145.67948717948718</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6705,7 +6708,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>24.6</v>
+        <v>20.8</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6864,7 +6867,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>16369</v>
+        <v>15028</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6872,7 +6875,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>16369</v>
+        <v>15028</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6880,15 +6883,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>34597</v>
+        <v>35938</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>17071</v>
+        <v>15730</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>209.85897435897436</v>
+        <v>192.66666666666666</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6912,7 +6915,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6934,8 +6937,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="40">
-        <f>1448-2</f>
-        <v>1446</v>
+        <f>968-2</f>
+        <v>966</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6943,7 +6946,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-46349</v>
+        <v>-46829</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6951,15 +6954,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>51912</v>
+        <v>52392</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-41069</v>
+        <v>-41549</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>9.0375</v>
+        <v>6.0375</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -6999,7 +7002,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7020,8 +7023,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="40">
-        <f>2304-1</f>
-        <v>2303</v>
+        <f>1594-1</f>
+        <v>1593</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7029,7 +7032,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-8800</v>
+        <v>-9510</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7037,15 +7040,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>17805</v>
+        <v>18515</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-7840</v>
+        <v>-8550</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>14.39375</v>
+        <v>9.95625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7073,7 +7076,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7095,8 +7098,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="37">
-        <f>2359+1</f>
-        <v>2360</v>
+        <f>649+1</f>
+        <v>650</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7104,7 +7107,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-602</v>
+        <v>-2312</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7112,15 +7115,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>3884</v>
+        <v>5594</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>1158</v>
+        <v>-552</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>14.75</v>
+        <v>4.0625</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7144,7 +7147,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7234,8 +7237,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="37">
-        <f>1+1</f>
-        <v>2</v>
+        <f>1211+1+15680</f>
+        <v>16892</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7243,7 +7246,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>16886</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7251,15 +7254,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>30488</v>
+        <v>13598</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>2876</v>
+        <v>19766</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>0.0125</v>
+        <v>105.575</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7283,7 +7286,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7476,7 +7479,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>4125</v>
+        <v>3255</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7488,7 +7491,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>25.78125</v>
+        <v>20.34375</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7512,7 +7515,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8194,7 +8197,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>18251</v>
+        <v>12986</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8202,7 +8205,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-22379</v>
+        <v>-27644</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8210,15 +8213,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>34355</v>
+        <v>39620</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-16229</v>
+        <v>-21494</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>365.02</v>
+        <v>259.72</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8242,7 +8245,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8263,7 +8266,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>98</v>
+        <f>68+1350</f>
+        <v>1418</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8271,7 +8275,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>1418</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8279,15 +8283,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>52508</v>
+        <v>51188</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>6248</v>
+        <v>7568</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>1.96</v>
+        <v>28.36</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8311,7 +8315,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8541,7 +8545,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>11389</v>
+        <v>11919</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8549,7 +8553,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>11389</v>
+        <v>11919</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8557,15 +8561,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>41217</v>
+        <v>40687</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>17539</v>
+        <v>18069</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>227.78</v>
+        <v>238.38</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8589,7 +8593,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8944,8 +8948,8 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="37">
-        <f>10524+2</f>
-        <v>10526</v>
+        <f>8482+2</f>
+        <v>8484</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8953,7 +8957,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>10526</v>
+        <v>8484</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8962,11 +8966,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>10526</v>
+        <v>8484</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>65.7875</v>
+        <v>53.025</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8990,7 +8994,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9011,8 +9015,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>20521-1-1</f>
-        <v>20519</v>
+        <f>16519-1-1</f>
+        <v>16517</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9020,7 +9024,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>20519</v>
+        <v>16517</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9029,11 +9033,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>20519</v>
+        <v>16517</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>128.24375</v>
+        <v>103.23125</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9057,7 +9061,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9078,8 +9082,8 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="40">
-        <f>1778-2-1</f>
-        <v>1775</v>
+        <f>233-2-1</f>
+        <v>230</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9087,7 +9091,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>1775</v>
+        <v>230</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9096,11 +9100,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>1775</v>
+        <v>230</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>11.09375</v>
+        <v>1.4375</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9124,7 +9128,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9145,7 +9149,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>34625</v>
+        <v>32609</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9153,7 +9157,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>34625</v>
+        <v>32609</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9162,11 +9166,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>34625</v>
+        <v>32609</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>216.40625</v>
+        <v>203.80625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9190,7 +9194,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9475,7 +9479,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="33">
-        <v>2659</v>
+        <v>2265</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9483,7 +9487,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>2659</v>
+        <v>2265</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9492,11 +9496,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>2659</v>
+        <v>2265</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>31.654761904761905</v>
+        <v>26.964285714285715</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9541,7 +9545,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>9827</v>
+        <v>9405</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9553,7 +9557,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>196.54</v>
+        <v>188.1</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9577,7 +9581,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>13.4</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9598,7 +9602,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>31554</v>
+        <v>31380</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9610,7 +9614,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>232.01470588235293</v>
+        <v>230.73529411764707</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9634,7 +9638,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9826,7 +9830,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>11165</v>
+        <v>10835</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9838,7 +9842,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>69.78125</v>
+        <v>67.71875</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9862,7 +9866,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9883,7 +9887,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3026</v>
+        <v>3011</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9895,7 +9899,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>18.9125</v>
+        <v>18.81875</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10084,26 +10088,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>574447</v>
+        <v>532894</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>257443</v>
+        <v>217701</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>607070</v>
+        <v>636813</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>355415</v>
+        <v>315673</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>6767.066166505065</v>
+        <v>6198.197304190909</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -1261,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1514,6 +1514,7 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2989,7 +2990,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3003,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.75</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3057,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>174134</v>
+        <v>129654</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3065,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>2176.675</v>
+        <v>1620.675</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3089,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2433</v>
+        <v>21345</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3097,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>30.4125</v>
+        <v>266.8125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3120,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8307</v>
+        <v>252</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3128,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>103.8375</v>
+        <v>3.15</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3151,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16105</v>
+        <v>3923</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3159,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>201.3125</v>
+        <v>49.0375</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3213,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>58564</v>
+        <v>64074</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3221,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>732.05</v>
+        <v>800.925</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3244,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3362</v>
+        <v>2640</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3252,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>42.025</v>
+        <v>33</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3275,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20240</v>
+        <v>39827</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3283,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>253</v>
+        <v>497.8375</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3306,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3375</v>
+        <v>2569</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3314,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>42.1875</v>
+        <v>32.1125</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3368,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24895</v>
+        <v>23489</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3376,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>319.1666666666667</v>
+        <v>301.14102564102564</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3399,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25077</v>
+        <v>33423</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3407,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>321.5</v>
+        <v>428.5</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>6.6</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3430,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5370</v>
+        <v>1383</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3438,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>68.84615384615384</v>
+        <v>17.73076923076923</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3461,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11363</v>
+        <v>9466</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3469,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>145.67948717948718</v>
+        <v>121.35897435897436</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>20.8</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3523,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15028</v>
+        <v>13574</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3531,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>192.66666666666666</v>
+        <v>174.02564102564102</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>21.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3554,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>966</v>
+        <v>746</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,7 +3562,7 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>6.0375</v>
+        <v>4.6625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
@@ -3584,7 +3585,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1593</v>
+        <v>1473</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3593,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>9.95625</v>
+        <v>9.20625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3616,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3624,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>4.0625</v>
+        <v>1.5625</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3647,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16892</v>
+        <v>27146</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3655,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>105.575</v>
+        <v>169.6625</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3678,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3255</v>
+        <v>1660</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3686,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>20.34375</v>
+        <v>10.375</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3709,7 +3710,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12986</v>
+        <v>6546</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3717,14 +3718,14 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>259.72</v>
+        <v>130.92</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
       </c>
       <c r="J26" s="47">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3740,7 +3741,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1418</v>
+        <v>558</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3749,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>28.36</v>
+        <v>11.16</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3772,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11919</v>
+        <v>8534</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3780,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>238.38</v>
+        <v>170.68</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3834,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8484</v>
+        <v>5514</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3842,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>53.025</v>
+        <v>34.4625</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3865,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16517</v>
+        <v>12681</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3873,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>103.23125</v>
+        <v>79.25625</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3895,7 +3896,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,7 +3904,7 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>1.4375</v>
+        <v>1.0625</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
@@ -3926,7 +3927,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32609</v>
+        <v>28129</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3935,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>203.80625</v>
+        <v>175.80625</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4082,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2265</v>
+        <v>1557</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4090,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>26.964285714285715</v>
+        <v>18.535714285714285</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4113,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9405</v>
+        <v>8781</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4121,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>188.1</v>
+        <v>175.62</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4144,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31380</v>
+        <v>30774</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4152,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>230.73529411764707</v>
+        <v>226.27941176470588</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4175,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10835</v>
+        <v>10508</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4183,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>67.71875</v>
+        <v>65.675</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4206,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3011</v>
+        <v>2919</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4214,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>18.81875</v>
+        <v>18.24375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4270,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>532894</v>
+        <v>493791</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>6198.197304190909</v>
+        <v>5652.042786306832</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4680,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5238,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>118374+29040+26720</f>
-        <v>174134</v>
+        <f>113974+15680</f>
+        <v>129654</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5247,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>174134</v>
+        <v>129654</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5255,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-122926</v>
+        <v>-78446</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>193734</v>
+        <v>149254</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>2176.675</v>
+        <v>1620.675</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5315,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5339,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="33">
-        <f>113+2320</f>
-        <v>2433</v>
+        <f>4465+16880</f>
+        <v>21345</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5348,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>2433</v>
+        <v>21345</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5356,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-2229</v>
+        <v>-21141</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>2433</v>
+        <v>21345</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>30.4125</v>
+        <v>266.8125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5416,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5438,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>8307</v>
+        <v>252</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-15109</v>
+        <v>-23164</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>142</v>
+        <v>8197</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>-9989</v>
+        <v>-18044</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>103.8375</v>
+        <v>3.15</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5535,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>16105</v>
+        <v>3923</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>16102</v>
+        <v>3920</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-10500</v>
+        <v>1682</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>20822</v>
+        <v>8640</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>201.3125</v>
+        <v>49.0375</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33">
-        <f>40164+18400</f>
-        <v>58564</v>
+        <f>44794+19280</f>
+        <v>64074</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>55088</v>
+        <v>60598</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-49207</v>
+        <v>-54717</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>55728</v>
+        <v>61238</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>732.05</v>
+        <v>800.925</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>3362</v>
+        <v>2640</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5916,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>3361</v>
+        <v>2639</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5924,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-2837</v>
+        <v>-2115</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>3361</v>
+        <v>2639</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>42.025</v>
+        <v>33</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6075,8 +6076,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>4400+15840</f>
-        <v>20240</v>
+        <f>23987+15840</f>
+        <v>39827</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6085,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>20240</v>
+        <v>39827</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6093,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-20240</v>
+        <v>-39827</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>20240</v>
+        <v>39827</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>253</v>
+        <v>497.8375</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6141,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>8.3</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6163,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>3375</v>
+        <v>2569</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6171,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-47555</v>
+        <v>-48361</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6179,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-3375</v>
+        <v>-2569</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-47555</v>
+        <v>-48361</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>42.1875</v>
+        <v>32.1125</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6227,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6332,9 +6333,8 @@
         <v>78</v>
       </c>
       <c r="I36" s="32"/>
-      <c r="J36" s="40">
-        <f>24896-1</f>
-        <v>24895</v>
+      <c r="J36" s="33">
+        <v>23489</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>7344</v>
+        <v>5938</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>26999</v>
+        <v>28405</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>9450</v>
+        <v>8044</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>319.1666666666667</v>
+        <v>301.14102564102564</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,8 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="33">
-        <f>2613+22464</f>
-        <v>25077</v>
+        <f>24143+9280</f>
+        <v>33423</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>17232</v>
+        <v>25578</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-7615</v>
+        <v>-15961</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>19728</v>
+        <v>28074</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>321.5</v>
+        <v>428.5</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>6.6</v>
+        <v>8.7</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6504,9 +6504,8 @@
         <v>78</v>
       </c>
       <c r="I38" s="32"/>
-      <c r="J38" s="37">
-        <f>5369+1</f>
-        <v>5370</v>
+      <c r="J38" s="33">
+        <v>1383</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6513,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-17909</v>
+        <v>-21896</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6521,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>34227</v>
+        <v>38214</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-15257</v>
+        <v>-19244</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>68.84615384615384</v>
+        <v>17.73076923076923</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6570,7 +6569,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6659,8 +6658,9 @@
         <v>78</v>
       </c>
       <c r="I40" s="32"/>
-      <c r="J40" s="33">
-        <v>11363</v>
+      <c r="J40" s="40">
+        <f>9467-1</f>
+        <v>9466</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>11363</v>
+        <v>9466</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6676,15 +6676,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>39603</v>
+        <v>41500</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>12065</v>
+        <v>10168</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>145.67948717948718</v>
+        <v>121.35897435897436</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>20.8</v>
+        <v>17.3</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>15028</v>
+        <v>13574</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>15028</v>
+        <v>13574</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6883,15 +6883,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>35938</v>
+        <v>37392</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>15730</v>
+        <v>14276</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>192.66666666666666</v>
+        <v>174.02564102564102</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>21.4</v>
+        <v>19.3</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6936,9 +6936,8 @@
         <v>160</v>
       </c>
       <c r="I44" s="44"/>
-      <c r="J44" s="40">
-        <f>968-2</f>
-        <v>966</v>
+      <c r="J44" s="23">
+        <v>746</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6946,7 +6945,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-46829</v>
+        <v>-47049</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6954,15 +6953,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>52392</v>
+        <v>52612</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-41549</v>
+        <v>-41769</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>6.0375</v>
+        <v>4.6625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7022,9 +7021,8 @@
         <v>160</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="40">
-        <f>1594-1</f>
-        <v>1593</v>
+      <c r="J45" s="33">
+        <v>1473</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7032,7 +7030,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-9510</v>
+        <v>-9630</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7040,15 +7038,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>18515</v>
+        <v>18635</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-8550</v>
+        <v>-8670</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>9.95625</v>
+        <v>9.20625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7076,7 +7074,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7097,9 +7095,8 @@
         <v>160</v>
       </c>
       <c r="I46" s="32"/>
-      <c r="J46" s="37">
-        <f>649+1</f>
-        <v>650</v>
+      <c r="J46" s="33">
+        <v>250</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7107,7 +7104,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-2312</v>
+        <v>-2712</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7115,15 +7112,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>5594</v>
+        <v>5994</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>-552</v>
+        <v>-952</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>4.0625</v>
+        <v>1.5625</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7147,7 +7144,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,9 +7233,9 @@
         <v>160</v>
       </c>
       <c r="I48" s="32"/>
-      <c r="J48" s="37">
-        <f>1211+1+15680</f>
-        <v>16892</v>
+      <c r="J48" s="33">
+        <f>15602+11544</f>
+        <v>27146</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7246,7 +7243,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>16886</v>
+        <v>27140</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7254,15 +7251,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>13598</v>
+        <v>3344</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>19766</v>
+        <v>30020</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>105.575</v>
+        <v>169.6625</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7286,7 +7283,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7479,7 +7476,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>3255</v>
+        <v>1660</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7491,7 +7488,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>20.34375</v>
+        <v>10.375</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7515,7 +7512,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8197,7 +8194,7 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="23">
-        <v>12986</v>
+        <v>6546</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8205,7 +8202,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-27644</v>
+        <v>-34084</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8213,15 +8210,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>39620</v>
+        <v>46060</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-21494</v>
+        <v>-27934</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>259.72</v>
+        <v>130.92</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8245,7 +8242,7 @@
       </c>
       <c r="AJ63" s="47">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AN63" s="114"/>
     </row>
@@ -8266,8 +8263,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>68+1350</f>
-        <v>1418</v>
+        <v>558</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8275,7 +8271,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>1418</v>
+        <v>558</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8283,15 +8279,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>51188</v>
+        <v>52048</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>7568</v>
+        <v>6708</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>28.36</v>
+        <v>11.16</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8315,7 +8311,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8545,7 +8541,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="33">
-        <v>11919</v>
+        <v>8534</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8553,7 +8549,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>11919</v>
+        <v>8534</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8561,15 +8557,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>40687</v>
+        <v>44072</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>18069</v>
+        <v>14684</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>238.38</v>
+        <v>170.68</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8593,7 +8589,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8613,8 +8609,7 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="40">
-        <f>29-1</f>
+      <c r="J69" s="33">
         <v>28</v>
       </c>
       <c r="K69" s="58"/>
@@ -8947,9 +8942,8 @@
         <v>160</v>
       </c>
       <c r="I74" s="53"/>
-      <c r="J74" s="37">
-        <f>8482+2</f>
-        <v>8484</v>
+      <c r="J74" s="23">
+        <v>5514</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8957,7 +8951,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>8484</v>
+        <v>5514</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8966,11 +8960,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>8484</v>
+        <v>5514</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>53.025</v>
+        <v>34.4625</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8994,7 +8988,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9015,8 +9009,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>16519-1-1</f>
-        <v>16517</v>
+        <f>12682-1</f>
+        <v>12681</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9024,7 +9018,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>16517</v>
+        <v>12681</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9033,11 +9027,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>16517</v>
+        <v>12681</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>103.23125</v>
+        <v>79.25625</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9061,7 +9055,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9081,9 +9075,8 @@
         <v>160</v>
       </c>
       <c r="I76" s="58"/>
-      <c r="J76" s="40">
-        <f>233-2-1</f>
-        <v>230</v>
+      <c r="J76" s="33">
+        <v>170</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9091,7 +9084,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9100,11 +9093,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>1.4375</v>
+        <v>1.0625</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9149,7 +9142,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>32609</v>
+        <v>28129</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9157,7 +9150,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>32609</v>
+        <v>28129</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9166,11 +9159,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>32609</v>
+        <v>28129</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>203.80625</v>
+        <v>175.80625</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9194,7 +9187,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9222,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9478,8 +9471,9 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="33">
-        <v>2265</v>
+      <c r="J82" s="152">
+        <f>1555+2</f>
+        <v>1557</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9487,7 +9481,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>2265</v>
+        <v>1557</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9496,11 +9490,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>2265</v>
+        <v>1557</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>26.964285714285715</v>
+        <v>18.535714285714285</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9545,7 +9539,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>9405</v>
+        <v>8781</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9557,7 +9551,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>188.1</v>
+        <v>175.62</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9581,7 +9575,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,7 +9596,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>31380</v>
+        <v>30774</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9614,7 +9608,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>230.73529411764707</v>
+        <v>226.27941176470588</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9638,35 +9632,35 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
     <row r="85" ht="27.95" customHeight="1" hidden="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A85" s="152" t="s">
+      <c r="A85" s="153" t="s">
         <v>209</v>
       </c>
-      <c r="B85" s="153" t="s">
+      <c r="B85" s="154" t="s">
         <v>210</v>
       </c>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
-      <c r="E85" s="155"/>
-      <c r="F85" s="156"/>
-      <c r="G85" s="156"/>
-      <c r="H85" s="155">
+      <c r="C85" s="155"/>
+      <c r="D85" s="155"/>
+      <c r="E85" s="156"/>
+      <c r="F85" s="157"/>
+      <c r="G85" s="157"/>
+      <c r="H85" s="156">
         <v>78</v>
       </c>
-      <c r="I85" s="156"/>
+      <c r="I85" s="157"/>
       <c r="J85" s="54">
         <v>0</v>
       </c>
-      <c r="K85" s="156"/>
-      <c r="L85" s="157" t="s">
+      <c r="K85" s="157"/>
+      <c r="L85" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="M85" s="158"/>
-      <c r="N85" s="159"/>
+      <c r="M85" s="159"/>
+      <c r="N85" s="160"/>
       <c r="O85" s="127"/>
       <c r="P85" s="127"/>
       <c r="Q85" s="54">
@@ -9706,8 +9700,8 @@
       <c r="B86" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="C86" s="160"/>
-      <c r="D86" s="160"/>
+      <c r="C86" s="161"/>
+      <c r="D86" s="161"/>
       <c r="E86" s="68"/>
       <c r="F86" s="69"/>
       <c r="G86" s="69"/>
@@ -9722,8 +9716,8 @@
       <c r="L86" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M86" s="161"/>
-      <c r="N86" s="162"/>
+      <c r="M86" s="162"/>
+      <c r="N86" s="163"/>
       <c r="O86" s="118"/>
       <c r="P86" s="118"/>
       <c r="Q86" s="48">
@@ -9763,8 +9757,8 @@
       <c r="B87" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="C87" s="160"/>
-      <c r="D87" s="160"/>
+      <c r="C87" s="161"/>
+      <c r="D87" s="161"/>
       <c r="E87" s="68"/>
       <c r="F87" s="69"/>
       <c r="G87" s="69"/>
@@ -9779,8 +9773,8 @@
       <c r="L87" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M87" s="161"/>
-      <c r="N87" s="162"/>
+      <c r="M87" s="162"/>
+      <c r="N87" s="163"/>
       <c r="O87" s="118"/>
       <c r="P87" s="118"/>
       <c r="Q87" s="48">
@@ -9820,8 +9814,8 @@
       <c r="B88" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="160"/>
-      <c r="D88" s="160"/>
+      <c r="C88" s="161"/>
+      <c r="D88" s="161"/>
       <c r="E88" s="68"/>
       <c r="F88" s="69"/>
       <c r="G88" s="69"/>
@@ -9830,19 +9824,19 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>10835</v>
+        <v>10508</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M88" s="161"/>
-      <c r="N88" s="162"/>
+      <c r="M88" s="162"/>
+      <c r="N88" s="163"/>
       <c r="O88" s="118"/>
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>67.71875</v>
+        <v>65.675</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9866,7 +9860,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9877,8 +9871,8 @@
       <c r="B89" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="160"/>
-      <c r="D89" s="160"/>
+      <c r="C89" s="161"/>
+      <c r="D89" s="161"/>
       <c r="E89" s="68"/>
       <c r="F89" s="69"/>
       <c r="G89" s="69"/>
@@ -9887,19 +9881,19 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>3011</v>
+        <v>2919</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="161"/>
-      <c r="N89" s="162"/>
+      <c r="M89" s="162"/>
+      <c r="N89" s="163"/>
       <c r="O89" s="118"/>
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>18.81875</v>
+        <v>18.24375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -9934,8 +9928,8 @@
       <c r="B90" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="163"/>
-      <c r="D90" s="163"/>
+      <c r="C90" s="164"/>
+      <c r="D90" s="164"/>
       <c r="E90" s="73"/>
       <c r="F90" s="74"/>
       <c r="G90" s="74"/>
@@ -9950,31 +9944,31 @@
       <c r="L90" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="M90" s="164"/>
-      <c r="N90" s="165"/>
-      <c r="O90" s="166"/>
-      <c r="P90" s="166"/>
+      <c r="M90" s="165"/>
+      <c r="N90" s="166"/>
+      <c r="O90" s="167"/>
+      <c r="P90" s="167"/>
       <c r="Q90" s="77">
         <f>+J90/H90</f>
         <v>0</v>
       </c>
-      <c r="R90" s="167"/>
-      <c r="S90" s="167"/>
-      <c r="T90" s="167"/>
-      <c r="U90" s="168"/>
-      <c r="V90" s="169"/>
-      <c r="W90" s="167"/>
-      <c r="X90" s="169"/>
-      <c r="Y90" s="167"/>
-      <c r="Z90" s="167"/>
-      <c r="AA90" s="167"/>
-      <c r="AB90" s="167"/>
-      <c r="AC90" s="170"/>
-      <c r="AD90" s="171"/>
-      <c r="AE90" s="167"/>
-      <c r="AF90" s="167"/>
-      <c r="AG90" s="167"/>
-      <c r="AH90" s="167"/>
+      <c r="R90" s="168"/>
+      <c r="S90" s="168"/>
+      <c r="T90" s="168"/>
+      <c r="U90" s="169"/>
+      <c r="V90" s="170"/>
+      <c r="W90" s="168"/>
+      <c r="X90" s="170"/>
+      <c r="Y90" s="168"/>
+      <c r="Z90" s="168"/>
+      <c r="AA90" s="168"/>
+      <c r="AB90" s="168"/>
+      <c r="AC90" s="171"/>
+      <c r="AD90" s="172"/>
+      <c r="AE90" s="168"/>
+      <c r="AF90" s="168"/>
+      <c r="AG90" s="168"/>
+      <c r="AH90" s="168"/>
       <c r="AI90" s="78">
         <v>0</v>
       </c>
@@ -9985,32 +9979,32 @@
       <c r="AN90" s="114"/>
     </row>
     <row r="91" ht="18.75" customHeight="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A91" s="172" t="s">
+      <c r="A91" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="B91" s="172" t="s">
+      <c r="B91" s="173" t="s">
         <v>216</v>
       </c>
-      <c r="C91" s="172"/>
-      <c r="D91" s="172"/>
-      <c r="E91" s="172"/>
-      <c r="F91" s="172"/>
-      <c r="G91" s="172"/>
-      <c r="H91" s="172">
+      <c r="C91" s="173"/>
+      <c r="D91" s="173"/>
+      <c r="E91" s="173"/>
+      <c r="F91" s="173"/>
+      <c r="G91" s="173"/>
+      <c r="H91" s="173">
         <v>70</v>
       </c>
-      <c r="I91" s="172"/>
-      <c r="J91" s="173">
-        <v>0</v>
-      </c>
-      <c r="K91" s="173"/>
-      <c r="L91" s="173" t="s">
+      <c r="I91" s="173"/>
+      <c r="J91" s="174">
+        <v>0</v>
+      </c>
+      <c r="K91" s="174"/>
+      <c r="L91" s="174" t="s">
         <v>16</v>
       </c>
       <c r="M91" s="105"/>
       <c r="N91" s="28"/>
       <c r="P91" s="106"/>
-      <c r="Q91" s="173"/>
+      <c r="Q91" s="174"/>
       <c r="U91" s="82"/>
       <c r="AC91" s="28"/>
       <c r="AG91" s="28"/>
@@ -10019,43 +10013,43 @@
       <c r="AJ91" s="28"/>
     </row>
     <row r="92" ht="18.75" customHeight="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A92" s="172" t="s">
+      <c r="A92" s="173" t="s">
         <v>217</v>
       </c>
-      <c r="B92" s="172" t="s">
+      <c r="B92" s="173" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="172"/>
-      <c r="D92" s="172"/>
-      <c r="E92" s="172"/>
-      <c r="F92" s="172"/>
-      <c r="G92" s="172"/>
-      <c r="H92" s="172">
+      <c r="C92" s="173"/>
+      <c r="D92" s="173"/>
+      <c r="E92" s="173"/>
+      <c r="F92" s="173"/>
+      <c r="G92" s="173"/>
+      <c r="H92" s="173">
         <v>70</v>
       </c>
-      <c r="I92" s="172"/>
-      <c r="J92" s="173">
-        <v>0</v>
-      </c>
-      <c r="K92" s="173"/>
-      <c r="L92" s="173" t="s">
+      <c r="I92" s="173"/>
+      <c r="J92" s="174">
+        <v>0</v>
+      </c>
+      <c r="K92" s="174"/>
+      <c r="L92" s="174" t="s">
         <v>16</v>
       </c>
       <c r="M92" s="105">
         <f>+J92-N92</f>
         <v>0</v>
       </c>
-      <c r="N92" s="173">
+      <c r="N92" s="174">
         <f>+IFERROR(VLOOKUP(A92,$R$26:$U$119,4,FALSE),0)-0</f>
         <v>0</v>
       </c>
-      <c r="P92" s="174">
+      <c r="P92" s="175">
         <f>J92-IFERROR(VLOOKUP(A92,$R$26:$U$119,4,FALSE),0)+0</f>
         <v>0</v>
       </c>
-      <c r="Q92" s="173"/>
+      <c r="Q92" s="174"/>
       <c r="U92" s="82"/>
-      <c r="AC92" s="175"/>
+      <c r="AC92" s="176"/>
       <c r="AG92" s="28"/>
       <c r="AH92" s="28"/>
       <c r="AI92" s="28"/>
@@ -10074,7 +10068,7 @@
       <c r="P93" s="106"/>
       <c r="Q93" s="81"/>
       <c r="U93" s="82"/>
-      <c r="AC93" s="175"/>
+      <c r="AC93" s="176"/>
     </row>
     <row r="94" ht="26.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="82"/>
@@ -10088,31 +10082,31 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>532894</v>
+        <v>493791</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
-      <c r="M94" s="176">
+      <c r="M94" s="177">
         <f>SUM(M14:M93)</f>
-        <v>217701</v>
+        <v>181842</v>
       </c>
       <c r="N94" s="82"/>
-      <c r="O94" s="177">
+      <c r="O94" s="178">
         <f>SUM(O14:O93)</f>
-        <v>636813</v>
-      </c>
-      <c r="P94" s="178">
+        <v>660618</v>
+      </c>
+      <c r="P94" s="179">
         <f>SUM(P14:P93)</f>
-        <v>315673</v>
+        <v>279814</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>6198.197304190909</v>
+        <v>5652.042786306832</v>
       </c>
       <c r="R94" s="103"/>
-      <c r="U94" s="179"/>
+      <c r="U94" s="180"/>
       <c r="AB94" s="103"/>
-      <c r="AC94" s="175"/>
+      <c r="AC94" s="176"/>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="80"/>
@@ -10127,7 +10121,7 @@
       <c r="P95" s="107"/>
       <c r="Q95" s="81"/>
       <c r="R95" s="103"/>
-      <c r="U95" s="179"/>
+      <c r="U95" s="180"/>
       <c r="AB95" s="103"/>
       <c r="AC95" s="28"/>
     </row>
@@ -10192,7 +10186,7 @@
       <c r="P100" s="107"/>
       <c r="Q100" s="81"/>
       <c r="U100" s="82"/>
-      <c r="AC100" s="173">
+      <c r="AC100" s="174">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -10205,19 +10199,19 @@
         <f>+J101-N101</f>
         <v>0</v>
       </c>
-      <c r="N101" s="173">
+      <c r="N101" s="174">
         <f>+IFERROR(VLOOKUP(A101,$R$26:$U$119,4,FALSE),0)-0</f>
         <v>0</v>
       </c>
-      <c r="P101" s="174">
+      <c r="P101" s="175">
         <f>J101-IFERROR(VLOOKUP(A101,$R$26:$U$119,4,FALSE),0)+0</f>
         <v>0</v>
       </c>
       <c r="Q101" s="81"/>
       <c r="R101" s="103"/>
-      <c r="U101" s="179"/>
+      <c r="U101" s="180"/>
       <c r="AB101" s="103"/>
-      <c r="AC101" s="173">
+      <c r="AC101" s="174">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -10246,7 +10240,7 @@
       <c r="P103" s="107"/>
       <c r="Q103" s="81"/>
       <c r="R103" s="103"/>
-      <c r="U103" s="179"/>
+      <c r="U103" s="180"/>
       <c r="AB103" s="103"/>
       <c r="AC103" s="28">
         <f t="shared" si="14"/>
@@ -10262,7 +10256,7 @@
       <c r="P104" s="107"/>
       <c r="Q104" s="81"/>
       <c r="R104" s="103"/>
-      <c r="U104" s="179"/>
+      <c r="U104" s="180"/>
       <c r="AB104" s="103"/>
       <c r="AC104" s="28">
         <f t="shared" si="14"/>
@@ -10278,7 +10272,7 @@
       <c r="P105" s="107"/>
       <c r="Q105" s="81"/>
       <c r="R105" s="103"/>
-      <c r="U105" s="179"/>
+      <c r="U105" s="180"/>
       <c r="AB105" s="103"/>
       <c r="AC105" s="28">
         <f t="shared" si="14"/>
@@ -10291,12 +10285,12 @@
       <c r="L106" s="28"/>
       <c r="M106" s="105"/>
       <c r="N106" s="85"/>
-      <c r="O106" s="180"/>
+      <c r="O106" s="181"/>
       <c r="P106" s="106"/>
       <c r="Q106" s="81"/>
       <c r="R106" s="103"/>
       <c r="S106" s="28"/>
-      <c r="U106" s="179"/>
+      <c r="U106" s="180"/>
       <c r="AB106" s="103"/>
       <c r="AC106" s="85">
         <f>+IFERROR(VLOOKUP(T106,$R$26:$U$119,4,FALSE),0)-0-1920-640-320</f>
@@ -10312,7 +10306,7 @@
       <c r="P107" s="107"/>
       <c r="Q107" s="81"/>
       <c r="R107" s="103"/>
-      <c r="U107" s="179"/>
+      <c r="U107" s="180"/>
       <c r="AB107" s="103"/>
       <c r="AC107" s="28">
         <f>+IFERROR(VLOOKUP(T107,$R$26:$U$119,4,FALSE),0)</f>
@@ -10325,12 +10319,12 @@
       <c r="L108" s="28"/>
       <c r="M108" s="105"/>
       <c r="N108" s="85"/>
-      <c r="O108" s="180"/>
+      <c r="O108" s="181"/>
       <c r="P108" s="106"/>
       <c r="Q108" s="81"/>
-      <c r="R108" s="181"/>
-      <c r="S108" s="182"/>
-      <c r="U108" s="179"/>
+      <c r="R108" s="182"/>
+      <c r="S108" s="183"/>
+      <c r="U108" s="180"/>
       <c r="AB108" s="103"/>
       <c r="AC108" s="85">
         <f>+IFERROR(VLOOKUP(T108,$R$26:$U$119,4,FALSE),0)-0-2964-3588-2730-5226-1716-1716-2340-3354</f>
@@ -10346,8 +10340,8 @@
       <c r="P109" s="107"/>
       <c r="Q109" s="81"/>
       <c r="R109" s="103"/>
-      <c r="S109" s="182"/>
-      <c r="U109" s="179"/>
+      <c r="S109" s="183"/>
+      <c r="U109" s="180"/>
       <c r="AB109" s="103"/>
       <c r="AC109" s="28">
         <f>+IFERROR(VLOOKUP(T109,$R$26:$U$119,4,FALSE),0)</f>
@@ -10360,11 +10354,11 @@
       <c r="L110" s="28"/>
       <c r="M110" s="105"/>
       <c r="N110" s="85"/>
-      <c r="O110" s="180"/>
+      <c r="O110" s="181"/>
       <c r="P110" s="106"/>
       <c r="Q110" s="81"/>
       <c r="R110" s="103"/>
-      <c r="U110" s="179"/>
+      <c r="U110" s="180"/>
       <c r="AB110" s="103"/>
       <c r="AC110" s="85">
         <f>+IFERROR(VLOOKUP(T110,$R$26:$U$119,4,FALSE),0)-0-1950-1482-702</f>
@@ -10380,7 +10374,7 @@
       <c r="P111" s="107"/>
       <c r="Q111" s="81"/>
       <c r="R111" s="103"/>
-      <c r="U111" s="179"/>
+      <c r="U111" s="180"/>
       <c r="AB111" s="103"/>
       <c r="AC111" s="28">
         <f>+IFERROR(VLOOKUP(T111,$R$26:$U$119,4,FALSE),0)</f>
@@ -10410,7 +10404,7 @@
       <c r="L113" s="28"/>
       <c r="M113" s="105"/>
       <c r="N113" s="85"/>
-      <c r="O113" s="180"/>
+      <c r="O113" s="181"/>
       <c r="P113" s="106"/>
       <c r="Q113" s="81"/>
       <c r="S113" s="28"/>
@@ -10436,7 +10430,7 @@
       <c r="J115" s="85"/>
       <c r="M115" s="105"/>
       <c r="N115" s="85"/>
-      <c r="O115" s="180"/>
+      <c r="O115" s="181"/>
       <c r="P115" s="106"/>
       <c r="Q115" s="81"/>
       <c r="S115" s="28"/>
@@ -10450,7 +10444,7 @@
       <c r="J116" s="85"/>
       <c r="M116" s="105"/>
       <c r="N116" s="85"/>
-      <c r="O116" s="180"/>
+      <c r="O116" s="181"/>
       <c r="P116" s="106"/>
       <c r="Q116" s="81"/>
       <c r="R116" s="28"/>
@@ -10464,10 +10458,10 @@
       <c r="J117" s="85"/>
       <c r="M117" s="105"/>
       <c r="N117" s="85"/>
-      <c r="O117" s="180"/>
+      <c r="O117" s="181"/>
       <c r="P117" s="106"/>
       <c r="Q117" s="81"/>
-      <c r="R117" s="183"/>
+      <c r="R117" s="184"/>
       <c r="U117" s="82"/>
       <c r="AC117" s="85">
         <f>+IFERROR(VLOOKUP(T117,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -10478,7 +10472,7 @@
       <c r="J118" s="85"/>
       <c r="M118" s="105"/>
       <c r="N118" s="85"/>
-      <c r="O118" s="180"/>
+      <c r="O118" s="181"/>
       <c r="P118" s="106"/>
       <c r="Q118" s="81"/>
       <c r="U118" s="82"/>
@@ -10491,7 +10485,7 @@
       <c r="J119" s="85"/>
       <c r="M119" s="105"/>
       <c r="N119" s="85"/>
-      <c r="O119" s="180"/>
+      <c r="O119" s="181"/>
       <c r="P119" s="107"/>
       <c r="Q119" s="81"/>
       <c r="U119" s="82"/>
@@ -10507,7 +10501,7 @@
     </row>
     <row r="121" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J121" s="28"/>
-      <c r="O121" s="184"/>
+      <c r="O121" s="185"/>
     </row>
     <row r="122" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O122" s="28"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.6041666666678793</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3057,7 +3057,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>55307</v>
+        <v>74507</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3065,14 +3065,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>691.3375</v>
+        <v>931.3375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3089,7 +3089,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12289</v>
+        <v>24529</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>153.6125</v>
+        <v>306.6125</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3120,7 +3120,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>53072</v>
+        <v>61472</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3128,14 +3128,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>663.4</v>
+        <v>768.4</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>58</v>
+        <v>6786</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3438,14 +3438,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>0.7435897435897436</v>
+        <v>87</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3585,7 +3585,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2693</v>
+        <v>9093</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3593,14 +3593,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>16.83125</v>
+        <v>56.83125</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4270,13 +4270,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>418990</v>
+        <v>471958</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4639.3399550204695</v>
+        <v>5263.596365276879</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5238,8 +5238,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>23227+2000+30080</f>
-        <v>55307</v>
+        <f>23227+2000+30080+9600+9600</f>
+        <v>74507</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>55307</v>
+        <v>74507</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5255,15 +5255,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-4099</v>
+        <v>-23299</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>74907</v>
+        <v>94107</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>691.3375</v>
+        <v>931.3375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5339,8 +5339,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>11649+160+480</f>
-        <v>12289</v>
+        <f>11649+160+480+12240</f>
+        <v>24529</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>12289</v>
+        <v>24529</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5356,15 +5356,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-12085</v>
+        <v>-24325</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>12289</v>
+        <v>24529</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>153.6125</v>
+        <v>306.6125</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5438,8 +5438,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>13732+16880+22460</f>
-        <v>53072</v>
+        <f>13732+16880+22460+8400</f>
+        <v>61472</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>29656</v>
+        <v>38056</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5455,15 +5455,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-44623</v>
+        <v>-53023</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>34776</v>
+        <v>43176</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>663.4</v>
+        <v>768.4</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -6507,7 +6507,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>58</v>
+        <f>58+5460+1268</f>
+        <v>6786</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6515,7 +6516,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-23221</v>
+        <v>-16493</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6523,15 +6524,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>39539</v>
+        <v>32811</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-20569</v>
+        <v>-13841</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>0.7435897435897436</v>
+        <v>87</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6571,7 +6572,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -7024,7 +7025,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>2693</v>
+        <f>2693+6400</f>
+        <v>9093</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7032,7 +7034,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-8410</v>
+        <v>-2010</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7040,15 +7042,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>17415</v>
+        <v>11015</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-7450</v>
+        <v>-1050</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>16.83125</v>
+        <v>56.83125</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7076,7 +7078,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -9218,7 +9220,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10085,26 +10087,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>418990</v>
+        <v>471958</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="177">
         <f>SUM(M14:M93)</f>
-        <v>105752</v>
+        <v>158720</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="178">
         <f>SUM(O14:O93)</f>
-        <v>719404</v>
+        <v>666436</v>
       </c>
       <c r="P94" s="179">
         <f>SUM(P14:P93)</f>
-        <v>203724</v>
+        <v>256692</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4639.3399550204695</v>
+        <v>5263.596365276879</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="180"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -1261,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1514,7 +1514,6 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2990,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3003,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.6041666666678793</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3057,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>74507</v>
+        <v>72923</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3065,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>931.3375</v>
+        <v>911.5375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3089,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24529</v>
+        <v>42992</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3097,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>306.6125</v>
+        <v>537.4</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3120,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>61472</v>
+        <v>72111</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3128,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>768.4</v>
+        <v>901.3875</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3151,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24938</v>
+        <v>13026</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3159,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>311.725</v>
+        <v>162.825</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3213,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>51277</v>
+        <v>11811</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3221,17 +3220,17 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>640.9625</v>
+        <v>147.6375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
         <v>27</v>
       </c>
@@ -3244,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>952</v>
+        <v>229</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3252,17 +3251,17 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>11.9</v>
+        <v>2.8625</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
         <v>29</v>
       </c>
@@ -3275,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>29230</v>
+        <v>19969</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3283,17 +3282,17 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>365.375</v>
+        <v>249.6125</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="13" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="13" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
         <v>32</v>
       </c>
@@ -3306,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3314,17 +3313,17 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>1.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>34</v>
       </c>
@@ -3337,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11325</v>
+        <v>219</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3345,17 +3344,17 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>145.19230769230768</v>
+        <v>2.8076923076923075</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="15" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>36</v>
       </c>
@@ -3368,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18204</v>
+        <v>13566</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3376,17 +3375,17 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>233.3846153846154</v>
+        <v>173.92307692307693</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="16" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="16" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>38</v>
       </c>
@@ -3399,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23379</v>
+        <v>14736</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3407,17 +3406,17 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>299.7307692307692</v>
+        <v>188.92307692307693</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="17" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="17" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
         <v>40</v>
       </c>
@@ -3430,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6786</v>
+        <v>37715</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3438,17 +3437,17 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>87</v>
+        <v>483.52564102564105</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="18" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="18" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>42</v>
       </c>
@@ -3461,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4332</v>
+        <v>1228</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3469,17 +3468,17 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>55.53846153846154</v>
+        <v>15.743589743589743</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="19" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="19" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
         <v>44</v>
       </c>
@@ -3510,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>46</v>
       </c>
@@ -3523,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9850</v>
+        <v>8127</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3531,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>126.28205128205128</v>
+        <v>104.1923076923077</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3554,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5788</v>
+        <v>788</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3562,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>36.175</v>
+        <v>4.925</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3585,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9093</v>
+        <v>888</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3593,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>56.83125</v>
+        <v>5.55</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3616,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10130</v>
+        <v>13118</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3624,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>63.3125</v>
+        <v>81.9875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3647,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18494</v>
+        <v>13144</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3655,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>115.5875</v>
+        <v>82.15</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3678,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5000</v>
+        <v>4615</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3686,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>31.25</v>
+        <v>28.84375</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3710,7 +3709,7 @@
       <c r="D26" s="53"/>
       <c r="E26" s="54">
         <f>VLOOKUP(A26,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="45" t="s">
@@ -3718,7 +3717,7 @@
       </c>
       <c r="H26" s="23">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="46">
         <v>108</v>
@@ -3741,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3749,7 +3748,7 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>1.34</v>
+        <v>0.54</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
@@ -3772,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>692</v>
+        <v>1092</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3780,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>13.84</v>
+        <v>21.84</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3803,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28</v>
+        <v>4578</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3811,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>0.56</v>
+        <v>91.56</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3834,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3742</v>
+        <v>6142</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3842,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>23.3875</v>
+        <v>38.3875</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3865,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4999</v>
+        <v>6804</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3873,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>31.24375</v>
+        <v>42.525</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3896,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3904,7 +3903,7 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
@@ -3927,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>21044</v>
+        <v>13824</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3935,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>131.525</v>
+        <v>86.4</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>8.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4082,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1033</v>
+        <v>364</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4090,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>12.297619047619047</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4113,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7968</v>
+        <v>7480</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4121,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>159.36</v>
+        <v>149.6</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4144,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>30046</v>
+        <v>28956</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4152,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>220.9264705882353</v>
+        <v>212.91176470588235</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>8.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4175,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>10059</v>
+        <v>9324</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4183,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>62.86875</v>
+        <v>58.275</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>31.4</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4206,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2858</v>
+        <v>2833</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4214,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>17.8625</v>
+        <v>17.70625</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4270,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>471958</v>
+        <v>422665</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5263.596365276879</v>
+        <v>4810.363303167421</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4680,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46317</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4693,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.75</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5238,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>23227+2000+30080+9600+9600</f>
-        <v>74507</v>
+        <f>34483+19160+19280</f>
+        <v>72923</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5247,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>74507</v>
+        <v>72923</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5255,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-23299</v>
+        <v>-21715</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>94107</v>
+        <v>92523</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>931.3375</v>
+        <v>911.5375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5315,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5339,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>11649+160+480+12240</f>
-        <v>24529</v>
+        <f>27168+160+15664</f>
+        <v>42992</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5348,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>24529</v>
+        <v>42992</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5356,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-24325</v>
+        <v>-42788</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>24529</v>
+        <v>42992</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>306.6125</v>
+        <v>537.4</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5416,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5438,8 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>13732+16880+22460+8400</f>
-        <v>61472</v>
+        <f>56512+15599</f>
+        <v>72111</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5447,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>38056</v>
+        <v>48695</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5455,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-53023</v>
+        <v>-63662</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>43176</v>
+        <v>53815</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>768.4</v>
+        <v>901.3875</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5515,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5536,8 +5535,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <f>3285+21653</f>
-        <v>24938</v>
+        <v>13026</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5545,7 +5543,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>24935</v>
+        <v>13023</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5553,15 +5551,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-19333</v>
+        <v>-7421</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>29655</v>
+        <v>17743</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>311.725</v>
+        <v>162.825</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5613,7 +5611,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5731,8 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>51278-1</f>
-        <v>51277</v>
+        <f>11812-1</f>
+        <v>11811</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5740,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>47801</v>
+        <v>8335</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5748,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-41920</v>
+        <v>-2454</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>48441</v>
+        <v>8975</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>640.9625</v>
+        <v>147.6375</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5808,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5911,7 +5909,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>952</v>
+        <v>229</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5919,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>951</v>
+        <v>228</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5927,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-427</v>
+        <v>296</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>951</v>
+        <v>228</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>11.9</v>
+        <v>2.8625</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5975,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6078,7 +6076,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>29230</v>
+        <v>19969</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6086,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>29230</v>
+        <v>19969</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6094,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-29230</v>
+        <v>-19969</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>29230</v>
+        <v>19969</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>365.375</v>
+        <v>249.6125</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6142,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6164,7 +6162,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6172,7 +6170,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-50825</v>
+        <v>-50895</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6180,15 +6178,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-105</v>
+        <v>-35</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-50825</v>
+        <v>-50895</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>1.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6228,7 +6226,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6249,8 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>5320-1+6006</f>
-        <v>11325</v>
+        <f>221-2</f>
+        <v>219</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6258,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-16985</v>
+        <v>-28091</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6266,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>121616</v>
+        <v>132722</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-13787</v>
+        <v>-24893</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>145.19230769230768</v>
+        <v>2.8076923076923075</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6314,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6335,8 +6333,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>18360-156</f>
-        <v>18204</v>
+        <f>13722-156</f>
+        <v>13566</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6344,7 +6342,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>653</v>
+        <v>-3985</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6352,15 +6350,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>33690</v>
+        <v>38328</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>2759</v>
+        <v>-1879</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>233.3846153846154</v>
+        <v>173.92307692307693</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6400,7 +6398,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>16.7</v>
+        <v>12.4</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6421,8 +6419,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="40">
-        <f>23380-1</f>
-        <v>23379</v>
+        <f>14737-1</f>
+        <v>14736</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6430,7 +6428,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>15534</v>
+        <v>6891</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6438,15 +6436,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>-5917</v>
+        <v>2726</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>18030</v>
+        <v>9387</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>299.7307692307692</v>
+        <v>188.92307692307693</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6486,7 +6484,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6507,8 +6505,8 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <f>58+5460+1268</f>
-        <v>6786</v>
+        <f>24236+13479</f>
+        <v>37715</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6516,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-16493</v>
+        <v>14436</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6524,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>32811</v>
+        <v>1882</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-13841</v>
+        <v>17088</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>87</v>
+        <v>483.52564102564105</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6572,7 +6570,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>10.7</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6662,8 +6660,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="40">
-        <f>4333-1</f>
-        <v>4332</v>
+        <f>1229-1</f>
+        <v>1228</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6671,7 +6669,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>4332</v>
+        <v>1228</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6679,15 +6677,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>46634</v>
+        <v>49738</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>5034</v>
+        <v>1930</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>55.53846153846154</v>
+        <v>15.743589743589743</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6711,7 +6709,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>7.9</v>
+        <v>2.2</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6870,7 +6868,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>9850</v>
+        <v>8127</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6878,7 +6876,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>9850</v>
+        <v>8127</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6886,15 +6884,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>41116</v>
+        <v>42839</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>10552</v>
+        <v>8829</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>126.28205128205128</v>
+        <v>104.1923076923077</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6918,7 +6916,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>11.6</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6940,7 +6938,7 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <v>5788</v>
+        <v>788</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6948,7 +6946,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-42007</v>
+        <v>-47007</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6956,15 +6954,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>47570</v>
+        <v>52570</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-36727</v>
+        <v>-41727</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>36.175</v>
+        <v>4.925</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7004,7 +7002,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7025,8 +7023,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <f>2693+6400</f>
-        <v>9093</v>
+        <v>888</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7034,7 +7031,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-2010</v>
+        <v>-10215</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7042,15 +7039,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>11015</v>
+        <v>19220</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-1050</v>
+        <v>-9255</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>56.83125</v>
+        <v>5.55</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7078,7 +7075,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7100,8 +7097,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <f>4370+5760</f>
-        <v>10130</v>
+        <v>13118</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7109,7 +7105,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>7168</v>
+        <v>10156</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7117,15 +7113,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-3886</v>
+        <v>-6874</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>8928</v>
+        <v>11916</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>63.3125</v>
+        <v>81.9875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7149,7 +7145,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7239,7 +7235,7 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <v>18494</v>
+        <v>13144</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7247,7 +7243,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>18488</v>
+        <v>13138</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7255,15 +7251,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>11996</v>
+        <v>17346</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>21368</v>
+        <v>16018</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>115.5875</v>
+        <v>82.15</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7287,7 +7283,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7480,7 +7476,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>5000</v>
+        <v>4615</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7492,7 +7488,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>31.25</v>
+        <v>28.84375</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7516,7 +7512,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8198,8 +8194,8 @@
       </c>
       <c r="I63" s="53"/>
       <c r="J63" s="40">
-        <f>21-1</f>
-        <v>20</v>
+        <f>1-1</f>
+        <v>0</v>
       </c>
       <c r="K63" s="53"/>
       <c r="L63" s="45" t="s">
@@ -8207,7 +8203,7 @@
       </c>
       <c r="M63" s="124">
         <f t="shared" si="1"/>
-        <v>-40610</v>
+        <v>-40630</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="8"/>
@@ -8215,15 +8211,15 @@
       </c>
       <c r="O63" s="126">
         <f t="shared" ref="O63:O69" si="10">52606-J63</f>
-        <v>52586</v>
+        <v>52606</v>
       </c>
       <c r="P63" s="127">
         <f t="shared" ref="P63:P69" si="11">J63-IFERROR(VLOOKUP(A63,$R$26:$U$119,4,FALSE),0)+6150</f>
-        <v>-34460</v>
+        <v>-34480</v>
       </c>
       <c r="Q63" s="23">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R63" s="44"/>
       <c r="S63" s="44"/>
@@ -8268,7 +8264,7 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8276,7 +8272,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8284,15 +8280,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>52539</v>
+        <v>52579</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>6217</v>
+        <v>6177</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>1.34</v>
+        <v>0.54</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8545,8 +8541,8 @@
         <v>50</v>
       </c>
       <c r="I68" s="58"/>
-      <c r="J68" s="33">
-        <v>692</v>
+      <c r="J68" s="48">
+        <v>1092</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8554,7 +8550,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>692</v>
+        <v>1092</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8562,15 +8558,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>51914</v>
+        <v>51514</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6842</v>
+        <v>7242</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>13.84</v>
+        <v>21.84</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8594,7 +8590,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8615,7 +8611,7 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="33">
-        <v>28</v>
+        <v>4578</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8623,7 +8619,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>4578</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8631,15 +8627,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52578</v>
+        <v>48028</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6178</v>
+        <v>10728</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>0.56</v>
+        <v>91.56</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8663,7 +8659,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8948,7 +8944,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>3742</v>
+        <v>6142</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8956,7 +8952,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>3742</v>
+        <v>6142</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8965,11 +8961,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>3742</v>
+        <v>6142</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>23.3875</v>
+        <v>38.3875</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8993,7 +8989,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9014,8 +9010,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>5000-1</f>
-        <v>4999</v>
+        <f>6805-1</f>
+        <v>6804</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9023,7 +9019,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>4999</v>
+        <v>6804</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9032,11 +9028,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>4999</v>
+        <v>6804</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>31.24375</v>
+        <v>42.525</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9060,7 +9056,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9081,7 +9077,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9089,7 +9085,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9098,11 +9094,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9147,7 +9143,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>21044</v>
+        <v>13824</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9155,7 +9151,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>21044</v>
+        <v>13824</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9164,11 +9160,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>21044</v>
+        <v>13824</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>131.525</v>
+        <v>86.4</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9192,7 +9188,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>8.8</v>
+        <v>5.8</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9220,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9476,9 +9472,8 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="152">
-        <f>1031+2</f>
-        <v>1033</v>
+      <c r="J82" s="65">
+        <v>364</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9486,7 +9481,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>1033</v>
+        <v>364</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9495,11 +9490,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>1033</v>
+        <v>364</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>12.297619047619047</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9544,7 +9539,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>7968</v>
+        <v>7480</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9556,7 +9551,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>159.36</v>
+        <v>149.6</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9580,7 +9575,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9601,7 +9596,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>30046</v>
+        <v>28956</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9613,7 +9608,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>220.9264705882353</v>
+        <v>212.91176470588235</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9637,35 +9632,35 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>8.2</v>
+        <v>7.9</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
     <row r="85" ht="27.95" customHeight="1" hidden="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A85" s="153" t="s">
+      <c r="A85" s="152" t="s">
         <v>209</v>
       </c>
-      <c r="B85" s="154" t="s">
+      <c r="B85" s="153" t="s">
         <v>210</v>
       </c>
-      <c r="C85" s="155"/>
-      <c r="D85" s="155"/>
-      <c r="E85" s="156"/>
-      <c r="F85" s="157"/>
-      <c r="G85" s="157"/>
-      <c r="H85" s="156">
+      <c r="C85" s="154"/>
+      <c r="D85" s="154"/>
+      <c r="E85" s="155"/>
+      <c r="F85" s="156"/>
+      <c r="G85" s="156"/>
+      <c r="H85" s="155">
         <v>78</v>
       </c>
-      <c r="I85" s="157"/>
+      <c r="I85" s="156"/>
       <c r="J85" s="54">
         <v>0</v>
       </c>
-      <c r="K85" s="157"/>
-      <c r="L85" s="158" t="s">
+      <c r="K85" s="156"/>
+      <c r="L85" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="M85" s="159"/>
-      <c r="N85" s="160"/>
+      <c r="M85" s="158"/>
+      <c r="N85" s="159"/>
       <c r="O85" s="127"/>
       <c r="P85" s="127"/>
       <c r="Q85" s="54">
@@ -9705,8 +9700,8 @@
       <c r="B86" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="C86" s="161"/>
-      <c r="D86" s="161"/>
+      <c r="C86" s="160"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="68"/>
       <c r="F86" s="69"/>
       <c r="G86" s="69"/>
@@ -9721,8 +9716,8 @@
       <c r="L86" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M86" s="162"/>
-      <c r="N86" s="163"/>
+      <c r="M86" s="161"/>
+      <c r="N86" s="162"/>
       <c r="O86" s="118"/>
       <c r="P86" s="118"/>
       <c r="Q86" s="48">
@@ -9762,8 +9757,8 @@
       <c r="B87" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="C87" s="161"/>
-      <c r="D87" s="161"/>
+      <c r="C87" s="160"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="68"/>
       <c r="F87" s="69"/>
       <c r="G87" s="69"/>
@@ -9778,8 +9773,8 @@
       <c r="L87" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M87" s="162"/>
-      <c r="N87" s="163"/>
+      <c r="M87" s="161"/>
+      <c r="N87" s="162"/>
       <c r="O87" s="118"/>
       <c r="P87" s="118"/>
       <c r="Q87" s="48">
@@ -9819,8 +9814,8 @@
       <c r="B88" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="161"/>
-      <c r="D88" s="161"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="68"/>
       <c r="F88" s="69"/>
       <c r="G88" s="69"/>
@@ -9829,19 +9824,19 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>10059</v>
+        <v>9324</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M88" s="162"/>
-      <c r="N88" s="163"/>
+      <c r="M88" s="161"/>
+      <c r="N88" s="162"/>
       <c r="O88" s="118"/>
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>62.86875</v>
+        <v>58.275</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9865,7 +9860,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>31.4</v>
+        <v>29.1</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9876,8 +9871,8 @@
       <c r="B89" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="161"/>
-      <c r="D89" s="161"/>
+      <c r="C89" s="160"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="68"/>
       <c r="F89" s="69"/>
       <c r="G89" s="69"/>
@@ -9886,19 +9881,19 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>2858</v>
+        <v>2833</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="162"/>
-      <c r="N89" s="163"/>
+      <c r="M89" s="161"/>
+      <c r="N89" s="162"/>
       <c r="O89" s="118"/>
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>17.8625</v>
+        <v>17.70625</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -9933,8 +9928,8 @@
       <c r="B90" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="164"/>
-      <c r="D90" s="164"/>
+      <c r="C90" s="163"/>
+      <c r="D90" s="163"/>
       <c r="E90" s="73"/>
       <c r="F90" s="74"/>
       <c r="G90" s="74"/>
@@ -9949,31 +9944,31 @@
       <c r="L90" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="M90" s="165"/>
-      <c r="N90" s="166"/>
-      <c r="O90" s="167"/>
-      <c r="P90" s="167"/>
+      <c r="M90" s="164"/>
+      <c r="N90" s="165"/>
+      <c r="O90" s="166"/>
+      <c r="P90" s="166"/>
       <c r="Q90" s="77">
         <f>+J90/H90</f>
         <v>0</v>
       </c>
-      <c r="R90" s="168"/>
-      <c r="S90" s="168"/>
-      <c r="T90" s="168"/>
-      <c r="U90" s="169"/>
-      <c r="V90" s="170"/>
-      <c r="W90" s="168"/>
-      <c r="X90" s="170"/>
-      <c r="Y90" s="168"/>
-      <c r="Z90" s="168"/>
-      <c r="AA90" s="168"/>
-      <c r="AB90" s="168"/>
-      <c r="AC90" s="171"/>
-      <c r="AD90" s="172"/>
-      <c r="AE90" s="168"/>
-      <c r="AF90" s="168"/>
-      <c r="AG90" s="168"/>
-      <c r="AH90" s="168"/>
+      <c r="R90" s="167"/>
+      <c r="S90" s="167"/>
+      <c r="T90" s="167"/>
+      <c r="U90" s="168"/>
+      <c r="V90" s="169"/>
+      <c r="W90" s="167"/>
+      <c r="X90" s="169"/>
+      <c r="Y90" s="167"/>
+      <c r="Z90" s="167"/>
+      <c r="AA90" s="167"/>
+      <c r="AB90" s="167"/>
+      <c r="AC90" s="170"/>
+      <c r="AD90" s="171"/>
+      <c r="AE90" s="167"/>
+      <c r="AF90" s="167"/>
+      <c r="AG90" s="167"/>
+      <c r="AH90" s="167"/>
       <c r="AI90" s="78">
         <v>0</v>
       </c>
@@ -9984,32 +9979,32 @@
       <c r="AN90" s="114"/>
     </row>
     <row r="91" ht="18.75" customHeight="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A91" s="173" t="s">
+      <c r="A91" s="172" t="s">
         <v>215</v>
       </c>
-      <c r="B91" s="173" t="s">
+      <c r="B91" s="172" t="s">
         <v>216</v>
       </c>
-      <c r="C91" s="173"/>
-      <c r="D91" s="173"/>
-      <c r="E91" s="173"/>
-      <c r="F91" s="173"/>
-      <c r="G91" s="173"/>
-      <c r="H91" s="173">
+      <c r="C91" s="172"/>
+      <c r="D91" s="172"/>
+      <c r="E91" s="172"/>
+      <c r="F91" s="172"/>
+      <c r="G91" s="172"/>
+      <c r="H91" s="172">
         <v>70</v>
       </c>
-      <c r="I91" s="173"/>
-      <c r="J91" s="174">
-        <v>0</v>
-      </c>
-      <c r="K91" s="174"/>
-      <c r="L91" s="174" t="s">
+      <c r="I91" s="172"/>
+      <c r="J91" s="173">
+        <v>0</v>
+      </c>
+      <c r="K91" s="173"/>
+      <c r="L91" s="173" t="s">
         <v>16</v>
       </c>
       <c r="M91" s="105"/>
       <c r="N91" s="28"/>
       <c r="P91" s="106"/>
-      <c r="Q91" s="174"/>
+      <c r="Q91" s="173"/>
       <c r="U91" s="82"/>
       <c r="AC91" s="28"/>
       <c r="AG91" s="28"/>
@@ -10018,43 +10013,43 @@
       <c r="AJ91" s="28"/>
     </row>
     <row r="92" ht="18.75" customHeight="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A92" s="173" t="s">
+      <c r="A92" s="172" t="s">
         <v>217</v>
       </c>
-      <c r="B92" s="173" t="s">
+      <c r="B92" s="172" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="173"/>
-      <c r="D92" s="173"/>
-      <c r="E92" s="173"/>
-      <c r="F92" s="173"/>
-      <c r="G92" s="173"/>
-      <c r="H92" s="173">
+      <c r="C92" s="172"/>
+      <c r="D92" s="172"/>
+      <c r="E92" s="172"/>
+      <c r="F92" s="172"/>
+      <c r="G92" s="172"/>
+      <c r="H92" s="172">
         <v>70</v>
       </c>
-      <c r="I92" s="173"/>
-      <c r="J92" s="174">
-        <v>0</v>
-      </c>
-      <c r="K92" s="174"/>
-      <c r="L92" s="174" t="s">
+      <c r="I92" s="172"/>
+      <c r="J92" s="173">
+        <v>0</v>
+      </c>
+      <c r="K92" s="173"/>
+      <c r="L92" s="173" t="s">
         <v>16</v>
       </c>
       <c r="M92" s="105">
         <f>+J92-N92</f>
         <v>0</v>
       </c>
-      <c r="N92" s="174">
+      <c r="N92" s="173">
         <f>+IFERROR(VLOOKUP(A92,$R$26:$U$119,4,FALSE),0)-0</f>
         <v>0</v>
       </c>
-      <c r="P92" s="175">
+      <c r="P92" s="174">
         <f>J92-IFERROR(VLOOKUP(A92,$R$26:$U$119,4,FALSE),0)+0</f>
         <v>0</v>
       </c>
-      <c r="Q92" s="174"/>
+      <c r="Q92" s="173"/>
       <c r="U92" s="82"/>
-      <c r="AC92" s="176"/>
+      <c r="AC92" s="175"/>
       <c r="AG92" s="28"/>
       <c r="AH92" s="28"/>
       <c r="AI92" s="28"/>
@@ -10073,7 +10068,7 @@
       <c r="P93" s="106"/>
       <c r="Q93" s="81"/>
       <c r="U93" s="82"/>
-      <c r="AC93" s="176"/>
+      <c r="AC93" s="175"/>
     </row>
     <row r="94" ht="26.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="82"/>
@@ -10087,31 +10082,31 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>471958</v>
+        <v>422665</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
-      <c r="M94" s="177">
+      <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>158720</v>
+        <v>112150</v>
       </c>
       <c r="N94" s="82"/>
-      <c r="O94" s="178">
+      <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>666436</v>
-      </c>
-      <c r="P94" s="179">
+        <v>709312</v>
+      </c>
+      <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>256692</v>
+        <v>210122</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5263.596365276879</v>
+        <v>4810.363303167421</v>
       </c>
       <c r="R94" s="103"/>
-      <c r="U94" s="180"/>
+      <c r="U94" s="179"/>
       <c r="AB94" s="103"/>
-      <c r="AC94" s="176"/>
+      <c r="AC94" s="175"/>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="80"/>
@@ -10126,7 +10121,7 @@
       <c r="P95" s="107"/>
       <c r="Q95" s="81"/>
       <c r="R95" s="103"/>
-      <c r="U95" s="180"/>
+      <c r="U95" s="179"/>
       <c r="AB95" s="103"/>
       <c r="AC95" s="28"/>
     </row>
@@ -10191,7 +10186,7 @@
       <c r="P100" s="107"/>
       <c r="Q100" s="81"/>
       <c r="U100" s="82"/>
-      <c r="AC100" s="174">
+      <c r="AC100" s="173">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -10204,19 +10199,19 @@
         <f>+J101-N101</f>
         <v>0</v>
       </c>
-      <c r="N101" s="174">
+      <c r="N101" s="173">
         <f>+IFERROR(VLOOKUP(A101,$R$26:$U$119,4,FALSE),0)-0</f>
         <v>0</v>
       </c>
-      <c r="P101" s="175">
+      <c r="P101" s="174">
         <f>J101-IFERROR(VLOOKUP(A101,$R$26:$U$119,4,FALSE),0)+0</f>
         <v>0</v>
       </c>
       <c r="Q101" s="81"/>
       <c r="R101" s="103"/>
-      <c r="U101" s="180"/>
+      <c r="U101" s="179"/>
       <c r="AB101" s="103"/>
-      <c r="AC101" s="174">
+      <c r="AC101" s="173">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -10245,7 +10240,7 @@
       <c r="P103" s="107"/>
       <c r="Q103" s="81"/>
       <c r="R103" s="103"/>
-      <c r="U103" s="180"/>
+      <c r="U103" s="179"/>
       <c r="AB103" s="103"/>
       <c r="AC103" s="28">
         <f t="shared" si="14"/>
@@ -10261,7 +10256,7 @@
       <c r="P104" s="107"/>
       <c r="Q104" s="81"/>
       <c r="R104" s="103"/>
-      <c r="U104" s="180"/>
+      <c r="U104" s="179"/>
       <c r="AB104" s="103"/>
       <c r="AC104" s="28">
         <f t="shared" si="14"/>
@@ -10277,7 +10272,7 @@
       <c r="P105" s="107"/>
       <c r="Q105" s="81"/>
       <c r="R105" s="103"/>
-      <c r="U105" s="180"/>
+      <c r="U105" s="179"/>
       <c r="AB105" s="103"/>
       <c r="AC105" s="28">
         <f t="shared" si="14"/>
@@ -10290,12 +10285,12 @@
       <c r="L106" s="28"/>
       <c r="M106" s="105"/>
       <c r="N106" s="85"/>
-      <c r="O106" s="181"/>
+      <c r="O106" s="180"/>
       <c r="P106" s="106"/>
       <c r="Q106" s="81"/>
       <c r="R106" s="103"/>
       <c r="S106" s="28"/>
-      <c r="U106" s="180"/>
+      <c r="U106" s="179"/>
       <c r="AB106" s="103"/>
       <c r="AC106" s="85">
         <f>+IFERROR(VLOOKUP(T106,$R$26:$U$119,4,FALSE),0)-0-1920-640-320</f>
@@ -10311,7 +10306,7 @@
       <c r="P107" s="107"/>
       <c r="Q107" s="81"/>
       <c r="R107" s="103"/>
-      <c r="U107" s="180"/>
+      <c r="U107" s="179"/>
       <c r="AB107" s="103"/>
       <c r="AC107" s="28">
         <f>+IFERROR(VLOOKUP(T107,$R$26:$U$119,4,FALSE),0)</f>
@@ -10324,12 +10319,12 @@
       <c r="L108" s="28"/>
       <c r="M108" s="105"/>
       <c r="N108" s="85"/>
-      <c r="O108" s="181"/>
+      <c r="O108" s="180"/>
       <c r="P108" s="106"/>
       <c r="Q108" s="81"/>
-      <c r="R108" s="182"/>
-      <c r="S108" s="183"/>
-      <c r="U108" s="180"/>
+      <c r="R108" s="181"/>
+      <c r="S108" s="182"/>
+      <c r="U108" s="179"/>
       <c r="AB108" s="103"/>
       <c r="AC108" s="85">
         <f>+IFERROR(VLOOKUP(T108,$R$26:$U$119,4,FALSE),0)-0-2964-3588-2730-5226-1716-1716-2340-3354</f>
@@ -10345,8 +10340,8 @@
       <c r="P109" s="107"/>
       <c r="Q109" s="81"/>
       <c r="R109" s="103"/>
-      <c r="S109" s="183"/>
-      <c r="U109" s="180"/>
+      <c r="S109" s="182"/>
+      <c r="U109" s="179"/>
       <c r="AB109" s="103"/>
       <c r="AC109" s="28">
         <f>+IFERROR(VLOOKUP(T109,$R$26:$U$119,4,FALSE),0)</f>
@@ -10359,11 +10354,11 @@
       <c r="L110" s="28"/>
       <c r="M110" s="105"/>
       <c r="N110" s="85"/>
-      <c r="O110" s="181"/>
+      <c r="O110" s="180"/>
       <c r="P110" s="106"/>
       <c r="Q110" s="81"/>
       <c r="R110" s="103"/>
-      <c r="U110" s="180"/>
+      <c r="U110" s="179"/>
       <c r="AB110" s="103"/>
       <c r="AC110" s="85">
         <f>+IFERROR(VLOOKUP(T110,$R$26:$U$119,4,FALSE),0)-0-1950-1482-702</f>
@@ -10379,7 +10374,7 @@
       <c r="P111" s="107"/>
       <c r="Q111" s="81"/>
       <c r="R111" s="103"/>
-      <c r="U111" s="180"/>
+      <c r="U111" s="179"/>
       <c r="AB111" s="103"/>
       <c r="AC111" s="28">
         <f>+IFERROR(VLOOKUP(T111,$R$26:$U$119,4,FALSE),0)</f>
@@ -10409,7 +10404,7 @@
       <c r="L113" s="28"/>
       <c r="M113" s="105"/>
       <c r="N113" s="85"/>
-      <c r="O113" s="181"/>
+      <c r="O113" s="180"/>
       <c r="P113" s="106"/>
       <c r="Q113" s="81"/>
       <c r="S113" s="28"/>
@@ -10435,7 +10430,7 @@
       <c r="J115" s="85"/>
       <c r="M115" s="105"/>
       <c r="N115" s="85"/>
-      <c r="O115" s="181"/>
+      <c r="O115" s="180"/>
       <c r="P115" s="106"/>
       <c r="Q115" s="81"/>
       <c r="S115" s="28"/>
@@ -10449,7 +10444,7 @@
       <c r="J116" s="85"/>
       <c r="M116" s="105"/>
       <c r="N116" s="85"/>
-      <c r="O116" s="181"/>
+      <c r="O116" s="180"/>
       <c r="P116" s="106"/>
       <c r="Q116" s="81"/>
       <c r="R116" s="28"/>
@@ -10463,10 +10458,10 @@
       <c r="J117" s="85"/>
       <c r="M117" s="105"/>
       <c r="N117" s="85"/>
-      <c r="O117" s="181"/>
+      <c r="O117" s="180"/>
       <c r="P117" s="106"/>
       <c r="Q117" s="81"/>
-      <c r="R117" s="184"/>
+      <c r="R117" s="183"/>
       <c r="U117" s="82"/>
       <c r="AC117" s="85">
         <f>+IFERROR(VLOOKUP(T117,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -10477,7 +10472,7 @@
       <c r="J118" s="85"/>
       <c r="M118" s="105"/>
       <c r="N118" s="85"/>
-      <c r="O118" s="181"/>
+      <c r="O118" s="180"/>
       <c r="P118" s="106"/>
       <c r="Q118" s="81"/>
       <c r="U118" s="82"/>
@@ -10490,7 +10485,7 @@
       <c r="J119" s="85"/>
       <c r="M119" s="105"/>
       <c r="N119" s="85"/>
-      <c r="O119" s="181"/>
+      <c r="O119" s="180"/>
       <c r="P119" s="107"/>
       <c r="Q119" s="81"/>
       <c r="U119" s="82"/>
@@ -10506,7 +10501,7 @@
     </row>
     <row r="121" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J121" s="28"/>
-      <c r="O121" s="185"/>
+      <c r="O121" s="184"/>
     </row>
     <row r="122" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O122" s="28"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.5833333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>72923</v>
+        <v>100603</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>911.5375</v>
+        <v>1257.5375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>42992</v>
+        <v>52357</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>537.4</v>
+        <v>654.4625</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11811</v>
+        <v>16371</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>147.6375</v>
+        <v>204.6375</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>219</v>
+        <v>8799</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>2.8076923076923075</v>
+        <v>112.8076923076923</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>788</v>
+        <v>6068</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>4.925</v>
+        <v>37.925</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>422665</v>
+        <v>478130</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4810.363303167421</v>
+        <v>5473.42580316742</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>34483+19160+19280</f>
-        <v>72923</v>
+        <f>34483+19160+19280+9600+8000+10080</f>
+        <v>100603</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>72923</v>
+        <v>100603</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-21715</v>
+        <v>-49395</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>92523</v>
+        <v>120203</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>911.5375</v>
+        <v>1257.5375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>27168+160+15664</f>
-        <v>42992</v>
+        <f>27168+160+15664+7125+2240</f>
+        <v>52357</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>42992</v>
+        <v>52357</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-42788</v>
+        <v>-52153</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>42992</v>
+        <v>52357</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>537.4</v>
+        <v>654.4625</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5729,8 +5729,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>11812-1</f>
-        <v>11811</v>
+        <f>11812-1+4080+480</f>
+        <v>16371</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>8335</v>
+        <v>12895</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5746,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-2454</v>
+        <v>-7014</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>8975</v>
+        <v>13535</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>147.6375</v>
+        <v>204.6375</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -6247,8 +6247,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>221-2</f>
-        <v>219</v>
+        <f>221-2+5460+3120</f>
+        <v>8799</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-28091</v>
+        <v>-19511</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6264,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>132722</v>
+        <v>124142</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-24893</v>
+        <v>-16313</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>2.8076923076923075</v>
+        <v>112.8076923076923</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6938,7 +6938,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <v>788</v>
+        <f>788+3520+1760</f>
+        <v>6068</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6946,7 +6947,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-47007</v>
+        <v>-41727</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6954,15 +6955,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>52570</v>
+        <v>47290</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-41727</v>
+        <v>-36447</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>4.925</v>
+        <v>37.925</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7002,7 +7003,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -9216,7 +9217,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -10082,26 +10083,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>422665</v>
+        <v>478130</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>112150</v>
+        <v>167615</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>709312</v>
+        <v>653847</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>210122</v>
+        <v>265587</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4810.363303167421</v>
+        <v>5473.42580316742</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="7335" yWindow="7335" windowWidth="21570" windowHeight="7845" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.5833333333321207</v>
+        <v>0.3541666666678793</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>100603</v>
+        <v>74427</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>1257.5375</v>
+        <v>930.3375</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>52357</v>
+        <v>35012</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>654.4625</v>
+        <v>437.65</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>72111</v>
+        <v>48002</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>901.3875</v>
+        <v>600.025</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13026</v>
+        <v>480</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>162.825</v>
+        <v>6</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16371</v>
+        <v>18711</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>204.6375</v>
+        <v>233.8875</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>229</v>
+        <v>6139</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>2.8625</v>
+        <v>76.7375</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>19969</v>
+        <v>12237</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>249.6125</v>
+        <v>152.9625</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>35</v>
+        <v>6639</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>0.4375</v>
+        <v>82.9875</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8799</v>
+        <v>20434</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>112.8076923076923</v>
+        <v>261.97435897435895</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13566</v>
+        <v>11705</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>173.92307692307693</v>
+        <v>150.06410256410257</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>14736</v>
+        <v>7921</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>188.92307692307693</v>
+        <v>101.55128205128206</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>37715</v>
+        <v>31071</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>483.52564102564105</v>
+        <v>398.34615384615387</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1228</v>
+        <v>13</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>15.743589743589743</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8127</v>
+        <v>6916</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>104.1923076923077</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>11.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6068</v>
+        <v>12953</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>37.925</v>
+        <v>80.95625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>888</v>
+        <v>268</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>5.55</v>
+        <v>1.675</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13118</v>
+        <v>8103</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>81.9875</v>
+        <v>50.64375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13144</v>
+        <v>7029</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>82.15</v>
+        <v>43.93125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4615</v>
+        <v>3120</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>28.84375</v>
+        <v>19.5</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>27</v>
+        <v>9017</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>0.54</v>
+        <v>180.34</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1092</v>
+        <v>3107</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>21.84</v>
+        <v>62.14</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4578</v>
+        <v>1039</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>91.56</v>
+        <v>20.78</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6142</v>
+        <v>862</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>38.3875</v>
+        <v>5.3875</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6804</v>
+        <v>1024</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>42.525</v>
+        <v>6.4</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13824</v>
+        <v>13400</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>86.4</v>
+        <v>83.75</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>4.333333333333333</v>
+        <v>1.6785714285714286</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7480</v>
+        <v>7026</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>149.6</v>
+        <v>140.52</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28956</v>
+        <v>28464</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>212.91176470588235</v>
+        <v>209.2941176470588</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9324</v>
+        <v>9068</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>58.275</v>
+        <v>56.675</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2833</v>
+        <v>2798</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>17.70625</v>
+        <v>17.4875</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>478130</v>
+        <v>387127</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>5473.42580316742</v>
+        <v>4502.528490357682</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46320</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="23">
-        <f>34483+19160+19280+9600+8000+10080</f>
-        <v>100603</v>
+        <f>25867+23680+24880</f>
+        <v>74427</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>100603</v>
+        <v>74427</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-49395</v>
+        <v>-23219</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>120203</v>
+        <v>94027</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>1257.5375</v>
+        <v>930.3375</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>27168+160+15664+7125+2240</f>
-        <v>52357</v>
+        <f>34852+160</f>
+        <v>35012</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>52357</v>
+        <v>35012</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-52153</v>
+        <v>-34808</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>52357</v>
+        <v>35012</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>654.4625</v>
+        <v>437.65</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5437,7 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>56512+15599</f>
-        <v>72111</v>
+        <v>48002</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5445,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>48695</v>
+        <v>24586</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5453,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-63662</v>
+        <v>-39553</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>53815</v>
+        <v>29706</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>901.3875</v>
+        <v>600.025</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5514,7 +5513,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5535,7 +5534,7 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>13026</v>
+        <v>480</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5543,7 +5542,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>13023</v>
+        <v>477</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5551,15 +5550,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-7421</v>
+        <v>5125</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>17743</v>
+        <v>5197</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>162.825</v>
+        <v>6</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5611,7 +5610,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5729,8 +5728,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>11812-1+4080+480</f>
-        <v>16371</v>
+        <f>1352-1+17360</f>
+        <v>18711</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5738,7 +5737,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>12895</v>
+        <v>15235</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5746,15 +5745,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-7014</v>
+        <v>-9354</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>13535</v>
+        <v>15875</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>204.6375</v>
+        <v>233.8875</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5909,7 +5908,8 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>229</v>
+        <f>139+6000</f>
+        <v>6139</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>228</v>
+        <v>6138</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5925,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>296</v>
+        <v>-5614</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>228</v>
+        <v>6138</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>2.8625</v>
+        <v>76.7375</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>12.8</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>19969</v>
+        <v>12237</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>19969</v>
+        <v>12237</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6092,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-19969</v>
+        <v>-12237</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>19969</v>
+        <v>12237</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>249.6125</v>
+        <v>152.9625</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,7 +6162,8 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <v>35</v>
+        <f>25+6614</f>
+        <v>6639</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6170,7 +6171,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-50895</v>
+        <v>-44291</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6178,15 +6179,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-35</v>
+        <v>-6639</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-50895</v>
+        <v>-44291</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>0.4375</v>
+        <v>82.9875</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6226,7 +6227,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>13.8</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6247,8 +6248,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>221-2+5460+3120</f>
-        <v>8799</v>
+        <f>156-2+20280</f>
+        <v>20434</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6256,7 +6257,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-19511</v>
+        <v>-7876</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6264,15 +6265,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>124142</v>
+        <v>112507</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-16313</v>
+        <v>-4678</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>112.8076923076923</v>
+        <v>261.97435897435895</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6312,7 +6313,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6333,8 +6334,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>13722-156</f>
-        <v>13566</v>
+        <f>11861-156</f>
+        <v>11705</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6342,7 +6343,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-3985</v>
+        <v>-5846</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6350,15 +6351,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>38328</v>
+        <v>40189</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-1879</v>
+        <v>-3740</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>173.92307692307693</v>
+        <v>150.06410256410257</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6398,7 +6399,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6419,8 +6420,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="40">
-        <f>14737-1</f>
-        <v>14736</v>
+        <f>7922-1</f>
+        <v>7921</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6428,7 +6429,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>6891</v>
+        <v>76</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6436,15 +6437,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>2726</v>
+        <v>9541</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>9387</v>
+        <v>2572</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>188.92307692307693</v>
+        <v>101.55128205128206</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6484,7 +6485,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6505,8 +6506,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <f>24236+13479</f>
-        <v>37715</v>
+        <v>31071</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>14436</v>
+        <v>7792</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6522,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>1882</v>
+        <v>8526</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>17088</v>
+        <v>10444</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>483.52564102564105</v>
+        <v>398.34615384615387</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6660,8 +6660,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="40">
-        <f>1229-1</f>
-        <v>1228</v>
+        <f>14-1</f>
+        <v>13</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>1228</v>
+        <v>13</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6677,15 +6677,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>49738</v>
+        <v>50953</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>1930</v>
+        <v>715</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>15.743589743589743</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>8127</v>
+        <v>6916</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>8127</v>
+        <v>6916</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6884,15 +6884,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>42839</v>
+        <v>44050</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>8829</v>
+        <v>7618</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>104.1923076923077</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>11.6</v>
+        <v>9.9</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6938,8 +6938,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="23">
-        <f>788+3520+1760</f>
-        <v>6068</v>
+        <f>1273+11680</f>
+        <v>12953</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-41727</v>
+        <v>-34842</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6955,15 +6955,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>47290</v>
+        <v>40405</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-36447</v>
+        <v>-29562</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>37.925</v>
+        <v>80.95625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>888</v>
+        <v>268</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-10215</v>
+        <v>-10835</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7040,15 +7040,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>19220</v>
+        <v>19840</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-9255</v>
+        <v>-9875</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>5.55</v>
+        <v>1.675</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>13118</v>
+        <v>8103</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>10156</v>
+        <v>5141</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7114,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-6874</v>
+        <v>-1859</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>11916</v>
+        <v>6901</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>81.9875</v>
+        <v>50.64375</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <v>13144</v>
+        <v>7029</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>13138</v>
+        <v>7023</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7252,15 +7252,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>17346</v>
+        <v>23461</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>16018</v>
+        <v>9903</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>82.15</v>
+        <v>43.93125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>4615</v>
+        <v>3120</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7489,7 +7489,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>28.84375</v>
+        <v>19.5</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8265,7 +8265,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <v>27</v>
+        <f>17+6200+1400+1400</f>
+        <v>9017</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8273,7 +8274,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>9017</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8281,15 +8282,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>52579</v>
+        <v>43589</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>6177</v>
+        <v>15167</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>0.54</v>
+        <v>180.34</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8313,7 +8314,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8543,7 +8544,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="48">
-        <v>1092</v>
+        <v>3107</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8551,7 +8552,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>1092</v>
+        <v>3107</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8559,15 +8560,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>51514</v>
+        <v>49499</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>7242</v>
+        <v>9257</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>21.84</v>
+        <v>62.14</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8591,7 +8592,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8611,8 +8612,9 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="33">
-        <v>4578</v>
+      <c r="J69" s="40">
+        <f>1043-3-1</f>
+        <v>1039</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8620,7 +8622,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>4578</v>
+        <v>1039</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8628,15 +8630,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>48028</v>
+        <v>51567</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>10728</v>
+        <v>7189</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>91.56</v>
+        <v>20.78</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8660,7 +8662,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8945,7 +8947,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>6142</v>
+        <v>862</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8953,7 +8955,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>6142</v>
+        <v>862</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8962,11 +8964,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>6142</v>
+        <v>862</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>38.3875</v>
+        <v>5.3875</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8990,7 +8992,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9011,8 +9013,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>6805-1</f>
-        <v>6804</v>
+        <f>1025-1</f>
+        <v>1024</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9020,7 +9022,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>6804</v>
+        <v>1024</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9029,11 +9031,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>6804</v>
+        <v>1024</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>42.525</v>
+        <v>6.4</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9057,7 +9059,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9143,8 +9145,9 @@
         <v>160</v>
       </c>
       <c r="I77" s="58"/>
-      <c r="J77" s="33">
-        <v>13824</v>
+      <c r="J77" s="37">
+        <f>8919+1+4480</f>
+        <v>13400</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9152,7 +9155,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>13824</v>
+        <v>13400</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9161,11 +9164,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>13824</v>
+        <v>13400</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>86.4</v>
+        <v>83.75</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9189,7 +9192,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9474,7 +9477,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9482,7 +9485,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9491,11 +9494,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>4.333333333333333</v>
+        <v>1.6785714285714286</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9540,7 +9543,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>7480</v>
+        <v>7026</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9552,7 +9555,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>149.6</v>
+        <v>140.52</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9576,7 +9579,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9597,7 +9600,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>28956</v>
+        <v>28464</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9609,7 +9612,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>212.91176470588235</v>
+        <v>209.2941176470588</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9633,7 +9636,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9825,7 +9828,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>9324</v>
+        <v>9068</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9837,7 +9840,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>58.275</v>
+        <v>56.675</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9861,7 +9864,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9882,7 +9885,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>2833</v>
+        <v>2798</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9894,7 +9897,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>17.70625</v>
+        <v>17.4875</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10083,26 +10086,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>478130</v>
+        <v>387127</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>167615</v>
+        <v>79344</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>653847</v>
+        <v>730411</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>265587</v>
+        <v>177316</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>5473.42580316742</v>
+        <v>4502.528490357682</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="7335" yWindow="7335" windowWidth="21570" windowHeight="7845" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="28" name="Existencia Sistema" state="visible" r:id="rId4"/>
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>74427</v>
+        <v>76189</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>930.3375</v>
+        <v>952.3625</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>35012</v>
+        <v>23648</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>437.65</v>
+        <v>295.6</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>48002</v>
+        <v>56226</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>600.025</v>
+        <v>702.825</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>480</v>
+        <v>2192</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>27.4</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18711</v>
+        <v>25637</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>233.8875</v>
+        <v>320.4625</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6139</v>
+        <v>15612</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>76.7375</v>
+        <v>195.15</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12237</v>
+        <v>7068</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>152.9625</v>
+        <v>88.35</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6639</v>
+        <v>6075</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>82.9875</v>
+        <v>75.9375</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>20434</v>
+        <v>9650</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>261.97435897435895</v>
+        <v>123.71794871794872</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11705</v>
+        <v>9523</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>150.06410256410257</v>
+        <v>122.08974358974359</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7921</v>
+        <v>4681</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>101.55128205128206</v>
+        <v>60.01282051282051</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>31071</v>
+        <v>32342</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>398.34615384615387</v>
+        <v>414.64102564102564</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>8.9</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13</v>
+        <v>13626</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>174.69230769230768</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6916</v>
+        <v>5853</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>88.66666666666667</v>
+        <v>75.03846153846153</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>9.9</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12953</v>
+        <v>4800</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>80.95625</v>
+        <v>30</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>268</v>
+        <v>3098</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>1.675</v>
+        <v>19.3625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8103</v>
+        <v>13739</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>50.64375</v>
+        <v>85.86875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7029</v>
+        <v>2093</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>43.93125</v>
+        <v>13.08125</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3120</v>
+        <v>2562</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>19.5</v>
+        <v>16.0125</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9017</v>
+        <v>13984</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>180.34</v>
+        <v>279.68</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3107</v>
+        <v>12</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>62.14</v>
+        <v>0.24</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1039</v>
+        <v>3475</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>20.78</v>
+        <v>69.5</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>862</v>
+        <v>482</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>5.3875</v>
+        <v>3.0125</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>1024</v>
+        <v>124</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>6.4</v>
+        <v>0.775</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
       </c>
       <c r="J31" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13400</v>
+        <v>8983</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>83.75</v>
+        <v>56.14375</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>1.6785714285714286</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7026</v>
+        <v>6584</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>140.52</v>
+        <v>131.68</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28464</v>
+        <v>28203</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>209.2941176470588</v>
+        <v>207.375</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9068</v>
+        <v>8723</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>56.675</v>
+        <v>54.51875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>28.3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2798</v>
+        <v>2774</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>17.4875</v>
+        <v>17.3375</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>387127</v>
+        <v>388009</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4502.528490357682</v>
+        <v>4613.475366300366</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46321</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.75</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5236,9 +5236,9 @@
         <v>80</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="23">
-        <f>25867+23680+24880</f>
-        <v>74427</v>
+      <c r="J24" s="40">
+        <f>44419-1+13451+18320</f>
+        <v>76189</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>74427</v>
+        <v>76189</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-23219</v>
+        <v>-24981</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>94027</v>
+        <v>95789</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>930.3375</v>
+        <v>952.3625</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>34852+160</f>
-        <v>35012</v>
+        <f>23488+160</f>
+        <v>23648</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>35012</v>
+        <v>23648</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-34808</v>
+        <v>-23444</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>35012</v>
+        <v>23648</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>437.65</v>
+        <v>295.6</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,7 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <v>48002</v>
+        <f>34826+21400</f>
+        <v>56226</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5445,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>24586</v>
+        <v>32810</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5453,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-39553</v>
+        <v>-47777</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>29706</v>
+        <v>37930</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>600.025</v>
+        <v>702.825</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5513,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,7 +5535,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="33">
-        <v>480</v>
+        <f>32+2160</f>
+        <v>2192</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5542,7 +5544,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>477</v>
+        <v>2189</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5550,15 +5552,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>5125</v>
+        <v>3413</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>5197</v>
+        <v>6909</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>27.4</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5610,7 +5612,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5728,8 +5730,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>1352-1+17360</f>
-        <v>18711</v>
+        <f>9958-1+15680</f>
+        <v>25637</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5737,7 +5739,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>15235</v>
+        <v>22161</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5745,15 +5747,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-9354</v>
+        <v>-16280</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>15875</v>
+        <v>22801</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>233.8875</v>
+        <v>320.4625</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5805,7 +5807,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5908,8 +5910,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <f>139+6000</f>
-        <v>6139</v>
+        <v>15612</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5917,7 +5918,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>6138</v>
+        <v>15611</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5925,15 +5926,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-5614</v>
+        <v>-15087</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>6138</v>
+        <v>15611</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>76.7375</v>
+        <v>195.15</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5973,7 +5974,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>12.8</v>
+        <v>32.5</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6076,7 +6077,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <v>12237</v>
+        <f>4828+2240</f>
+        <v>7068</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6084,7 +6086,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>12237</v>
+        <v>7068</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6092,15 +6094,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-12237</v>
+        <v>-7068</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>12237</v>
+        <v>7068</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>152.9625</v>
+        <v>88.35</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6140,7 +6142,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6162,8 +6164,7 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33">
-        <f>25+6614</f>
-        <v>6639</v>
+        <v>6075</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6171,7 +6172,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-44291</v>
+        <v>-44855</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6179,15 +6180,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-6639</v>
+        <v>-6075</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-44291</v>
+        <v>-44855</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>82.9875</v>
+        <v>75.9375</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6227,7 +6228,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6248,8 +6249,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>156-2+20280</f>
-        <v>20434</v>
+        <f>7468-2+2184</f>
+        <v>9650</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6257,7 +6258,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-7876</v>
+        <v>-18660</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6265,15 +6266,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>112507</v>
+        <v>123291</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-4678</v>
+        <v>-15462</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>261.97435897435895</v>
+        <v>123.71794871794872</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6313,7 +6314,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6334,8 +6335,8 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="40">
-        <f>11861-156</f>
-        <v>11705</v>
+        <f>9679-156</f>
+        <v>9523</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6343,7 +6344,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-5846</v>
+        <v>-8028</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6351,15 +6352,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>40189</v>
+        <v>42371</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-3740</v>
+        <v>-5922</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>150.06410256410257</v>
+        <v>122.08974358974359</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6399,7 +6400,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>10.7</v>
+        <v>8.7</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6420,8 +6421,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="40">
-        <f>7922-1</f>
-        <v>7921</v>
+        <f>2888-1+1794</f>
+        <v>4681</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6429,7 +6430,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>-3164</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6437,15 +6438,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>9541</v>
+        <v>12781</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>2572</v>
+        <v>-668</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>101.55128205128206</v>
+        <v>60.01282051282051</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6485,7 +6486,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6506,7 +6507,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>31071</v>
+        <v>32342</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6514,7 +6515,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>7792</v>
+        <v>9063</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6522,15 +6523,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>8526</v>
+        <v>7255</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>10444</v>
+        <v>11715</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>398.34615384615387</v>
+        <v>414.64102564102564</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6570,7 +6571,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>8.9</v>
+        <v>9.2</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6660,8 +6661,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="40">
-        <f>14-1</f>
-        <v>13</v>
+        <f>2042-1+11585</f>
+        <v>13626</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6669,7 +6670,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>13</v>
+        <v>13626</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6677,15 +6678,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>50953</v>
+        <v>37340</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>715</v>
+        <v>14328</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>0.16666666666666666</v>
+        <v>174.69230769230768</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6709,7 +6710,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6868,7 +6869,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>6916</v>
+        <v>5853</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6876,7 +6877,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>6916</v>
+        <v>5853</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6884,15 +6885,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>44050</v>
+        <v>45113</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>7618</v>
+        <v>6555</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>88.66666666666667</v>
+        <v>75.03846153846153</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6916,7 +6917,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>9.9</v>
+        <v>8.3</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6937,9 +6938,9 @@
         <v>160</v>
       </c>
       <c r="I44" s="44"/>
-      <c r="J44" s="23">
-        <f>1273+11680</f>
-        <v>12953</v>
+      <c r="J44" s="37">
+        <f>4799+1</f>
+        <v>4800</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6947,7 +6948,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-34842</v>
+        <v>-42995</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6955,15 +6956,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>40405</v>
+        <v>48558</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-29562</v>
+        <v>-37715</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>80.95625</v>
+        <v>30</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7003,7 +7004,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7024,7 +7025,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <v>268</v>
+        <f>58+3040</f>
+        <v>3098</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7032,7 +7034,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-10835</v>
+        <v>-8005</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7040,15 +7042,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>19840</v>
+        <v>17010</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-9875</v>
+        <v>-7045</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>1.675</v>
+        <v>19.3625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7076,7 +7078,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7098,7 +7100,8 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>8103</v>
+        <f>7717+6022</f>
+        <v>13739</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7106,7 +7109,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>5141</v>
+        <v>10777</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7114,15 +7117,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-1859</v>
+        <v>-7495</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>6901</v>
+        <v>12537</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>50.64375</v>
+        <v>85.86875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7146,7 +7149,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7236,7 +7239,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <v>7029</v>
+        <f>2093</f>
+        <v>2093</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7244,7 +7248,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>7023</v>
+        <v>2087</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7252,15 +7256,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>23461</v>
+        <v>28397</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>9903</v>
+        <v>4967</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>43.93125</v>
+        <v>13.08125</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7284,7 +7288,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7477,7 +7481,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>3120</v>
+        <v>2562</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7489,7 +7493,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>19.5</v>
+        <v>16.0125</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7513,7 +7517,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8265,8 +8269,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>17+6200+1400+1400</f>
-        <v>9017</v>
+        <f>5934+8050</f>
+        <v>13984</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8274,7 +8278,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>9017</v>
+        <v>13984</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8282,15 +8286,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>43589</v>
+        <v>38622</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>15167</v>
+        <v>20134</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>180.34</v>
+        <v>279.68</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8314,7 +8318,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8544,7 +8548,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="48">
-        <v>3107</v>
+        <v>12</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8552,7 +8556,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>3107</v>
+        <v>12</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8560,15 +8564,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>49499</v>
+        <v>52594</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>9257</v>
+        <v>6162</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>62.14</v>
+        <v>0.24</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8592,7 +8596,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8613,8 +8617,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="40">
-        <f>1043-3-1</f>
-        <v>1039</v>
+        <f>77-1-1+1400+1400+600</f>
+        <v>3475</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8622,7 +8626,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>1039</v>
+        <v>3475</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8630,15 +8634,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>51567</v>
+        <v>49131</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>7189</v>
+        <v>9625</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>20.78</v>
+        <v>69.5</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8662,7 +8666,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8947,7 +8951,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>862</v>
+        <v>482</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8955,7 +8959,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>862</v>
+        <v>482</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8964,11 +8968,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>862</v>
+        <v>482</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>5.3875</v>
+        <v>3.0125</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8992,7 +8996,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9013,8 +9017,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>1025-1</f>
-        <v>1024</v>
+        <f>125-1</f>
+        <v>124</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9022,7 +9026,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>1024</v>
+        <v>124</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9031,11 +9035,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>1024</v>
+        <v>124</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>6.4</v>
+        <v>0.775</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9059,7 +9063,7 @@
       </c>
       <c r="AJ75" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AN75" s="114"/>
     </row>
@@ -9145,9 +9149,8 @@
         <v>160</v>
       </c>
       <c r="I77" s="58"/>
-      <c r="J77" s="37">
-        <f>8919+1+4480</f>
-        <v>13400</v>
+      <c r="J77" s="33">
+        <v>8983</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9155,7 +9158,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>13400</v>
+        <v>8983</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9164,11 +9167,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>13400</v>
+        <v>8983</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>83.75</v>
+        <v>56.14375</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9192,7 +9195,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9220,7 +9223,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="124">
-        <f t="shared" ref="M78:M82" si="13">+J78-N78</f>
+        <f t="shared" ref="M78:M101" si="13">+J78-N78</f>
         <v>0</v>
       </c>
       <c r="N78" s="125">
@@ -9477,7 +9480,7 @@
       </c>
       <c r="I82" s="62"/>
       <c r="J82" s="65">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9485,7 +9488,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9494,11 +9497,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>1.6785714285714286</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9543,7 +9546,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>7026</v>
+        <v>6584</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9555,7 +9558,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>140.52</v>
+        <v>131.68</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9579,7 +9582,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9600,7 +9603,7 @@
       </c>
       <c r="I84" s="62"/>
       <c r="J84" s="65">
-        <v>28464</v>
+        <v>28203</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9612,7 +9615,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>209.2941176470588</v>
+        <v>207.375</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9636,7 +9639,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9828,7 +9831,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>9068</v>
+        <v>8723</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9840,7 +9843,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>56.675</v>
+        <v>54.51875</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9864,7 +9867,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>28.3</v>
+        <v>27.3</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9885,7 +9888,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>2798</v>
+        <v>2774</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9897,7 +9900,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>17.4875</v>
+        <v>17.3375</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10086,26 +10089,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>387127</v>
+        <v>388009</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>79344</v>
+        <v>81856</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>730411</v>
+        <v>722111</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>177316</v>
+        <v>179828</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4502.528490357682</v>
+        <v>4613.475366300366</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.3541666666678793</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>76189</v>
+        <v>30540</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>952.3625</v>
+        <v>381.75</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>23648</v>
+        <v>624</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>295.6</v>
+        <v>7.8</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>56226</v>
+        <v>15591</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>702.825</v>
+        <v>194.8875</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2192</v>
+        <v>32048</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>27.4</v>
+        <v>400.6</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>25637</v>
+        <v>28082</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>320.4625</v>
+        <v>351.025</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15612</v>
+        <v>15166</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>195.15</v>
+        <v>189.575</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>7068</v>
+        <v>18446</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>88.35</v>
+        <v>230.575</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6075</v>
+        <v>4954</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>75.9375</v>
+        <v>61.925</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>12.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9650</v>
+        <v>15709</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>123.71794871794872</v>
+        <v>201.39743589743588</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>9523</v>
+        <v>4605</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>122.08974358974359</v>
+        <v>59.03846153846154</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>8.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4681</v>
+        <v>2370</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>60.01282051282051</v>
+        <v>30.384615384615383</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32342</v>
+        <v>16028</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>414.64102564102564</v>
+        <v>205.48717948717947</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>9.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13626</v>
+        <v>11070</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>174.69230769230768</v>
+        <v>141.92307692307693</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5853</v>
+        <v>2396</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>75.03846153846153</v>
+        <v>30.71794871794872</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>8.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4800</v>
+        <v>585</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>3.65625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
       </c>
       <c r="J21" s="47">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3098</v>
+        <v>24426</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>19.3625</v>
+        <v>152.6625</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13739</v>
+        <v>527</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>85.86875</v>
+        <v>3.29375</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2093</v>
+        <v>2683</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>13.08125</v>
+        <v>16.76875</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2562</v>
+        <v>912</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>16.0125</v>
+        <v>5.7</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>13984</v>
+        <v>12371</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>279.68</v>
+        <v>247.42</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>2.94</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>3475</v>
+        <v>195</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>69.5</v>
+        <v>3.9</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
       </c>
       <c r="J29" s="36">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
       <c r="D30" s="53"/>
       <c r="E30" s="23">
         <f>VLOOKUP(A30,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>482</v>
+        <v>162</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="45" t="s">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="H30" s="23">
         <f t="shared" si="1"/>
-        <v>3.0125</v>
+        <v>1.0125</v>
       </c>
       <c r="I30" s="46">
         <v>15</v>
       </c>
       <c r="J30" s="47">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="33">
         <f>VLOOKUP(A31,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="34" t="s">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="H31" s="33">
         <f t="shared" si="1"/>
-        <v>0.775</v>
+        <v>0.275</v>
       </c>
       <c r="I31" s="35">
         <v>24</v>
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8983</v>
+        <v>188</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>56.14375</v>
+        <v>1.175</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
       <c r="D38" s="62"/>
       <c r="E38" s="63">
         <f>VLOOKUP(A38,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="64" t="s">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="1"/>
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="I38" s="35">
         <v>0</v>
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>6584</v>
+        <v>5535</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>131.68</v>
+        <v>110.7</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28203</v>
+        <v>26650</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>207.375</v>
+        <v>195.9558823529412</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8723</v>
+        <v>8062</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>54.51875</v>
+        <v>50.3875</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
       <c r="D42" s="69"/>
       <c r="E42" s="48">
         <f>VLOOKUP(A42,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2774</v>
+        <v>2701</v>
       </c>
       <c r="F42" s="69"/>
       <c r="G42" s="70" t="s">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H42" s="48">
         <f>+E42/C42</f>
-        <v>17.3375</v>
+        <v>16.88125</v>
       </c>
       <c r="I42" s="35">
         <v>0</v>
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>388009</v>
+        <v>282818</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>4613.475366300366</v>
+        <v>3299.827420814479</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K2" s="7"/>
       <c r="AJ2" s="8">
-        <v>0.3333333333321207</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>44419-1+13451+18320</f>
-        <v>76189</v>
+        <f>301-1+18160+6960+3520+1600</f>
+        <v>30540</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>76189</v>
+        <v>30540</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>-24981</v>
+        <v>20668</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>95789</v>
+        <v>50140</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>952.3625</v>
+        <v>381.75</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>23488+160</f>
-        <v>23648</v>
+        <f>622+2</f>
+        <v>624</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>23648</v>
+        <v>624</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-23444</v>
+        <v>-420</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>23648</v>
+        <v>624</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>295.6</v>
+        <v>7.8</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>34826+21400</f>
-        <v>56226</v>
+        <f>8951+3120+3520</f>
+        <v>15591</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>32810</v>
+        <v>-7825</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-47777</v>
+        <v>-7142</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>37930</v>
+        <v>-2705</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>702.825</v>
+        <v>194.8875</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5534,9 +5534,9 @@
         <v>80</v>
       </c>
       <c r="I27" s="32"/>
-      <c r="J27" s="33">
-        <f>32+2160</f>
-        <v>2192</v>
+      <c r="J27" s="40">
+        <f>32128-80</f>
+        <v>32048</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>2189</v>
+        <v>32045</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5552,15 +5552,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>3413</v>
+        <v>-26443</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>6909</v>
+        <v>36765</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>27.4</v>
+        <v>400.6</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5730,8 +5730,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>9958-1+15680</f>
-        <v>25637</v>
+        <f>16266-1-10+11827</f>
+        <v>28082</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>22161</v>
+        <v>24606</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5747,15 +5747,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-16280</v>
+        <v>-18725</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>22801</v>
+        <v>25246</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>320.4625</v>
+        <v>351.025</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>15612</v>
+        <v>15166</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>15611</v>
+        <v>15165</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5926,15 +5926,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-15087</v>
+        <v>-14641</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>15611</v>
+        <v>15165</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>195.15</v>
+        <v>189.575</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6077,8 +6077,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>4828+2240</f>
-        <v>7068</v>
+        <f>46+14240+4160</f>
+        <v>18446</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>7068</v>
+        <v>18446</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6094,15 +6094,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-7068</v>
+        <v>-18446</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>7068</v>
+        <v>18446</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>88.35</v>
+        <v>230.575</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6163,8 +6163,9 @@
         <v>80</v>
       </c>
       <c r="I34" s="32"/>
-      <c r="J34" s="33">
-        <v>6075</v>
+      <c r="J34" s="37">
+        <f>4874+80</f>
+        <v>4954</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6172,7 +6173,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-44855</v>
+        <v>-45976</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6180,15 +6181,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-6075</v>
+        <v>-4954</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-44855</v>
+        <v>-45976</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>75.9375</v>
+        <v>61.925</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6228,7 +6229,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>12.7</v>
+        <v>10.3</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6249,8 +6250,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>7468-2+2184</f>
-        <v>9650</v>
+        <f>10105-2+5606</f>
+        <v>15709</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6258,7 +6259,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-18660</v>
+        <v>-12601</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6266,15 +6267,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>123291</v>
+        <v>117232</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-15462</v>
+        <v>-9403</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>123.71794871794872</v>
+        <v>201.39743589743588</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6314,7 +6315,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6334,9 +6335,8 @@
         <v>78</v>
       </c>
       <c r="I36" s="32"/>
-      <c r="J36" s="40">
-        <f>9679-156</f>
-        <v>9523</v>
+      <c r="J36" s="33">
+        <v>4605</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-8028</v>
+        <v>-12946</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6352,15 +6352,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>42371</v>
+        <v>47289</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-5922</v>
+        <v>-10840</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>122.08974358974359</v>
+        <v>59.03846153846154</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>8.7</v>
+        <v>4.2</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6421,8 +6421,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="40">
-        <f>2888-1+1794</f>
-        <v>4681</v>
+        <f>2371-1</f>
+        <v>2370</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-3164</v>
+        <v>-5475</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6438,15 +6438,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>12781</v>
+        <v>15092</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-668</v>
+        <v>-2979</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>60.01282051282051</v>
+        <v>30.384615384615383</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>32342</v>
+        <v>16028</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>9063</v>
+        <v>-7251</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6523,15 +6523,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>7255</v>
+        <v>23569</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>11715</v>
+        <v>-4599</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>414.64102564102564</v>
+        <v>205.48717948717947</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>9.2</v>
+        <v>4.6</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6661,8 +6661,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="40">
-        <f>2042-1+11585</f>
-        <v>13626</v>
+        <f>11071-1</f>
+        <v>11070</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>13626</v>
+        <v>11070</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6678,15 +6678,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>37340</v>
+        <v>39896</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>14328</v>
+        <v>11772</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>174.69230769230768</v>
+        <v>141.92307692307693</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>5853</v>
+        <v>2396</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>5853</v>
+        <v>2396</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6885,15 +6885,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>45113</v>
+        <v>48570</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>6555</v>
+        <v>3098</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>75.03846153846153</v>
+        <v>30.71794871794872</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>8.3</v>
+        <v>3.4</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6939,8 +6939,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="37">
-        <f>4799+1</f>
-        <v>4800</v>
+        <f>584+1</f>
+        <v>585</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-42995</v>
+        <v>-47210</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6956,15 +6956,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>48558</v>
+        <v>52773</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-37715</v>
+        <v>-41930</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>3.65625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="AJ44" s="47">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="AN44" s="114"/>
     </row>
@@ -7025,8 +7025,8 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <f>58+3040</f>
-        <v>3098</v>
+        <f>18036+6390</f>
+        <v>24426</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>-8005</v>
+        <v>13323</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7042,15 +7042,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>17010</v>
+        <v>-4318</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>-7045</v>
+        <v>14283</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>19.3625</v>
+        <v>152.6625</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>25.4</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7100,8 +7100,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <f>7717+6022</f>
-        <v>13739</v>
+        <v>527</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7109,7 +7108,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>10777</v>
+        <v>-2435</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7117,15 +7116,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>-7495</v>
+        <v>5717</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>12537</v>
+        <v>-675</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>85.86875</v>
+        <v>3.29375</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7149,7 +7148,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7239,8 +7238,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <f>2093</f>
-        <v>2093</v>
+        <f>123+2560</f>
+        <v>2683</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7248,7 +7247,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>2087</v>
+        <v>2677</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7256,15 +7255,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>28397</v>
+        <v>27807</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>4967</v>
+        <v>5557</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>13.08125</v>
+        <v>16.76875</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7288,7 +7287,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7481,7 +7480,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>2562</v>
+        <v>912</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7493,7 +7492,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>16.0125</v>
+        <v>5.7</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7517,7 +7516,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8269,8 +8268,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>5934+8050</f>
-        <v>13984</v>
+        <f>3471+8050+850</f>
+        <v>12371</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8278,7 +8277,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>13984</v>
+        <v>12371</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8286,15 +8285,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>38622</v>
+        <v>40235</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>20134</v>
+        <v>18521</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>279.68</v>
+        <v>247.42</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8318,7 +8317,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8548,7 +8547,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="48">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8556,7 +8555,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8564,15 +8563,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52594</v>
+        <v>52459</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6162</v>
+        <v>6297</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>0.24</v>
+        <v>2.94</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8596,7 +8595,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8617,8 +8616,8 @@
       </c>
       <c r="I69" s="58"/>
       <c r="J69" s="40">
-        <f>77-1-1+1400+1400+600</f>
-        <v>3475</v>
+        <f>197-2</f>
+        <v>195</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8626,7 +8625,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>3475</v>
+        <v>195</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8634,15 +8633,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>49131</v>
+        <v>52411</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>9625</v>
+        <v>6345</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>69.5</v>
+        <v>3.9</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -8666,7 +8665,7 @@
       </c>
       <c r="AJ69" s="36">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AN69" s="114"/>
     </row>
@@ -8951,7 +8950,7 @@
       </c>
       <c r="I74" s="53"/>
       <c r="J74" s="23">
-        <v>482</v>
+        <v>162</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="45" t="s">
@@ -8959,7 +8958,7 @@
       </c>
       <c r="M74" s="124">
         <f t="shared" si="1"/>
-        <v>482</v>
+        <v>162</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="8"/>
@@ -8968,11 +8967,11 @@
       <c r="O74" s="126"/>
       <c r="P74" s="127">
         <f t="shared" si="12"/>
-        <v>482</v>
+        <v>162</v>
       </c>
       <c r="Q74" s="23">
         <f t="shared" si="5"/>
-        <v>3.0125</v>
+        <v>1.0125</v>
       </c>
       <c r="R74" s="44"/>
       <c r="S74" s="44"/>
@@ -8996,7 +8995,7 @@
       </c>
       <c r="AJ74" s="47">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN74" s="114"/>
     </row>
@@ -9017,8 +9016,8 @@
       </c>
       <c r="I75" s="58"/>
       <c r="J75" s="40">
-        <f>125-1</f>
-        <v>124</v>
+        <f>45-1</f>
+        <v>44</v>
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="34" t="s">
@@ -9026,7 +9025,7 @@
       </c>
       <c r="M75" s="115">
         <f t="shared" si="1"/>
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="N75" s="116">
         <f t="shared" si="8"/>
@@ -9035,11 +9034,11 @@
       <c r="O75" s="117"/>
       <c r="P75" s="118">
         <f t="shared" si="12"/>
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="Q75" s="33">
         <f t="shared" si="5"/>
-        <v>0.775</v>
+        <v>0.275</v>
       </c>
       <c r="R75" s="32"/>
       <c r="S75" s="32"/>
@@ -9150,7 +9149,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>8983</v>
+        <v>188</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9158,7 +9157,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>8983</v>
+        <v>188</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9167,11 +9166,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>8983</v>
+        <v>188</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>56.14375</v>
+        <v>1.175</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9195,7 +9194,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9479,8 +9478,9 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="65">
-        <v>50</v>
+      <c r="J82" s="63">
+        <f>15-15</f>
+        <v>0</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="64" t="s">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="M82" s="115">
         <f t="shared" si="13"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N82" s="116">
         <f t="shared" si="8"/>
@@ -9497,11 +9497,11 @@
       <c r="O82" s="117"/>
       <c r="P82" s="118">
         <f t="shared" si="12"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="33">
         <f t="shared" si="5"/>
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="R82" s="32"/>
       <c r="S82" s="32"/>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>6584</v>
+        <v>5535</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9558,7 +9558,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>131.68</v>
+        <v>110.7</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,8 +9602,9 @@
         <v>136</v>
       </c>
       <c r="I84" s="62"/>
-      <c r="J84" s="65">
-        <v>28203</v>
+      <c r="J84" s="37">
+        <f>26635+15</f>
+        <v>26650</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9615,7 +9616,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>207.375</v>
+        <v>195.9558823529412</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9639,7 +9640,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9831,7 +9832,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>8723</v>
+        <v>8062</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9843,7 +9844,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>54.51875</v>
+        <v>50.3875</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9867,7 +9868,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -9888,7 +9889,7 @@
       </c>
       <c r="I89" s="69"/>
       <c r="J89" s="48">
-        <v>2774</v>
+        <v>2701</v>
       </c>
       <c r="K89" s="69"/>
       <c r="L89" s="70" t="s">
@@ -9900,7 +9901,7 @@
       <c r="P89" s="118"/>
       <c r="Q89" s="48">
         <f>+J89/H89</f>
-        <v>17.3375</v>
+        <v>16.88125</v>
       </c>
       <c r="R89" s="32"/>
       <c r="S89" s="32"/>
@@ -10089,26 +10090,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>388009</v>
+        <v>282818</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>81856</v>
+        <v>-18349</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>722111</v>
+        <v>813071</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>179828</v>
+        <v>79623</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>4613.475366300366</v>
+        <v>3299.827420814479</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>

--- a/uploads/logistica/stock-producto-terminado.xlsx
+++ b/uploads/logistica/stock-producto-terminado.xlsx
@@ -2989,7 +2989,7 @@
       <c r="F1" s="3"/>
       <c r="J1" s="4">
         <f>TODAY()</f>
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="J2" s="8">
-        <v>0.4375</v>
+        <v>0.3333333333321207</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       <c r="D5" s="22"/>
       <c r="E5" s="23">
         <f>VLOOKUP(A5,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>30540</v>
+        <v>23670</v>
       </c>
       <c r="F5" s="24"/>
       <c r="G5" s="24" t="s">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="H5" s="25">
         <f>+E5/C5</f>
-        <v>381.75</v>
+        <v>295.875</v>
       </c>
       <c r="I5" s="26">
         <v>804</v>
       </c>
       <c r="J5" s="27">
         <f t="shared" ref="J5:J43" si="0">IFERROR(ROUND((+H5/I5),1),0)</f>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3088,7 +3088,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="33">
         <f>VLOOKUP(A6,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>624</v>
+        <v>7143</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34" t="s">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" ref="H6:H41" si="1">+E6/C6</f>
-        <v>7.8</v>
+        <v>89.2875</v>
       </c>
       <c r="I6" s="35">
         <v>111</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       <c r="D7" s="32"/>
       <c r="E7" s="37">
         <f>VLOOKUP(A7,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15591</v>
+        <v>26866</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="1"/>
-        <v>194.8875</v>
+        <v>335.825</v>
       </c>
       <c r="I7" s="35">
         <v>240</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="32"/>
       <c r="E8" s="33">
         <f>VLOOKUP(A8,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>32048</v>
+        <v>25108</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34" t="s">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="1"/>
-        <v>400.6</v>
+        <v>313.85</v>
       </c>
       <c r="I8" s="35">
         <v>83</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="33">
         <f>VLOOKUP(A10,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>28082</v>
+        <v>8377</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34" t="s">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="H10" s="33">
         <f t="shared" si="1"/>
-        <v>351.025</v>
+        <v>104.7125</v>
       </c>
       <c r="I10" s="35">
         <v>261</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
       <c r="D11" s="32"/>
       <c r="E11" s="33">
         <f>VLOOKUP(A11,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15166</v>
+        <v>14294</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34" t="s">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="H11" s="33">
         <f t="shared" si="1"/>
-        <v>189.575</v>
+        <v>178.675</v>
       </c>
       <c r="I11" s="35">
         <v>6</v>
       </c>
       <c r="J11" s="36">
         <f t="shared" si="0"/>
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,7 +3274,7 @@
       <c r="D12" s="32"/>
       <c r="E12" s="40">
         <f>VLOOKUP(A12,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>18446</v>
+        <v>33399</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="1"/>
-        <v>230.575</v>
+        <v>417.4875</v>
       </c>
       <c r="I12" s="35">
         <v>60</v>
       </c>
       <c r="J12" s="36">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
       <c r="D13" s="32"/>
       <c r="E13" s="33">
         <f>VLOOKUP(A13,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4954</v>
+        <v>4508</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="H13" s="33">
         <f t="shared" si="1"/>
-        <v>61.925</v>
+        <v>56.35</v>
       </c>
       <c r="I13" s="35">
         <v>6</v>
       </c>
       <c r="J13" s="36">
         <f t="shared" si="0"/>
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="23">
         <f>VLOOKUP(A14,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>15709</v>
+        <v>6680</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45" t="s">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="1"/>
-        <v>201.39743589743588</v>
+        <v>85.64102564102564</v>
       </c>
       <c r="I14" s="46">
         <v>118</v>
       </c>
       <c r="J14" s="47">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
       <c r="D15" s="32"/>
       <c r="E15" s="40">
         <f>VLOOKUP(A15,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>4605</v>
+        <v>2677</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="H15" s="33">
         <f t="shared" si="1"/>
-        <v>59.03846153846154</v>
+        <v>34.32051282051282</v>
       </c>
       <c r="I15" s="35">
         <v>14</v>
       </c>
       <c r="J15" s="36">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="33">
         <f>VLOOKUP(A16,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2370</v>
+        <v>973</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="34" t="s">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="1"/>
-        <v>30.384615384615383</v>
+        <v>12.474358974358974</v>
       </c>
       <c r="I16" s="35">
         <v>49</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
       <c r="D17" s="32"/>
       <c r="E17" s="37">
         <f>VLOOKUP(A17,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>16028</v>
+        <v>12898</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34" t="s">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="H17" s="33">
         <f t="shared" si="1"/>
-        <v>205.48717948717947</v>
+        <v>165.35897435897436</v>
       </c>
       <c r="I17" s="35">
         <v>45</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
       <c r="D18" s="32"/>
       <c r="E18" s="33">
         <f>VLOOKUP(A18,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>11070</v>
+        <v>9178</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="32" t="s">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
-        <v>141.92307692307693</v>
+        <v>117.66666666666667</v>
       </c>
       <c r="I18" s="35">
         <v>7</v>
       </c>
       <c r="J18" s="36">
         <f t="shared" si="0"/>
-        <v>20.3</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="48">
         <f>VLOOKUP(A20,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2396</v>
+        <v>609</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32" t="s">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="1"/>
-        <v>30.71794871794872</v>
+        <v>7.8076923076923075</v>
       </c>
       <c r="I20" s="35">
         <v>9</v>
       </c>
       <c r="J20" s="36">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
       <c r="D21" s="44"/>
       <c r="E21" s="23">
         <f>VLOOKUP(A21,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>585</v>
+        <v>425</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H21" s="23">
         <f t="shared" si="1"/>
-        <v>3.65625</v>
+        <v>2.65625</v>
       </c>
       <c r="I21" s="46">
         <v>46</v>
@@ -3584,7 +3584,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="33">
         <f>VLOOKUP(A22,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>24426</v>
+        <v>22806</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="H22" s="33">
         <f t="shared" si="1"/>
-        <v>152.6625</v>
+        <v>142.5375</v>
       </c>
       <c r="I22" s="35">
         <v>6</v>
       </c>
       <c r="J22" s="36">
         <f t="shared" si="0"/>
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="23" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="33">
         <f>VLOOKUP(A23,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>527</v>
+        <v>187</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
@@ -3623,14 +3623,14 @@
       </c>
       <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>3.29375</v>
+        <v>1.16875</v>
       </c>
       <c r="I23" s="35">
         <v>20</v>
       </c>
       <c r="J23" s="36">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3646,7 +3646,7 @@
       <c r="D24" s="32"/>
       <c r="E24" s="33">
         <f>VLOOKUP(A24,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>2683</v>
+        <v>15763</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="49" t="s">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="1"/>
-        <v>16.76875</v>
+        <v>98.51875</v>
       </c>
       <c r="I24" s="35">
         <v>20</v>
       </c>
       <c r="J24" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="25" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
       <c r="D25" s="32"/>
       <c r="E25" s="33">
         <f>VLOOKUP(A25,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>912</v>
+        <v>421</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="H25" s="33">
         <f t="shared" si="1"/>
-        <v>5.7</v>
+        <v>2.63125</v>
       </c>
       <c r="I25" s="35">
         <v>4</v>
       </c>
       <c r="J25" s="36">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -3740,7 +3740,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="33">
         <f>VLOOKUP(A27,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>12371</v>
+        <v>17121</v>
       </c>
       <c r="F27" s="58"/>
       <c r="G27" s="34" t="s">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="H27" s="33">
         <f t="shared" si="1"/>
-        <v>247.42</v>
+        <v>342.42</v>
       </c>
       <c r="I27" s="35">
         <v>130</v>
       </c>
       <c r="J27" s="36">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="33">
         <f>VLOOKUP(A28,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="34" t="s">
@@ -3779,14 +3779,14 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="1"/>
-        <v>2.94</v>
+        <v>2.02</v>
       </c>
       <c r="I28" s="35">
         <v>46</v>
       </c>
       <c r="J28" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="33">
         <f>VLOOKUP(A29,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="F29" s="58"/>
       <c r="G29" s="34" t="s">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H29" s="33">
         <f t="shared" si="1"/>
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="I29" s="35">
         <v>80</v>
@@ -3895,7 +3895,7 @@
       <c r="D32" s="58"/>
       <c r="E32" s="33">
         <f>VLOOKUP(A32,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="F32" s="58"/>
       <c r="G32" s="34" t="s">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.8125</v>
       </c>
       <c r="I32" s="35">
         <v>21</v>
       </c>
       <c r="J32" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="33">
         <f>VLOOKUP(A33,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="F33" s="58"/>
       <c r="G33" s="34" t="s">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="H33" s="33">
         <f t="shared" si="1"/>
-        <v>1.175</v>
+        <v>0.29375</v>
       </c>
       <c r="I33" s="35">
         <v>15</v>
       </c>
       <c r="J33" s="36">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4112,7 +4112,7 @@
       <c r="D39" s="62"/>
       <c r="E39" s="65">
         <f>VLOOKUP(A39,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>5535</v>
+        <v>6668</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="64" t="s">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="H39" s="33">
         <f t="shared" si="1"/>
-        <v>110.7</v>
+        <v>133.36</v>
       </c>
       <c r="I39" s="35">
         <v>14</v>
       </c>
       <c r="J39" s="36">
         <f t="shared" si="0"/>
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       <c r="D40" s="62"/>
       <c r="E40" s="63">
         <f>VLOOKUP(A40,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>26650</v>
+        <v>26165</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="64" t="s">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="1"/>
-        <v>195.9558823529412</v>
+        <v>192.38970588235293</v>
       </c>
       <c r="I40" s="35">
         <v>27</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="41" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       <c r="D41" s="69"/>
       <c r="E41" s="33">
         <f>VLOOKUP(A41,'Existencia Sistemaac'!$A$13:$AJ$90,10,FALSE)</f>
-        <v>8062</v>
+        <v>7623</v>
       </c>
       <c r="F41" s="69"/>
       <c r="G41" s="70" t="s">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="H41" s="48">
         <f t="shared" si="1"/>
-        <v>50.3875</v>
+        <v>47.64375</v>
       </c>
       <c r="I41" s="35">
         <v>2</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="42" ht="27.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4269,13 +4269,13 @@
       <c r="D45" s="82"/>
       <c r="E45" s="83">
         <f>SUM(E5:E44)</f>
-        <v>282818</v>
+        <v>279764</v>
       </c>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="84">
         <f>SUM(H5:H44)</f>
-        <v>3299.827420814479</v>
+        <v>3220.745507164404</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
       <c r="M1" s="87"/>
       <c r="O1" s="88"/>
       <c r="AJ1" s="4">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -5237,8 +5237,8 @@
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="40">
-        <f>301-1+18160+6960+3520+1600</f>
-        <v>30540</v>
+        <f>151-1+8800+14720</f>
+        <v>23670</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M24" s="109">
         <f t="shared" si="1"/>
-        <v>30540</v>
+        <v>23670</v>
       </c>
       <c r="N24" s="110">
         <f t="shared" si="4"/>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="O24" s="111">
         <f>51208-J24</f>
-        <v>20668</v>
+        <v>27538</v>
       </c>
       <c r="P24" s="111">
         <f>J24-IFERROR(VLOOKUP(A24,$R$26:$U$119,4,FALSE),0)+19600</f>
-        <v>50140</v>
+        <v>43270</v>
       </c>
       <c r="Q24" s="25">
         <f>+J24/H24</f>
-        <v>381.75</v>
+        <v>295.875</v>
       </c>
       <c r="R24" s="22" t="s">
         <v>14</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AJ24" s="27">
         <f>IFERROR(ROUND((+Q24/AI24),1),0)</f>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN24" s="114" t="s">
         <v>132</v>
@@ -5338,8 +5338,8 @@
       </c>
       <c r="I25" s="32"/>
       <c r="J25" s="37">
-        <f>622+2</f>
-        <v>624</v>
+        <f>580+2+1+6560</f>
+        <v>7143</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34" t="s">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M25" s="115">
         <f t="shared" si="1"/>
-        <v>624</v>
+        <v>7143</v>
       </c>
       <c r="N25" s="116">
         <f t="shared" si="4"/>
@@ -5355,15 +5355,15 @@
       </c>
       <c r="O25" s="117">
         <f>204-J25</f>
-        <v>-420</v>
+        <v>-6939</v>
       </c>
       <c r="P25" s="118">
         <f>J25-IFERROR(VLOOKUP(A25,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>624</v>
+        <v>7143</v>
       </c>
       <c r="Q25" s="33">
         <f t="shared" ref="Q25:Q88" si="5">+J25/H25</f>
-        <v>7.8</v>
+        <v>89.2875</v>
       </c>
       <c r="R25" s="32" t="s">
         <v>17</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AJ25" s="36">
         <f>IFERROR(ROUND((+Q25/AI25),1),0)</f>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="114"/>
@@ -5437,8 +5437,8 @@
       </c>
       <c r="I26" s="32"/>
       <c r="J26" s="33">
-        <f>8951+3120+3520</f>
-        <v>15591</v>
+        <f>9106+17760</f>
+        <v>26866</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="M26" s="115">
         <f t="shared" si="1"/>
-        <v>-7825</v>
+        <v>3450</v>
       </c>
       <c r="N26" s="116">
         <f t="shared" si="4"/>
@@ -5454,15 +5454,15 @@
       </c>
       <c r="O26" s="117">
         <f>8449-J26</f>
-        <v>-7142</v>
+        <v>-18417</v>
       </c>
       <c r="P26" s="118">
         <f>J26-IFERROR(VLOOKUP(A26,$R$26:$U$119,4,FALSE),0)+5120</f>
-        <v>-2705</v>
+        <v>8570</v>
       </c>
       <c r="Q26" s="33">
         <f t="shared" si="5"/>
-        <v>194.8875</v>
+        <v>335.825</v>
       </c>
       <c r="R26" s="32" t="s">
         <v>19</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ26" s="36">
         <f t="shared" ref="AJ26:AJ89" si="6">IFERROR(ROUND((+Q26/AI26),1),0)</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AN26" s="114"/>
     </row>
@@ -5535,8 +5535,8 @@
       </c>
       <c r="I27" s="32"/>
       <c r="J27" s="40">
-        <f>32128-80</f>
-        <v>32048</v>
+        <f>25188-80</f>
+        <v>25108</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34" t="s">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M27" s="115">
         <f t="shared" si="1"/>
-        <v>32045</v>
+        <v>25105</v>
       </c>
       <c r="N27" s="116">
         <f t="shared" si="4"/>
@@ -5552,15 +5552,15 @@
       </c>
       <c r="O27" s="117">
         <f>5605-J27</f>
-        <v>-26443</v>
+        <v>-19503</v>
       </c>
       <c r="P27" s="118">
         <f>J27-IFERROR(VLOOKUP(A27,$R$26:$U$119,4,FALSE),0)+4720+0</f>
-        <v>36765</v>
+        <v>29825</v>
       </c>
       <c r="Q27" s="33">
         <f t="shared" si="5"/>
-        <v>400.6</v>
+        <v>313.85</v>
       </c>
       <c r="R27" s="32" t="s">
         <v>21</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AJ27" s="36">
         <f t="shared" si="6"/>
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AN27" s="114"/>
     </row>
@@ -5730,8 +5730,8 @@
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="40">
-        <f>16266-1-10+11827</f>
-        <v>28082</v>
+        <f>8388-10-1</f>
+        <v>8377</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34" t="s">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="M29" s="115">
         <f t="shared" si="1"/>
-        <v>24606</v>
+        <v>4901</v>
       </c>
       <c r="N29" s="116">
         <f t="shared" si="4"/>
@@ -5747,15 +5747,15 @@
       </c>
       <c r="O29" s="117">
         <f>9357-J29</f>
-        <v>-18725</v>
+        <v>980</v>
       </c>
       <c r="P29" s="118">
         <f>J29-IFERROR(VLOOKUP(A29,$R$26:$U$119,4,FALSE),0)+640</f>
-        <v>25246</v>
+        <v>5541</v>
       </c>
       <c r="Q29" s="33">
         <f t="shared" si="5"/>
-        <v>351.025</v>
+        <v>104.7125</v>
       </c>
       <c r="R29" s="32" t="s">
         <v>58</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AJ29" s="36">
         <f t="shared" si="6"/>
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="AN29" s="114"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33">
-        <v>15166</v>
+        <v>14294</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34" t="s">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M31" s="115">
         <f t="shared" si="1"/>
-        <v>15165</v>
+        <v>14293</v>
       </c>
       <c r="N31" s="116">
         <f t="shared" si="4"/>
@@ -5926,15 +5926,15 @@
       </c>
       <c r="O31" s="117">
         <f>525-J31</f>
-        <v>-14641</v>
+        <v>-13769</v>
       </c>
       <c r="P31" s="118">
         <f>J31-IFERROR(VLOOKUP(A31,$R$26:$U$119,4,FALSE),0)+0</f>
-        <v>15165</v>
+        <v>14293</v>
       </c>
       <c r="Q31" s="33">
         <f t="shared" si="5"/>
-        <v>189.575</v>
+        <v>178.675</v>
       </c>
       <c r="R31" s="32" t="s">
         <v>34</v>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AJ31" s="36">
         <f t="shared" si="6"/>
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
       <c r="AN31" s="114"/>
     </row>
@@ -6077,8 +6077,8 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33">
-        <f>46+14240+4160</f>
-        <v>18446</v>
+        <f>22166+11233</f>
+        <v>33399</v>
       </c>
       <c r="K33" s="32"/>
       <c r="L33" s="32" t="s">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="M33" s="115">
         <f t="shared" si="1"/>
-        <v>18446</v>
+        <v>33399</v>
       </c>
       <c r="N33" s="116">
         <f>+IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6094,15 +6094,15 @@
       </c>
       <c r="O33" s="117">
         <f>0-J33</f>
-        <v>-18446</v>
+        <v>-33399</v>
       </c>
       <c r="P33" s="118">
         <f>J33-IFERROR(VLOOKUP(A33,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>18446</v>
+        <v>33399</v>
       </c>
       <c r="Q33" s="33">
         <f t="shared" si="5"/>
-        <v>230.575</v>
+        <v>417.4875</v>
       </c>
       <c r="R33" s="32" t="s">
         <v>38</v>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ33" s="36">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AM33" s="123"/>
       <c r="AN33" s="114"/>
@@ -6164,8 +6164,8 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="37">
-        <f>4874+80</f>
-        <v>4954</v>
+        <f>4428+80</f>
+        <v>4508</v>
       </c>
       <c r="K34" s="32"/>
       <c r="L34" s="32" t="s">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M34" s="115">
         <f t="shared" si="1"/>
-        <v>-45976</v>
+        <v>-46422</v>
       </c>
       <c r="N34" s="116">
         <f>+IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)-0</f>
@@ -6181,15 +6181,15 @@
       </c>
       <c r="O34" s="117">
         <f>0-J34</f>
-        <v>-4954</v>
+        <v>-4508</v>
       </c>
       <c r="P34" s="118">
         <f>J34-IFERROR(VLOOKUP(A34,$R$24:$U$119,4,FALSE),0)+0</f>
-        <v>-45976</v>
+        <v>-46422</v>
       </c>
       <c r="Q34" s="33">
         <f t="shared" si="5"/>
-        <v>61.925</v>
+        <v>56.35</v>
       </c>
       <c r="R34" s="32" t="s">
         <v>40</v>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AJ34" s="36">
         <f t="shared" si="6"/>
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="AN34" s="114"/>
     </row>
@@ -6250,8 +6250,8 @@
       </c>
       <c r="I35" s="44"/>
       <c r="J35" s="40">
-        <f>10105-2+5606</f>
-        <v>15709</v>
+        <f>3484-2+3198</f>
+        <v>6680</v>
       </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45" t="s">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="M35" s="124">
         <f t="shared" si="1"/>
-        <v>-12601</v>
+        <v>-21630</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" ref="N35:N48" si="7">+IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)-0</f>
@@ -6267,15 +6267,15 @@
       </c>
       <c r="O35" s="126">
         <f>132941-J35</f>
-        <v>117232</v>
+        <v>126261</v>
       </c>
       <c r="P35" s="127">
         <f>J35-IFERROR(VLOOKUP(A35,$R$26:$U$119,4,FALSE),0)+3198</f>
-        <v>-9403</v>
+        <v>-18432</v>
       </c>
       <c r="Q35" s="23">
         <f t="shared" si="5"/>
-        <v>201.39743589743588</v>
+        <v>85.64102564102564</v>
       </c>
       <c r="R35" s="44" t="s">
         <v>48</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AJ35" s="47">
         <f t="shared" si="6"/>
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="AN35" s="114"/>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="33">
-        <v>4605</v>
+        <v>2677</v>
       </c>
       <c r="K36" s="34"/>
       <c r="L36" s="34" t="s">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="M36" s="115">
         <f t="shared" si="1"/>
-        <v>-12946</v>
+        <v>-14874</v>
       </c>
       <c r="N36" s="116">
         <f t="shared" si="7"/>
@@ -6352,15 +6352,15 @@
       </c>
       <c r="O36" s="117">
         <f>51894-J36</f>
-        <v>47289</v>
+        <v>49217</v>
       </c>
       <c r="P36" s="118">
         <f>J36-IFERROR(VLOOKUP(A36,$R$26:$U$119,4,FALSE),0)+2106</f>
-        <v>-10840</v>
+        <v>-12768</v>
       </c>
       <c r="Q36" s="33">
         <f t="shared" si="5"/>
-        <v>59.03846153846154</v>
+        <v>34.32051282051282</v>
       </c>
       <c r="R36" s="32" t="s">
         <v>50</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AJ36" s="36">
         <f t="shared" si="6"/>
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AN36" s="114"/>
     </row>
@@ -6421,8 +6421,8 @@
       </c>
       <c r="I37" s="32"/>
       <c r="J37" s="40">
-        <f>2371-1</f>
-        <v>2370</v>
+        <f>974-1</f>
+        <v>973</v>
       </c>
       <c r="K37" s="34"/>
       <c r="L37" s="34" t="s">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="M37" s="115">
         <f t="shared" si="1"/>
-        <v>-5475</v>
+        <v>-6872</v>
       </c>
       <c r="N37" s="116">
         <f t="shared" si="7"/>
@@ -6438,15 +6438,15 @@
       </c>
       <c r="O37" s="118">
         <f>17462-J37</f>
-        <v>15092</v>
+        <v>16489</v>
       </c>
       <c r="P37" s="118">
         <f>J37-IFERROR(VLOOKUP(A37,$R$26:$U$119,4,FALSE),0)+2496</f>
-        <v>-2979</v>
+        <v>-4376</v>
       </c>
       <c r="Q37" s="33">
         <f t="shared" si="5"/>
-        <v>30.384615384615383</v>
+        <v>12.474358974358974</v>
       </c>
       <c r="R37" s="32" t="s">
         <v>52</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AJ37" s="36">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AN37" s="114"/>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33">
-        <v>16028</v>
+        <v>12898</v>
       </c>
       <c r="K38" s="34"/>
       <c r="L38" s="34" t="s">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="M38" s="115">
         <f t="shared" si="1"/>
-        <v>-7251</v>
+        <v>-10381</v>
       </c>
       <c r="N38" s="116">
         <f t="shared" si="7"/>
@@ -6523,15 +6523,15 @@
       </c>
       <c r="O38" s="117">
         <f>39597-J38</f>
-        <v>23569</v>
+        <v>26699</v>
       </c>
       <c r="P38" s="118">
         <f>J38-IFERROR(VLOOKUP(A38,$R$26:$U$119,4,FALSE),0)+2652</f>
-        <v>-4599</v>
+        <v>-7729</v>
       </c>
       <c r="Q38" s="33">
         <f t="shared" si="5"/>
-        <v>205.48717948717947</v>
+        <v>165.35897435897436</v>
       </c>
       <c r="R38" s="32" t="s">
         <v>54</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AJ38" s="36">
         <f t="shared" si="6"/>
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN38" s="114"/>
     </row>
@@ -6661,8 +6661,8 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="40">
-        <f>11071-1</f>
-        <v>11070</v>
+        <f>9179-1</f>
+        <v>9178</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="32" t="s">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="M40" s="115">
         <f>+J40-N40</f>
-        <v>11070</v>
+        <v>9178</v>
       </c>
       <c r="N40" s="116">
         <f t="shared" si="7"/>
@@ -6678,15 +6678,15 @@
       </c>
       <c r="O40" s="117">
         <f>50966-J40</f>
-        <v>39896</v>
+        <v>41788</v>
       </c>
       <c r="P40" s="118">
         <f>J40-IFERROR(VLOOKUP(A40,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>11772</v>
+        <v>9880</v>
       </c>
       <c r="Q40" s="33">
         <f t="shared" si="5"/>
-        <v>141.92307692307693</v>
+        <v>117.66666666666667</v>
       </c>
       <c r="R40" s="32"/>
       <c r="S40" s="32"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AJ40" s="36">
         <f t="shared" si="6"/>
-        <v>20.3</v>
+        <v>16.8</v>
       </c>
       <c r="AN40" s="114"/>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="33">
-        <v>2396</v>
+        <v>609</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="32" t="s">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="M43" s="115">
         <f>+J43-N43</f>
-        <v>2396</v>
+        <v>609</v>
       </c>
       <c r="N43" s="116">
         <f t="shared" si="7"/>
@@ -6885,15 +6885,15 @@
       </c>
       <c r="O43" s="117">
         <f>50966-J43</f>
-        <v>48570</v>
+        <v>50357</v>
       </c>
       <c r="P43" s="118">
         <f>J43-IFERROR(VLOOKUP(A43,$R$26:$U$119,4,FALSE),0)+702</f>
-        <v>3098</v>
+        <v>1311</v>
       </c>
       <c r="Q43" s="33">
         <f t="shared" si="5"/>
-        <v>30.71794871794872</v>
+        <v>7.8076923076923075</v>
       </c>
       <c r="R43" s="32"/>
       <c r="S43" s="32"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AJ43" s="36">
         <f t="shared" si="6"/>
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="AM43" s="123"/>
       <c r="AN43" s="114"/>
@@ -6939,8 +6939,8 @@
       </c>
       <c r="I44" s="44"/>
       <c r="J44" s="37">
-        <f>584+1</f>
-        <v>585</v>
+        <f>424+1</f>
+        <v>425</v>
       </c>
       <c r="K44" s="44"/>
       <c r="L44" s="44" t="s">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="M44" s="124">
         <f t="shared" si="1"/>
-        <v>-47210</v>
+        <v>-47370</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="7"/>
@@ -6956,15 +6956,15 @@
       </c>
       <c r="O44" s="126">
         <f>53358-J44</f>
-        <v>52773</v>
+        <v>52933</v>
       </c>
       <c r="P44" s="127">
         <f>J44-IFERROR(VLOOKUP(A44,$R$26:$U$119,4,FALSE),0)+5280</f>
-        <v>-41930</v>
+        <v>-42090</v>
       </c>
       <c r="Q44" s="23">
         <f t="shared" si="5"/>
-        <v>3.65625</v>
+        <v>2.65625</v>
       </c>
       <c r="R44" s="44" t="s">
         <v>32</v>
@@ -7025,8 +7025,7 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33">
-        <f>18036+6390</f>
-        <v>24426</v>
+        <v>22806</v>
       </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32" t="s">
@@ -7034,7 +7033,7 @@
       </c>
       <c r="M45" s="115">
         <f t="shared" si="1"/>
-        <v>13323</v>
+        <v>11703</v>
       </c>
       <c r="N45" s="116">
         <f t="shared" si="7"/>
@@ -7042,15 +7041,15 @@
       </c>
       <c r="O45" s="117">
         <f>20108-J45</f>
-        <v>-4318</v>
+        <v>-2698</v>
       </c>
       <c r="P45" s="118">
         <f>J45-IFERROR(VLOOKUP(A45,$R$26:$U$119,4,FALSE),0)+960</f>
-        <v>14283</v>
+        <v>12663</v>
       </c>
       <c r="Q45" s="33">
         <f t="shared" si="5"/>
-        <v>152.6625</v>
+        <v>142.5375</v>
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="32"/>
@@ -7078,7 +7077,7 @@
       </c>
       <c r="AJ45" s="36">
         <f t="shared" si="6"/>
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
       <c r="AM45" s="129"/>
       <c r="AN45" s="114"/>
@@ -7100,7 +7099,7 @@
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="33">
-        <v>527</v>
+        <v>187</v>
       </c>
       <c r="K46" s="32"/>
       <c r="L46" s="32" t="s">
@@ -7108,7 +7107,7 @@
       </c>
       <c r="M46" s="115">
         <f t="shared" si="1"/>
-        <v>-2435</v>
+        <v>-2775</v>
       </c>
       <c r="N46" s="116">
         <f t="shared" si="7"/>
@@ -7116,15 +7115,15 @@
       </c>
       <c r="O46" s="117">
         <f>6244-J46</f>
-        <v>5717</v>
+        <v>6057</v>
       </c>
       <c r="P46" s="118">
         <f>J46-IFERROR(VLOOKUP(A46,$R$26:$U$119,4,FALSE),0)+1760</f>
-        <v>-675</v>
+        <v>-1015</v>
       </c>
       <c r="Q46" s="33">
         <f t="shared" si="5"/>
-        <v>3.29375</v>
+        <v>1.16875</v>
       </c>
       <c r="R46" s="120"/>
       <c r="S46" s="32"/>
@@ -7148,7 +7147,7 @@
       </c>
       <c r="AJ46" s="36">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AN46" s="114"/>
     </row>
@@ -7238,8 +7237,8 @@
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33">
-        <f>123+2560</f>
-        <v>2683</v>
+        <f>8243+7520</f>
+        <v>15763</v>
       </c>
       <c r="K48" s="32"/>
       <c r="L48" s="49" t="s">
@@ -7247,7 +7246,7 @@
       </c>
       <c r="M48" s="115">
         <f t="shared" si="1"/>
-        <v>2677</v>
+        <v>15757</v>
       </c>
       <c r="N48" s="116">
         <f t="shared" si="7"/>
@@ -7255,15 +7254,15 @@
       </c>
       <c r="O48" s="117">
         <f>30490-J48</f>
-        <v>27807</v>
+        <v>14727</v>
       </c>
       <c r="P48" s="118">
         <f>J48-IFERROR(VLOOKUP(A48,$R$26:$U$119,4,FALSE),0)+2880+0</f>
-        <v>5557</v>
+        <v>18637</v>
       </c>
       <c r="Q48" s="33">
         <f t="shared" si="5"/>
-        <v>16.76875</v>
+        <v>98.51875</v>
       </c>
       <c r="R48" s="32"/>
       <c r="S48" s="32"/>
@@ -7287,7 +7286,7 @@
       </c>
       <c r="AJ48" s="36">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="AM48" s="129"/>
       <c r="AN48" s="114"/>
@@ -7480,7 +7479,7 @@
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33">
-        <v>912</v>
+        <v>421</v>
       </c>
       <c r="K52" s="32"/>
       <c r="L52" s="32" t="s">
@@ -7492,7 +7491,7 @@
       <c r="P52" s="118"/>
       <c r="Q52" s="33">
         <f t="shared" si="5"/>
-        <v>5.7</v>
+        <v>2.63125</v>
       </c>
       <c r="R52" s="32"/>
       <c r="S52" s="32"/>
@@ -7516,7 +7515,7 @@
       </c>
       <c r="AJ52" s="36">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="AN52" s="114"/>
       <c r="AP52" s="28"/>
@@ -8268,8 +8267,8 @@
       </c>
       <c r="I64" s="58"/>
       <c r="J64" s="33">
-        <f>3471+8050+850</f>
-        <v>12371</v>
+        <f>10721+6400</f>
+        <v>17121</v>
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="34" t="s">
@@ -8277,7 +8276,7 @@
       </c>
       <c r="M64" s="115">
         <f t="shared" si="1"/>
-        <v>12371</v>
+        <v>17121</v>
       </c>
       <c r="N64" s="116">
         <f t="shared" si="8"/>
@@ -8285,15 +8284,15 @@
       </c>
       <c r="O64" s="117">
         <f t="shared" si="10"/>
-        <v>40235</v>
+        <v>35485</v>
       </c>
       <c r="P64" s="118">
         <f t="shared" si="11"/>
-        <v>18521</v>
+        <v>23271</v>
       </c>
       <c r="Q64" s="33">
         <f t="shared" si="5"/>
-        <v>247.42</v>
+        <v>342.42</v>
       </c>
       <c r="R64" s="32"/>
       <c r="S64" s="32"/>
@@ -8317,7 +8316,7 @@
       </c>
       <c r="AJ64" s="36">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AN64" s="114"/>
     </row>
@@ -8547,7 +8546,7 @@
       </c>
       <c r="I68" s="58"/>
       <c r="J68" s="48">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="34" t="s">
@@ -8555,7 +8554,7 @@
       </c>
       <c r="M68" s="115">
         <f t="shared" si="1"/>
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="N68" s="116">
         <f t="shared" si="8"/>
@@ -8563,15 +8562,15 @@
       </c>
       <c r="O68" s="117">
         <f t="shared" si="10"/>
-        <v>52459</v>
+        <v>52505</v>
       </c>
       <c r="P68" s="118">
         <f t="shared" si="11"/>
-        <v>6297</v>
+        <v>6251</v>
       </c>
       <c r="Q68" s="33">
         <f t="shared" si="5"/>
-        <v>2.94</v>
+        <v>2.02</v>
       </c>
       <c r="R68" s="32"/>
       <c r="S68" s="32"/>
@@ -8595,7 +8594,7 @@
       </c>
       <c r="AJ68" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN68" s="114"/>
     </row>
@@ -8615,9 +8614,8 @@
         <v>50</v>
       </c>
       <c r="I69" s="58"/>
-      <c r="J69" s="40">
-        <f>197-2</f>
-        <v>195</v>
+      <c r="J69" s="33">
+        <v>139</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="34" t="s">
@@ -8625,7 +8623,7 @@
       </c>
       <c r="M69" s="115">
         <f t="shared" si="1"/>
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="N69" s="116">
         <f t="shared" si="8"/>
@@ -8633,15 +8631,15 @@
       </c>
       <c r="O69" s="117">
         <f t="shared" si="10"/>
-        <v>52411</v>
+        <v>52467</v>
       </c>
       <c r="P69" s="118">
         <f t="shared" si="11"/>
-        <v>6345</v>
+        <v>6289</v>
       </c>
       <c r="Q69" s="33">
         <f t="shared" si="5"/>
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32"/>
@@ -9083,7 +9081,7 @@
       </c>
       <c r="I76" s="58"/>
       <c r="J76" s="33">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="34" t="s">
@@ -9091,7 +9089,7 @@
       </c>
       <c r="M76" s="115">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="N76" s="116">
         <f t="shared" si="8"/>
@@ -9100,11 +9098,11 @@
       <c r="O76" s="117"/>
       <c r="P76" s="118">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="Q76" s="33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>18.8125</v>
       </c>
       <c r="R76" s="32"/>
       <c r="S76" s="32"/>
@@ -9128,7 +9126,7 @@
       </c>
       <c r="AJ76" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AN76" s="114"/>
     </row>
@@ -9149,7 +9147,7 @@
       </c>
       <c r="I77" s="58"/>
       <c r="J77" s="33">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="34" t="s">
@@ -9157,7 +9155,7 @@
       </c>
       <c r="M77" s="115">
         <f t="shared" si="1"/>
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="N77" s="116">
         <f t="shared" si="8"/>
@@ -9166,11 +9164,11 @@
       <c r="O77" s="117"/>
       <c r="P77" s="118">
         <f t="shared" si="12"/>
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="Q77" s="33">
         <f t="shared" si="5"/>
-        <v>1.175</v>
+        <v>0.29375</v>
       </c>
       <c r="R77" s="32"/>
       <c r="S77" s="32"/>
@@ -9194,7 +9192,7 @@
       </c>
       <c r="AJ77" s="36">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN77" s="114"/>
     </row>
@@ -9478,8 +9476,7 @@
         <v>84</v>
       </c>
       <c r="I82" s="62"/>
-      <c r="J82" s="63">
-        <f>15-15</f>
+      <c r="J82" s="65">
         <v>0</v>
       </c>
       <c r="K82" s="62"/>
@@ -9546,7 +9543,7 @@
       </c>
       <c r="I83" s="62"/>
       <c r="J83" s="65">
-        <v>5535</v>
+        <v>6668</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="64" t="s">
@@ -9558,7 +9555,7 @@
       <c r="P83" s="118"/>
       <c r="Q83" s="33">
         <f t="shared" si="5"/>
-        <v>110.7</v>
+        <v>133.36</v>
       </c>
       <c r="R83" s="32"/>
       <c r="S83" s="32"/>
@@ -9582,7 +9579,7 @@
       </c>
       <c r="AJ83" s="36">
         <f t="shared" si="6"/>
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="AN83" s="114"/>
     </row>
@@ -9602,9 +9599,8 @@
         <v>136</v>
       </c>
       <c r="I84" s="62"/>
-      <c r="J84" s="37">
-        <f>26635+15</f>
-        <v>26650</v>
+      <c r="J84" s="33">
+        <v>26165</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="64" t="s">
@@ -9616,7 +9612,7 @@
       <c r="P84" s="118"/>
       <c r="Q84" s="33">
         <f t="shared" si="5"/>
-        <v>195.9558823529412</v>
+        <v>192.38970588235293</v>
       </c>
       <c r="R84" s="32"/>
       <c r="S84" s="32"/>
@@ -9640,7 +9636,7 @@
       </c>
       <c r="AJ84" s="36">
         <f t="shared" si="6"/>
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AN84" s="114"/>
     </row>
@@ -9832,7 +9828,7 @@
       </c>
       <c r="I88" s="69"/>
       <c r="J88" s="33">
-        <v>8062</v>
+        <v>7623</v>
       </c>
       <c r="K88" s="69"/>
       <c r="L88" s="70" t="s">
@@ -9844,7 +9840,7 @@
       <c r="P88" s="118"/>
       <c r="Q88" s="48">
         <f t="shared" si="5"/>
-        <v>50.3875</v>
+        <v>47.64375</v>
       </c>
       <c r="R88" s="32"/>
       <c r="S88" s="32"/>
@@ -9868,7 +9864,7 @@
       </c>
       <c r="AJ88" s="36">
         <f t="shared" si="6"/>
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
       <c r="AN88" s="114"/>
     </row>
@@ -10090,26 +10086,26 @@
       <c r="I94" s="82"/>
       <c r="J94" s="83">
         <f>SUM(J24:J93)</f>
-        <v>282818</v>
+        <v>279764</v>
       </c>
       <c r="K94" s="82"/>
       <c r="L94" s="82"/>
       <c r="M94" s="176">
         <f>SUM(M14:M93)</f>
-        <v>-18349</v>
+        <v>-21121</v>
       </c>
       <c r="N94" s="82"/>
       <c r="O94" s="177">
         <f>SUM(O14:O93)</f>
-        <v>813071</v>
+        <v>818712</v>
       </c>
       <c r="P94" s="178">
         <f>SUM(P14:P93)</f>
-        <v>79623</v>
+        <v>76851</v>
       </c>
       <c r="Q94" s="84">
         <f>SUM(Q24:Q93)</f>
-        <v>3299.827420814479</v>
+        <v>3220.745507164404</v>
       </c>
       <c r="R94" s="103"/>
       <c r="U94" s="179"/>
